--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3836" uniqueCount="1483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="1512">
   <si>
     <t>#</t>
   </si>
@@ -4090,6 +4090,33 @@
     <t>守卫龙城通过地狱100层数</t>
   </si>
   <si>
+    <t>初出茅庐4</t>
+  </si>
+  <si>
+    <t>小试牛刀4</t>
+  </si>
+  <si>
+    <t>初露锋芒4</t>
+  </si>
+  <si>
+    <t>武林新秀4</t>
+  </si>
+  <si>
+    <t>声名鹊起4</t>
+  </si>
+  <si>
+    <t>过关斩将4</t>
+  </si>
+  <si>
+    <t>独孤求败4</t>
+  </si>
+  <si>
+    <t>武林至尊4</t>
+  </si>
+  <si>
+    <t>天下无敌4</t>
+  </si>
+  <si>
     <t>攀登者1</t>
   </si>
   <si>
@@ -4541,6 +4568,66 @@
   </si>
   <si>
     <t>攀登者150</t>
+  </si>
+  <si>
+    <t>攀登者151</t>
+  </si>
+  <si>
+    <t>攀登者152</t>
+  </si>
+  <si>
+    <t>攀登者153</t>
+  </si>
+  <si>
+    <t>攀登者154</t>
+  </si>
+  <si>
+    <t>攀登者155</t>
+  </si>
+  <si>
+    <t>攀登者156</t>
+  </si>
+  <si>
+    <t>攀登者157</t>
+  </si>
+  <si>
+    <t>攀登者158</t>
+  </si>
+  <si>
+    <t>攀登者159</t>
+  </si>
+  <si>
+    <t>攀登者160</t>
+  </si>
+  <si>
+    <t>攀登者161</t>
+  </si>
+  <si>
+    <t>攀登者162</t>
+  </si>
+  <si>
+    <t>攀登者163</t>
+  </si>
+  <si>
+    <t>攀登者164</t>
+  </si>
+  <si>
+    <t>攀登者165</t>
+  </si>
+  <si>
+    <t>攀登者166</t>
+  </si>
+  <si>
+    <t>攀登者167</t>
+  </si>
+  <si>
+    <t>攀登者168</t>
+  </si>
+  <si>
+    <t>攀登者169</t>
+  </si>
+  <si>
+    <t>攀登者170</t>
   </si>
 </sst>
 </file>
@@ -5548,7 +5635,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K1420"/>
+  <dimension ref="A2:K1450"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="7"/>
@@ -20101,7 +20188,7 @@
         <v>1</v>
       </c>
       <c r="F487" s="7">
-        <f t="shared" ref="F487:F496" si="11">F486+72</f>
+        <f t="shared" ref="F487:F497" si="11">F486+72</f>
         <v>11952</v>
       </c>
       <c r="G487" s="7">
@@ -20401,7 +20488,7 @@
         <v>1</v>
       </c>
       <c r="F497" s="4">
-        <f>F496+72</f>
+        <f t="shared" si="11"/>
         <v>12600</v>
       </c>
       <c r="G497" s="4">
@@ -34681,7 +34768,7 @@
         <v>2</v>
       </c>
       <c r="F978" s="6">
-        <f>(C978-2000)*12</f>
+        <f t="shared" ref="F978:F987" si="20">(C978-2000)*12</f>
         <v>5712</v>
       </c>
       <c r="G978" s="6">
@@ -34711,7 +34798,7 @@
         <v>2</v>
       </c>
       <c r="F979" s="6">
-        <f>(C979-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5724</v>
       </c>
       <c r="G979" s="6">
@@ -34741,7 +34828,7 @@
         <v>2</v>
       </c>
       <c r="F980" s="6">
-        <f>(C980-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5736</v>
       </c>
       <c r="G980" s="6">
@@ -34771,7 +34858,7 @@
         <v>2</v>
       </c>
       <c r="F981" s="6">
-        <f>(C981-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5748</v>
       </c>
       <c r="G981" s="6">
@@ -34801,7 +34888,7 @@
         <v>2</v>
       </c>
       <c r="F982" s="6">
-        <f>(C982-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5760</v>
       </c>
       <c r="G982" s="6">
@@ -34831,7 +34918,7 @@
         <v>2</v>
       </c>
       <c r="F983" s="6">
-        <f>(C983-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5772</v>
       </c>
       <c r="G983" s="6">
@@ -34861,7 +34948,7 @@
         <v>2</v>
       </c>
       <c r="F984" s="6">
-        <f>(C984-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5784</v>
       </c>
       <c r="G984" s="6">
@@ -34891,7 +34978,7 @@
         <v>2</v>
       </c>
       <c r="F985" s="6">
-        <f>(C985-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5796</v>
       </c>
       <c r="G985" s="6">
@@ -34921,7 +35008,7 @@
         <v>2</v>
       </c>
       <c r="F986" s="6">
-        <f>(C986-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5808</v>
       </c>
       <c r="G986" s="6">
@@ -34951,7 +35038,7 @@
         <v>2</v>
       </c>
       <c r="F987" s="9">
-        <f>(C987-2000)*12</f>
+        <f t="shared" si="20"/>
         <v>5820</v>
       </c>
       <c r="G987" s="9">
@@ -34981,7 +35068,7 @@
         <v>2</v>
       </c>
       <c r="F988" s="6">
-        <f t="shared" ref="F988:F1001" si="20">(F987)+36</f>
+        <f t="shared" ref="F988:F1002" si="21">(F987)+36</f>
         <v>5856</v>
       </c>
       <c r="G988" s="6">
@@ -35011,7 +35098,7 @@
         <v>2</v>
       </c>
       <c r="F989" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5892</v>
       </c>
       <c r="G989" s="6">
@@ -35041,7 +35128,7 @@
         <v>2</v>
       </c>
       <c r="F990" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5928</v>
       </c>
       <c r="G990" s="6">
@@ -35071,7 +35158,7 @@
         <v>2</v>
       </c>
       <c r="F991" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5964</v>
       </c>
       <c r="G991" s="6">
@@ -35101,7 +35188,7 @@
         <v>2</v>
       </c>
       <c r="F992" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6000</v>
       </c>
       <c r="G992" s="6">
@@ -35131,7 +35218,7 @@
         <v>2</v>
       </c>
       <c r="F993" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6036</v>
       </c>
       <c r="G993" s="6">
@@ -35161,7 +35248,7 @@
         <v>2</v>
       </c>
       <c r="F994" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6072</v>
       </c>
       <c r="G994" s="6">
@@ -35191,7 +35278,7 @@
         <v>2</v>
       </c>
       <c r="F995" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6108</v>
       </c>
       <c r="G995" s="6">
@@ -35221,7 +35308,7 @@
         <v>2</v>
       </c>
       <c r="F996" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6144</v>
       </c>
       <c r="G996" s="6">
@@ -35251,7 +35338,7 @@
         <v>2</v>
       </c>
       <c r="F997" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6180</v>
       </c>
       <c r="G997" s="6">
@@ -35281,7 +35368,7 @@
         <v>2</v>
       </c>
       <c r="F998" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6216</v>
       </c>
       <c r="G998" s="6">
@@ -35311,7 +35398,7 @@
         <v>2</v>
       </c>
       <c r="F999" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6252</v>
       </c>
       <c r="G999" s="6">
@@ -35341,7 +35428,7 @@
         <v>2</v>
       </c>
       <c r="F1000" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6288</v>
       </c>
       <c r="G1000" s="6">
@@ -35371,7 +35458,7 @@
         <v>2</v>
       </c>
       <c r="F1001" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6324</v>
       </c>
       <c r="G1001" s="6">
@@ -35401,7 +35488,7 @@
         <v>2</v>
       </c>
       <c r="F1002" s="9">
-        <f>(F1001)+36</f>
+        <f t="shared" si="21"/>
         <v>6360</v>
       </c>
       <c r="G1002" s="9">
@@ -35899,7 +35986,7 @@
         <v>3</v>
       </c>
       <c r="F1028" s="7">
-        <f t="shared" ref="F1028:F1047" si="21">F1027+30000</f>
+        <f t="shared" ref="F1028:F1047" si="22">F1027+30000</f>
         <v>330000</v>
       </c>
       <c r="G1028" s="7">
@@ -35926,7 +36013,7 @@
         <v>3</v>
       </c>
       <c r="F1029" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>360000</v>
       </c>
       <c r="G1029" s="7">
@@ -35953,7 +36040,7 @@
         <v>3</v>
       </c>
       <c r="F1030" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>390000</v>
       </c>
       <c r="G1030" s="7">
@@ -35980,7 +36067,7 @@
         <v>3</v>
       </c>
       <c r="F1031" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>420000</v>
       </c>
       <c r="G1031" s="7">
@@ -36007,7 +36094,7 @@
         <v>3</v>
       </c>
       <c r="F1032" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>450000</v>
       </c>
       <c r="G1032" s="7">
@@ -36034,7 +36121,7 @@
         <v>3</v>
       </c>
       <c r="F1033" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>480000</v>
       </c>
       <c r="G1033" s="7">
@@ -36061,7 +36148,7 @@
         <v>3</v>
       </c>
       <c r="F1034" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>510000</v>
       </c>
       <c r="G1034" s="7">
@@ -36088,7 +36175,7 @@
         <v>3</v>
       </c>
       <c r="F1035" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>540000</v>
       </c>
       <c r="G1035" s="7">
@@ -36115,7 +36202,7 @@
         <v>3</v>
       </c>
       <c r="F1036" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>570000</v>
       </c>
       <c r="G1036" s="7">
@@ -36142,7 +36229,7 @@
         <v>3</v>
       </c>
       <c r="F1037" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>600000</v>
       </c>
       <c r="G1037" s="7">
@@ -36169,7 +36256,7 @@
         <v>3</v>
       </c>
       <c r="F1038" s="7">
-        <f t="shared" ref="F1038:F1047" si="22">F1037+40000</f>
+        <f t="shared" ref="F1038:F1047" si="23">F1037+40000</f>
         <v>640000</v>
       </c>
       <c r="G1038" s="7">
@@ -36196,7 +36283,7 @@
         <v>3</v>
       </c>
       <c r="F1039" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>680000</v>
       </c>
       <c r="G1039" s="7">
@@ -36223,7 +36310,7 @@
         <v>3</v>
       </c>
       <c r="F1040" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>720000</v>
       </c>
       <c r="G1040" s="7">
@@ -36250,7 +36337,7 @@
         <v>3</v>
       </c>
       <c r="F1041" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>760000</v>
       </c>
       <c r="G1041" s="7">
@@ -36277,7 +36364,7 @@
         <v>3</v>
       </c>
       <c r="F1042" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>800000</v>
       </c>
       <c r="G1042" s="7">
@@ -36304,7 +36391,7 @@
         <v>3</v>
       </c>
       <c r="F1043" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>840000</v>
       </c>
       <c r="G1043" s="7">
@@ -36331,7 +36418,7 @@
         <v>3</v>
       </c>
       <c r="F1044" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>880000</v>
       </c>
       <c r="G1044" s="7">
@@ -36358,7 +36445,7 @@
         <v>3</v>
       </c>
       <c r="F1045" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>920000</v>
       </c>
       <c r="G1045" s="7">
@@ -36385,7 +36472,7 @@
         <v>3</v>
       </c>
       <c r="F1046" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>960000</v>
       </c>
       <c r="G1046" s="7">
@@ -36412,7 +36499,7 @@
         <v>3</v>
       </c>
       <c r="F1047" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1000000</v>
       </c>
       <c r="G1047" s="7">
@@ -36829,7 +36916,7 @@
         <v>4</v>
       </c>
       <c r="F1065" s="7">
-        <f t="shared" ref="F1065:F1074" si="23">F1064+250</f>
+        <f t="shared" ref="F1065:F1074" si="24">F1064+250</f>
         <v>3000</v>
       </c>
       <c r="G1065" s="7">
@@ -36856,7 +36943,7 @@
         <v>4</v>
       </c>
       <c r="F1066" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3250</v>
       </c>
       <c r="G1066" s="7">
@@ -36883,7 +36970,7 @@
         <v>4</v>
       </c>
       <c r="F1067" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3500</v>
       </c>
       <c r="G1067" s="7">
@@ -36910,7 +36997,7 @@
         <v>4</v>
       </c>
       <c r="F1068" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="G1068" s="7">
@@ -36937,7 +37024,7 @@
         <v>4</v>
       </c>
       <c r="F1069" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="G1069" s="7">
@@ -36964,7 +37051,7 @@
         <v>4</v>
       </c>
       <c r="F1070" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4250</v>
       </c>
       <c r="G1070" s="7">
@@ -36991,7 +37078,7 @@
         <v>4</v>
       </c>
       <c r="F1071" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4500</v>
       </c>
       <c r="G1071" s="7">
@@ -37018,7 +37105,7 @@
         <v>4</v>
       </c>
       <c r="F1072" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4750</v>
       </c>
       <c r="G1072" s="7">
@@ -37045,7 +37132,7 @@
         <v>4</v>
       </c>
       <c r="F1073" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="G1073" s="7">
@@ -37072,7 +37159,7 @@
         <v>4</v>
       </c>
       <c r="F1074" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5250</v>
       </c>
       <c r="G1074" s="7">
@@ -37099,7 +37186,7 @@
         <v>5</v>
       </c>
       <c r="F1076" s="7">
-        <f t="shared" ref="F1076:F1085" si="24">(C1076-5000)*1000</f>
+        <f t="shared" ref="F1076:F1085" si="25">(C1076-5000)*1000</f>
         <v>1000</v>
       </c>
       <c r="G1076" s="7">
@@ -37126,7 +37213,7 @@
         <v>5</v>
       </c>
       <c r="F1077" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2000</v>
       </c>
       <c r="G1077" s="7">
@@ -37153,7 +37240,7 @@
         <v>5</v>
       </c>
       <c r="F1078" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3000</v>
       </c>
       <c r="G1078" s="7">
@@ -37180,7 +37267,7 @@
         <v>5</v>
       </c>
       <c r="F1079" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4000</v>
       </c>
       <c r="G1079" s="7">
@@ -37207,7 +37294,7 @@
         <v>5</v>
       </c>
       <c r="F1080" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5000</v>
       </c>
       <c r="G1080" s="7">
@@ -37234,7 +37321,7 @@
         <v>5</v>
       </c>
       <c r="F1081" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6000</v>
       </c>
       <c r="G1081" s="7">
@@ -37261,7 +37348,7 @@
         <v>5</v>
       </c>
       <c r="F1082" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7000</v>
       </c>
       <c r="G1082" s="7">
@@ -37288,7 +37375,7 @@
         <v>5</v>
       </c>
       <c r="F1083" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8000</v>
       </c>
       <c r="G1083" s="7">
@@ -37315,7 +37402,7 @@
         <v>5</v>
       </c>
       <c r="F1084" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9000</v>
       </c>
       <c r="G1084" s="7">
@@ -37342,7 +37429,7 @@
         <v>5</v>
       </c>
       <c r="F1085" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>10000</v>
       </c>
       <c r="G1085" s="7">
@@ -37369,7 +37456,7 @@
         <v>5</v>
       </c>
       <c r="F1086" s="7">
-        <f t="shared" ref="F1086:F1101" si="25">F1085+1000</f>
+        <f t="shared" ref="F1086:F1101" si="26">F1085+1000</f>
         <v>11000</v>
       </c>
       <c r="G1086" s="7">
@@ -37396,7 +37483,7 @@
         <v>5</v>
       </c>
       <c r="F1087" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12000</v>
       </c>
       <c r="G1087" s="7">
@@ -37423,7 +37510,7 @@
         <v>5</v>
       </c>
       <c r="F1088" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13000</v>
       </c>
       <c r="G1088" s="7">
@@ -37450,7 +37537,7 @@
         <v>5</v>
       </c>
       <c r="F1089" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>14000</v>
       </c>
       <c r="G1089" s="7">
@@ -37477,7 +37564,7 @@
         <v>5</v>
       </c>
       <c r="F1090" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15000</v>
       </c>
       <c r="G1090" s="7">
@@ -37504,7 +37591,7 @@
         <v>5</v>
       </c>
       <c r="F1091" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16000</v>
       </c>
       <c r="G1091" s="7">
@@ -37531,7 +37618,7 @@
         <v>5</v>
       </c>
       <c r="F1092" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17000</v>
       </c>
       <c r="G1092" s="7">
@@ -37558,7 +37645,7 @@
         <v>5</v>
       </c>
       <c r="F1093" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>18000</v>
       </c>
       <c r="G1093" s="7">
@@ -37585,7 +37672,7 @@
         <v>5</v>
       </c>
       <c r="F1094" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>19000</v>
       </c>
       <c r="G1094" s="7">
@@ -37612,7 +37699,7 @@
         <v>5</v>
       </c>
       <c r="F1095" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20000</v>
       </c>
       <c r="G1095" s="7">
@@ -37639,7 +37726,7 @@
         <v>5</v>
       </c>
       <c r="F1096" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>21000</v>
       </c>
       <c r="G1096" s="7">
@@ -37666,7 +37753,7 @@
         <v>5</v>
       </c>
       <c r="F1097" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>22000</v>
       </c>
       <c r="G1097" s="7">
@@ -37693,7 +37780,7 @@
         <v>5</v>
       </c>
       <c r="F1098" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>23000</v>
       </c>
       <c r="G1098" s="7">
@@ -37720,7 +37807,7 @@
         <v>5</v>
       </c>
       <c r="F1099" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>24000</v>
       </c>
       <c r="G1099" s="7">
@@ -37747,7 +37834,7 @@
         <v>5</v>
       </c>
       <c r="F1100" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>25000</v>
       </c>
       <c r="G1100" s="7">
@@ -37774,7 +37861,7 @@
         <v>5</v>
       </c>
       <c r="F1101" s="7">
-        <f t="shared" ref="F1101:F1120" si="26">F1100+2000</f>
+        <f t="shared" ref="F1101:F1120" si="27">F1100+2000</f>
         <v>27000</v>
       </c>
       <c r="G1101" s="7">
@@ -37801,7 +37888,7 @@
         <v>5</v>
       </c>
       <c r="F1102" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>29000</v>
       </c>
       <c r="G1102" s="7">
@@ -37828,7 +37915,7 @@
         <v>5</v>
       </c>
       <c r="F1103" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>31000</v>
       </c>
       <c r="G1103" s="7">
@@ -37855,7 +37942,7 @@
         <v>5</v>
       </c>
       <c r="F1104" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>33000</v>
       </c>
       <c r="G1104" s="7">
@@ -37882,7 +37969,7 @@
         <v>5</v>
       </c>
       <c r="F1105" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>35000</v>
       </c>
       <c r="G1105" s="7">
@@ -37909,7 +37996,7 @@
         <v>5</v>
       </c>
       <c r="F1106" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>37000</v>
       </c>
       <c r="G1106" s="7">
@@ -37936,7 +38023,7 @@
         <v>5</v>
       </c>
       <c r="F1107" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>39000</v>
       </c>
       <c r="G1107" s="7">
@@ -37963,7 +38050,7 @@
         <v>5</v>
       </c>
       <c r="F1108" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>41000</v>
       </c>
       <c r="G1108" s="7">
@@ -37990,7 +38077,7 @@
         <v>5</v>
       </c>
       <c r="F1109" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>43000</v>
       </c>
       <c r="G1109" s="7">
@@ -38017,7 +38104,7 @@
         <v>5</v>
       </c>
       <c r="F1110" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>45000</v>
       </c>
       <c r="G1110" s="7">
@@ -38044,7 +38131,7 @@
         <v>5</v>
       </c>
       <c r="F1111" s="7">
-        <f t="shared" ref="F1111:F1127" si="27">F1110+3000</f>
+        <f t="shared" ref="F1111:F1127" si="28">F1110+3000</f>
         <v>48000</v>
       </c>
       <c r="G1111" s="7">
@@ -38071,7 +38158,7 @@
         <v>5</v>
       </c>
       <c r="F1112" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>51000</v>
       </c>
       <c r="G1112" s="7">
@@ -38098,7 +38185,7 @@
         <v>5</v>
       </c>
       <c r="F1113" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>54000</v>
       </c>
       <c r="G1113" s="7">
@@ -38125,7 +38212,7 @@
         <v>5</v>
       </c>
       <c r="F1114" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>57000</v>
       </c>
       <c r="G1114" s="7">
@@ -38152,7 +38239,7 @@
         <v>5</v>
       </c>
       <c r="F1115" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>60000</v>
       </c>
       <c r="G1115" s="7">
@@ -38179,7 +38266,7 @@
         <v>5</v>
       </c>
       <c r="F1116" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>63000</v>
       </c>
       <c r="G1116" s="7">
@@ -38206,7 +38293,7 @@
         <v>5</v>
       </c>
       <c r="F1117" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>66000</v>
       </c>
       <c r="G1117" s="7">
@@ -38233,7 +38320,7 @@
         <v>5</v>
       </c>
       <c r="F1118" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>69000</v>
       </c>
       <c r="G1118" s="7">
@@ -38260,7 +38347,7 @@
         <v>5</v>
       </c>
       <c r="F1119" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>72000</v>
       </c>
       <c r="G1119" s="7">
@@ -38287,7 +38374,7 @@
         <v>5</v>
       </c>
       <c r="F1120" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>75000</v>
       </c>
       <c r="G1120" s="7">
@@ -38314,7 +38401,7 @@
         <v>5</v>
       </c>
       <c r="F1121" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>78000</v>
       </c>
       <c r="G1121" s="7">
@@ -38341,7 +38428,7 @@
         <v>5</v>
       </c>
       <c r="F1122" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>81000</v>
       </c>
       <c r="G1122" s="7">
@@ -38368,7 +38455,7 @@
         <v>5</v>
       </c>
       <c r="F1123" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>84000</v>
       </c>
       <c r="G1123" s="7">
@@ -38395,7 +38482,7 @@
         <v>5</v>
       </c>
       <c r="F1124" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>87000</v>
       </c>
       <c r="G1124" s="7">
@@ -38422,7 +38509,7 @@
         <v>5</v>
       </c>
       <c r="F1125" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>90000</v>
       </c>
       <c r="G1125" s="7">
@@ -38449,7 +38536,7 @@
         <v>5</v>
       </c>
       <c r="F1126" s="7">
-        <f t="shared" ref="F1126:F1130" si="28">F1125+4000</f>
+        <f t="shared" ref="F1126:F1130" si="29">F1125+4000</f>
         <v>94000</v>
       </c>
       <c r="G1126" s="7">
@@ -38476,7 +38563,7 @@
         <v>5</v>
       </c>
       <c r="F1127" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>98000</v>
       </c>
       <c r="G1127" s="7">
@@ -38503,7 +38590,7 @@
         <v>5</v>
       </c>
       <c r="F1128" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>102000</v>
       </c>
       <c r="G1128" s="7">
@@ -38530,7 +38617,7 @@
         <v>5</v>
       </c>
       <c r="F1129" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>106000</v>
       </c>
       <c r="G1129" s="7">
@@ -38557,7 +38644,7 @@
         <v>5</v>
       </c>
       <c r="F1130" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>110000</v>
       </c>
       <c r="G1130" s="7">
@@ -39104,7 +39191,7 @@
         <v>6</v>
       </c>
       <c r="F1152" s="7">
-        <f t="shared" ref="F1152:F1166" si="29">F1151+100</f>
+        <f t="shared" ref="F1152:F1166" si="30">F1151+100</f>
         <v>2100</v>
       </c>
       <c r="G1152" s="7">
@@ -39131,7 +39218,7 @@
         <v>6</v>
       </c>
       <c r="F1153" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2200</v>
       </c>
       <c r="G1153" s="7">
@@ -39158,7 +39245,7 @@
         <v>6</v>
       </c>
       <c r="F1154" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2300</v>
       </c>
       <c r="G1154" s="7">
@@ -39185,7 +39272,7 @@
         <v>6</v>
       </c>
       <c r="F1155" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2400</v>
       </c>
       <c r="G1155" s="7">
@@ -39212,7 +39299,7 @@
         <v>6</v>
       </c>
       <c r="F1156" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2500</v>
       </c>
       <c r="G1156" s="7">
@@ -39239,7 +39326,7 @@
         <v>6</v>
       </c>
       <c r="F1157" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2600</v>
       </c>
       <c r="G1157" s="7">
@@ -39266,7 +39353,7 @@
         <v>6</v>
       </c>
       <c r="F1158" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2700</v>
       </c>
       <c r="G1158" s="7">
@@ -39293,7 +39380,7 @@
         <v>6</v>
       </c>
       <c r="F1159" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2800</v>
       </c>
       <c r="G1159" s="7">
@@ -39320,7 +39407,7 @@
         <v>6</v>
       </c>
       <c r="F1160" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2900</v>
       </c>
       <c r="G1160" s="7">
@@ -39347,7 +39434,7 @@
         <v>6</v>
       </c>
       <c r="F1161" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3000</v>
       </c>
       <c r="G1161" s="7">
@@ -39509,7 +39596,7 @@
         <v>6</v>
       </c>
       <c r="F1167" s="7">
-        <f t="shared" ref="F1167:F1176" si="30">F1166+300</f>
+        <f t="shared" ref="F1167:F1176" si="31">F1166+300</f>
         <v>4300</v>
       </c>
       <c r="G1167" s="7">
@@ -39536,7 +39623,7 @@
         <v>6</v>
       </c>
       <c r="F1168" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4600</v>
       </c>
       <c r="G1168" s="7">
@@ -39563,7 +39650,7 @@
         <v>6</v>
       </c>
       <c r="F1169" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4900</v>
       </c>
       <c r="G1169" s="7">
@@ -39590,7 +39677,7 @@
         <v>6</v>
       </c>
       <c r="F1170" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5200</v>
       </c>
       <c r="G1170" s="7">
@@ -39617,7 +39704,7 @@
         <v>6</v>
       </c>
       <c r="F1171" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5500</v>
       </c>
       <c r="G1171" s="7">
@@ -39644,7 +39731,7 @@
         <v>6</v>
       </c>
       <c r="F1172" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5800</v>
       </c>
       <c r="G1172" s="7">
@@ -39671,7 +39758,7 @@
         <v>6</v>
       </c>
       <c r="F1173" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6100</v>
       </c>
       <c r="G1173" s="7">
@@ -39698,7 +39785,7 @@
         <v>6</v>
       </c>
       <c r="F1174" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6400</v>
       </c>
       <c r="G1174" s="7">
@@ -39725,7 +39812,7 @@
         <v>6</v>
       </c>
       <c r="F1175" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6700</v>
       </c>
       <c r="G1175" s="7">
@@ -39752,7 +39839,7 @@
         <v>6</v>
       </c>
       <c r="F1176" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7000</v>
       </c>
       <c r="G1176" s="7">
@@ -39779,7 +39866,7 @@
         <v>6</v>
       </c>
       <c r="F1177" s="7">
-        <f t="shared" ref="F1177:F1196" si="31">F1176+400</f>
+        <f t="shared" ref="F1177:F1196" si="32">F1176+400</f>
         <v>7400</v>
       </c>
       <c r="G1177" s="7">
@@ -39806,7 +39893,7 @@
         <v>6</v>
       </c>
       <c r="F1178" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>7800</v>
       </c>
       <c r="G1178" s="7">
@@ -39833,7 +39920,7 @@
         <v>6</v>
       </c>
       <c r="F1179" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8200</v>
       </c>
       <c r="G1179" s="7">
@@ -39860,7 +39947,7 @@
         <v>6</v>
       </c>
       <c r="F1180" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8600</v>
       </c>
       <c r="G1180" s="7">
@@ -39887,7 +39974,7 @@
         <v>6</v>
       </c>
       <c r="F1181" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9000</v>
       </c>
       <c r="G1181" s="7">
@@ -39914,7 +40001,7 @@
         <v>6</v>
       </c>
       <c r="F1182" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9400</v>
       </c>
       <c r="G1182" s="7">
@@ -39941,7 +40028,7 @@
         <v>6</v>
       </c>
       <c r="F1183" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9800</v>
       </c>
       <c r="G1183" s="7">
@@ -39968,7 +40055,7 @@
         <v>6</v>
       </c>
       <c r="F1184" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>10200</v>
       </c>
       <c r="G1184" s="7">
@@ -39995,7 +40082,7 @@
         <v>6</v>
       </c>
       <c r="F1185" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>10600</v>
       </c>
       <c r="G1185" s="7">
@@ -40022,7 +40109,7 @@
         <v>6</v>
       </c>
       <c r="F1186" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>11000</v>
       </c>
       <c r="G1186" s="7">
@@ -40049,7 +40136,7 @@
         <v>6</v>
       </c>
       <c r="F1187" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>11400</v>
       </c>
       <c r="G1187" s="7">
@@ -40076,7 +40163,7 @@
         <v>6</v>
       </c>
       <c r="F1188" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>11800</v>
       </c>
       <c r="G1188" s="7">
@@ -40103,7 +40190,7 @@
         <v>6</v>
       </c>
       <c r="F1189" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12200</v>
       </c>
       <c r="G1189" s="7">
@@ -40130,7 +40217,7 @@
         <v>6</v>
       </c>
       <c r="F1190" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12600</v>
       </c>
       <c r="G1190" s="7">
@@ -40157,7 +40244,7 @@
         <v>6</v>
       </c>
       <c r="F1191" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>13000</v>
       </c>
       <c r="G1191" s="7">
@@ -40184,7 +40271,7 @@
         <v>6</v>
       </c>
       <c r="F1192" s="7">
-        <f t="shared" ref="F1192:F1201" si="32">F1191+500</f>
+        <f t="shared" ref="F1192:F1201" si="33">F1191+500</f>
         <v>13500</v>
       </c>
       <c r="G1192" s="7">
@@ -40211,7 +40298,7 @@
         <v>6</v>
       </c>
       <c r="F1193" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>14000</v>
       </c>
       <c r="G1193" s="7">
@@ -40238,7 +40325,7 @@
         <v>6</v>
       </c>
       <c r="F1194" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>14500</v>
       </c>
       <c r="G1194" s="7">
@@ -40265,7 +40352,7 @@
         <v>6</v>
       </c>
       <c r="F1195" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15000</v>
       </c>
       <c r="G1195" s="7">
@@ -40292,7 +40379,7 @@
         <v>6</v>
       </c>
       <c r="F1196" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15500</v>
       </c>
       <c r="G1196" s="7">
@@ -40319,7 +40406,7 @@
         <v>6</v>
       </c>
       <c r="F1197" s="7">
-        <f t="shared" ref="F1197:F1202" si="33">F1196+750</f>
+        <f t="shared" ref="F1197:F1202" si="34">F1196+750</f>
         <v>16250</v>
       </c>
       <c r="G1197" s="7">
@@ -40346,7 +40433,7 @@
         <v>6</v>
       </c>
       <c r="F1198" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>17000</v>
       </c>
       <c r="G1198" s="7">
@@ -40373,7 +40460,7 @@
         <v>6</v>
       </c>
       <c r="F1199" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>17750</v>
       </c>
       <c r="G1199" s="7">
@@ -40400,7 +40487,7 @@
         <v>6</v>
       </c>
       <c r="F1200" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>18500</v>
       </c>
       <c r="G1200" s="7">
@@ -40427,7 +40514,7 @@
         <v>6</v>
       </c>
       <c r="F1201" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>19250</v>
       </c>
       <c r="G1201" s="7">
@@ -40454,7 +40541,7 @@
         <v>6</v>
       </c>
       <c r="F1202" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>20000</v>
       </c>
       <c r="G1202" s="7">
@@ -40481,7 +40568,7 @@
         <v>6</v>
       </c>
       <c r="F1203" s="7">
-        <f t="shared" ref="F1203:F1222" si="34">F1202+1500</f>
+        <f t="shared" ref="F1203:F1222" si="35">F1202+1500</f>
         <v>21500</v>
       </c>
       <c r="G1203" s="7">
@@ -40508,7 +40595,7 @@
         <v>6</v>
       </c>
       <c r="F1204" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>23000</v>
       </c>
       <c r="G1204" s="7">
@@ -40535,7 +40622,7 @@
         <v>6</v>
       </c>
       <c r="F1205" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>24500</v>
       </c>
       <c r="G1205" s="7">
@@ -40562,7 +40649,7 @@
         <v>6</v>
       </c>
       <c r="F1206" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>26000</v>
       </c>
       <c r="G1206" s="7">
@@ -40589,7 +40676,7 @@
         <v>6</v>
       </c>
       <c r="F1207" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>27500</v>
       </c>
       <c r="G1207" s="7">
@@ -40616,7 +40703,7 @@
         <v>6</v>
       </c>
       <c r="F1208" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>29000</v>
       </c>
       <c r="G1208" s="7">
@@ -40643,7 +40730,7 @@
         <v>6</v>
       </c>
       <c r="F1209" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>30500</v>
       </c>
       <c r="G1209" s="7">
@@ -40670,7 +40757,7 @@
         <v>6</v>
       </c>
       <c r="F1210" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>32000</v>
       </c>
       <c r="G1210" s="7">
@@ -40697,7 +40784,7 @@
         <v>6</v>
       </c>
       <c r="F1211" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>33500</v>
       </c>
       <c r="G1211" s="7">
@@ -40724,7 +40811,7 @@
         <v>6</v>
       </c>
       <c r="F1212" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>35000</v>
       </c>
       <c r="G1212" s="7">
@@ -40751,7 +40838,7 @@
         <v>6</v>
       </c>
       <c r="F1213" s="7">
-        <f t="shared" ref="F1213:F1221" si="35">F1212+2000</f>
+        <f t="shared" ref="F1213:F1221" si="36">F1212+2000</f>
         <v>37000</v>
       </c>
       <c r="G1213" s="7">
@@ -40778,7 +40865,7 @@
         <v>6</v>
       </c>
       <c r="F1214" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>39000</v>
       </c>
       <c r="G1214" s="7">
@@ -40805,7 +40892,7 @@
         <v>6</v>
       </c>
       <c r="F1215" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>41000</v>
       </c>
       <c r="G1215" s="7">
@@ -40832,7 +40919,7 @@
         <v>6</v>
       </c>
       <c r="F1216" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>43000</v>
       </c>
       <c r="G1216" s="7">
@@ -40859,7 +40946,7 @@
         <v>6</v>
       </c>
       <c r="F1217" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>45000</v>
       </c>
       <c r="G1217" s="7">
@@ -40886,7 +40973,7 @@
         <v>6</v>
       </c>
       <c r="F1218" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>47000</v>
       </c>
       <c r="G1218" s="7">
@@ -40913,7 +41000,7 @@
         <v>6</v>
       </c>
       <c r="F1219" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>49000</v>
       </c>
       <c r="G1219" s="7">
@@ -40940,7 +41027,7 @@
         <v>6</v>
       </c>
       <c r="F1220" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>51000</v>
       </c>
       <c r="G1220" s="7">
@@ -40967,7 +41054,7 @@
         <v>6</v>
       </c>
       <c r="F1221" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>53000</v>
       </c>
       <c r="G1221" s="7">
@@ -40994,7 +41081,7 @@
         <v>6</v>
       </c>
       <c r="F1222" s="7">
-        <f t="shared" ref="F1222:F1231" si="36">F1221+3000</f>
+        <f t="shared" ref="F1222:F1231" si="37">F1221+3000</f>
         <v>56000</v>
       </c>
       <c r="G1222" s="7">
@@ -41021,7 +41108,7 @@
         <v>6</v>
       </c>
       <c r="F1223" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>59000</v>
       </c>
       <c r="G1223" s="7">
@@ -41048,7 +41135,7 @@
         <v>6</v>
       </c>
       <c r="F1224" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>62000</v>
       </c>
       <c r="G1224" s="7">
@@ -41075,7 +41162,7 @@
         <v>6</v>
       </c>
       <c r="F1225" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>65000</v>
       </c>
       <c r="G1225" s="7">
@@ -41102,7 +41189,7 @@
         <v>6</v>
       </c>
       <c r="F1226" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>68000</v>
       </c>
       <c r="G1226" s="7">
@@ -41129,7 +41216,7 @@
         <v>6</v>
       </c>
       <c r="F1227" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>71000</v>
       </c>
       <c r="G1227" s="7">
@@ -41156,7 +41243,7 @@
         <v>6</v>
       </c>
       <c r="F1228" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>74000</v>
       </c>
       <c r="G1228" s="7">
@@ -41183,7 +41270,7 @@
         <v>6</v>
       </c>
       <c r="F1229" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>77000</v>
       </c>
       <c r="G1229" s="7">
@@ -41210,7 +41297,7 @@
         <v>6</v>
       </c>
       <c r="F1230" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>80000</v>
       </c>
       <c r="G1230" s="7">
@@ -41237,7 +41324,7 @@
         <v>6</v>
       </c>
       <c r="F1231" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>83000</v>
       </c>
       <c r="G1231" s="7">
@@ -42210,4103 +42297,4924 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="1271" customHeight="1" spans="3:10">
+    <row r="1267" customHeight="1" spans="3:11">
+      <c r="C1267" s="7">
+        <v>8034</v>
+      </c>
+      <c r="D1267" s="10" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E1267" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1267" s="7">
+        <v>420</v>
+      </c>
+      <c r="G1267" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1267" s="5">
+        <v>2004</v>
+      </c>
+      <c r="I1267" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1267" s="5" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K1267" s="12" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="1268" customHeight="1" spans="3:11">
+      <c r="C1268" s="7">
+        <v>8035</v>
+      </c>
+      <c r="D1268" s="10" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E1268" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1268" s="7">
+        <v>430</v>
+      </c>
+      <c r="G1268" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1268" s="5">
+        <v>2005</v>
+      </c>
+      <c r="I1268" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1268" s="5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="K1268" s="12" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1269" customHeight="1" spans="3:11">
+      <c r="C1269" s="7">
+        <v>8036</v>
+      </c>
+      <c r="D1269" s="10" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E1269" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1269" s="7">
+        <v>440</v>
+      </c>
+      <c r="G1269" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1269" s="5">
+        <v>2006</v>
+      </c>
+      <c r="I1269" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1269" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K1269" s="12" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="1270" customHeight="1" spans="3:11">
+      <c r="C1270" s="7">
+        <v>8037</v>
+      </c>
+      <c r="D1270" s="11" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E1270" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1270" s="7">
+        <v>450</v>
+      </c>
+      <c r="G1270" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1270" s="7">
+        <v>2003</v>
+      </c>
+      <c r="I1270" s="7">
+        <v>90</v>
+      </c>
+      <c r="J1270" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="K1270" s="12" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1271" customHeight="1" spans="3:11">
       <c r="C1271" s="7">
-        <v>9001</v>
-      </c>
-      <c r="D1271" s="7" t="s">
-        <v>1332</v>
+        <v>8038</v>
+      </c>
+      <c r="D1271" s="10" t="s">
+        <v>1336</v>
       </c>
       <c r="E1271" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1271" s="7">
-        <v>10</v>
-      </c>
-      <c r="G1271" s="7">
+        <v>460</v>
+      </c>
+      <c r="G1271" s="5">
         <v>1</v>
       </c>
       <c r="H1271" s="7">
-        <v>18</v>
+        <v>2002</v>
       </c>
       <c r="I1271" s="7">
-        <v>50</v>
-      </c>
-      <c r="J1271" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1272" customHeight="1" spans="3:10">
+        <v>80</v>
+      </c>
+      <c r="J1271" s="5" t="s">
+        <v>1323</v>
+      </c>
+      <c r="K1271" s="12" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="1272" customHeight="1" spans="3:11">
       <c r="C1272" s="7">
-        <v>9002</v>
-      </c>
-      <c r="D1272" s="7" t="s">
-        <v>1334</v>
+        <v>8039</v>
+      </c>
+      <c r="D1272" s="10" t="s">
+        <v>1337</v>
       </c>
       <c r="E1272" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1272" s="7">
-        <f t="shared" ref="F1272:F1335" si="37">F1271+10</f>
-        <v>20</v>
-      </c>
-      <c r="G1272" s="7">
+        <v>470</v>
+      </c>
+      <c r="G1272" s="5">
         <v>1</v>
       </c>
       <c r="H1272" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1272" s="7">
-        <v>50</v>
-      </c>
-      <c r="J1272" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1273" customHeight="1" spans="3:10">
+        <v>2001</v>
+      </c>
+      <c r="I1272" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1272" s="5" t="s">
+        <v>1325</v>
+      </c>
+      <c r="K1272" s="12" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="1273" customHeight="1" spans="3:11">
       <c r="C1273" s="7">
-        <v>9003</v>
-      </c>
-      <c r="D1273" s="7" t="s">
-        <v>1335</v>
+        <v>8040</v>
+      </c>
+      <c r="D1273" s="10" t="s">
+        <v>1338</v>
       </c>
       <c r="E1273" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1273" s="7">
-        <f t="shared" si="37"/>
+        <v>480</v>
+      </c>
+      <c r="G1273" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1273" s="7">
+        <v>2011</v>
+      </c>
+      <c r="I1273" s="5">
         <v>30</v>
       </c>
-      <c r="G1273" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1273" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1273" s="7">
-        <v>50</v>
-      </c>
-      <c r="J1273" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1274" customHeight="1" spans="3:10">
+      <c r="J1273" s="5" t="s">
+        <v>1327</v>
+      </c>
+      <c r="K1273" s="12" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1274" customHeight="1" spans="3:11">
       <c r="C1274" s="7">
-        <v>9004</v>
-      </c>
-      <c r="D1274" s="7" t="s">
-        <v>1336</v>
+        <v>8041</v>
+      </c>
+      <c r="D1274" s="10" t="s">
+        <v>1339</v>
       </c>
       <c r="E1274" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1274" s="7">
-        <f t="shared" si="37"/>
-        <v>40</v>
-      </c>
-      <c r="G1274" s="7">
+        <v>490</v>
+      </c>
+      <c r="G1274" s="5">
         <v>1</v>
       </c>
       <c r="H1274" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1274" s="7">
-        <v>50</v>
-      </c>
-      <c r="J1274" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1275" customHeight="1" spans="3:10">
+        <v>2010</v>
+      </c>
+      <c r="I1274" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1274" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="K1274" s="12" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="1275" customHeight="1" spans="3:11">
       <c r="C1275" s="7">
-        <v>9005</v>
-      </c>
-      <c r="D1275" s="7" t="s">
-        <v>1337</v>
+        <v>8042</v>
+      </c>
+      <c r="D1275" s="10" t="s">
+        <v>1340</v>
       </c>
       <c r="E1275" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1275" s="7">
-        <f t="shared" si="37"/>
-        <v>50</v>
-      </c>
-      <c r="G1275" s="7">
+        <v>500</v>
+      </c>
+      <c r="G1275" s="5">
         <v>1</v>
       </c>
       <c r="H1275" s="7">
-        <v>18</v>
+        <v>2003</v>
       </c>
       <c r="I1275" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1275" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1276" customHeight="1" spans="3:10">
-      <c r="C1276" s="7">
-        <v>9006</v>
-      </c>
-      <c r="D1276" s="7" t="s">
-        <v>1338</v>
-      </c>
-      <c r="E1276" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1276" s="7">
-        <f t="shared" si="37"/>
-        <v>60</v>
-      </c>
-      <c r="G1276" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1276" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1276" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1276" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1277" customHeight="1" spans="3:10">
-      <c r="C1277" s="7">
-        <v>9007</v>
-      </c>
-      <c r="D1277" s="7" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E1277" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1277" s="7">
-        <f t="shared" si="37"/>
-        <v>70</v>
-      </c>
-      <c r="G1277" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1277" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1277" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1277" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1278" customHeight="1" spans="3:10">
-      <c r="C1278" s="7">
-        <v>9008</v>
-      </c>
-      <c r="D1278" s="7" t="s">
-        <v>1340</v>
-      </c>
-      <c r="E1278" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1278" s="7">
-        <f t="shared" si="37"/>
-        <v>80</v>
-      </c>
-      <c r="G1278" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1278" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1278" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1278" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1279" customHeight="1" spans="3:10">
-      <c r="C1279" s="7">
-        <v>9009</v>
-      </c>
-      <c r="D1279" s="7" t="s">
-        <v>1341</v>
-      </c>
-      <c r="E1279" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1279" s="7">
-        <f t="shared" si="37"/>
         <v>90</v>
       </c>
-      <c r="G1279" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1279" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1279" s="7">
-        <v>70</v>
-      </c>
-      <c r="J1279" s="7" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="1280" customHeight="1" spans="3:10">
-      <c r="C1280" s="7">
-        <v>9010</v>
-      </c>
-      <c r="D1280" s="7" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E1280" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1280" s="7">
-        <f t="shared" si="37"/>
-        <v>100</v>
-      </c>
-      <c r="G1280" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1280" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1280" s="7">
-        <v>70</v>
-      </c>
-      <c r="J1280" s="7" t="s">
-        <v>1333</v>
+      <c r="J1275" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="K1275" s="12" t="s">
+        <v>1299</v>
       </c>
     </row>
     <row r="1281" customHeight="1" spans="3:10">
       <c r="C1281" s="7">
-        <v>9011</v>
+        <v>9001</v>
       </c>
       <c r="D1281" s="7" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="E1281" s="7">
         <v>9</v>
       </c>
       <c r="F1281" s="7">
-        <f t="shared" si="37"/>
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G1281" s="7">
         <v>1</v>
       </c>
       <c r="H1281" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1281" s="7">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J1281" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1282" customHeight="1" spans="3:10">
       <c r="C1282" s="7">
-        <v>9012</v>
+        <v>9002</v>
       </c>
       <c r="D1282" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="E1282" s="7">
         <v>9</v>
       </c>
       <c r="F1282" s="7">
-        <f t="shared" si="37"/>
-        <v>120</v>
+        <f t="shared" ref="F1282:F1345" si="38">F1281+10</f>
+        <v>20</v>
       </c>
       <c r="G1282" s="7">
         <v>1</v>
       </c>
       <c r="H1282" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1282" s="7">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J1282" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1283" customHeight="1" spans="3:10">
       <c r="C1283" s="7">
-        <v>9013</v>
+        <v>9003</v>
       </c>
       <c r="D1283" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="E1283" s="7">
         <v>9</v>
       </c>
       <c r="F1283" s="7">
-        <f t="shared" si="37"/>
-        <v>130</v>
+        <f t="shared" si="38"/>
+        <v>30</v>
       </c>
       <c r="G1283" s="7">
         <v>1</v>
       </c>
       <c r="H1283" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1283" s="7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J1283" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1284" customHeight="1" spans="3:10">
       <c r="C1284" s="7">
-        <v>9014</v>
+        <v>9004</v>
       </c>
       <c r="D1284" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="E1284" s="7">
         <v>9</v>
       </c>
       <c r="F1284" s="7">
-        <f t="shared" si="37"/>
-        <v>140</v>
+        <f t="shared" si="38"/>
+        <v>40</v>
       </c>
       <c r="G1284" s="7">
         <v>1</v>
       </c>
       <c r="H1284" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1284" s="7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J1284" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1285" customHeight="1" spans="3:10">
       <c r="C1285" s="7">
-        <v>9015</v>
+        <v>9005</v>
       </c>
       <c r="D1285" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="E1285" s="7">
         <v>9</v>
       </c>
       <c r="F1285" s="7">
-        <f t="shared" si="37"/>
-        <v>150</v>
+        <f t="shared" si="38"/>
+        <v>50</v>
       </c>
       <c r="G1285" s="7">
         <v>1</v>
       </c>
       <c r="H1285" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1285" s="7">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J1285" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1286" customHeight="1" spans="3:10">
       <c r="C1286" s="7">
-        <v>9016</v>
+        <v>9006</v>
       </c>
       <c r="D1286" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="E1286" s="7">
         <v>9</v>
       </c>
       <c r="F1286" s="7">
-        <f t="shared" si="37"/>
-        <v>160</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="G1286" s="7">
         <v>1</v>
       </c>
       <c r="H1286" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1286" s="7">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J1286" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1287" customHeight="1" spans="3:10">
       <c r="C1287" s="7">
-        <v>9017</v>
+        <v>9007</v>
       </c>
       <c r="D1287" s="7" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="E1287" s="7">
         <v>9</v>
       </c>
       <c r="F1287" s="7">
-        <f t="shared" si="37"/>
-        <v>170</v>
+        <f t="shared" si="38"/>
+        <v>70</v>
       </c>
       <c r="G1287" s="7">
         <v>1</v>
       </c>
       <c r="H1287" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1287" s="7">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J1287" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1288" customHeight="1" spans="3:10">
       <c r="C1288" s="7">
-        <v>9018</v>
+        <v>9008</v>
       </c>
       <c r="D1288" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="E1288" s="7">
         <v>9</v>
       </c>
       <c r="F1288" s="7">
-        <f t="shared" si="37"/>
-        <v>180</v>
+        <f t="shared" si="38"/>
+        <v>80</v>
       </c>
       <c r="G1288" s="7">
         <v>1</v>
       </c>
       <c r="H1288" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1288" s="7">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J1288" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1289" customHeight="1" spans="3:10">
       <c r="C1289" s="7">
-        <v>9019</v>
+        <v>9009</v>
       </c>
       <c r="D1289" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E1289" s="7">
         <v>9</v>
       </c>
       <c r="F1289" s="7">
-        <f t="shared" si="37"/>
-        <v>190</v>
+        <f t="shared" si="38"/>
+        <v>90</v>
       </c>
       <c r="G1289" s="7">
         <v>1</v>
       </c>
       <c r="H1289" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1289" s="7">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J1289" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1290" customHeight="1" spans="3:10">
       <c r="C1290" s="7">
-        <v>9020</v>
+        <v>9010</v>
       </c>
       <c r="D1290" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="E1290" s="7">
         <v>9</v>
       </c>
       <c r="F1290" s="7">
-        <f t="shared" si="37"/>
-        <v>200</v>
+        <f t="shared" si="38"/>
+        <v>100</v>
       </c>
       <c r="G1290" s="7">
         <v>1</v>
       </c>
       <c r="H1290" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1290" s="7">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J1290" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1291" customHeight="1" spans="3:10">
       <c r="C1291" s="7">
-        <v>9021</v>
+        <v>9011</v>
       </c>
       <c r="D1291" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="E1291" s="7">
         <v>9</v>
       </c>
       <c r="F1291" s="7">
-        <f t="shared" si="37"/>
-        <v>210</v>
+        <f t="shared" si="38"/>
+        <v>110</v>
       </c>
       <c r="G1291" s="7">
         <v>1</v>
       </c>
       <c r="H1291" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1291" s="7">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J1291" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1292" customHeight="1" spans="3:10">
       <c r="C1292" s="7">
-        <v>9022</v>
+        <v>9012</v>
       </c>
       <c r="D1292" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E1292" s="7">
         <v>9</v>
       </c>
       <c r="F1292" s="7">
-        <f t="shared" si="37"/>
-        <v>220</v>
+        <f t="shared" si="38"/>
+        <v>120</v>
       </c>
       <c r="G1292" s="7">
         <v>1</v>
       </c>
       <c r="H1292" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1292" s="7">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J1292" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1293" customHeight="1" spans="3:10">
       <c r="C1293" s="7">
-        <v>9023</v>
+        <v>9013</v>
       </c>
       <c r="D1293" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="E1293" s="7">
         <v>9</v>
       </c>
       <c r="F1293" s="7">
-        <f t="shared" si="37"/>
-        <v>230</v>
+        <f t="shared" si="38"/>
+        <v>130</v>
       </c>
       <c r="G1293" s="7">
         <v>1</v>
       </c>
       <c r="H1293" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1293" s="7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J1293" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1294" customHeight="1" spans="3:10">
       <c r="C1294" s="7">
-        <v>9024</v>
+        <v>9014</v>
       </c>
       <c r="D1294" s="7" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="E1294" s="7">
         <v>9</v>
       </c>
       <c r="F1294" s="7">
-        <f t="shared" si="37"/>
-        <v>240</v>
+        <f t="shared" si="38"/>
+        <v>140</v>
       </c>
       <c r="G1294" s="7">
         <v>1</v>
       </c>
       <c r="H1294" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1294" s="7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J1294" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1295" customHeight="1" spans="3:10">
       <c r="C1295" s="7">
-        <v>9025</v>
+        <v>9015</v>
       </c>
       <c r="D1295" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E1295" s="7">
         <v>9</v>
       </c>
       <c r="F1295" s="7">
-        <f t="shared" si="37"/>
-        <v>250</v>
+        <f t="shared" si="38"/>
+        <v>150</v>
       </c>
       <c r="G1295" s="7">
         <v>1</v>
       </c>
       <c r="H1295" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1295" s="7">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J1295" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1296" customHeight="1" spans="3:10">
       <c r="C1296" s="7">
-        <v>9026</v>
+        <v>9016</v>
       </c>
       <c r="D1296" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="E1296" s="7">
         <v>9</v>
       </c>
       <c r="F1296" s="7">
-        <f t="shared" si="37"/>
-        <v>260</v>
+        <f t="shared" si="38"/>
+        <v>160</v>
       </c>
       <c r="G1296" s="7">
         <v>1</v>
       </c>
       <c r="H1296" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1296" s="7">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J1296" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1297" customHeight="1" spans="3:10">
       <c r="C1297" s="7">
-        <v>9027</v>
+        <v>9017</v>
       </c>
       <c r="D1297" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="E1297" s="7">
         <v>9</v>
       </c>
       <c r="F1297" s="7">
-        <f t="shared" si="37"/>
-        <v>270</v>
+        <f t="shared" si="38"/>
+        <v>170</v>
       </c>
       <c r="G1297" s="7">
         <v>1</v>
       </c>
       <c r="H1297" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1297" s="7">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J1297" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1298" customHeight="1" spans="3:10">
       <c r="C1298" s="7">
-        <v>9028</v>
+        <v>9018</v>
       </c>
       <c r="D1298" s="7" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E1298" s="7">
         <v>9</v>
       </c>
       <c r="F1298" s="7">
-        <f t="shared" si="37"/>
-        <v>280</v>
+        <f t="shared" si="38"/>
+        <v>180</v>
       </c>
       <c r="G1298" s="7">
         <v>1</v>
       </c>
       <c r="H1298" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1298" s="7">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J1298" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1299" customHeight="1" spans="3:10">
       <c r="C1299" s="7">
-        <v>9029</v>
+        <v>9019</v>
       </c>
       <c r="D1299" s="7" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E1299" s="7">
         <v>9</v>
       </c>
       <c r="F1299" s="7">
-        <f t="shared" si="37"/>
-        <v>290</v>
+        <f t="shared" si="38"/>
+        <v>190</v>
       </c>
       <c r="G1299" s="7">
         <v>1</v>
       </c>
       <c r="H1299" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1299" s="7">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J1299" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1300" customHeight="1" spans="3:10">
       <c r="C1300" s="7">
-        <v>9030</v>
+        <v>9020</v>
       </c>
       <c r="D1300" s="7" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E1300" s="7">
         <v>9</v>
       </c>
       <c r="F1300" s="7">
-        <f t="shared" si="37"/>
-        <v>300</v>
+        <f t="shared" si="38"/>
+        <v>200</v>
       </c>
       <c r="G1300" s="7">
         <v>1</v>
       </c>
       <c r="H1300" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1300" s="7">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J1300" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1301" customHeight="1" spans="3:10">
       <c r="C1301" s="7">
-        <v>9031</v>
+        <v>9021</v>
       </c>
       <c r="D1301" s="7" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E1301" s="7">
         <v>9</v>
       </c>
       <c r="F1301" s="7">
-        <f t="shared" si="37"/>
-        <v>310</v>
+        <f t="shared" si="38"/>
+        <v>210</v>
       </c>
       <c r="G1301" s="7">
         <v>1</v>
       </c>
       <c r="H1301" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1301" s="7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1301" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1302" customHeight="1" spans="3:10">
       <c r="C1302" s="7">
-        <v>9032</v>
+        <v>9022</v>
       </c>
       <c r="D1302" s="7" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="E1302" s="7">
         <v>9</v>
       </c>
       <c r="F1302" s="7">
-        <f t="shared" si="37"/>
-        <v>320</v>
+        <f t="shared" si="38"/>
+        <v>220</v>
       </c>
       <c r="G1302" s="7">
         <v>1</v>
       </c>
       <c r="H1302" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1302" s="7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1302" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1303" customHeight="1" spans="3:10">
       <c r="C1303" s="7">
-        <v>9033</v>
+        <v>9023</v>
       </c>
       <c r="D1303" s="7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="E1303" s="7">
         <v>9</v>
       </c>
       <c r="F1303" s="7">
-        <f t="shared" si="37"/>
-        <v>330</v>
+        <f t="shared" si="38"/>
+        <v>230</v>
       </c>
       <c r="G1303" s="7">
         <v>1</v>
       </c>
       <c r="H1303" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1303" s="7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="J1303" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1304" customHeight="1" spans="3:10">
       <c r="C1304" s="7">
-        <v>9034</v>
+        <v>9024</v>
       </c>
       <c r="D1304" s="7" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="E1304" s="7">
         <v>9</v>
       </c>
       <c r="F1304" s="7">
-        <f t="shared" si="37"/>
-        <v>340</v>
+        <f t="shared" si="38"/>
+        <v>240</v>
       </c>
       <c r="G1304" s="7">
         <v>1</v>
       </c>
       <c r="H1304" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1304" s="7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="J1304" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1305" customHeight="1" spans="3:10">
       <c r="C1305" s="7">
-        <v>9035</v>
+        <v>9025</v>
       </c>
       <c r="D1305" s="7" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="E1305" s="7">
         <v>9</v>
       </c>
       <c r="F1305" s="7">
-        <f t="shared" si="37"/>
-        <v>350</v>
+        <f t="shared" si="38"/>
+        <v>250</v>
       </c>
       <c r="G1305" s="7">
         <v>1</v>
       </c>
       <c r="H1305" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1305" s="7">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J1305" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1306" customHeight="1" spans="3:10">
       <c r="C1306" s="7">
-        <v>9036</v>
+        <v>9026</v>
       </c>
       <c r="D1306" s="7" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="E1306" s="7">
         <v>9</v>
       </c>
       <c r="F1306" s="7">
-        <f t="shared" si="37"/>
-        <v>360</v>
+        <f t="shared" si="38"/>
+        <v>260</v>
       </c>
       <c r="G1306" s="7">
         <v>1</v>
       </c>
       <c r="H1306" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1306" s="7">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J1306" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1307" customHeight="1" spans="3:10">
       <c r="C1307" s="7">
-        <v>9037</v>
+        <v>9027</v>
       </c>
       <c r="D1307" s="7" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E1307" s="7">
         <v>9</v>
       </c>
       <c r="F1307" s="7">
-        <f t="shared" si="37"/>
-        <v>370</v>
+        <f t="shared" si="38"/>
+        <v>270</v>
       </c>
       <c r="G1307" s="7">
         <v>1</v>
       </c>
       <c r="H1307" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1307" s="7">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="J1307" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1308" customHeight="1" spans="3:10">
       <c r="C1308" s="7">
-        <v>9038</v>
+        <v>9028</v>
       </c>
       <c r="D1308" s="7" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="E1308" s="7">
         <v>9</v>
       </c>
       <c r="F1308" s="7">
-        <f t="shared" si="37"/>
-        <v>380</v>
+        <f t="shared" si="38"/>
+        <v>280</v>
       </c>
       <c r="G1308" s="7">
         <v>1</v>
       </c>
       <c r="H1308" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1308" s="7">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="J1308" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1309" customHeight="1" spans="3:10">
       <c r="C1309" s="7">
-        <v>9039</v>
+        <v>9029</v>
       </c>
       <c r="D1309" s="7" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E1309" s="7">
         <v>9</v>
       </c>
       <c r="F1309" s="7">
-        <f t="shared" si="37"/>
-        <v>390</v>
+        <f t="shared" si="38"/>
+        <v>290</v>
       </c>
       <c r="G1309" s="7">
         <v>1</v>
       </c>
       <c r="H1309" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1309" s="7">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="J1309" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1310" customHeight="1" spans="3:10">
       <c r="C1310" s="7">
-        <v>9040</v>
+        <v>9030</v>
       </c>
       <c r="D1310" s="7" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="E1310" s="7">
         <v>9</v>
       </c>
       <c r="F1310" s="7">
-        <f t="shared" si="37"/>
-        <v>400</v>
+        <f t="shared" si="38"/>
+        <v>300</v>
       </c>
       <c r="G1310" s="7">
         <v>1</v>
       </c>
       <c r="H1310" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1310" s="7">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="J1310" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1311" customHeight="1" spans="3:10">
       <c r="C1311" s="7">
-        <v>9041</v>
+        <v>9031</v>
       </c>
       <c r="D1311" s="7" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="E1311" s="7">
         <v>9</v>
       </c>
       <c r="F1311" s="7">
-        <f t="shared" si="37"/>
-        <v>410</v>
+        <f t="shared" si="38"/>
+        <v>310</v>
       </c>
       <c r="G1311" s="7">
         <v>1</v>
       </c>
       <c r="H1311" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1311" s="7">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J1311" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1312" customHeight="1" spans="3:10">
       <c r="C1312" s="7">
-        <v>9042</v>
+        <v>9032</v>
       </c>
       <c r="D1312" s="7" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="E1312" s="7">
         <v>9</v>
       </c>
       <c r="F1312" s="7">
-        <f t="shared" si="37"/>
-        <v>420</v>
+        <f t="shared" si="38"/>
+        <v>320</v>
       </c>
       <c r="G1312" s="7">
         <v>1</v>
       </c>
       <c r="H1312" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1312" s="7">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J1312" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1313" customHeight="1" spans="3:10">
       <c r="C1313" s="7">
-        <v>9043</v>
+        <v>9033</v>
       </c>
       <c r="D1313" s="7" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E1313" s="7">
         <v>9</v>
       </c>
       <c r="F1313" s="7">
-        <f t="shared" si="37"/>
-        <v>430</v>
+        <f t="shared" si="38"/>
+        <v>330</v>
       </c>
       <c r="G1313" s="7">
         <v>1</v>
       </c>
       <c r="H1313" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1313" s="7">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="J1313" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1314" customHeight="1" spans="3:10">
       <c r="C1314" s="7">
-        <v>9044</v>
+        <v>9034</v>
       </c>
       <c r="D1314" s="7" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E1314" s="7">
         <v>9</v>
       </c>
       <c r="F1314" s="7">
-        <f t="shared" si="37"/>
-        <v>440</v>
+        <f t="shared" si="38"/>
+        <v>340</v>
       </c>
       <c r="G1314" s="7">
         <v>1</v>
       </c>
       <c r="H1314" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1314" s="7">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="J1314" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1315" customHeight="1" spans="3:10">
       <c r="C1315" s="7">
-        <v>9045</v>
+        <v>9035</v>
       </c>
       <c r="D1315" s="7" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E1315" s="7">
         <v>9</v>
       </c>
       <c r="F1315" s="7">
-        <f t="shared" si="37"/>
-        <v>450</v>
+        <f t="shared" si="38"/>
+        <v>350</v>
       </c>
       <c r="G1315" s="7">
         <v>1</v>
       </c>
       <c r="H1315" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1315" s="7">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="J1315" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1316" customHeight="1" spans="3:10">
       <c r="C1316" s="7">
-        <v>9046</v>
+        <v>9036</v>
       </c>
       <c r="D1316" s="7" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="E1316" s="7">
         <v>9</v>
       </c>
       <c r="F1316" s="7">
-        <f t="shared" si="37"/>
-        <v>460</v>
+        <f t="shared" si="38"/>
+        <v>360</v>
       </c>
       <c r="G1316" s="7">
         <v>1</v>
       </c>
       <c r="H1316" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1316" s="7">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="J1316" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1317" customHeight="1" spans="3:10">
       <c r="C1317" s="7">
-        <v>9047</v>
+        <v>9037</v>
       </c>
       <c r="D1317" s="7" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="E1317" s="7">
         <v>9</v>
       </c>
       <c r="F1317" s="7">
-        <f t="shared" si="37"/>
-        <v>470</v>
+        <f t="shared" si="38"/>
+        <v>370</v>
       </c>
       <c r="G1317" s="7">
         <v>1</v>
       </c>
       <c r="H1317" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1317" s="7">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J1317" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1318" customHeight="1" spans="3:10">
       <c r="C1318" s="7">
-        <v>9048</v>
+        <v>9038</v>
       </c>
       <c r="D1318" s="7" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E1318" s="7">
         <v>9</v>
       </c>
       <c r="F1318" s="7">
-        <f t="shared" si="37"/>
-        <v>480</v>
+        <f t="shared" si="38"/>
+        <v>380</v>
       </c>
       <c r="G1318" s="7">
         <v>1</v>
       </c>
       <c r="H1318" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1318" s="7">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J1318" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1319" customHeight="1" spans="3:10">
       <c r="C1319" s="7">
-        <v>9049</v>
+        <v>9039</v>
       </c>
       <c r="D1319" s="7" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E1319" s="7">
         <v>9</v>
       </c>
       <c r="F1319" s="7">
-        <f t="shared" si="37"/>
-        <v>490</v>
+        <f t="shared" si="38"/>
+        <v>390</v>
       </c>
       <c r="G1319" s="7">
         <v>1</v>
       </c>
       <c r="H1319" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1319" s="7">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="J1319" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1320" customHeight="1" spans="3:10">
       <c r="C1320" s="7">
-        <v>9050</v>
+        <v>9040</v>
       </c>
       <c r="D1320" s="7" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="E1320" s="7">
         <v>9</v>
       </c>
       <c r="F1320" s="7">
-        <f t="shared" si="37"/>
-        <v>500</v>
+        <f t="shared" si="38"/>
+        <v>400</v>
       </c>
       <c r="G1320" s="7">
         <v>1</v>
       </c>
       <c r="H1320" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1320" s="7">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="J1320" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1321" customHeight="1" spans="3:10">
       <c r="C1321" s="7">
-        <v>9051</v>
+        <v>9041</v>
       </c>
       <c r="D1321" s="7" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E1321" s="7">
         <v>9</v>
       </c>
       <c r="F1321" s="7">
-        <f t="shared" si="37"/>
-        <v>510</v>
+        <f t="shared" si="38"/>
+        <v>410</v>
       </c>
       <c r="G1321" s="7">
         <v>1</v>
       </c>
       <c r="H1321" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1321" s="7">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="J1321" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1322" customHeight="1" spans="3:10">
       <c r="C1322" s="7">
-        <v>9052</v>
+        <v>9042</v>
       </c>
       <c r="D1322" s="7" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E1322" s="7">
         <v>9</v>
       </c>
       <c r="F1322" s="7">
-        <f t="shared" si="37"/>
-        <v>520</v>
+        <f t="shared" si="38"/>
+        <v>420</v>
       </c>
       <c r="G1322" s="7">
         <v>1</v>
       </c>
       <c r="H1322" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1322" s="7">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="J1322" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1323" customHeight="1" spans="3:10">
       <c r="C1323" s="7">
-        <v>9053</v>
+        <v>9043</v>
       </c>
       <c r="D1323" s="7" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E1323" s="7">
         <v>9</v>
       </c>
       <c r="F1323" s="7">
-        <f t="shared" si="37"/>
-        <v>530</v>
+        <f t="shared" si="38"/>
+        <v>430</v>
       </c>
       <c r="G1323" s="7">
         <v>1</v>
       </c>
       <c r="H1323" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1323" s="7">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="J1323" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1324" customHeight="1" spans="3:10">
       <c r="C1324" s="7">
-        <v>9054</v>
+        <v>9044</v>
       </c>
       <c r="D1324" s="7" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="E1324" s="7">
         <v>9</v>
       </c>
       <c r="F1324" s="7">
-        <f t="shared" si="37"/>
-        <v>540</v>
+        <f t="shared" si="38"/>
+        <v>440</v>
       </c>
       <c r="G1324" s="7">
         <v>1</v>
       </c>
       <c r="H1324" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1324" s="7">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="J1324" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1325" customHeight="1" spans="3:10">
       <c r="C1325" s="7">
-        <v>9055</v>
+        <v>9045</v>
       </c>
       <c r="D1325" s="7" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="E1325" s="7">
         <v>9</v>
       </c>
       <c r="F1325" s="7">
-        <f t="shared" si="37"/>
-        <v>550</v>
+        <f t="shared" si="38"/>
+        <v>450</v>
       </c>
       <c r="G1325" s="7">
         <v>1</v>
       </c>
       <c r="H1325" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1325" s="7">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="J1325" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1326" customHeight="1" spans="3:10">
       <c r="C1326" s="7">
-        <v>9056</v>
+        <v>9046</v>
       </c>
       <c r="D1326" s="7" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E1326" s="7">
         <v>9</v>
       </c>
       <c r="F1326" s="7">
-        <f t="shared" si="37"/>
-        <v>560</v>
+        <f t="shared" si="38"/>
+        <v>460</v>
       </c>
       <c r="G1326" s="7">
         <v>1</v>
       </c>
       <c r="H1326" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1326" s="7">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="J1326" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1327" customHeight="1" spans="3:10">
       <c r="C1327" s="7">
-        <v>9057</v>
+        <v>9047</v>
       </c>
       <c r="D1327" s="7" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E1327" s="7">
         <v>9</v>
       </c>
       <c r="F1327" s="7">
-        <f t="shared" si="37"/>
-        <v>570</v>
+        <f t="shared" si="38"/>
+        <v>470</v>
       </c>
       <c r="G1327" s="7">
         <v>1</v>
       </c>
       <c r="H1327" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1327" s="7">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="J1327" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1328" customHeight="1" spans="3:10">
       <c r="C1328" s="7">
-        <v>9058</v>
+        <v>9048</v>
       </c>
       <c r="D1328" s="7" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E1328" s="7">
         <v>9</v>
       </c>
       <c r="F1328" s="7">
-        <f t="shared" si="37"/>
-        <v>580</v>
+        <f t="shared" si="38"/>
+        <v>480</v>
       </c>
       <c r="G1328" s="7">
         <v>1</v>
       </c>
       <c r="H1328" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1328" s="7">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="J1328" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1329" customHeight="1" spans="3:10">
       <c r="C1329" s="7">
-        <v>9059</v>
+        <v>9049</v>
       </c>
       <c r="D1329" s="7" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="E1329" s="7">
         <v>9</v>
       </c>
       <c r="F1329" s="7">
-        <f t="shared" si="37"/>
-        <v>590</v>
+        <f t="shared" si="38"/>
+        <v>490</v>
       </c>
       <c r="G1329" s="7">
         <v>1</v>
       </c>
       <c r="H1329" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1329" s="7">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="J1329" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1330" customHeight="1" spans="3:10">
       <c r="C1330" s="7">
-        <v>9060</v>
+        <v>9050</v>
       </c>
       <c r="D1330" s="7" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E1330" s="7">
         <v>9</v>
       </c>
       <c r="F1330" s="7">
-        <f t="shared" si="37"/>
-        <v>600</v>
+        <f t="shared" si="38"/>
+        <v>500</v>
       </c>
       <c r="G1330" s="7">
         <v>1</v>
       </c>
       <c r="H1330" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1330" s="7">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="J1330" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1331" customHeight="1" spans="3:10">
       <c r="C1331" s="7">
-        <v>9061</v>
+        <v>9051</v>
       </c>
       <c r="D1331" s="7" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E1331" s="7">
         <v>9</v>
       </c>
       <c r="F1331" s="7">
-        <f t="shared" si="37"/>
-        <v>610</v>
+        <f t="shared" si="38"/>
+        <v>510</v>
       </c>
       <c r="G1331" s="7">
         <v>1</v>
       </c>
       <c r="H1331" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1331" s="7">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="J1331" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1332" customHeight="1" spans="3:10">
       <c r="C1332" s="7">
-        <v>9062</v>
+        <v>9052</v>
       </c>
       <c r="D1332" s="7" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E1332" s="7">
         <v>9</v>
       </c>
       <c r="F1332" s="7">
-        <f t="shared" si="37"/>
-        <v>620</v>
+        <f t="shared" si="38"/>
+        <v>520</v>
       </c>
       <c r="G1332" s="7">
         <v>1</v>
       </c>
       <c r="H1332" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1332" s="7">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="J1332" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1333" customHeight="1" spans="3:10">
       <c r="C1333" s="7">
-        <v>9063</v>
+        <v>9053</v>
       </c>
       <c r="D1333" s="7" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="E1333" s="7">
         <v>9</v>
       </c>
       <c r="F1333" s="7">
-        <f t="shared" si="37"/>
-        <v>630</v>
+        <f t="shared" si="38"/>
+        <v>530</v>
       </c>
       <c r="G1333" s="7">
         <v>1</v>
       </c>
       <c r="H1333" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1333" s="7">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="J1333" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1334" customHeight="1" spans="3:10">
       <c r="C1334" s="7">
-        <v>9064</v>
+        <v>9054</v>
       </c>
       <c r="D1334" s="7" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="E1334" s="7">
         <v>9</v>
       </c>
       <c r="F1334" s="7">
-        <f t="shared" si="37"/>
-        <v>640</v>
+        <f t="shared" si="38"/>
+        <v>540</v>
       </c>
       <c r="G1334" s="7">
         <v>1</v>
       </c>
       <c r="H1334" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1334" s="7">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="J1334" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1335" customHeight="1" spans="3:10">
       <c r="C1335" s="7">
-        <v>9065</v>
+        <v>9055</v>
       </c>
       <c r="D1335" s="7" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="E1335" s="7">
         <v>9</v>
       </c>
       <c r="F1335" s="7">
-        <f t="shared" si="37"/>
-        <v>650</v>
+        <f t="shared" si="38"/>
+        <v>550</v>
       </c>
       <c r="G1335" s="7">
         <v>1</v>
       </c>
       <c r="H1335" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1335" s="7">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="J1335" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1336" customHeight="1" spans="3:10">
       <c r="C1336" s="7">
-        <v>9066</v>
+        <v>9056</v>
       </c>
       <c r="D1336" s="7" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="E1336" s="7">
         <v>9</v>
       </c>
       <c r="F1336" s="7">
-        <f t="shared" ref="F1336:F1399" si="38">F1335+10</f>
-        <v>660</v>
+        <f t="shared" si="38"/>
+        <v>560</v>
       </c>
       <c r="G1336" s="7">
         <v>1</v>
       </c>
       <c r="H1336" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1336" s="7">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="J1336" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1337" customHeight="1" spans="3:10">
       <c r="C1337" s="7">
-        <v>9067</v>
+        <v>9057</v>
       </c>
       <c r="D1337" s="7" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="E1337" s="7">
         <v>9</v>
       </c>
       <c r="F1337" s="7">
         <f t="shared" si="38"/>
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="G1337" s="7">
         <v>1</v>
       </c>
       <c r="H1337" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1337" s="7">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="J1337" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1338" customHeight="1" spans="3:10">
       <c r="C1338" s="7">
-        <v>9068</v>
+        <v>9058</v>
       </c>
       <c r="D1338" s="7" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="E1338" s="7">
         <v>9</v>
       </c>
       <c r="F1338" s="7">
         <f t="shared" si="38"/>
-        <v>680</v>
+        <v>580</v>
       </c>
       <c r="G1338" s="7">
         <v>1</v>
       </c>
       <c r="H1338" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1338" s="7">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="J1338" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1339" customHeight="1" spans="3:10">
       <c r="C1339" s="7">
-        <v>9069</v>
+        <v>9059</v>
       </c>
       <c r="D1339" s="7" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="E1339" s="7">
         <v>9</v>
       </c>
       <c r="F1339" s="7">
         <f t="shared" si="38"/>
-        <v>690</v>
+        <v>590</v>
       </c>
       <c r="G1339" s="7">
         <v>1</v>
       </c>
       <c r="H1339" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1339" s="7">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="J1339" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1340" customHeight="1" spans="3:10">
       <c r="C1340" s="7">
-        <v>9070</v>
+        <v>9060</v>
       </c>
       <c r="D1340" s="7" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E1340" s="7">
         <v>9</v>
       </c>
       <c r="F1340" s="7">
         <f t="shared" si="38"/>
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G1340" s="7">
         <v>1</v>
       </c>
       <c r="H1340" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1340" s="7">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="J1340" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1341" customHeight="1" spans="3:10">
       <c r="C1341" s="7">
-        <v>9071</v>
+        <v>9061</v>
       </c>
       <c r="D1341" s="7" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E1341" s="7">
         <v>9</v>
       </c>
       <c r="F1341" s="7">
         <f t="shared" si="38"/>
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="G1341" s="7">
         <v>1</v>
       </c>
       <c r="H1341" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1341" s="7">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="J1341" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1342" customHeight="1" spans="3:10">
       <c r="C1342" s="7">
-        <v>9072</v>
+        <v>9062</v>
       </c>
       <c r="D1342" s="7" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E1342" s="7">
         <v>9</v>
       </c>
       <c r="F1342" s="7">
         <f t="shared" si="38"/>
-        <v>720</v>
+        <v>620</v>
       </c>
       <c r="G1342" s="7">
         <v>1</v>
       </c>
       <c r="H1342" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1342" s="7">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="J1342" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1343" customHeight="1" spans="3:10">
       <c r="C1343" s="7">
-        <v>9073</v>
+        <v>9063</v>
       </c>
       <c r="D1343" s="7" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="E1343" s="7">
         <v>9</v>
       </c>
       <c r="F1343" s="7">
         <f t="shared" si="38"/>
-        <v>730</v>
+        <v>630</v>
       </c>
       <c r="G1343" s="7">
         <v>1</v>
       </c>
       <c r="H1343" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1343" s="7">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="J1343" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1344" customHeight="1" spans="3:10">
       <c r="C1344" s="7">
-        <v>9074</v>
+        <v>9064</v>
       </c>
       <c r="D1344" s="7" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E1344" s="7">
         <v>9</v>
       </c>
       <c r="F1344" s="7">
         <f t="shared" si="38"/>
-        <v>740</v>
+        <v>640</v>
       </c>
       <c r="G1344" s="7">
         <v>1</v>
       </c>
       <c r="H1344" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1344" s="7">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="J1344" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1345" customHeight="1" spans="3:10">
       <c r="C1345" s="7">
-        <v>9075</v>
+        <v>9065</v>
       </c>
       <c r="D1345" s="7" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="E1345" s="7">
         <v>9</v>
       </c>
       <c r="F1345" s="7">
         <f t="shared" si="38"/>
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="G1345" s="7">
         <v>1</v>
       </c>
       <c r="H1345" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1345" s="7">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="J1345" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1346" customHeight="1" spans="3:10">
       <c r="C1346" s="7">
-        <v>9076</v>
+        <v>9066</v>
       </c>
       <c r="D1346" s="7" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E1346" s="7">
         <v>9</v>
       </c>
       <c r="F1346" s="7">
-        <f t="shared" si="38"/>
-        <v>760</v>
+        <f t="shared" ref="F1346:F1409" si="39">F1345+10</f>
+        <v>660</v>
       </c>
       <c r="G1346" s="7">
         <v>1</v>
       </c>
       <c r="H1346" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1346" s="7">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="J1346" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1347" customHeight="1" spans="3:10">
       <c r="C1347" s="7">
-        <v>9077</v>
+        <v>9067</v>
       </c>
       <c r="D1347" s="7" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E1347" s="7">
         <v>9</v>
       </c>
       <c r="F1347" s="7">
-        <f t="shared" si="38"/>
-        <v>770</v>
+        <f t="shared" si="39"/>
+        <v>670</v>
       </c>
       <c r="G1347" s="7">
         <v>1</v>
       </c>
       <c r="H1347" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1347" s="7">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="J1347" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1348" customHeight="1" spans="3:10">
       <c r="C1348" s="7">
-        <v>9078</v>
+        <v>9068</v>
       </c>
       <c r="D1348" s="7" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E1348" s="7">
         <v>9</v>
       </c>
       <c r="F1348" s="7">
-        <f t="shared" si="38"/>
-        <v>780</v>
+        <f t="shared" si="39"/>
+        <v>680</v>
       </c>
       <c r="G1348" s="7">
         <v>1</v>
       </c>
       <c r="H1348" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1348" s="7">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="J1348" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1349" customHeight="1" spans="3:10">
       <c r="C1349" s="7">
-        <v>9079</v>
+        <v>9069</v>
       </c>
       <c r="D1349" s="7" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E1349" s="7">
         <v>9</v>
       </c>
       <c r="F1349" s="7">
-        <f t="shared" si="38"/>
-        <v>790</v>
+        <f t="shared" si="39"/>
+        <v>690</v>
       </c>
       <c r="G1349" s="7">
         <v>1</v>
       </c>
       <c r="H1349" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1349" s="7">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="J1349" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1350" customHeight="1" spans="3:10">
       <c r="C1350" s="7">
-        <v>9080</v>
+        <v>9070</v>
       </c>
       <c r="D1350" s="7" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="E1350" s="7">
         <v>9</v>
       </c>
       <c r="F1350" s="7">
-        <f t="shared" si="38"/>
-        <v>800</v>
+        <f t="shared" si="39"/>
+        <v>700</v>
       </c>
       <c r="G1350" s="7">
         <v>1</v>
       </c>
       <c r="H1350" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1350" s="7">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="J1350" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1351" customHeight="1" spans="3:10">
       <c r="C1351" s="7">
-        <v>9081</v>
+        <v>9071</v>
       </c>
       <c r="D1351" s="7" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E1351" s="7">
         <v>9</v>
       </c>
       <c r="F1351" s="7">
-        <f t="shared" si="38"/>
-        <v>810</v>
+        <f t="shared" si="39"/>
+        <v>710</v>
       </c>
       <c r="G1351" s="7">
         <v>1</v>
       </c>
       <c r="H1351" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1351" s="7">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="J1351" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1352" customHeight="1" spans="3:10">
       <c r="C1352" s="7">
-        <v>9082</v>
+        <v>9072</v>
       </c>
       <c r="D1352" s="7" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E1352" s="7">
         <v>9</v>
       </c>
       <c r="F1352" s="7">
-        <f t="shared" si="38"/>
-        <v>820</v>
+        <f t="shared" si="39"/>
+        <v>720</v>
       </c>
       <c r="G1352" s="7">
         <v>1</v>
       </c>
       <c r="H1352" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1352" s="7">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="J1352" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1353" customHeight="1" spans="3:10">
       <c r="C1353" s="7">
-        <v>9083</v>
+        <v>9073</v>
       </c>
       <c r="D1353" s="7" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E1353" s="7">
         <v>9</v>
       </c>
       <c r="F1353" s="7">
-        <f t="shared" si="38"/>
-        <v>830</v>
+        <f t="shared" si="39"/>
+        <v>730</v>
       </c>
       <c r="G1353" s="7">
         <v>1</v>
       </c>
       <c r="H1353" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1353" s="7">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="J1353" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1354" customHeight="1" spans="3:10">
       <c r="C1354" s="7">
-        <v>9084</v>
+        <v>9074</v>
       </c>
       <c r="D1354" s="7" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="E1354" s="7">
         <v>9</v>
       </c>
       <c r="F1354" s="7">
-        <f t="shared" si="38"/>
-        <v>840</v>
+        <f t="shared" si="39"/>
+        <v>740</v>
       </c>
       <c r="G1354" s="7">
         <v>1</v>
       </c>
       <c r="H1354" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1354" s="7">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="J1354" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1355" customHeight="1" spans="3:10">
       <c r="C1355" s="7">
-        <v>9085</v>
+        <v>9075</v>
       </c>
       <c r="D1355" s="7" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E1355" s="7">
         <v>9</v>
       </c>
       <c r="F1355" s="7">
-        <f t="shared" si="38"/>
-        <v>850</v>
+        <f t="shared" si="39"/>
+        <v>750</v>
       </c>
       <c r="G1355" s="7">
         <v>1</v>
       </c>
       <c r="H1355" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1355" s="7">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="J1355" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1356" customHeight="1" spans="3:10">
       <c r="C1356" s="7">
-        <v>9086</v>
+        <v>9076</v>
       </c>
       <c r="D1356" s="7" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E1356" s="7">
         <v>9</v>
       </c>
       <c r="F1356" s="7">
-        <f t="shared" si="38"/>
-        <v>860</v>
+        <f t="shared" si="39"/>
+        <v>760</v>
       </c>
       <c r="G1356" s="7">
         <v>1</v>
       </c>
       <c r="H1356" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1356" s="7">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="J1356" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1357" customHeight="1" spans="3:10">
       <c r="C1357" s="7">
-        <v>9087</v>
+        <v>9077</v>
       </c>
       <c r="D1357" s="7" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="E1357" s="7">
         <v>9</v>
       </c>
       <c r="F1357" s="7">
-        <f t="shared" si="38"/>
-        <v>870</v>
+        <f t="shared" si="39"/>
+        <v>770</v>
       </c>
       <c r="G1357" s="7">
         <v>1</v>
       </c>
       <c r="H1357" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1357" s="7">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="J1357" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1358" customHeight="1" spans="3:10">
       <c r="C1358" s="7">
-        <v>9088</v>
+        <v>9078</v>
       </c>
       <c r="D1358" s="7" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E1358" s="7">
         <v>9</v>
       </c>
       <c r="F1358" s="7">
-        <f t="shared" si="38"/>
-        <v>880</v>
+        <f t="shared" si="39"/>
+        <v>780</v>
       </c>
       <c r="G1358" s="7">
         <v>1</v>
       </c>
       <c r="H1358" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1358" s="7">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="J1358" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1359" customHeight="1" spans="3:10">
       <c r="C1359" s="7">
-        <v>9089</v>
+        <v>9079</v>
       </c>
       <c r="D1359" s="7" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E1359" s="7">
         <v>9</v>
       </c>
       <c r="F1359" s="7">
-        <f t="shared" si="38"/>
-        <v>890</v>
+        <f t="shared" si="39"/>
+        <v>790</v>
       </c>
       <c r="G1359" s="7">
         <v>1</v>
       </c>
       <c r="H1359" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1359" s="7">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="J1359" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1360" customHeight="1" spans="3:10">
       <c r="C1360" s="7">
-        <v>9090</v>
+        <v>9080</v>
       </c>
       <c r="D1360" s="7" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E1360" s="7">
         <v>9</v>
       </c>
       <c r="F1360" s="7">
-        <f t="shared" si="38"/>
-        <v>900</v>
+        <f t="shared" si="39"/>
+        <v>800</v>
       </c>
       <c r="G1360" s="7">
         <v>1</v>
       </c>
       <c r="H1360" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1360" s="7">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="J1360" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1361" customHeight="1" spans="3:10">
       <c r="C1361" s="7">
-        <v>9091</v>
+        <v>9081</v>
       </c>
       <c r="D1361" s="7" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="E1361" s="7">
         <v>9</v>
       </c>
       <c r="F1361" s="7">
-        <f t="shared" si="38"/>
-        <v>910</v>
+        <f t="shared" si="39"/>
+        <v>810</v>
       </c>
       <c r="G1361" s="7">
         <v>1</v>
       </c>
       <c r="H1361" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1361" s="7">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="J1361" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1362" customHeight="1" spans="3:10">
       <c r="C1362" s="7">
-        <v>9092</v>
+        <v>9082</v>
       </c>
       <c r="D1362" s="7" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="E1362" s="7">
         <v>9</v>
       </c>
       <c r="F1362" s="7">
-        <f t="shared" si="38"/>
-        <v>920</v>
+        <f t="shared" si="39"/>
+        <v>820</v>
       </c>
       <c r="G1362" s="7">
         <v>1</v>
       </c>
       <c r="H1362" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1362" s="7">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="J1362" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1363" customHeight="1" spans="3:10">
       <c r="C1363" s="7">
-        <v>9093</v>
+        <v>9083</v>
       </c>
       <c r="D1363" s="7" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="E1363" s="7">
         <v>9</v>
       </c>
       <c r="F1363" s="7">
-        <f t="shared" si="38"/>
-        <v>930</v>
+        <f t="shared" si="39"/>
+        <v>830</v>
       </c>
       <c r="G1363" s="7">
         <v>1</v>
       </c>
       <c r="H1363" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1363" s="7">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="J1363" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1364" customHeight="1" spans="3:10">
       <c r="C1364" s="7">
-        <v>9094</v>
+        <v>9084</v>
       </c>
       <c r="D1364" s="7" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="E1364" s="7">
         <v>9</v>
       </c>
       <c r="F1364" s="7">
-        <f t="shared" si="38"/>
-        <v>940</v>
+        <f t="shared" si="39"/>
+        <v>840</v>
       </c>
       <c r="G1364" s="7">
         <v>1</v>
       </c>
       <c r="H1364" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1364" s="7">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="J1364" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1365" customHeight="1" spans="3:10">
       <c r="C1365" s="7">
-        <v>9095</v>
+        <v>9085</v>
       </c>
       <c r="D1365" s="7" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="E1365" s="7">
         <v>9</v>
       </c>
       <c r="F1365" s="7">
-        <f t="shared" si="38"/>
-        <v>950</v>
+        <f t="shared" si="39"/>
+        <v>850</v>
       </c>
       <c r="G1365" s="7">
         <v>1</v>
       </c>
       <c r="H1365" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1365" s="7">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="J1365" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1366" customHeight="1" spans="3:10">
       <c r="C1366" s="7">
-        <v>9096</v>
+        <v>9086</v>
       </c>
       <c r="D1366" s="7" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E1366" s="7">
         <v>9</v>
       </c>
       <c r="F1366" s="7">
-        <f t="shared" si="38"/>
-        <v>960</v>
+        <f t="shared" si="39"/>
+        <v>860</v>
       </c>
       <c r="G1366" s="7">
         <v>1</v>
       </c>
       <c r="H1366" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1366" s="7">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="J1366" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1367" customHeight="1" spans="3:10">
       <c r="C1367" s="7">
-        <v>9097</v>
+        <v>9087</v>
       </c>
       <c r="D1367" s="7" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E1367" s="7">
         <v>9</v>
       </c>
       <c r="F1367" s="7">
-        <f t="shared" si="38"/>
-        <v>970</v>
+        <f t="shared" si="39"/>
+        <v>870</v>
       </c>
       <c r="G1367" s="7">
         <v>1</v>
       </c>
       <c r="H1367" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1367" s="7">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="J1367" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1368" customHeight="1" spans="3:10">
       <c r="C1368" s="7">
-        <v>9098</v>
+        <v>9088</v>
       </c>
       <c r="D1368" s="7" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="E1368" s="7">
         <v>9</v>
       </c>
       <c r="F1368" s="7">
-        <f t="shared" si="38"/>
-        <v>980</v>
+        <f t="shared" si="39"/>
+        <v>880</v>
       </c>
       <c r="G1368" s="7">
         <v>1</v>
       </c>
       <c r="H1368" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1368" s="7">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="J1368" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1369" customHeight="1" spans="3:10">
       <c r="C1369" s="7">
-        <v>9099</v>
+        <v>9089</v>
       </c>
       <c r="D1369" s="7" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E1369" s="7">
         <v>9</v>
       </c>
       <c r="F1369" s="7">
-        <f t="shared" si="38"/>
-        <v>990</v>
+        <f t="shared" si="39"/>
+        <v>890</v>
       </c>
       <c r="G1369" s="7">
         <v>1</v>
       </c>
       <c r="H1369" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1369" s="7">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J1369" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1370" customHeight="1" spans="3:10">
       <c r="C1370" s="7">
-        <v>9100</v>
+        <v>9090</v>
       </c>
       <c r="D1370" s="7" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E1370" s="7">
         <v>9</v>
       </c>
       <c r="F1370" s="7">
-        <f t="shared" si="38"/>
-        <v>1000</v>
+        <f t="shared" si="39"/>
+        <v>900</v>
       </c>
       <c r="G1370" s="7">
         <v>1</v>
       </c>
       <c r="H1370" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1370" s="7">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J1370" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1371" customHeight="1" spans="3:10">
       <c r="C1371" s="7">
-        <v>9101</v>
+        <v>9091</v>
       </c>
       <c r="D1371" s="7" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="E1371" s="7">
         <v>9</v>
       </c>
       <c r="F1371" s="7">
-        <f t="shared" ref="F1371:F1420" si="39">F1370+20</f>
-        <v>1020</v>
+        <f t="shared" si="39"/>
+        <v>910</v>
       </c>
       <c r="G1371" s="7">
         <v>1</v>
       </c>
       <c r="H1371" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1371" s="7">
-        <f t="shared" ref="I1371:I1420" si="40">I1367+10</f>
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="J1371" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1372" customHeight="1" spans="3:10">
       <c r="C1372" s="7">
-        <v>9102</v>
+        <v>9092</v>
       </c>
       <c r="D1372" s="7" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E1372" s="7">
         <v>9</v>
       </c>
       <c r="F1372" s="7">
         <f t="shared" si="39"/>
-        <v>1040</v>
+        <v>920</v>
       </c>
       <c r="G1372" s="7">
         <v>1</v>
       </c>
       <c r="H1372" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1372" s="7">
-        <f t="shared" si="40"/>
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="J1372" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1373" customHeight="1" spans="3:10">
       <c r="C1373" s="7">
-        <v>9103</v>
+        <v>9093</v>
       </c>
       <c r="D1373" s="7" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E1373" s="7">
         <v>9</v>
       </c>
       <c r="F1373" s="7">
         <f t="shared" si="39"/>
-        <v>1060</v>
+        <v>930</v>
       </c>
       <c r="G1373" s="7">
         <v>1</v>
       </c>
       <c r="H1373" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1373" s="7">
-        <f t="shared" si="40"/>
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="J1373" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1374" customHeight="1" spans="3:10">
       <c r="C1374" s="7">
-        <v>9104</v>
+        <v>9094</v>
       </c>
       <c r="D1374" s="7" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E1374" s="7">
         <v>9</v>
       </c>
       <c r="F1374" s="7">
         <f t="shared" si="39"/>
-        <v>1080</v>
+        <v>940</v>
       </c>
       <c r="G1374" s="7">
         <v>1</v>
       </c>
       <c r="H1374" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1374" s="7">
-        <f t="shared" si="40"/>
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="J1374" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1375" customHeight="1" spans="3:10">
       <c r="C1375" s="7">
-        <v>9105</v>
+        <v>9095</v>
       </c>
       <c r="D1375" s="7" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="E1375" s="7">
         <v>9</v>
       </c>
       <c r="F1375" s="7">
         <f t="shared" si="39"/>
-        <v>1100</v>
+        <v>950</v>
       </c>
       <c r="G1375" s="7">
         <v>1</v>
       </c>
       <c r="H1375" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1375" s="7">
-        <f t="shared" si="40"/>
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="J1375" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1376" customHeight="1" spans="3:10">
       <c r="C1376" s="7">
-        <v>9106</v>
+        <v>9096</v>
       </c>
       <c r="D1376" s="7" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E1376" s="7">
         <v>9</v>
       </c>
       <c r="F1376" s="7">
         <f t="shared" si="39"/>
-        <v>1120</v>
+        <v>960</v>
       </c>
       <c r="G1376" s="7">
         <v>1</v>
       </c>
       <c r="H1376" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1376" s="7">
-        <f t="shared" si="40"/>
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="J1376" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1377" customHeight="1" spans="3:10">
       <c r="C1377" s="7">
-        <v>9107</v>
+        <v>9097</v>
       </c>
       <c r="D1377" s="7" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E1377" s="7">
         <v>9</v>
       </c>
       <c r="F1377" s="7">
         <f t="shared" si="39"/>
-        <v>1140</v>
+        <v>970</v>
       </c>
       <c r="G1377" s="7">
         <v>1</v>
       </c>
       <c r="H1377" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1377" s="7">
-        <f t="shared" si="40"/>
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="J1377" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1378" customHeight="1" spans="3:10">
       <c r="C1378" s="7">
-        <v>9108</v>
+        <v>9098</v>
       </c>
       <c r="D1378" s="7" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E1378" s="7">
         <v>9</v>
       </c>
       <c r="F1378" s="7">
         <f t="shared" si="39"/>
-        <v>1160</v>
+        <v>980</v>
       </c>
       <c r="G1378" s="7">
         <v>1</v>
       </c>
       <c r="H1378" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1378" s="7">
-        <f t="shared" si="40"/>
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="J1378" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1379" customHeight="1" spans="3:10">
       <c r="C1379" s="7">
-        <v>9109</v>
+        <v>9099</v>
       </c>
       <c r="D1379" s="7" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E1379" s="7">
         <v>9</v>
       </c>
       <c r="F1379" s="7">
         <f t="shared" si="39"/>
-        <v>1180</v>
+        <v>990</v>
       </c>
       <c r="G1379" s="7">
         <v>1</v>
       </c>
       <c r="H1379" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1379" s="7">
-        <f t="shared" si="40"/>
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="J1379" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1380" customHeight="1" spans="3:10">
       <c r="C1380" s="7">
-        <v>9110</v>
+        <v>9100</v>
       </c>
       <c r="D1380" s="7" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E1380" s="7">
         <v>9</v>
       </c>
       <c r="F1380" s="7">
         <f t="shared" si="39"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="G1380" s="7">
         <v>1</v>
       </c>
       <c r="H1380" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1380" s="7">
-        <f t="shared" si="40"/>
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="J1380" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1381" customHeight="1" spans="3:10">
       <c r="C1381" s="7">
-        <v>9111</v>
+        <v>9101</v>
       </c>
       <c r="D1381" s="7" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E1381" s="7">
         <v>9</v>
       </c>
       <c r="F1381" s="7">
-        <f t="shared" si="39"/>
-        <v>1220</v>
+        <f t="shared" ref="F1381:F1444" si="40">F1380+20</f>
+        <v>1020</v>
       </c>
       <c r="G1381" s="7">
         <v>1</v>
       </c>
       <c r="H1381" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1381" s="7">
-        <f t="shared" si="40"/>
-        <v>320</v>
+        <f t="shared" ref="I1381:I1444" si="41">I1377+10</f>
+        <v>300</v>
       </c>
       <c r="J1381" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1382" customHeight="1" spans="3:10">
       <c r="C1382" s="7">
-        <v>9112</v>
+        <v>9102</v>
       </c>
       <c r="D1382" s="7" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E1382" s="7">
         <v>9</v>
       </c>
       <c r="F1382" s="7">
-        <f t="shared" si="39"/>
-        <v>1240</v>
+        <f t="shared" si="40"/>
+        <v>1040</v>
       </c>
       <c r="G1382" s="7">
         <v>1</v>
       </c>
       <c r="H1382" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1382" s="7">
-        <f t="shared" si="40"/>
-        <v>320</v>
+        <f t="shared" si="41"/>
+        <v>300</v>
       </c>
       <c r="J1382" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1383" customHeight="1" spans="3:10">
       <c r="C1383" s="7">
-        <v>9113</v>
+        <v>9103</v>
       </c>
       <c r="D1383" s="7" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="E1383" s="7">
         <v>9</v>
       </c>
       <c r="F1383" s="7">
-        <f t="shared" si="39"/>
-        <v>1260</v>
+        <f t="shared" si="40"/>
+        <v>1060</v>
       </c>
       <c r="G1383" s="7">
         <v>1</v>
       </c>
       <c r="H1383" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1383" s="7">
-        <f t="shared" si="40"/>
-        <v>330</v>
+        <f t="shared" si="41"/>
+        <v>300</v>
       </c>
       <c r="J1383" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1384" customHeight="1" spans="3:10">
       <c r="C1384" s="7">
-        <v>9114</v>
+        <v>9104</v>
       </c>
       <c r="D1384" s="7" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="E1384" s="7">
         <v>9</v>
       </c>
       <c r="F1384" s="7">
-        <f t="shared" si="39"/>
-        <v>1280</v>
+        <f t="shared" si="40"/>
+        <v>1080</v>
       </c>
       <c r="G1384" s="7">
         <v>1</v>
       </c>
       <c r="H1384" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1384" s="7">
-        <f t="shared" si="40"/>
-        <v>330</v>
+        <f t="shared" si="41"/>
+        <v>300</v>
       </c>
       <c r="J1384" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1385" customHeight="1" spans="3:10">
       <c r="C1385" s="7">
-        <v>9115</v>
+        <v>9105</v>
       </c>
       <c r="D1385" s="7" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="E1385" s="7">
         <v>9</v>
       </c>
       <c r="F1385" s="7">
-        <f t="shared" si="39"/>
-        <v>1300</v>
+        <f t="shared" si="40"/>
+        <v>1100</v>
       </c>
       <c r="G1385" s="7">
         <v>1</v>
       </c>
       <c r="H1385" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1385" s="7">
-        <f t="shared" si="40"/>
-        <v>330</v>
+        <f t="shared" si="41"/>
+        <v>310</v>
       </c>
       <c r="J1385" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1386" customHeight="1" spans="3:10">
       <c r="C1386" s="7">
-        <v>9116</v>
+        <v>9106</v>
       </c>
       <c r="D1386" s="7" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E1386" s="7">
         <v>9</v>
       </c>
       <c r="F1386" s="7">
-        <f t="shared" si="39"/>
-        <v>1320</v>
+        <f t="shared" si="40"/>
+        <v>1120</v>
       </c>
       <c r="G1386" s="7">
         <v>1</v>
       </c>
       <c r="H1386" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1386" s="7">
-        <f t="shared" si="40"/>
-        <v>330</v>
+        <f t="shared" si="41"/>
+        <v>310</v>
       </c>
       <c r="J1386" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1387" customHeight="1" spans="3:10">
       <c r="C1387" s="7">
-        <v>9117</v>
+        <v>9107</v>
       </c>
       <c r="D1387" s="7" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="E1387" s="7">
         <v>9</v>
       </c>
       <c r="F1387" s="7">
-        <f t="shared" si="39"/>
-        <v>1340</v>
+        <f t="shared" si="40"/>
+        <v>1140</v>
       </c>
       <c r="G1387" s="7">
         <v>1</v>
       </c>
       <c r="H1387" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1387" s="7">
-        <f t="shared" si="40"/>
-        <v>340</v>
+        <f t="shared" si="41"/>
+        <v>310</v>
       </c>
       <c r="J1387" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1388" customHeight="1" spans="3:10">
       <c r="C1388" s="7">
-        <v>9118</v>
+        <v>9108</v>
       </c>
       <c r="D1388" s="7" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="E1388" s="7">
         <v>9</v>
       </c>
       <c r="F1388" s="7">
-        <f t="shared" si="39"/>
-        <v>1360</v>
+        <f t="shared" si="40"/>
+        <v>1160</v>
       </c>
       <c r="G1388" s="7">
         <v>1</v>
       </c>
       <c r="H1388" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1388" s="7">
-        <f t="shared" si="40"/>
-        <v>340</v>
+        <f t="shared" si="41"/>
+        <v>310</v>
       </c>
       <c r="J1388" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1389" customHeight="1" spans="3:10">
       <c r="C1389" s="7">
-        <v>9119</v>
+        <v>9109</v>
       </c>
       <c r="D1389" s="7" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="E1389" s="7">
         <v>9</v>
       </c>
       <c r="F1389" s="7">
-        <f t="shared" si="39"/>
-        <v>1380</v>
+        <f t="shared" si="40"/>
+        <v>1180</v>
       </c>
       <c r="G1389" s="7">
         <v>1</v>
       </c>
       <c r="H1389" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1389" s="7">
-        <f t="shared" si="40"/>
-        <v>340</v>
+        <f t="shared" si="41"/>
+        <v>320</v>
       </c>
       <c r="J1389" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1390" customHeight="1" spans="3:10">
       <c r="C1390" s="7">
-        <v>9120</v>
+        <v>9110</v>
       </c>
       <c r="D1390" s="7" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="E1390" s="7">
         <v>9</v>
       </c>
       <c r="F1390" s="7">
-        <f t="shared" si="39"/>
-        <v>1400</v>
+        <f t="shared" si="40"/>
+        <v>1200</v>
       </c>
       <c r="G1390" s="7">
         <v>1</v>
       </c>
       <c r="H1390" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1390" s="7">
-        <f t="shared" si="40"/>
-        <v>340</v>
+        <f t="shared" si="41"/>
+        <v>320</v>
       </c>
       <c r="J1390" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1391" customHeight="1" spans="3:10">
       <c r="C1391" s="7">
-        <v>9121</v>
+        <v>9111</v>
       </c>
       <c r="D1391" s="7" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="E1391" s="7">
         <v>9</v>
       </c>
       <c r="F1391" s="7">
-        <f t="shared" si="39"/>
-        <v>1420</v>
+        <f t="shared" si="40"/>
+        <v>1220</v>
       </c>
       <c r="G1391" s="7">
         <v>1</v>
       </c>
       <c r="H1391" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1391" s="7">
-        <f t="shared" si="40"/>
-        <v>350</v>
+        <f t="shared" si="41"/>
+        <v>320</v>
       </c>
       <c r="J1391" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1392" customHeight="1" spans="3:10">
       <c r="C1392" s="7">
-        <v>9122</v>
+        <v>9112</v>
       </c>
       <c r="D1392" s="7" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="E1392" s="7">
         <v>9</v>
       </c>
       <c r="F1392" s="7">
-        <f t="shared" si="39"/>
-        <v>1440</v>
+        <f t="shared" si="40"/>
+        <v>1240</v>
       </c>
       <c r="G1392" s="7">
         <v>1</v>
       </c>
       <c r="H1392" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1392" s="7">
-        <f t="shared" si="40"/>
-        <v>350</v>
+        <f t="shared" si="41"/>
+        <v>320</v>
       </c>
       <c r="J1392" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1393" customHeight="1" spans="3:10">
       <c r="C1393" s="7">
-        <v>9123</v>
+        <v>9113</v>
       </c>
       <c r="D1393" s="7" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E1393" s="7">
         <v>9</v>
       </c>
       <c r="F1393" s="7">
-        <f t="shared" si="39"/>
-        <v>1460</v>
+        <f t="shared" si="40"/>
+        <v>1260</v>
       </c>
       <c r="G1393" s="7">
         <v>1</v>
       </c>
       <c r="H1393" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1393" s="7">
-        <f t="shared" si="40"/>
-        <v>350</v>
+        <f t="shared" si="41"/>
+        <v>330</v>
       </c>
       <c r="J1393" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1394" customHeight="1" spans="3:10">
       <c r="C1394" s="7">
-        <v>9124</v>
+        <v>9114</v>
       </c>
       <c r="D1394" s="7" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E1394" s="7">
         <v>9</v>
       </c>
       <c r="F1394" s="7">
-        <f t="shared" si="39"/>
-        <v>1480</v>
+        <f t="shared" si="40"/>
+        <v>1280</v>
       </c>
       <c r="G1394" s="7">
         <v>1</v>
       </c>
       <c r="H1394" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1394" s="7">
-        <f t="shared" si="40"/>
-        <v>350</v>
+        <f t="shared" si="41"/>
+        <v>330</v>
       </c>
       <c r="J1394" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1395" customHeight="1" spans="3:10">
       <c r="C1395" s="7">
-        <v>9125</v>
+        <v>9115</v>
       </c>
       <c r="D1395" s="7" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="E1395" s="7">
         <v>9</v>
       </c>
       <c r="F1395" s="7">
-        <f t="shared" si="39"/>
-        <v>1500</v>
+        <f t="shared" si="40"/>
+        <v>1300</v>
       </c>
       <c r="G1395" s="7">
         <v>1</v>
       </c>
       <c r="H1395" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1395" s="7">
-        <f t="shared" si="40"/>
-        <v>360</v>
+        <f t="shared" si="41"/>
+        <v>330</v>
       </c>
       <c r="J1395" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1396" customHeight="1" spans="3:10">
       <c r="C1396" s="7">
-        <v>9126</v>
+        <v>9116</v>
       </c>
       <c r="D1396" s="7" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="E1396" s="7">
         <v>9</v>
       </c>
       <c r="F1396" s="7">
-        <f t="shared" si="39"/>
-        <v>1520</v>
+        <f t="shared" si="40"/>
+        <v>1320</v>
       </c>
       <c r="G1396" s="7">
         <v>1</v>
       </c>
       <c r="H1396" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1396" s="7">
-        <f t="shared" si="40"/>
-        <v>360</v>
+        <f t="shared" si="41"/>
+        <v>330</v>
       </c>
       <c r="J1396" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1397" customHeight="1" spans="3:10">
       <c r="C1397" s="7">
-        <v>9127</v>
+        <v>9117</v>
       </c>
       <c r="D1397" s="7" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="E1397" s="7">
         <v>9</v>
       </c>
       <c r="F1397" s="7">
-        <f t="shared" si="39"/>
-        <v>1540</v>
+        <f t="shared" si="40"/>
+        <v>1340</v>
       </c>
       <c r="G1397" s="7">
         <v>1</v>
       </c>
       <c r="H1397" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1397" s="7">
-        <f t="shared" si="40"/>
-        <v>360</v>
+        <f t="shared" si="41"/>
+        <v>340</v>
       </c>
       <c r="J1397" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1398" customHeight="1" spans="3:10">
       <c r="C1398" s="7">
-        <v>9128</v>
+        <v>9118</v>
       </c>
       <c r="D1398" s="7" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="E1398" s="7">
         <v>9</v>
       </c>
       <c r="F1398" s="7">
-        <f t="shared" si="39"/>
-        <v>1560</v>
+        <f t="shared" si="40"/>
+        <v>1360</v>
       </c>
       <c r="G1398" s="7">
         <v>1</v>
       </c>
       <c r="H1398" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1398" s="7">
-        <f t="shared" si="40"/>
-        <v>360</v>
+        <f t="shared" si="41"/>
+        <v>340</v>
       </c>
       <c r="J1398" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1399" customHeight="1" spans="3:10">
       <c r="C1399" s="7">
-        <v>9129</v>
+        <v>9119</v>
       </c>
       <c r="D1399" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="E1399" s="7">
         <v>9</v>
       </c>
       <c r="F1399" s="7">
-        <f t="shared" si="39"/>
-        <v>1580</v>
+        <f t="shared" si="40"/>
+        <v>1380</v>
       </c>
       <c r="G1399" s="7">
         <v>1</v>
       </c>
       <c r="H1399" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1399" s="7">
-        <f t="shared" si="40"/>
-        <v>370</v>
+        <f t="shared" si="41"/>
+        <v>340</v>
       </c>
       <c r="J1399" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1400" customHeight="1" spans="3:10">
       <c r="C1400" s="7">
-        <v>9130</v>
+        <v>9120</v>
       </c>
       <c r="D1400" s="7" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="E1400" s="7">
         <v>9</v>
       </c>
       <c r="F1400" s="7">
-        <f t="shared" si="39"/>
-        <v>1600</v>
+        <f t="shared" si="40"/>
+        <v>1400</v>
       </c>
       <c r="G1400" s="7">
         <v>1</v>
       </c>
       <c r="H1400" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1400" s="7">
-        <f t="shared" si="40"/>
-        <v>370</v>
+        <f t="shared" si="41"/>
+        <v>340</v>
       </c>
       <c r="J1400" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1401" customHeight="1" spans="3:10">
       <c r="C1401" s="7">
-        <v>9131</v>
+        <v>9121</v>
       </c>
       <c r="D1401" s="7" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E1401" s="7">
         <v>9</v>
       </c>
       <c r="F1401" s="7">
-        <f t="shared" si="39"/>
-        <v>1620</v>
+        <f t="shared" si="40"/>
+        <v>1420</v>
       </c>
       <c r="G1401" s="7">
         <v>1</v>
       </c>
       <c r="H1401" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1401" s="7">
-        <f t="shared" si="40"/>
-        <v>370</v>
+        <f t="shared" si="41"/>
+        <v>350</v>
       </c>
       <c r="J1401" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1402" customHeight="1" spans="3:10">
       <c r="C1402" s="7">
-        <v>9132</v>
+        <v>9122</v>
       </c>
       <c r="D1402" s="7" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="E1402" s="7">
         <v>9</v>
       </c>
       <c r="F1402" s="7">
-        <f t="shared" si="39"/>
-        <v>1640</v>
+        <f t="shared" si="40"/>
+        <v>1440</v>
       </c>
       <c r="G1402" s="7">
         <v>1</v>
       </c>
       <c r="H1402" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1402" s="7">
-        <f t="shared" si="40"/>
-        <v>370</v>
+        <f t="shared" si="41"/>
+        <v>350</v>
       </c>
       <c r="J1402" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1403" customHeight="1" spans="3:10">
       <c r="C1403" s="7">
-        <v>9133</v>
+        <v>9123</v>
       </c>
       <c r="D1403" s="7" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="E1403" s="7">
         <v>9</v>
       </c>
       <c r="F1403" s="7">
-        <f t="shared" si="39"/>
-        <v>1660</v>
+        <f t="shared" si="40"/>
+        <v>1460</v>
       </c>
       <c r="G1403" s="7">
         <v>1</v>
       </c>
       <c r="H1403" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1403" s="7">
-        <f t="shared" si="40"/>
-        <v>380</v>
+        <f t="shared" si="41"/>
+        <v>350</v>
       </c>
       <c r="J1403" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1404" customHeight="1" spans="3:10">
       <c r="C1404" s="7">
-        <v>9134</v>
+        <v>9124</v>
       </c>
       <c r="D1404" s="7" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="E1404" s="7">
         <v>9</v>
       </c>
       <c r="F1404" s="7">
-        <f t="shared" si="39"/>
-        <v>1680</v>
+        <f t="shared" si="40"/>
+        <v>1480</v>
       </c>
       <c r="G1404" s="7">
         <v>1</v>
       </c>
       <c r="H1404" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1404" s="7">
-        <f t="shared" si="40"/>
-        <v>380</v>
+        <f t="shared" si="41"/>
+        <v>350</v>
       </c>
       <c r="J1404" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1405" customHeight="1" spans="3:10">
       <c r="C1405" s="7">
-        <v>9135</v>
+        <v>9125</v>
       </c>
       <c r="D1405" s="7" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="E1405" s="7">
         <v>9</v>
       </c>
       <c r="F1405" s="7">
-        <f t="shared" si="39"/>
-        <v>1700</v>
+        <f t="shared" si="40"/>
+        <v>1500</v>
       </c>
       <c r="G1405" s="7">
         <v>1</v>
       </c>
       <c r="H1405" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1405" s="7">
-        <f t="shared" si="40"/>
-        <v>380</v>
+        <f t="shared" si="41"/>
+        <v>360</v>
       </c>
       <c r="J1405" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1406" customHeight="1" spans="3:10">
       <c r="C1406" s="7">
-        <v>9136</v>
+        <v>9126</v>
       </c>
       <c r="D1406" s="7" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="E1406" s="7">
         <v>9</v>
       </c>
       <c r="F1406" s="7">
-        <f t="shared" si="39"/>
-        <v>1720</v>
+        <f t="shared" si="40"/>
+        <v>1520</v>
       </c>
       <c r="G1406" s="7">
         <v>1</v>
       </c>
       <c r="H1406" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1406" s="7">
-        <f t="shared" si="40"/>
-        <v>380</v>
+        <f t="shared" si="41"/>
+        <v>360</v>
       </c>
       <c r="J1406" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1407" customHeight="1" spans="3:10">
       <c r="C1407" s="7">
-        <v>9137</v>
+        <v>9127</v>
       </c>
       <c r="D1407" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="E1407" s="7">
         <v>9</v>
       </c>
       <c r="F1407" s="7">
-        <f t="shared" si="39"/>
-        <v>1740</v>
+        <f t="shared" si="40"/>
+        <v>1540</v>
       </c>
       <c r="G1407" s="7">
         <v>1</v>
       </c>
       <c r="H1407" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1407" s="7">
-        <f t="shared" si="40"/>
-        <v>390</v>
+        <f t="shared" si="41"/>
+        <v>360</v>
       </c>
       <c r="J1407" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1408" customHeight="1" spans="3:10">
       <c r="C1408" s="7">
-        <v>9138</v>
+        <v>9128</v>
       </c>
       <c r="D1408" s="7" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E1408" s="7">
         <v>9</v>
       </c>
       <c r="F1408" s="7">
-        <f t="shared" si="39"/>
-        <v>1760</v>
+        <f t="shared" si="40"/>
+        <v>1560</v>
       </c>
       <c r="G1408" s="7">
         <v>1</v>
       </c>
       <c r="H1408" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1408" s="7">
-        <f t="shared" si="40"/>
-        <v>390</v>
+        <f t="shared" si="41"/>
+        <v>360</v>
       </c>
       <c r="J1408" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1409" customHeight="1" spans="3:10">
       <c r="C1409" s="7">
-        <v>9139</v>
+        <v>9129</v>
       </c>
       <c r="D1409" s="7" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="E1409" s="7">
         <v>9</v>
       </c>
       <c r="F1409" s="7">
-        <f t="shared" si="39"/>
-        <v>1780</v>
+        <f t="shared" si="40"/>
+        <v>1580</v>
       </c>
       <c r="G1409" s="7">
         <v>1</v>
       </c>
       <c r="H1409" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1409" s="7">
-        <f t="shared" si="40"/>
-        <v>390</v>
+        <f t="shared" si="41"/>
+        <v>370</v>
       </c>
       <c r="J1409" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1410" customHeight="1" spans="3:10">
       <c r="C1410" s="7">
-        <v>9140</v>
+        <v>9130</v>
       </c>
       <c r="D1410" s="7" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="E1410" s="7">
         <v>9</v>
       </c>
       <c r="F1410" s="7">
-        <f t="shared" si="39"/>
-        <v>1800</v>
+        <f t="shared" si="40"/>
+        <v>1600</v>
       </c>
       <c r="G1410" s="7">
         <v>1</v>
       </c>
       <c r="H1410" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1410" s="7">
-        <f t="shared" si="40"/>
-        <v>390</v>
+        <f t="shared" si="41"/>
+        <v>370</v>
       </c>
       <c r="J1410" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1411" customHeight="1" spans="3:10">
       <c r="C1411" s="7">
-        <v>9141</v>
+        <v>9131</v>
       </c>
       <c r="D1411" s="7" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E1411" s="7">
         <v>9</v>
       </c>
       <c r="F1411" s="7">
-        <f t="shared" si="39"/>
-        <v>1820</v>
+        <f t="shared" si="40"/>
+        <v>1620</v>
       </c>
       <c r="G1411" s="7">
         <v>1</v>
       </c>
       <c r="H1411" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1411" s="7">
-        <f t="shared" si="40"/>
-        <v>400</v>
+        <f t="shared" si="41"/>
+        <v>370</v>
       </c>
       <c r="J1411" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1412" customHeight="1" spans="3:10">
       <c r="C1412" s="7">
-        <v>9142</v>
+        <v>9132</v>
       </c>
       <c r="D1412" s="7" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="E1412" s="7">
         <v>9</v>
       </c>
       <c r="F1412" s="7">
-        <f t="shared" si="39"/>
-        <v>1840</v>
+        <f t="shared" si="40"/>
+        <v>1640</v>
       </c>
       <c r="G1412" s="7">
         <v>1</v>
       </c>
       <c r="H1412" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1412" s="7">
-        <f t="shared" si="40"/>
-        <v>400</v>
+        <f t="shared" si="41"/>
+        <v>370</v>
       </c>
       <c r="J1412" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1413" customHeight="1" spans="3:10">
       <c r="C1413" s="7">
-        <v>9143</v>
+        <v>9133</v>
       </c>
       <c r="D1413" s="7" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="E1413" s="7">
         <v>9</v>
       </c>
       <c r="F1413" s="7">
-        <f t="shared" si="39"/>
-        <v>1860</v>
+        <f t="shared" si="40"/>
+        <v>1660</v>
       </c>
       <c r="G1413" s="7">
         <v>1</v>
       </c>
       <c r="H1413" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1413" s="7">
-        <f t="shared" si="40"/>
-        <v>400</v>
+        <f t="shared" si="41"/>
+        <v>380</v>
       </c>
       <c r="J1413" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1414" customHeight="1" spans="3:10">
       <c r="C1414" s="7">
-        <v>9144</v>
+        <v>9134</v>
       </c>
       <c r="D1414" s="7" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="E1414" s="7">
         <v>9</v>
       </c>
       <c r="F1414" s="7">
-        <f t="shared" si="39"/>
-        <v>1880</v>
+        <f t="shared" si="40"/>
+        <v>1680</v>
       </c>
       <c r="G1414" s="7">
         <v>1</v>
       </c>
       <c r="H1414" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1414" s="7">
-        <f t="shared" si="40"/>
-        <v>400</v>
+        <f t="shared" si="41"/>
+        <v>380</v>
       </c>
       <c r="J1414" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1415" customHeight="1" spans="3:10">
       <c r="C1415" s="7">
-        <v>9145</v>
+        <v>9135</v>
       </c>
       <c r="D1415" s="7" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="E1415" s="7">
         <v>9</v>
       </c>
       <c r="F1415" s="7">
-        <f t="shared" si="39"/>
-        <v>1900</v>
+        <f t="shared" si="40"/>
+        <v>1700</v>
       </c>
       <c r="G1415" s="7">
         <v>1</v>
       </c>
       <c r="H1415" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1415" s="7">
-        <f t="shared" si="40"/>
-        <v>410</v>
+        <f t="shared" si="41"/>
+        <v>380</v>
       </c>
       <c r="J1415" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1416" customHeight="1" spans="3:10">
       <c r="C1416" s="7">
-        <v>9146</v>
+        <v>9136</v>
       </c>
       <c r="D1416" s="7" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="E1416" s="7">
         <v>9</v>
       </c>
       <c r="F1416" s="7">
-        <f t="shared" si="39"/>
-        <v>1920</v>
+        <f t="shared" si="40"/>
+        <v>1720</v>
       </c>
       <c r="G1416" s="7">
         <v>1</v>
       </c>
       <c r="H1416" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1416" s="7">
-        <f t="shared" si="40"/>
-        <v>410</v>
+        <f t="shared" si="41"/>
+        <v>380</v>
       </c>
       <c r="J1416" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1417" customHeight="1" spans="3:10">
       <c r="C1417" s="7">
-        <v>9147</v>
+        <v>9137</v>
       </c>
       <c r="D1417" s="7" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="E1417" s="7">
         <v>9</v>
       </c>
       <c r="F1417" s="7">
-        <f t="shared" si="39"/>
-        <v>1940</v>
+        <f t="shared" si="40"/>
+        <v>1740</v>
       </c>
       <c r="G1417" s="7">
         <v>1</v>
       </c>
       <c r="H1417" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1417" s="7">
-        <f t="shared" si="40"/>
-        <v>410</v>
+        <f t="shared" si="41"/>
+        <v>390</v>
       </c>
       <c r="J1417" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1418" customHeight="1" spans="3:10">
       <c r="C1418" s="7">
-        <v>9148</v>
+        <v>9138</v>
       </c>
       <c r="D1418" s="7" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="E1418" s="7">
         <v>9</v>
       </c>
       <c r="F1418" s="7">
-        <f t="shared" si="39"/>
-        <v>1960</v>
+        <f t="shared" si="40"/>
+        <v>1760</v>
       </c>
       <c r="G1418" s="7">
         <v>1</v>
       </c>
       <c r="H1418" s="7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I1418" s="7">
-        <f t="shared" si="40"/>
-        <v>410</v>
+        <f t="shared" si="41"/>
+        <v>390</v>
       </c>
       <c r="J1418" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1419" customHeight="1" spans="3:10">
       <c r="C1419" s="7">
-        <v>9149</v>
+        <v>9139</v>
       </c>
       <c r="D1419" s="7" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E1419" s="7">
         <v>9</v>
       </c>
       <c r="F1419" s="7">
-        <f t="shared" si="39"/>
-        <v>1980</v>
+        <f t="shared" si="40"/>
+        <v>1780</v>
       </c>
       <c r="G1419" s="7">
         <v>1</v>
       </c>
       <c r="H1419" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1419" s="7">
-        <f t="shared" si="40"/>
-        <v>420</v>
+        <f t="shared" si="41"/>
+        <v>390</v>
       </c>
       <c r="J1419" s="7" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1420" customHeight="1" spans="3:10">
       <c r="C1420" s="7">
-        <v>9150</v>
+        <v>9140</v>
       </c>
       <c r="D1420" s="7" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E1420" s="7">
         <v>9</v>
       </c>
       <c r="F1420" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
+        <v>1800</v>
+      </c>
+      <c r="G1420" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1420" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1420" s="7">
+        <f t="shared" si="41"/>
+        <v>390</v>
+      </c>
+      <c r="J1420" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1421" customHeight="1" spans="3:10">
+      <c r="C1421" s="7">
+        <v>9141</v>
+      </c>
+      <c r="D1421" s="7" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E1421" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1421" s="7">
+        <f t="shared" si="40"/>
+        <v>1820</v>
+      </c>
+      <c r="G1421" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1421" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1421" s="7">
+        <f t="shared" si="41"/>
+        <v>400</v>
+      </c>
+      <c r="J1421" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1422" customHeight="1" spans="3:10">
+      <c r="C1422" s="7">
+        <v>9142</v>
+      </c>
+      <c r="D1422" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E1422" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1422" s="7">
+        <f t="shared" si="40"/>
+        <v>1840</v>
+      </c>
+      <c r="G1422" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1422" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1422" s="7">
+        <f t="shared" si="41"/>
+        <v>400</v>
+      </c>
+      <c r="J1422" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1423" customHeight="1" spans="3:10">
+      <c r="C1423" s="7">
+        <v>9143</v>
+      </c>
+      <c r="D1423" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E1423" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1423" s="7">
+        <f t="shared" si="40"/>
+        <v>1860</v>
+      </c>
+      <c r="G1423" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1423" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1423" s="7">
+        <f t="shared" si="41"/>
+        <v>400</v>
+      </c>
+      <c r="J1423" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1424" customHeight="1" spans="3:10">
+      <c r="C1424" s="7">
+        <v>9144</v>
+      </c>
+      <c r="D1424" s="7" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E1424" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1424" s="7">
+        <f t="shared" si="40"/>
+        <v>1880</v>
+      </c>
+      <c r="G1424" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1424" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1424" s="7">
+        <f t="shared" si="41"/>
+        <v>400</v>
+      </c>
+      <c r="J1424" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1425" customHeight="1" spans="3:10">
+      <c r="C1425" s="7">
+        <v>9145</v>
+      </c>
+      <c r="D1425" s="7" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E1425" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1425" s="7">
+        <f t="shared" si="40"/>
+        <v>1900</v>
+      </c>
+      <c r="G1425" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1425" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1425" s="7">
+        <f t="shared" si="41"/>
+        <v>410</v>
+      </c>
+      <c r="J1425" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1426" customHeight="1" spans="3:10">
+      <c r="C1426" s="7">
+        <v>9146</v>
+      </c>
+      <c r="D1426" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E1426" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1426" s="7">
+        <f t="shared" si="40"/>
+        <v>1920</v>
+      </c>
+      <c r="G1426" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1426" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1426" s="7">
+        <f t="shared" si="41"/>
+        <v>410</v>
+      </c>
+      <c r="J1426" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1427" customHeight="1" spans="3:10">
+      <c r="C1427" s="7">
+        <v>9147</v>
+      </c>
+      <c r="D1427" s="7" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E1427" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1427" s="7">
+        <f t="shared" si="40"/>
+        <v>1940</v>
+      </c>
+      <c r="G1427" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1427" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1427" s="7">
+        <f t="shared" si="41"/>
+        <v>410</v>
+      </c>
+      <c r="J1427" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1428" customHeight="1" spans="3:10">
+      <c r="C1428" s="7">
+        <v>9148</v>
+      </c>
+      <c r="D1428" s="7" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E1428" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1428" s="7">
+        <f t="shared" si="40"/>
+        <v>1960</v>
+      </c>
+      <c r="G1428" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1428" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1428" s="7">
+        <f t="shared" si="41"/>
+        <v>410</v>
+      </c>
+      <c r="J1428" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1429" customHeight="1" spans="3:10">
+      <c r="C1429" s="7">
+        <v>9149</v>
+      </c>
+      <c r="D1429" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E1429" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1429" s="7">
+        <f t="shared" si="40"/>
+        <v>1980</v>
+      </c>
+      <c r="G1429" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1429" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1429" s="7">
+        <f t="shared" si="41"/>
+        <v>420</v>
+      </c>
+      <c r="J1429" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1430" customHeight="1" spans="3:10">
+      <c r="C1430" s="7">
+        <v>9150</v>
+      </c>
+      <c r="D1430" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E1430" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1430" s="7">
+        <f t="shared" si="40"/>
         <v>2000</v>
       </c>
-      <c r="G1420" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1420" s="7">
+      <c r="G1430" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1430" s="7">
         <v>19</v>
       </c>
-      <c r="I1420" s="7">
+      <c r="I1430" s="7">
+        <f t="shared" si="41"/>
+        <v>420</v>
+      </c>
+      <c r="J1430" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1431" customHeight="1" spans="3:10">
+      <c r="C1431" s="7">
+        <v>9151</v>
+      </c>
+      <c r="D1431" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E1431" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1431" s="7">
         <f t="shared" si="40"/>
+        <v>2020</v>
+      </c>
+      <c r="G1431" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1431" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1431" s="7">
+        <f t="shared" si="41"/>
         <v>420</v>
       </c>
-      <c r="J1420" s="7" t="s">
-        <v>1333</v>
+      <c r="J1431" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1432" customHeight="1" spans="3:10">
+      <c r="C1432" s="7">
+        <v>9152</v>
+      </c>
+      <c r="D1432" s="7" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E1432" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1432" s="7">
+        <f t="shared" si="40"/>
+        <v>2040</v>
+      </c>
+      <c r="G1432" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1432" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1432" s="7">
+        <f t="shared" si="41"/>
+        <v>420</v>
+      </c>
+      <c r="J1432" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1433" customHeight="1" spans="3:10">
+      <c r="C1433" s="7">
+        <v>9153</v>
+      </c>
+      <c r="D1433" s="7" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E1433" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1433" s="7">
+        <f t="shared" si="40"/>
+        <v>2060</v>
+      </c>
+      <c r="G1433" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1433" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1433" s="7">
+        <f t="shared" si="41"/>
+        <v>430</v>
+      </c>
+      <c r="J1433" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1434" customHeight="1" spans="3:10">
+      <c r="C1434" s="7">
+        <v>9154</v>
+      </c>
+      <c r="D1434" s="7" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E1434" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1434" s="7">
+        <f t="shared" si="40"/>
+        <v>2080</v>
+      </c>
+      <c r="G1434" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1434" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1434" s="7">
+        <f t="shared" si="41"/>
+        <v>430</v>
+      </c>
+      <c r="J1434" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1435" customHeight="1" spans="3:10">
+      <c r="C1435" s="7">
+        <v>9155</v>
+      </c>
+      <c r="D1435" s="7" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E1435" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1435" s="7">
+        <f t="shared" si="40"/>
+        <v>2100</v>
+      </c>
+      <c r="G1435" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1435" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1435" s="7">
+        <f t="shared" si="41"/>
+        <v>430</v>
+      </c>
+      <c r="J1435" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1436" customHeight="1" spans="3:10">
+      <c r="C1436" s="7">
+        <v>9156</v>
+      </c>
+      <c r="D1436" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E1436" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1436" s="7">
+        <f t="shared" si="40"/>
+        <v>2120</v>
+      </c>
+      <c r="G1436" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1436" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1436" s="7">
+        <f t="shared" si="41"/>
+        <v>430</v>
+      </c>
+      <c r="J1436" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1437" customHeight="1" spans="3:10">
+      <c r="C1437" s="7">
+        <v>9157</v>
+      </c>
+      <c r="D1437" s="7" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E1437" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1437" s="7">
+        <f t="shared" si="40"/>
+        <v>2140</v>
+      </c>
+      <c r="G1437" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1437" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1437" s="7">
+        <f t="shared" si="41"/>
+        <v>440</v>
+      </c>
+      <c r="J1437" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1438" customHeight="1" spans="3:10">
+      <c r="C1438" s="7">
+        <v>9158</v>
+      </c>
+      <c r="D1438" s="7" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E1438" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1438" s="7">
+        <f t="shared" si="40"/>
+        <v>2160</v>
+      </c>
+      <c r="G1438" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1438" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1438" s="7">
+        <f t="shared" si="41"/>
+        <v>440</v>
+      </c>
+      <c r="J1438" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1439" customHeight="1" spans="3:10">
+      <c r="C1439" s="7">
+        <v>9159</v>
+      </c>
+      <c r="D1439" s="7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E1439" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1439" s="7">
+        <f t="shared" si="40"/>
+        <v>2180</v>
+      </c>
+      <c r="G1439" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1439" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1439" s="7">
+        <f t="shared" si="41"/>
+        <v>440</v>
+      </c>
+      <c r="J1439" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1440" customHeight="1" spans="3:10">
+      <c r="C1440" s="7">
+        <v>9160</v>
+      </c>
+      <c r="D1440" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E1440" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1440" s="7">
+        <f t="shared" si="40"/>
+        <v>2200</v>
+      </c>
+      <c r="G1440" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1440" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1440" s="7">
+        <f t="shared" si="41"/>
+        <v>440</v>
+      </c>
+      <c r="J1440" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1441" customHeight="1" spans="3:10">
+      <c r="C1441" s="7">
+        <v>9161</v>
+      </c>
+      <c r="D1441" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E1441" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1441" s="7">
+        <f t="shared" si="40"/>
+        <v>2220</v>
+      </c>
+      <c r="G1441" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1441" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1441" s="7">
+        <f t="shared" si="41"/>
+        <v>450</v>
+      </c>
+      <c r="J1441" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1442" customHeight="1" spans="3:10">
+      <c r="C1442" s="7">
+        <v>9162</v>
+      </c>
+      <c r="D1442" s="7" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E1442" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1442" s="7">
+        <f t="shared" si="40"/>
+        <v>2240</v>
+      </c>
+      <c r="G1442" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1442" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1442" s="7">
+        <f t="shared" si="41"/>
+        <v>450</v>
+      </c>
+      <c r="J1442" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1443" customHeight="1" spans="3:10">
+      <c r="C1443" s="7">
+        <v>9163</v>
+      </c>
+      <c r="D1443" s="7" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E1443" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1443" s="7">
+        <f t="shared" si="40"/>
+        <v>2260</v>
+      </c>
+      <c r="G1443" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1443" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1443" s="7">
+        <f t="shared" si="41"/>
+        <v>450</v>
+      </c>
+      <c r="J1443" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1444" customHeight="1" spans="3:10">
+      <c r="C1444" s="7">
+        <v>9164</v>
+      </c>
+      <c r="D1444" s="7" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E1444" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1444" s="7">
+        <f t="shared" si="40"/>
+        <v>2280</v>
+      </c>
+      <c r="G1444" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1444" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1444" s="7">
+        <f t="shared" si="41"/>
+        <v>450</v>
+      </c>
+      <c r="J1444" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1445" customHeight="1" spans="3:10">
+      <c r="C1445" s="7">
+        <v>9165</v>
+      </c>
+      <c r="D1445" s="7" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E1445" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1445" s="7">
+        <f t="shared" ref="F1445:F1450" si="42">F1444+20</f>
+        <v>2300</v>
+      </c>
+      <c r="G1445" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1445" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1445" s="7">
+        <f t="shared" ref="I1445:I1450" si="43">I1441+10</f>
+        <v>460</v>
+      </c>
+      <c r="J1445" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1446" customHeight="1" spans="3:10">
+      <c r="C1446" s="7">
+        <v>9166</v>
+      </c>
+      <c r="D1446" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E1446" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1446" s="7">
+        <f t="shared" si="42"/>
+        <v>2320</v>
+      </c>
+      <c r="G1446" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1446" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1446" s="7">
+        <f t="shared" si="43"/>
+        <v>460</v>
+      </c>
+      <c r="J1446" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1447" customHeight="1" spans="3:10">
+      <c r="C1447" s="7">
+        <v>9167</v>
+      </c>
+      <c r="D1447" s="7" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E1447" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1447" s="7">
+        <f t="shared" si="42"/>
+        <v>2340</v>
+      </c>
+      <c r="G1447" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1447" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1447" s="7">
+        <f t="shared" si="43"/>
+        <v>460</v>
+      </c>
+      <c r="J1447" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1448" customHeight="1" spans="3:10">
+      <c r="C1448" s="7">
+        <v>9168</v>
+      </c>
+      <c r="D1448" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E1448" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1448" s="7">
+        <f t="shared" si="42"/>
+        <v>2360</v>
+      </c>
+      <c r="G1448" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1448" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1448" s="7">
+        <f t="shared" si="43"/>
+        <v>460</v>
+      </c>
+      <c r="J1448" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1449" customHeight="1" spans="3:10">
+      <c r="C1449" s="7">
+        <v>9169</v>
+      </c>
+      <c r="D1449" s="7" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E1449" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1449" s="7">
+        <f t="shared" si="42"/>
+        <v>2380</v>
+      </c>
+      <c r="G1449" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1449" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1449" s="7">
+        <f t="shared" si="43"/>
+        <v>470</v>
+      </c>
+      <c r="J1449" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1450" customHeight="1" spans="3:10">
+      <c r="C1450" s="7">
+        <v>9170</v>
+      </c>
+      <c r="D1450" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E1450" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1450" s="7">
+        <f t="shared" si="42"/>
+        <v>2400</v>
+      </c>
+      <c r="G1450" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1450" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1450" s="7">
+        <f t="shared" si="43"/>
+        <v>470</v>
+      </c>
+      <c r="J1450" s="7" t="s">
+        <v>1342</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -46675,7 +46675,7 @@
         <v>1</v>
       </c>
       <c r="H1431" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1431" s="7">
         <f t="shared" si="41"/>
@@ -46703,7 +46703,7 @@
         <v>1</v>
       </c>
       <c r="H1432" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1432" s="7">
         <f t="shared" si="41"/>
@@ -46731,7 +46731,7 @@
         <v>1</v>
       </c>
       <c r="H1433" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1433" s="7">
         <f t="shared" si="41"/>
@@ -46787,7 +46787,7 @@
         <v>1</v>
       </c>
       <c r="H1435" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1435" s="7">
         <f t="shared" si="41"/>
@@ -46815,7 +46815,7 @@
         <v>1</v>
       </c>
       <c r="H1436" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1436" s="7">
         <f t="shared" si="41"/>
@@ -46843,7 +46843,7 @@
         <v>1</v>
       </c>
       <c r="H1437" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1437" s="7">
         <f t="shared" si="41"/>
@@ -46899,7 +46899,7 @@
         <v>1</v>
       </c>
       <c r="H1439" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1439" s="7">
         <f t="shared" si="41"/>
@@ -46927,7 +46927,7 @@
         <v>1</v>
       </c>
       <c r="H1440" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1440" s="7">
         <f t="shared" si="41"/>
@@ -46955,7 +46955,7 @@
         <v>1</v>
       </c>
       <c r="H1441" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1441" s="7">
         <f t="shared" si="41"/>
@@ -47011,7 +47011,7 @@
         <v>1</v>
       </c>
       <c r="H1443" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1443" s="7">
         <f t="shared" si="41"/>
@@ -47039,7 +47039,7 @@
         <v>1</v>
       </c>
       <c r="H1444" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1444" s="7">
         <f t="shared" si="41"/>
@@ -47067,7 +47067,7 @@
         <v>1</v>
       </c>
       <c r="H1445" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1445" s="7">
         <f t="shared" ref="I1445:I1450" si="43">I1441+10</f>
@@ -47123,7 +47123,7 @@
         <v>1</v>
       </c>
       <c r="H1447" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1447" s="7">
         <f t="shared" si="43"/>
@@ -47151,7 +47151,7 @@
         <v>1</v>
       </c>
       <c r="H1448" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1448" s="7">
         <f t="shared" si="43"/>
@@ -47179,7 +47179,7 @@
         <v>1</v>
       </c>
       <c r="H1449" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1449" s="7">
         <f t="shared" si="43"/>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="1512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3947" uniqueCount="1534">
   <si>
     <t>#</t>
   </si>
@@ -4628,6 +4628,72 @@
   </si>
   <si>
     <t>攀登者170</t>
+  </si>
+  <si>
+    <t>攀登者171</t>
+  </si>
+  <si>
+    <t>攀登者172</t>
+  </si>
+  <si>
+    <t>攀登者173</t>
+  </si>
+  <si>
+    <t>攀登者174</t>
+  </si>
+  <si>
+    <t>攀登者175</t>
+  </si>
+  <si>
+    <t>攀登者176</t>
+  </si>
+  <si>
+    <t>攀登者177</t>
+  </si>
+  <si>
+    <t>攀登者178</t>
+  </si>
+  <si>
+    <t>攀登者179</t>
+  </si>
+  <si>
+    <t>攀登者180</t>
+  </si>
+  <si>
+    <t>攀登者181</t>
+  </si>
+  <si>
+    <t>攀登者182</t>
+  </si>
+  <si>
+    <t>攀登者183</t>
+  </si>
+  <si>
+    <t>攀登者184</t>
+  </si>
+  <si>
+    <t>攀登者185</t>
+  </si>
+  <si>
+    <t>攀登者186</t>
+  </si>
+  <si>
+    <t>攀登者187</t>
+  </si>
+  <si>
+    <t>攀登者188</t>
+  </si>
+  <si>
+    <t>攀登者189</t>
+  </si>
+  <si>
+    <t>攀登者190</t>
+  </si>
+  <si>
+    <t>攀登者191</t>
+  </si>
+  <si>
+    <t>攀登者192</t>
   </si>
 </sst>
 </file>
@@ -5635,7 +5701,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K1450"/>
+  <dimension ref="A2:K1472"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="7"/>
@@ -47060,7 +47126,7 @@
         <v>9</v>
       </c>
       <c r="F1445" s="7">
-        <f t="shared" ref="F1445:F1450" si="42">F1444+20</f>
+        <f>F1444+20</f>
         <v>2300</v>
       </c>
       <c r="G1445" s="7">
@@ -47070,7 +47136,7 @@
         <v>18</v>
       </c>
       <c r="I1445" s="7">
-        <f t="shared" ref="I1445:I1450" si="43">I1441+10</f>
+        <f t="shared" ref="I1445:I1460" si="42">I1441+10</f>
         <v>460</v>
       </c>
       <c r="J1445" s="7" t="s">
@@ -47088,7 +47154,7 @@
         <v>9</v>
       </c>
       <c r="F1446" s="7">
-        <f t="shared" si="42"/>
+        <f>F1445+20</f>
         <v>2320</v>
       </c>
       <c r="G1446" s="7">
@@ -47098,7 +47164,7 @@
         <v>19</v>
       </c>
       <c r="I1446" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>460</v>
       </c>
       <c r="J1446" s="7" t="s">
@@ -47116,7 +47182,7 @@
         <v>9</v>
       </c>
       <c r="F1447" s="7">
-        <f t="shared" si="42"/>
+        <f>F1446+20</f>
         <v>2340</v>
       </c>
       <c r="G1447" s="7">
@@ -47126,7 +47192,7 @@
         <v>20</v>
       </c>
       <c r="I1447" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>460</v>
       </c>
       <c r="J1447" s="7" t="s">
@@ -47144,7 +47210,7 @@
         <v>9</v>
       </c>
       <c r="F1448" s="7">
-        <f t="shared" si="42"/>
+        <f>F1447+20</f>
         <v>2360</v>
       </c>
       <c r="G1448" s="7">
@@ -47154,7 +47220,7 @@
         <v>24</v>
       </c>
       <c r="I1448" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>460</v>
       </c>
       <c r="J1448" s="7" t="s">
@@ -47172,7 +47238,7 @@
         <v>9</v>
       </c>
       <c r="F1449" s="7">
-        <f t="shared" si="42"/>
+        <f>F1448+20</f>
         <v>2380</v>
       </c>
       <c r="G1449" s="7">
@@ -47182,7 +47248,7 @@
         <v>18</v>
       </c>
       <c r="I1449" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>470</v>
       </c>
       <c r="J1449" s="7" t="s">
@@ -47200,7 +47266,7 @@
         <v>9</v>
       </c>
       <c r="F1450" s="7">
-        <f t="shared" si="42"/>
+        <f>F1449+20</f>
         <v>2400</v>
       </c>
       <c r="G1450" s="7">
@@ -47210,10 +47276,626 @@
         <v>19</v>
       </c>
       <c r="I1450" s="7">
+        <f t="shared" si="42"/>
+        <v>470</v>
+      </c>
+      <c r="J1450" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1451" customHeight="1" spans="3:10">
+      <c r="C1451" s="7">
+        <v>9171</v>
+      </c>
+      <c r="D1451" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E1451" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1451" s="7">
+        <f t="shared" ref="F1451:F1472" si="43">F1450+30</f>
+        <v>2430</v>
+      </c>
+      <c r="G1451" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1451" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1451" s="7">
+        <f t="shared" si="42"/>
+        <v>470</v>
+      </c>
+      <c r="J1451" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1452" customHeight="1" spans="3:10">
+      <c r="C1452" s="7">
+        <v>9172</v>
+      </c>
+      <c r="D1452" s="7" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E1452" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1452" s="7">
         <f t="shared" si="43"/>
+        <v>2460</v>
+      </c>
+      <c r="G1452" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1452" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1452" s="7">
+        <f t="shared" si="42"/>
         <v>470</v>
       </c>
-      <c r="J1450" s="7" t="s">
+      <c r="J1452" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1453" customHeight="1" spans="3:10">
+      <c r="C1453" s="7">
+        <v>9173</v>
+      </c>
+      <c r="D1453" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E1453" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1453" s="7">
+        <f t="shared" si="43"/>
+        <v>2490</v>
+      </c>
+      <c r="G1453" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1453" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1453" s="7">
+        <f t="shared" si="42"/>
+        <v>480</v>
+      </c>
+      <c r="J1453" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1454" customHeight="1" spans="3:10">
+      <c r="C1454" s="7">
+        <v>9174</v>
+      </c>
+      <c r="D1454" s="7" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E1454" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1454" s="7">
+        <f t="shared" si="43"/>
+        <v>2520</v>
+      </c>
+      <c r="G1454" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1454" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1454" s="7">
+        <f t="shared" si="42"/>
+        <v>480</v>
+      </c>
+      <c r="J1454" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1455" customHeight="1" spans="3:10">
+      <c r="C1455" s="7">
+        <v>9175</v>
+      </c>
+      <c r="D1455" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E1455" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1455" s="7">
+        <f t="shared" si="43"/>
+        <v>2550</v>
+      </c>
+      <c r="G1455" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1455" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1455" s="7">
+        <f t="shared" si="42"/>
+        <v>480</v>
+      </c>
+      <c r="J1455" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1456" customHeight="1" spans="3:10">
+      <c r="C1456" s="7">
+        <v>9176</v>
+      </c>
+      <c r="D1456" s="7" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E1456" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1456" s="7">
+        <f t="shared" si="43"/>
+        <v>2580</v>
+      </c>
+      <c r="G1456" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1456" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1456" s="7">
+        <f t="shared" si="42"/>
+        <v>480</v>
+      </c>
+      <c r="J1456" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1457" customHeight="1" spans="3:10">
+      <c r="C1457" s="7">
+        <v>9177</v>
+      </c>
+      <c r="D1457" s="7" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E1457" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1457" s="7">
+        <f t="shared" si="43"/>
+        <v>2610</v>
+      </c>
+      <c r="G1457" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1457" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1457" s="7">
+        <f t="shared" si="42"/>
+        <v>490</v>
+      </c>
+      <c r="J1457" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1458" customHeight="1" spans="3:10">
+      <c r="C1458" s="7">
+        <v>9178</v>
+      </c>
+      <c r="D1458" s="7" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E1458" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1458" s="7">
+        <f t="shared" si="43"/>
+        <v>2640</v>
+      </c>
+      <c r="G1458" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1458" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1458" s="7">
+        <f t="shared" si="42"/>
+        <v>490</v>
+      </c>
+      <c r="J1458" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1459" customHeight="1" spans="3:10">
+      <c r="C1459" s="7">
+        <v>9179</v>
+      </c>
+      <c r="D1459" s="7" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E1459" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1459" s="7">
+        <f t="shared" si="43"/>
+        <v>2670</v>
+      </c>
+      <c r="G1459" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1459" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1459" s="7">
+        <f t="shared" si="42"/>
+        <v>490</v>
+      </c>
+      <c r="J1459" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1460" customHeight="1" spans="3:10">
+      <c r="C1460" s="7">
+        <v>9180</v>
+      </c>
+      <c r="D1460" s="7" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E1460" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1460" s="7">
+        <f t="shared" si="43"/>
+        <v>2700</v>
+      </c>
+      <c r="G1460" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1460" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1460" s="7">
+        <f t="shared" si="42"/>
+        <v>490</v>
+      </c>
+      <c r="J1460" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1461" customHeight="1" spans="3:10">
+      <c r="C1461" s="7">
+        <v>9181</v>
+      </c>
+      <c r="D1461" s="7" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E1461" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1461" s="7">
+        <f t="shared" si="43"/>
+        <v>2730</v>
+      </c>
+      <c r="G1461" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1461" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1461" s="7">
+        <f t="shared" ref="I1461:I1472" si="44">I1457+10</f>
+        <v>500</v>
+      </c>
+      <c r="J1461" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1462" customHeight="1" spans="3:10">
+      <c r="C1462" s="7">
+        <v>9182</v>
+      </c>
+      <c r="D1462" s="7" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E1462" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1462" s="7">
+        <f t="shared" si="43"/>
+        <v>2760</v>
+      </c>
+      <c r="G1462" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1462" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1462" s="7">
+        <f t="shared" si="44"/>
+        <v>500</v>
+      </c>
+      <c r="J1462" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1463" customHeight="1" spans="3:10">
+      <c r="C1463" s="7">
+        <v>9183</v>
+      </c>
+      <c r="D1463" s="7" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E1463" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1463" s="7">
+        <f t="shared" si="43"/>
+        <v>2790</v>
+      </c>
+      <c r="G1463" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1463" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1463" s="7">
+        <f t="shared" si="44"/>
+        <v>500</v>
+      </c>
+      <c r="J1463" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1464" customHeight="1" spans="3:10">
+      <c r="C1464" s="7">
+        <v>9184</v>
+      </c>
+      <c r="D1464" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E1464" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1464" s="7">
+        <f t="shared" si="43"/>
+        <v>2820</v>
+      </c>
+      <c r="G1464" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1464" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1464" s="7">
+        <f t="shared" si="44"/>
+        <v>500</v>
+      </c>
+      <c r="J1464" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1465" customHeight="1" spans="3:10">
+      <c r="C1465" s="7">
+        <v>9185</v>
+      </c>
+      <c r="D1465" s="7" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E1465" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1465" s="7">
+        <f t="shared" si="43"/>
+        <v>2850</v>
+      </c>
+      <c r="G1465" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1465" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1465" s="7">
+        <f t="shared" si="44"/>
+        <v>510</v>
+      </c>
+      <c r="J1465" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1466" customHeight="1" spans="3:10">
+      <c r="C1466" s="7">
+        <v>9186</v>
+      </c>
+      <c r="D1466" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E1466" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1466" s="7">
+        <f t="shared" si="43"/>
+        <v>2880</v>
+      </c>
+      <c r="G1466" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1466" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1466" s="7">
+        <f t="shared" si="44"/>
+        <v>510</v>
+      </c>
+      <c r="J1466" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1467" customHeight="1" spans="3:10">
+      <c r="C1467" s="7">
+        <v>9187</v>
+      </c>
+      <c r="D1467" s="7" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E1467" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1467" s="7">
+        <f t="shared" si="43"/>
+        <v>2910</v>
+      </c>
+      <c r="G1467" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1467" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1467" s="7">
+        <f t="shared" si="44"/>
+        <v>510</v>
+      </c>
+      <c r="J1467" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1468" customHeight="1" spans="3:10">
+      <c r="C1468" s="7">
+        <v>9188</v>
+      </c>
+      <c r="D1468" s="7" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E1468" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1468" s="7">
+        <f t="shared" si="43"/>
+        <v>2940</v>
+      </c>
+      <c r="G1468" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1468" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1468" s="7">
+        <f t="shared" si="44"/>
+        <v>510</v>
+      </c>
+      <c r="J1468" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1469" customHeight="1" spans="3:10">
+      <c r="C1469" s="7">
+        <v>9189</v>
+      </c>
+      <c r="D1469" s="7" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E1469" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1469" s="7">
+        <f t="shared" si="43"/>
+        <v>2970</v>
+      </c>
+      <c r="G1469" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1469" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1469" s="7">
+        <f t="shared" si="44"/>
+        <v>520</v>
+      </c>
+      <c r="J1469" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1470" customHeight="1" spans="3:10">
+      <c r="C1470" s="7">
+        <v>9190</v>
+      </c>
+      <c r="D1470" s="7" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E1470" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1470" s="7">
+        <f t="shared" si="43"/>
+        <v>3000</v>
+      </c>
+      <c r="G1470" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1470" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1470" s="7">
+        <f t="shared" si="44"/>
+        <v>520</v>
+      </c>
+      <c r="J1470" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1471" customHeight="1" spans="3:10">
+      <c r="C1471" s="7">
+        <v>9191</v>
+      </c>
+      <c r="D1471" s="7" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E1471" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1471" s="7">
+        <f>F1470+40</f>
+        <v>3040</v>
+      </c>
+      <c r="G1471" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1471" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1471" s="7">
+        <f t="shared" si="44"/>
+        <v>520</v>
+      </c>
+      <c r="J1471" s="7" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1472" customHeight="1" spans="3:10">
+      <c r="C1472" s="7">
+        <v>9192</v>
+      </c>
+      <c r="D1472" s="7" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E1472" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1472" s="7">
+        <f>F1471+40</f>
+        <v>3080</v>
+      </c>
+      <c r="G1472" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1472" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1472" s="7">
+        <f t="shared" si="44"/>
+        <v>520</v>
+      </c>
+      <c r="J1472" s="7" t="s">
         <v>1342</v>
       </c>
     </row>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1579">
   <si>
     <t>#</t>
   </si>
@@ -4793,6 +4793,42 @@
   </si>
   <si>
     <t>攀登者192</t>
+  </si>
+  <si>
+    <t>攀登者193</t>
+  </si>
+  <si>
+    <t>攀登者194</t>
+  </si>
+  <si>
+    <t>攀登者195</t>
+  </si>
+  <si>
+    <t>攀登者196</t>
+  </si>
+  <si>
+    <t>攀登者197</t>
+  </si>
+  <si>
+    <t>攀登者198</t>
+  </si>
+  <si>
+    <t>攀登者199</t>
+  </si>
+  <si>
+    <t>攀登者200</t>
+  </si>
+  <si>
+    <t>攀登者201</t>
+  </si>
+  <si>
+    <t>攀登者202</t>
+  </si>
+  <si>
+    <t>攀登者203</t>
+  </si>
+  <si>
+    <t>攀登者204</t>
   </si>
 </sst>
 </file>
@@ -5800,7 +5836,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K1517"/>
+  <dimension ref="A2:K1529"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="7"/>
@@ -20353,7 +20389,7 @@
         <v>1</v>
       </c>
       <c r="F487" s="7">
-        <f>F486+72</f>
+        <f t="shared" si="10"/>
         <v>11952</v>
       </c>
       <c r="G487" s="7">
@@ -20413,7 +20449,7 @@
         <v>1</v>
       </c>
       <c r="F489" s="7">
-        <f>F488+72</f>
+        <f t="shared" ref="F489:F497" si="11">F488+72</f>
         <v>12024</v>
       </c>
       <c r="G489" s="7">
@@ -20443,7 +20479,7 @@
         <v>1</v>
       </c>
       <c r="F490" s="7">
-        <f>F489+72</f>
+        <f t="shared" si="11"/>
         <v>12096</v>
       </c>
       <c r="G490" s="7">
@@ -20473,7 +20509,7 @@
         <v>1</v>
       </c>
       <c r="F491" s="7">
-        <f>F490+72</f>
+        <f t="shared" si="11"/>
         <v>12168</v>
       </c>
       <c r="G491" s="7">
@@ -20503,7 +20539,7 @@
         <v>1</v>
       </c>
       <c r="F492" s="7">
-        <f>F491+72</f>
+        <f t="shared" si="11"/>
         <v>12240</v>
       </c>
       <c r="G492" s="7">
@@ -20533,7 +20569,7 @@
         <v>1</v>
       </c>
       <c r="F493" s="7">
-        <f>F492+72</f>
+        <f t="shared" si="11"/>
         <v>12312</v>
       </c>
       <c r="G493" s="7">
@@ -20563,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="F494" s="7">
-        <f>F493+72</f>
+        <f t="shared" si="11"/>
         <v>12384</v>
       </c>
       <c r="G494" s="7">
@@ -20593,7 +20629,7 @@
         <v>1</v>
       </c>
       <c r="F495" s="7">
-        <f>F494+72</f>
+        <f t="shared" si="11"/>
         <v>12456</v>
       </c>
       <c r="G495" s="7">
@@ -20623,7 +20659,7 @@
         <v>1</v>
       </c>
       <c r="F496" s="7">
-        <f>F495+72</f>
+        <f t="shared" si="11"/>
         <v>12528</v>
       </c>
       <c r="G496" s="7">
@@ -20653,7 +20689,7 @@
         <v>1</v>
       </c>
       <c r="F497" s="4">
-        <f>F496+72</f>
+        <f t="shared" si="11"/>
         <v>12600</v>
       </c>
       <c r="G497" s="4">
@@ -20683,7 +20719,7 @@
         <v>1</v>
       </c>
       <c r="F498" s="7">
-        <f t="shared" ref="F498:F505" si="11">F497+96</f>
+        <f t="shared" ref="F498:F506" si="12">F497+96</f>
         <v>12696</v>
       </c>
       <c r="G498" s="7">
@@ -20713,7 +20749,7 @@
         <v>1</v>
       </c>
       <c r="F499" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12792</v>
       </c>
       <c r="G499" s="7">
@@ -20743,7 +20779,7 @@
         <v>1</v>
       </c>
       <c r="F500" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12888</v>
       </c>
       <c r="G500" s="7">
@@ -20773,7 +20809,7 @@
         <v>1</v>
       </c>
       <c r="F501" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12984</v>
       </c>
       <c r="G501" s="7">
@@ -20803,7 +20839,7 @@
         <v>1</v>
       </c>
       <c r="F502" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13080</v>
       </c>
       <c r="G502" s="7">
@@ -20833,7 +20869,7 @@
         <v>1</v>
       </c>
       <c r="F503" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13176</v>
       </c>
       <c r="G503" s="7">
@@ -20863,7 +20899,7 @@
         <v>1</v>
       </c>
       <c r="F504" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13272</v>
       </c>
       <c r="G504" s="7">
@@ -20893,7 +20929,7 @@
         <v>1</v>
       </c>
       <c r="F505" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13368</v>
       </c>
       <c r="G505" s="7">
@@ -20923,7 +20959,7 @@
         <v>1</v>
       </c>
       <c r="F506" s="4">
-        <f>F505+96</f>
+        <f t="shared" si="12"/>
         <v>13464</v>
       </c>
       <c r="G506" s="4">
@@ -20953,7 +20989,7 @@
         <v>1</v>
       </c>
       <c r="F507" s="7">
-        <f t="shared" ref="F507:F514" si="12">F506+96</f>
+        <f t="shared" ref="F507:F515" si="13">F506+96</f>
         <v>13560</v>
       </c>
       <c r="G507" s="7">
@@ -20983,7 +21019,7 @@
         <v>1</v>
       </c>
       <c r="F508" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13656</v>
       </c>
       <c r="G508" s="7">
@@ -21013,7 +21049,7 @@
         <v>1</v>
       </c>
       <c r="F509" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13752</v>
       </c>
       <c r="G509" s="7">
@@ -21043,7 +21079,7 @@
         <v>1</v>
       </c>
       <c r="F510" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13848</v>
       </c>
       <c r="G510" s="7">
@@ -21073,7 +21109,7 @@
         <v>1</v>
       </c>
       <c r="F511" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13944</v>
       </c>
       <c r="G511" s="7">
@@ -21103,7 +21139,7 @@
         <v>1</v>
       </c>
       <c r="F512" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14040</v>
       </c>
       <c r="G512" s="7">
@@ -21133,7 +21169,7 @@
         <v>1</v>
       </c>
       <c r="F513" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14136</v>
       </c>
       <c r="G513" s="7">
@@ -21163,7 +21199,7 @@
         <v>1</v>
       </c>
       <c r="F514" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14232</v>
       </c>
       <c r="G514" s="7">
@@ -21193,7 +21229,7 @@
         <v>1</v>
       </c>
       <c r="F515" s="4">
-        <f>F514+96</f>
+        <f t="shared" si="13"/>
         <v>14328</v>
       </c>
       <c r="G515" s="4">
@@ -21223,7 +21259,7 @@
         <v>2</v>
       </c>
       <c r="F523" s="7">
-        <f t="shared" ref="F523:F586" si="13">(C523-2000)*12</f>
+        <f t="shared" ref="F523:F586" si="14">(C523-2000)*12</f>
         <v>12</v>
       </c>
       <c r="G523" s="7">
@@ -21253,7 +21289,7 @@
         <v>2</v>
       </c>
       <c r="F524" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="G524" s="7">
@@ -21283,7 +21319,7 @@
         <v>2</v>
       </c>
       <c r="F525" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="G525" s="7">
@@ -21313,7 +21349,7 @@
         <v>2</v>
       </c>
       <c r="F526" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="G526" s="7">
@@ -21343,7 +21379,7 @@
         <v>2</v>
       </c>
       <c r="F527" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
       <c r="G527" s="7">
@@ -21373,7 +21409,7 @@
         <v>2</v>
       </c>
       <c r="F528" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>72</v>
       </c>
       <c r="G528" s="7">
@@ -21403,7 +21439,7 @@
         <v>2</v>
       </c>
       <c r="F529" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="G529" s="7">
@@ -21433,7 +21469,7 @@
         <v>2</v>
       </c>
       <c r="F530" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>96</v>
       </c>
       <c r="G530" s="7">
@@ -21463,7 +21499,7 @@
         <v>2</v>
       </c>
       <c r="F531" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>108</v>
       </c>
       <c r="G531" s="7">
@@ -21493,7 +21529,7 @@
         <v>2</v>
       </c>
       <c r="F532" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="G532" s="4">
@@ -21523,7 +21559,7 @@
         <v>2</v>
       </c>
       <c r="F533" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>132</v>
       </c>
       <c r="G533" s="7">
@@ -21553,7 +21589,7 @@
         <v>2</v>
       </c>
       <c r="F534" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>144</v>
       </c>
       <c r="G534" s="7">
@@ -21583,7 +21619,7 @@
         <v>2</v>
       </c>
       <c r="F535" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>156</v>
       </c>
       <c r="G535" s="7">
@@ -21613,7 +21649,7 @@
         <v>2</v>
       </c>
       <c r="F536" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="G536" s="7">
@@ -21643,7 +21679,7 @@
         <v>2</v>
       </c>
       <c r="F537" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>180</v>
       </c>
       <c r="G537" s="7">
@@ -21673,7 +21709,7 @@
         <v>2</v>
       </c>
       <c r="F538" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>192</v>
       </c>
       <c r="G538" s="7">
@@ -21703,7 +21739,7 @@
         <v>2</v>
       </c>
       <c r="F539" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>204</v>
       </c>
       <c r="G539" s="7">
@@ -21733,7 +21769,7 @@
         <v>2</v>
       </c>
       <c r="F540" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>216</v>
       </c>
       <c r="G540" s="7">
@@ -21763,7 +21799,7 @@
         <v>2</v>
       </c>
       <c r="F541" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>228</v>
       </c>
       <c r="G541" s="7">
@@ -21793,7 +21829,7 @@
         <v>2</v>
       </c>
       <c r="F542" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>240</v>
       </c>
       <c r="G542" s="4">
@@ -21823,7 +21859,7 @@
         <v>2</v>
       </c>
       <c r="F543" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>252</v>
       </c>
       <c r="G543" s="7">
@@ -21853,7 +21889,7 @@
         <v>2</v>
       </c>
       <c r="F544" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>264</v>
       </c>
       <c r="G544" s="7">
@@ -21883,7 +21919,7 @@
         <v>2</v>
       </c>
       <c r="F545" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>276</v>
       </c>
       <c r="G545" s="7">
@@ -21913,7 +21949,7 @@
         <v>2</v>
       </c>
       <c r="F546" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>288</v>
       </c>
       <c r="G546" s="7">
@@ -21943,7 +21979,7 @@
         <v>2</v>
       </c>
       <c r="F547" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>300</v>
       </c>
       <c r="G547" s="7">
@@ -21973,7 +22009,7 @@
         <v>2</v>
       </c>
       <c r="F548" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>312</v>
       </c>
       <c r="G548" s="7">
@@ -22003,7 +22039,7 @@
         <v>2</v>
       </c>
       <c r="F549" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>324</v>
       </c>
       <c r="G549" s="7">
@@ -22033,7 +22069,7 @@
         <v>2</v>
       </c>
       <c r="F550" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="G550" s="7">
@@ -22063,7 +22099,7 @@
         <v>2</v>
       </c>
       <c r="F551" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>348</v>
       </c>
       <c r="G551" s="7">
@@ -22093,7 +22129,7 @@
         <v>2</v>
       </c>
       <c r="F552" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>360</v>
       </c>
       <c r="G552" s="4">
@@ -22123,7 +22159,7 @@
         <v>2</v>
       </c>
       <c r="F553" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>372</v>
       </c>
       <c r="G553" s="7">
@@ -22153,7 +22189,7 @@
         <v>2</v>
       </c>
       <c r="F554" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>384</v>
       </c>
       <c r="G554" s="7">
@@ -22183,7 +22219,7 @@
         <v>2</v>
       </c>
       <c r="F555" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>396</v>
       </c>
       <c r="G555" s="7">
@@ -22213,7 +22249,7 @@
         <v>2</v>
       </c>
       <c r="F556" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>408</v>
       </c>
       <c r="G556" s="7">
@@ -22243,7 +22279,7 @@
         <v>2</v>
       </c>
       <c r="F557" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>420</v>
       </c>
       <c r="G557" s="7">
@@ -22273,7 +22309,7 @@
         <v>2</v>
       </c>
       <c r="F558" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>432</v>
       </c>
       <c r="G558" s="7">
@@ -22303,7 +22339,7 @@
         <v>2</v>
       </c>
       <c r="F559" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>444</v>
       </c>
       <c r="G559" s="7">
@@ -22333,7 +22369,7 @@
         <v>2</v>
       </c>
       <c r="F560" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>456</v>
       </c>
       <c r="G560" s="7">
@@ -22363,7 +22399,7 @@
         <v>2</v>
       </c>
       <c r="F561" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>468</v>
       </c>
       <c r="G561" s="7">
@@ -22393,7 +22429,7 @@
         <v>2</v>
       </c>
       <c r="F562" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>480</v>
       </c>
       <c r="G562" s="4">
@@ -22423,7 +22459,7 @@
         <v>2</v>
       </c>
       <c r="F563" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>492</v>
       </c>
       <c r="G563" s="7">
@@ -22453,7 +22489,7 @@
         <v>2</v>
       </c>
       <c r="F564" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>504</v>
       </c>
       <c r="G564" s="7">
@@ -22483,7 +22519,7 @@
         <v>2</v>
       </c>
       <c r="F565" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>516</v>
       </c>
       <c r="G565" s="7">
@@ -22513,7 +22549,7 @@
         <v>2</v>
       </c>
       <c r="F566" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>528</v>
       </c>
       <c r="G566" s="7">
@@ -22543,7 +22579,7 @@
         <v>2</v>
       </c>
       <c r="F567" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>540</v>
       </c>
       <c r="G567" s="7">
@@ -22573,7 +22609,7 @@
         <v>2</v>
       </c>
       <c r="F568" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>552</v>
       </c>
       <c r="G568" s="7">
@@ -22603,7 +22639,7 @@
         <v>2</v>
       </c>
       <c r="F569" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>564</v>
       </c>
       <c r="G569" s="7">
@@ -22633,7 +22669,7 @@
         <v>2</v>
       </c>
       <c r="F570" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>576</v>
       </c>
       <c r="G570" s="7">
@@ -22663,7 +22699,7 @@
         <v>2</v>
       </c>
       <c r="F571" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>588</v>
       </c>
       <c r="G571" s="7">
@@ -22693,7 +22729,7 @@
         <v>2</v>
       </c>
       <c r="F572" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>600</v>
       </c>
       <c r="G572" s="4">
@@ -22723,7 +22759,7 @@
         <v>2</v>
       </c>
       <c r="F573" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>612</v>
       </c>
       <c r="G573" s="7">
@@ -22753,7 +22789,7 @@
         <v>2</v>
       </c>
       <c r="F574" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>624</v>
       </c>
       <c r="G574" s="7">
@@ -22783,7 +22819,7 @@
         <v>2</v>
       </c>
       <c r="F575" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>636</v>
       </c>
       <c r="G575" s="7">
@@ -22813,7 +22849,7 @@
         <v>2</v>
       </c>
       <c r="F576" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>648</v>
       </c>
       <c r="G576" s="7">
@@ -22843,7 +22879,7 @@
         <v>2</v>
       </c>
       <c r="F577" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>660</v>
       </c>
       <c r="G577" s="7">
@@ -22873,7 +22909,7 @@
         <v>2</v>
       </c>
       <c r="F578" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>672</v>
       </c>
       <c r="G578" s="7">
@@ -22903,7 +22939,7 @@
         <v>2</v>
       </c>
       <c r="F579" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>684</v>
       </c>
       <c r="G579" s="7">
@@ -22933,7 +22969,7 @@
         <v>2</v>
       </c>
       <c r="F580" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>696</v>
       </c>
       <c r="G580" s="7">
@@ -22963,7 +22999,7 @@
         <v>2</v>
       </c>
       <c r="F581" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>708</v>
       </c>
       <c r="G581" s="7">
@@ -22993,7 +23029,7 @@
         <v>2</v>
       </c>
       <c r="F582" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
       <c r="G582" s="4">
@@ -23023,7 +23059,7 @@
         <v>2</v>
       </c>
       <c r="F583" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>732</v>
       </c>
       <c r="G583" s="7">
@@ -23053,7 +23089,7 @@
         <v>2</v>
       </c>
       <c r="F584" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>744</v>
       </c>
       <c r="G584" s="7">
@@ -23083,7 +23119,7 @@
         <v>2</v>
       </c>
       <c r="F585" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>756</v>
       </c>
       <c r="G585" s="7">
@@ -23113,7 +23149,7 @@
         <v>2</v>
       </c>
       <c r="F586" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>768</v>
       </c>
       <c r="G586" s="7">
@@ -23143,7 +23179,7 @@
         <v>2</v>
       </c>
       <c r="F587" s="7">
-        <f t="shared" ref="F587:F650" si="14">(C587-2000)*12</f>
+        <f t="shared" ref="F587:F650" si="15">(C587-2000)*12</f>
         <v>780</v>
       </c>
       <c r="G587" s="7">
@@ -23173,7 +23209,7 @@
         <v>2</v>
       </c>
       <c r="F588" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>792</v>
       </c>
       <c r="G588" s="7">
@@ -23203,7 +23239,7 @@
         <v>2</v>
       </c>
       <c r="F589" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>804</v>
       </c>
       <c r="G589" s="7">
@@ -23233,7 +23269,7 @@
         <v>2</v>
       </c>
       <c r="F590" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>816</v>
       </c>
       <c r="G590" s="7">
@@ -23263,7 +23299,7 @@
         <v>2</v>
       </c>
       <c r="F591" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>828</v>
       </c>
       <c r="G591" s="7">
@@ -23293,7 +23329,7 @@
         <v>2</v>
       </c>
       <c r="F592" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>840</v>
       </c>
       <c r="G592" s="4">
@@ -23323,7 +23359,7 @@
         <v>2</v>
       </c>
       <c r="F593" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>852</v>
       </c>
       <c r="G593" s="7">
@@ -23353,7 +23389,7 @@
         <v>2</v>
       </c>
       <c r="F594" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>864</v>
       </c>
       <c r="G594" s="7">
@@ -23383,7 +23419,7 @@
         <v>2</v>
       </c>
       <c r="F595" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>876</v>
       </c>
       <c r="G595" s="7">
@@ -23413,7 +23449,7 @@
         <v>2</v>
       </c>
       <c r="F596" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>888</v>
       </c>
       <c r="G596" s="7">
@@ -23443,7 +23479,7 @@
         <v>2</v>
       </c>
       <c r="F597" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>900</v>
       </c>
       <c r="G597" s="7">
@@ -23473,7 +23509,7 @@
         <v>2</v>
       </c>
       <c r="F598" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>912</v>
       </c>
       <c r="G598" s="7">
@@ -23503,7 +23539,7 @@
         <v>2</v>
       </c>
       <c r="F599" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>924</v>
       </c>
       <c r="G599" s="7">
@@ -23533,7 +23569,7 @@
         <v>2</v>
       </c>
       <c r="F600" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>936</v>
       </c>
       <c r="G600" s="7">
@@ -23563,7 +23599,7 @@
         <v>2</v>
       </c>
       <c r="F601" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>948</v>
       </c>
       <c r="G601" s="7">
@@ -23593,7 +23629,7 @@
         <v>2</v>
       </c>
       <c r="F602" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>960</v>
       </c>
       <c r="G602" s="4">
@@ -23623,7 +23659,7 @@
         <v>2</v>
       </c>
       <c r="F603" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>972</v>
       </c>
       <c r="G603" s="7">
@@ -23653,7 +23689,7 @@
         <v>2</v>
       </c>
       <c r="F604" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>984</v>
       </c>
       <c r="G604" s="7">
@@ -23683,7 +23719,7 @@
         <v>2</v>
       </c>
       <c r="F605" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>996</v>
       </c>
       <c r="G605" s="7">
@@ -23713,7 +23749,7 @@
         <v>2</v>
       </c>
       <c r="F606" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1008</v>
       </c>
       <c r="G606" s="7">
@@ -23743,7 +23779,7 @@
         <v>2</v>
       </c>
       <c r="F607" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1020</v>
       </c>
       <c r="G607" s="7">
@@ -23773,7 +23809,7 @@
         <v>2</v>
       </c>
       <c r="F608" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1032</v>
       </c>
       <c r="G608" s="7">
@@ -23803,7 +23839,7 @@
         <v>2</v>
       </c>
       <c r="F609" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1044</v>
       </c>
       <c r="G609" s="7">
@@ -23833,7 +23869,7 @@
         <v>2</v>
       </c>
       <c r="F610" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1056</v>
       </c>
       <c r="G610" s="7">
@@ -23863,7 +23899,7 @@
         <v>2</v>
       </c>
       <c r="F611" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1068</v>
       </c>
       <c r="G611" s="7">
@@ -23893,7 +23929,7 @@
         <v>2</v>
       </c>
       <c r="F612" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1080</v>
       </c>
       <c r="G612" s="4">
@@ -23923,7 +23959,7 @@
         <v>2</v>
       </c>
       <c r="F613" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1092</v>
       </c>
       <c r="G613" s="7">
@@ -23953,7 +23989,7 @@
         <v>2</v>
       </c>
       <c r="F614" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1104</v>
       </c>
       <c r="G614" s="7">
@@ -23983,7 +24019,7 @@
         <v>2</v>
       </c>
       <c r="F615" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1116</v>
       </c>
       <c r="G615" s="7">
@@ -24013,7 +24049,7 @@
         <v>2</v>
       </c>
       <c r="F616" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1128</v>
       </c>
       <c r="G616" s="7">
@@ -24043,7 +24079,7 @@
         <v>2</v>
       </c>
       <c r="F617" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1140</v>
       </c>
       <c r="G617" s="7">
@@ -24073,7 +24109,7 @@
         <v>2</v>
       </c>
       <c r="F618" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1152</v>
       </c>
       <c r="G618" s="7">
@@ -24103,7 +24139,7 @@
         <v>2</v>
       </c>
       <c r="F619" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1164</v>
       </c>
       <c r="G619" s="7">
@@ -24133,7 +24169,7 @@
         <v>2</v>
       </c>
       <c r="F620" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1176</v>
       </c>
       <c r="G620" s="7">
@@ -24163,7 +24199,7 @@
         <v>2</v>
       </c>
       <c r="F621" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1188</v>
       </c>
       <c r="G621" s="7">
@@ -24193,7 +24229,7 @@
         <v>2</v>
       </c>
       <c r="F622" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1200</v>
       </c>
       <c r="G622" s="4">
@@ -24223,7 +24259,7 @@
         <v>2</v>
       </c>
       <c r="F623" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1212</v>
       </c>
       <c r="G623" s="7">
@@ -24253,7 +24289,7 @@
         <v>2</v>
       </c>
       <c r="F624" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1224</v>
       </c>
       <c r="G624" s="7">
@@ -24283,7 +24319,7 @@
         <v>2</v>
       </c>
       <c r="F625" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1236</v>
       </c>
       <c r="G625" s="7">
@@ -24313,7 +24349,7 @@
         <v>2</v>
       </c>
       <c r="F626" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1248</v>
       </c>
       <c r="G626" s="7">
@@ -24343,7 +24379,7 @@
         <v>2</v>
       </c>
       <c r="F627" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1260</v>
       </c>
       <c r="G627" s="7">
@@ -24373,7 +24409,7 @@
         <v>2</v>
       </c>
       <c r="F628" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1272</v>
       </c>
       <c r="G628" s="7">
@@ -24403,7 +24439,7 @@
         <v>2</v>
       </c>
       <c r="F629" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1284</v>
       </c>
       <c r="G629" s="7">
@@ -24433,7 +24469,7 @@
         <v>2</v>
       </c>
       <c r="F630" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1296</v>
       </c>
       <c r="G630" s="7">
@@ -24463,7 +24499,7 @@
         <v>2</v>
       </c>
       <c r="F631" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1308</v>
       </c>
       <c r="G631" s="7">
@@ -24493,7 +24529,7 @@
         <v>2</v>
       </c>
       <c r="F632" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1320</v>
       </c>
       <c r="G632" s="4">
@@ -24523,7 +24559,7 @@
         <v>2</v>
       </c>
       <c r="F633" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1332</v>
       </c>
       <c r="G633" s="7">
@@ -24553,7 +24589,7 @@
         <v>2</v>
       </c>
       <c r="F634" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1344</v>
       </c>
       <c r="G634" s="7">
@@ -24583,7 +24619,7 @@
         <v>2</v>
       </c>
       <c r="F635" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1356</v>
       </c>
       <c r="G635" s="7">
@@ -24613,7 +24649,7 @@
         <v>2</v>
       </c>
       <c r="F636" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1368</v>
       </c>
       <c r="G636" s="7">
@@ -24643,7 +24679,7 @@
         <v>2</v>
       </c>
       <c r="F637" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1380</v>
       </c>
       <c r="G637" s="7">
@@ -24673,7 +24709,7 @@
         <v>2</v>
       </c>
       <c r="F638" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1392</v>
       </c>
       <c r="G638" s="7">
@@ -24703,7 +24739,7 @@
         <v>2</v>
       </c>
       <c r="F639" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1404</v>
       </c>
       <c r="G639" s="7">
@@ -24733,7 +24769,7 @@
         <v>2</v>
       </c>
       <c r="F640" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1416</v>
       </c>
       <c r="G640" s="7">
@@ -24763,7 +24799,7 @@
         <v>2</v>
       </c>
       <c r="F641" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1428</v>
       </c>
       <c r="G641" s="7">
@@ -24793,7 +24829,7 @@
         <v>2</v>
       </c>
       <c r="F642" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1440</v>
       </c>
       <c r="G642" s="4">
@@ -24823,7 +24859,7 @@
         <v>2</v>
       </c>
       <c r="F643" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1452</v>
       </c>
       <c r="G643" s="7">
@@ -24853,7 +24889,7 @@
         <v>2</v>
       </c>
       <c r="F644" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1464</v>
       </c>
       <c r="G644" s="7">
@@ -24883,7 +24919,7 @@
         <v>2</v>
       </c>
       <c r="F645" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1476</v>
       </c>
       <c r="G645" s="7">
@@ -24913,7 +24949,7 @@
         <v>2</v>
       </c>
       <c r="F646" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1488</v>
       </c>
       <c r="G646" s="7">
@@ -24943,7 +24979,7 @@
         <v>2</v>
       </c>
       <c r="F647" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1500</v>
       </c>
       <c r="G647" s="7">
@@ -24973,7 +25009,7 @@
         <v>2</v>
       </c>
       <c r="F648" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1512</v>
       </c>
       <c r="G648" s="7">
@@ -25003,7 +25039,7 @@
         <v>2</v>
       </c>
       <c r="F649" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1524</v>
       </c>
       <c r="G649" s="7">
@@ -25033,7 +25069,7 @@
         <v>2</v>
       </c>
       <c r="F650" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1536</v>
       </c>
       <c r="G650" s="7">
@@ -25063,7 +25099,7 @@
         <v>2</v>
       </c>
       <c r="F651" s="7">
-        <f t="shared" ref="F651:F714" si="15">(C651-2000)*12</f>
+        <f t="shared" ref="F651:F714" si="16">(C651-2000)*12</f>
         <v>1548</v>
       </c>
       <c r="G651" s="7">
@@ -25093,7 +25129,7 @@
         <v>2</v>
       </c>
       <c r="F652" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1560</v>
       </c>
       <c r="G652" s="4">
@@ -25123,7 +25159,7 @@
         <v>2</v>
       </c>
       <c r="F653" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1572</v>
       </c>
       <c r="G653" s="7">
@@ -25153,7 +25189,7 @@
         <v>2</v>
       </c>
       <c r="F654" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1584</v>
       </c>
       <c r="G654" s="7">
@@ -25183,7 +25219,7 @@
         <v>2</v>
       </c>
       <c r="F655" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1596</v>
       </c>
       <c r="G655" s="7">
@@ -25213,7 +25249,7 @@
         <v>2</v>
       </c>
       <c r="F656" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1608</v>
       </c>
       <c r="G656" s="7">
@@ -25243,7 +25279,7 @@
         <v>2</v>
       </c>
       <c r="F657" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1620</v>
       </c>
       <c r="G657" s="7">
@@ -25273,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="F658" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1632</v>
       </c>
       <c r="G658" s="7">
@@ -25303,7 +25339,7 @@
         <v>2</v>
       </c>
       <c r="F659" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1644</v>
       </c>
       <c r="G659" s="7">
@@ -25333,7 +25369,7 @@
         <v>2</v>
       </c>
       <c r="F660" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1656</v>
       </c>
       <c r="G660" s="7">
@@ -25363,7 +25399,7 @@
         <v>2</v>
       </c>
       <c r="F661" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1668</v>
       </c>
       <c r="G661" s="7">
@@ -25393,7 +25429,7 @@
         <v>2</v>
       </c>
       <c r="F662" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1680</v>
       </c>
       <c r="G662" s="4">
@@ -25423,7 +25459,7 @@
         <v>2</v>
       </c>
       <c r="F663" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1692</v>
       </c>
       <c r="G663" s="7">
@@ -25453,7 +25489,7 @@
         <v>2</v>
       </c>
       <c r="F664" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1704</v>
       </c>
       <c r="G664" s="7">
@@ -25483,7 +25519,7 @@
         <v>2</v>
       </c>
       <c r="F665" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1716</v>
       </c>
       <c r="G665" s="7">
@@ -25513,7 +25549,7 @@
         <v>2</v>
       </c>
       <c r="F666" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1728</v>
       </c>
       <c r="G666" s="7">
@@ -25543,7 +25579,7 @@
         <v>2</v>
       </c>
       <c r="F667" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1740</v>
       </c>
       <c r="G667" s="7">
@@ -25573,7 +25609,7 @@
         <v>2</v>
       </c>
       <c r="F668" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1752</v>
       </c>
       <c r="G668" s="7">
@@ -25603,7 +25639,7 @@
         <v>2</v>
       </c>
       <c r="F669" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1764</v>
       </c>
       <c r="G669" s="7">
@@ -25633,7 +25669,7 @@
         <v>2</v>
       </c>
       <c r="F670" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1776</v>
       </c>
       <c r="G670" s="7">
@@ -25663,7 +25699,7 @@
         <v>2</v>
       </c>
       <c r="F671" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1788</v>
       </c>
       <c r="G671" s="7">
@@ -25693,7 +25729,7 @@
         <v>2</v>
       </c>
       <c r="F672" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1800</v>
       </c>
       <c r="G672" s="4">
@@ -25723,7 +25759,7 @@
         <v>2</v>
       </c>
       <c r="F673" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1812</v>
       </c>
       <c r="G673" s="7">
@@ -25753,7 +25789,7 @@
         <v>2</v>
       </c>
       <c r="F674" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1824</v>
       </c>
       <c r="G674" s="7">
@@ -25783,7 +25819,7 @@
         <v>2</v>
       </c>
       <c r="F675" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1836</v>
       </c>
       <c r="G675" s="7">
@@ -25813,7 +25849,7 @@
         <v>2</v>
       </c>
       <c r="F676" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1848</v>
       </c>
       <c r="G676" s="7">
@@ -25843,7 +25879,7 @@
         <v>2</v>
       </c>
       <c r="F677" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1860</v>
       </c>
       <c r="G677" s="7">
@@ -25873,7 +25909,7 @@
         <v>2</v>
       </c>
       <c r="F678" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1872</v>
       </c>
       <c r="G678" s="7">
@@ -25903,7 +25939,7 @@
         <v>2</v>
       </c>
       <c r="F679" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1884</v>
       </c>
       <c r="G679" s="7">
@@ -25933,7 +25969,7 @@
         <v>2</v>
       </c>
       <c r="F680" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1896</v>
       </c>
       <c r="G680" s="7">
@@ -25963,7 +25999,7 @@
         <v>2</v>
       </c>
       <c r="F681" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1908</v>
       </c>
       <c r="G681" s="7">
@@ -25993,7 +26029,7 @@
         <v>2</v>
       </c>
       <c r="F682" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1920</v>
       </c>
       <c r="G682" s="4">
@@ -26023,7 +26059,7 @@
         <v>2</v>
       </c>
       <c r="F683" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1932</v>
       </c>
       <c r="G683" s="7">
@@ -26053,7 +26089,7 @@
         <v>2</v>
       </c>
       <c r="F684" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1944</v>
       </c>
       <c r="G684" s="7">
@@ -26083,7 +26119,7 @@
         <v>2</v>
       </c>
       <c r="F685" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1956</v>
       </c>
       <c r="G685" s="7">
@@ -26113,7 +26149,7 @@
         <v>2</v>
       </c>
       <c r="F686" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1968</v>
       </c>
       <c r="G686" s="7">
@@ -26143,7 +26179,7 @@
         <v>2</v>
       </c>
       <c r="F687" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1980</v>
       </c>
       <c r="G687" s="7">
@@ -26173,7 +26209,7 @@
         <v>2</v>
       </c>
       <c r="F688" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1992</v>
       </c>
       <c r="G688" s="7">
@@ -26203,7 +26239,7 @@
         <v>2</v>
       </c>
       <c r="F689" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2004</v>
       </c>
       <c r="G689" s="7">
@@ -26233,7 +26269,7 @@
         <v>2</v>
       </c>
       <c r="F690" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2016</v>
       </c>
       <c r="G690" s="7">
@@ -26263,7 +26299,7 @@
         <v>2</v>
       </c>
       <c r="F691" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2028</v>
       </c>
       <c r="G691" s="7">
@@ -26293,7 +26329,7 @@
         <v>2</v>
       </c>
       <c r="F692" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2040</v>
       </c>
       <c r="G692" s="4">
@@ -26323,7 +26359,7 @@
         <v>2</v>
       </c>
       <c r="F693" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2052</v>
       </c>
       <c r="G693" s="7">
@@ -26353,7 +26389,7 @@
         <v>2</v>
       </c>
       <c r="F694" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2064</v>
       </c>
       <c r="G694" s="7">
@@ -26383,7 +26419,7 @@
         <v>2</v>
       </c>
       <c r="F695" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2076</v>
       </c>
       <c r="G695" s="7">
@@ -26413,7 +26449,7 @@
         <v>2</v>
       </c>
       <c r="F696" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2088</v>
       </c>
       <c r="G696" s="7">
@@ -26443,7 +26479,7 @@
         <v>2</v>
       </c>
       <c r="F697" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2100</v>
       </c>
       <c r="G697" s="7">
@@ -26473,7 +26509,7 @@
         <v>2</v>
       </c>
       <c r="F698" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2112</v>
       </c>
       <c r="G698" s="7">
@@ -26503,7 +26539,7 @@
         <v>2</v>
       </c>
       <c r="F699" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2124</v>
       </c>
       <c r="G699" s="7">
@@ -26533,7 +26569,7 @@
         <v>2</v>
       </c>
       <c r="F700" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2136</v>
       </c>
       <c r="G700" s="7">
@@ -26563,7 +26599,7 @@
         <v>2</v>
       </c>
       <c r="F701" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2148</v>
       </c>
       <c r="G701" s="7">
@@ -26593,7 +26629,7 @@
         <v>2</v>
       </c>
       <c r="F702" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2160</v>
       </c>
       <c r="G702" s="4">
@@ -26623,7 +26659,7 @@
         <v>2</v>
       </c>
       <c r="F703" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2172</v>
       </c>
       <c r="G703" s="7">
@@ -26653,7 +26689,7 @@
         <v>2</v>
       </c>
       <c r="F704" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2184</v>
       </c>
       <c r="G704" s="7">
@@ -26683,7 +26719,7 @@
         <v>2</v>
       </c>
       <c r="F705" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2196</v>
       </c>
       <c r="G705" s="7">
@@ -26713,7 +26749,7 @@
         <v>2</v>
       </c>
       <c r="F706" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2208</v>
       </c>
       <c r="G706" s="7">
@@ -26743,7 +26779,7 @@
         <v>2</v>
       </c>
       <c r="F707" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2220</v>
       </c>
       <c r="G707" s="7">
@@ -26773,7 +26809,7 @@
         <v>2</v>
       </c>
       <c r="F708" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2232</v>
       </c>
       <c r="G708" s="7">
@@ -26803,7 +26839,7 @@
         <v>2</v>
       </c>
       <c r="F709" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2244</v>
       </c>
       <c r="G709" s="7">
@@ -26833,7 +26869,7 @@
         <v>2</v>
       </c>
       <c r="F710" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2256</v>
       </c>
       <c r="G710" s="7">
@@ -26863,7 +26899,7 @@
         <v>2</v>
       </c>
       <c r="F711" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2268</v>
       </c>
       <c r="G711" s="7">
@@ -26893,7 +26929,7 @@
         <v>2</v>
       </c>
       <c r="F712" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2280</v>
       </c>
       <c r="G712" s="4">
@@ -26923,7 +26959,7 @@
         <v>2</v>
       </c>
       <c r="F713" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2292</v>
       </c>
       <c r="G713" s="7">
@@ -26953,7 +26989,7 @@
         <v>2</v>
       </c>
       <c r="F714" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2304</v>
       </c>
       <c r="G714" s="7">
@@ -26983,7 +27019,7 @@
         <v>2</v>
       </c>
       <c r="F715" s="7">
-        <f t="shared" ref="F715:F741" si="16">(C715-2000)*12</f>
+        <f t="shared" ref="F715:F741" si="17">(C715-2000)*12</f>
         <v>2316</v>
       </c>
       <c r="G715" s="7">
@@ -27013,7 +27049,7 @@
         <v>2</v>
       </c>
       <c r="F716" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2328</v>
       </c>
       <c r="G716" s="7">
@@ -27043,7 +27079,7 @@
         <v>2</v>
       </c>
       <c r="F717" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2340</v>
       </c>
       <c r="G717" s="7">
@@ -27073,7 +27109,7 @@
         <v>2</v>
       </c>
       <c r="F718" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2352</v>
       </c>
       <c r="G718" s="7">
@@ -27103,7 +27139,7 @@
         <v>2</v>
       </c>
       <c r="F719" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2364</v>
       </c>
       <c r="G719" s="7">
@@ -27133,7 +27169,7 @@
         <v>2</v>
       </c>
       <c r="F720" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2376</v>
       </c>
       <c r="G720" s="7">
@@ -27163,7 +27199,7 @@
         <v>2</v>
       </c>
       <c r="F721" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2388</v>
       </c>
       <c r="G721" s="7">
@@ -27193,7 +27229,7 @@
         <v>2</v>
       </c>
       <c r="F722" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2400</v>
       </c>
       <c r="G722" s="4">
@@ -27223,7 +27259,7 @@
         <v>2</v>
       </c>
       <c r="F723" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2412</v>
       </c>
       <c r="G723" s="7">
@@ -27253,7 +27289,7 @@
         <v>2</v>
       </c>
       <c r="F724" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2424</v>
       </c>
       <c r="G724" s="7">
@@ -27283,7 +27319,7 @@
         <v>2</v>
       </c>
       <c r="F725" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2436</v>
       </c>
       <c r="G725" s="7">
@@ -27313,7 +27349,7 @@
         <v>2</v>
       </c>
       <c r="F726" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2448</v>
       </c>
       <c r="G726" s="7">
@@ -27343,7 +27379,7 @@
         <v>2</v>
       </c>
       <c r="F727" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2460</v>
       </c>
       <c r="G727" s="7">
@@ -27373,7 +27409,7 @@
         <v>2</v>
       </c>
       <c r="F728" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2472</v>
       </c>
       <c r="G728" s="7">
@@ -27403,7 +27439,7 @@
         <v>2</v>
       </c>
       <c r="F729" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2484</v>
       </c>
       <c r="G729" s="7">
@@ -27433,7 +27469,7 @@
         <v>2</v>
       </c>
       <c r="F730" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2496</v>
       </c>
       <c r="G730" s="7">
@@ -27463,7 +27499,7 @@
         <v>2</v>
       </c>
       <c r="F731" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2508</v>
       </c>
       <c r="G731" s="7">
@@ -27493,7 +27529,7 @@
         <v>2</v>
       </c>
       <c r="F732" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2520</v>
       </c>
       <c r="G732" s="7">
@@ -27523,7 +27559,7 @@
         <v>2</v>
       </c>
       <c r="F733" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2532</v>
       </c>
       <c r="G733" s="7">
@@ -27553,7 +27589,7 @@
         <v>2</v>
       </c>
       <c r="F734" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2544</v>
       </c>
       <c r="G734" s="7">
@@ -27583,7 +27619,7 @@
         <v>2</v>
       </c>
       <c r="F735" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2556</v>
       </c>
       <c r="G735" s="7">
@@ -27613,7 +27649,7 @@
         <v>2</v>
       </c>
       <c r="F736" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2568</v>
       </c>
       <c r="G736" s="7">
@@ -27643,7 +27679,7 @@
         <v>2</v>
       </c>
       <c r="F737" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2580</v>
       </c>
       <c r="G737" s="4">
@@ -27673,7 +27709,7 @@
         <v>2</v>
       </c>
       <c r="F738" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2592</v>
       </c>
       <c r="G738" s="7">
@@ -27703,7 +27739,7 @@
         <v>2</v>
       </c>
       <c r="F739" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2604</v>
       </c>
       <c r="G739" s="7">
@@ -27733,7 +27769,7 @@
         <v>2</v>
       </c>
       <c r="F740" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2616</v>
       </c>
       <c r="G740" s="7">
@@ -27763,7 +27799,7 @@
         <v>2</v>
       </c>
       <c r="F741" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2628</v>
       </c>
       <c r="G741" s="7">
@@ -27793,7 +27829,7 @@
         <v>2</v>
       </c>
       <c r="F742" s="7">
-        <f t="shared" ref="F742:F805" si="17">(C742-2000)*12</f>
+        <f t="shared" ref="F742:F805" si="18">(C742-2000)*12</f>
         <v>2640</v>
       </c>
       <c r="G742" s="7">
@@ -27823,7 +27859,7 @@
         <v>2</v>
       </c>
       <c r="F743" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2652</v>
       </c>
       <c r="G743" s="7">
@@ -27853,7 +27889,7 @@
         <v>2</v>
       </c>
       <c r="F744" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2664</v>
       </c>
       <c r="G744" s="7">
@@ -27883,7 +27919,7 @@
         <v>2</v>
       </c>
       <c r="F745" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2676</v>
       </c>
       <c r="G745" s="7">
@@ -27913,7 +27949,7 @@
         <v>2</v>
       </c>
       <c r="F746" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2688</v>
       </c>
       <c r="G746" s="7">
@@ -27943,7 +27979,7 @@
         <v>2</v>
       </c>
       <c r="F747" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2700</v>
       </c>
       <c r="G747" s="7">
@@ -27973,7 +28009,7 @@
         <v>2</v>
       </c>
       <c r="F748" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2712</v>
       </c>
       <c r="G748" s="7">
@@ -28003,7 +28039,7 @@
         <v>2</v>
       </c>
       <c r="F749" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2724</v>
       </c>
       <c r="G749" s="7">
@@ -28033,7 +28069,7 @@
         <v>2</v>
       </c>
       <c r="F750" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2736</v>
       </c>
       <c r="G750" s="7">
@@ -28063,7 +28099,7 @@
         <v>2</v>
       </c>
       <c r="F751" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2748</v>
       </c>
       <c r="G751" s="7">
@@ -28093,7 +28129,7 @@
         <v>2</v>
       </c>
       <c r="F752" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2760</v>
       </c>
       <c r="G752" s="4">
@@ -28123,7 +28159,7 @@
         <v>2</v>
       </c>
       <c r="F753" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2772</v>
       </c>
       <c r="G753" s="7">
@@ -28153,7 +28189,7 @@
         <v>2</v>
       </c>
       <c r="F754" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2784</v>
       </c>
       <c r="G754" s="7">
@@ -28183,7 +28219,7 @@
         <v>2</v>
       </c>
       <c r="F755" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2796</v>
       </c>
       <c r="G755" s="7">
@@ -28213,7 +28249,7 @@
         <v>2</v>
       </c>
       <c r="F756" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2808</v>
       </c>
       <c r="G756" s="7">
@@ -28243,7 +28279,7 @@
         <v>2</v>
       </c>
       <c r="F757" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2820</v>
       </c>
       <c r="G757" s="7">
@@ -28273,7 +28309,7 @@
         <v>2</v>
       </c>
       <c r="F758" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2832</v>
       </c>
       <c r="G758" s="7">
@@ -28303,7 +28339,7 @@
         <v>2</v>
       </c>
       <c r="F759" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2844</v>
       </c>
       <c r="G759" s="7">
@@ -28333,7 +28369,7 @@
         <v>2</v>
       </c>
       <c r="F760" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2856</v>
       </c>
       <c r="G760" s="7">
@@ -28363,7 +28399,7 @@
         <v>2</v>
       </c>
       <c r="F761" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2868</v>
       </c>
       <c r="G761" s="7">
@@ -28393,7 +28429,7 @@
         <v>2</v>
       </c>
       <c r="F762" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2880</v>
       </c>
       <c r="G762" s="7">
@@ -28423,7 +28459,7 @@
         <v>2</v>
       </c>
       <c r="F763" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2892</v>
       </c>
       <c r="G763" s="7">
@@ -28453,7 +28489,7 @@
         <v>2</v>
       </c>
       <c r="F764" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2904</v>
       </c>
       <c r="G764" s="7">
@@ -28483,7 +28519,7 @@
         <v>2</v>
       </c>
       <c r="F765" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2916</v>
       </c>
       <c r="G765" s="7">
@@ -28513,7 +28549,7 @@
         <v>2</v>
       </c>
       <c r="F766" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2928</v>
       </c>
       <c r="G766" s="7">
@@ -28543,7 +28579,7 @@
         <v>2</v>
       </c>
       <c r="F767" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2940</v>
       </c>
       <c r="G767" s="4">
@@ -28573,7 +28609,7 @@
         <v>2</v>
       </c>
       <c r="F768" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2952</v>
       </c>
       <c r="G768" s="7">
@@ -28603,7 +28639,7 @@
         <v>2</v>
       </c>
       <c r="F769" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2964</v>
       </c>
       <c r="G769" s="7">
@@ -28633,7 +28669,7 @@
         <v>2</v>
       </c>
       <c r="F770" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2976</v>
       </c>
       <c r="G770" s="7">
@@ -28663,7 +28699,7 @@
         <v>2</v>
       </c>
       <c r="F771" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2988</v>
       </c>
       <c r="G771" s="7">
@@ -28693,7 +28729,7 @@
         <v>2</v>
       </c>
       <c r="F772" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3000</v>
       </c>
       <c r="G772" s="7">
@@ -28723,7 +28759,7 @@
         <v>2</v>
       </c>
       <c r="F773" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3012</v>
       </c>
       <c r="G773" s="7">
@@ -28753,7 +28789,7 @@
         <v>2</v>
       </c>
       <c r="F774" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3024</v>
       </c>
       <c r="G774" s="7">
@@ -28783,7 +28819,7 @@
         <v>2</v>
       </c>
       <c r="F775" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3036</v>
       </c>
       <c r="G775" s="7">
@@ -28813,7 +28849,7 @@
         <v>2</v>
       </c>
       <c r="F776" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3048</v>
       </c>
       <c r="G776" s="7">
@@ -28843,7 +28879,7 @@
         <v>2</v>
       </c>
       <c r="F777" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3060</v>
       </c>
       <c r="G777" s="7">
@@ -28873,7 +28909,7 @@
         <v>2</v>
       </c>
       <c r="F778" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3072</v>
       </c>
       <c r="G778" s="7">
@@ -28903,7 +28939,7 @@
         <v>2</v>
       </c>
       <c r="F779" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3084</v>
       </c>
       <c r="G779" s="7">
@@ -28933,7 +28969,7 @@
         <v>2</v>
       </c>
       <c r="F780" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3096</v>
       </c>
       <c r="G780" s="7">
@@ -28963,7 +28999,7 @@
         <v>2</v>
       </c>
       <c r="F781" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3108</v>
       </c>
       <c r="G781" s="7">
@@ -28993,7 +29029,7 @@
         <v>2</v>
       </c>
       <c r="F782" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3120</v>
       </c>
       <c r="G782" s="4">
@@ -29023,7 +29059,7 @@
         <v>2</v>
       </c>
       <c r="F783" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3132</v>
       </c>
       <c r="G783" s="7">
@@ -29053,7 +29089,7 @@
         <v>2</v>
       </c>
       <c r="F784" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3144</v>
       </c>
       <c r="G784" s="7">
@@ -29083,7 +29119,7 @@
         <v>2</v>
       </c>
       <c r="F785" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3156</v>
       </c>
       <c r="G785" s="7">
@@ -29113,7 +29149,7 @@
         <v>2</v>
       </c>
       <c r="F786" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3168</v>
       </c>
       <c r="G786" s="7">
@@ -29143,7 +29179,7 @@
         <v>2</v>
       </c>
       <c r="F787" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3180</v>
       </c>
       <c r="G787" s="7">
@@ -29173,7 +29209,7 @@
         <v>2</v>
       </c>
       <c r="F788" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3192</v>
       </c>
       <c r="G788" s="7">
@@ -29203,7 +29239,7 @@
         <v>2</v>
       </c>
       <c r="F789" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3204</v>
       </c>
       <c r="G789" s="7">
@@ -29233,7 +29269,7 @@
         <v>2</v>
       </c>
       <c r="F790" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3216</v>
       </c>
       <c r="G790" s="7">
@@ -29263,7 +29299,7 @@
         <v>2</v>
       </c>
       <c r="F791" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3228</v>
       </c>
       <c r="G791" s="7">
@@ -29293,7 +29329,7 @@
         <v>2</v>
       </c>
       <c r="F792" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3240</v>
       </c>
       <c r="G792" s="7">
@@ -29323,7 +29359,7 @@
         <v>2</v>
       </c>
       <c r="F793" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3252</v>
       </c>
       <c r="G793" s="7">
@@ -29353,7 +29389,7 @@
         <v>2</v>
       </c>
       <c r="F794" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3264</v>
       </c>
       <c r="G794" s="7">
@@ -29383,7 +29419,7 @@
         <v>2</v>
       </c>
       <c r="F795" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3276</v>
       </c>
       <c r="G795" s="7">
@@ -29413,7 +29449,7 @@
         <v>2</v>
       </c>
       <c r="F796" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3288</v>
       </c>
       <c r="G796" s="7">
@@ -29443,7 +29479,7 @@
         <v>2</v>
       </c>
       <c r="F797" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3300</v>
       </c>
       <c r="G797" s="4">
@@ -29473,7 +29509,7 @@
         <v>2</v>
       </c>
       <c r="F798" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3312</v>
       </c>
       <c r="G798" s="7">
@@ -29503,7 +29539,7 @@
         <v>2</v>
       </c>
       <c r="F799" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3324</v>
       </c>
       <c r="G799" s="7">
@@ -29533,7 +29569,7 @@
         <v>2</v>
       </c>
       <c r="F800" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3336</v>
       </c>
       <c r="G800" s="7">
@@ -29563,7 +29599,7 @@
         <v>2</v>
       </c>
       <c r="F801" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3348</v>
       </c>
       <c r="G801" s="7">
@@ -29593,7 +29629,7 @@
         <v>2</v>
       </c>
       <c r="F802" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3360</v>
       </c>
       <c r="G802" s="7">
@@ -29623,7 +29659,7 @@
         <v>2</v>
       </c>
       <c r="F803" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3372</v>
       </c>
       <c r="G803" s="7">
@@ -29653,7 +29689,7 @@
         <v>2</v>
       </c>
       <c r="F804" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3384</v>
       </c>
       <c r="G804" s="7">
@@ -29683,7 +29719,7 @@
         <v>2</v>
       </c>
       <c r="F805" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3396</v>
       </c>
       <c r="G805" s="7">
@@ -29713,7 +29749,7 @@
         <v>2</v>
       </c>
       <c r="F806" s="7">
-        <f t="shared" ref="F806:F869" si="18">(C806-2000)*12</f>
+        <f t="shared" ref="F806:F869" si="19">(C806-2000)*12</f>
         <v>3408</v>
       </c>
       <c r="G806" s="7">
@@ -29743,7 +29779,7 @@
         <v>2</v>
       </c>
       <c r="F807" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3420</v>
       </c>
       <c r="G807" s="7">
@@ -29773,7 +29809,7 @@
         <v>2</v>
       </c>
       <c r="F808" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3432</v>
       </c>
       <c r="G808" s="7">
@@ -29803,7 +29839,7 @@
         <v>2</v>
       </c>
       <c r="F809" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3444</v>
       </c>
       <c r="G809" s="7">
@@ -29833,7 +29869,7 @@
         <v>2</v>
       </c>
       <c r="F810" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3456</v>
       </c>
       <c r="G810" s="7">
@@ -29863,7 +29899,7 @@
         <v>2</v>
       </c>
       <c r="F811" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3468</v>
       </c>
       <c r="G811" s="7">
@@ -29893,7 +29929,7 @@
         <v>2</v>
       </c>
       <c r="F812" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3480</v>
       </c>
       <c r="G812" s="4">
@@ -29923,7 +29959,7 @@
         <v>2</v>
       </c>
       <c r="F813" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3492</v>
       </c>
       <c r="G813" s="7">
@@ -29953,7 +29989,7 @@
         <v>2</v>
       </c>
       <c r="F814" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3504</v>
       </c>
       <c r="G814" s="7">
@@ -29983,7 +30019,7 @@
         <v>2</v>
       </c>
       <c r="F815" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3516</v>
       </c>
       <c r="G815" s="7">
@@ -30013,7 +30049,7 @@
         <v>2</v>
       </c>
       <c r="F816" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3528</v>
       </c>
       <c r="G816" s="7">
@@ -30043,7 +30079,7 @@
         <v>2</v>
       </c>
       <c r="F817" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3540</v>
       </c>
       <c r="G817" s="7">
@@ -30073,7 +30109,7 @@
         <v>2</v>
       </c>
       <c r="F818" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3552</v>
       </c>
       <c r="G818" s="7">
@@ -30103,7 +30139,7 @@
         <v>2</v>
       </c>
       <c r="F819" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3564</v>
       </c>
       <c r="G819" s="7">
@@ -30133,7 +30169,7 @@
         <v>2</v>
       </c>
       <c r="F820" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3576</v>
       </c>
       <c r="G820" s="7">
@@ -30163,7 +30199,7 @@
         <v>2</v>
       </c>
       <c r="F821" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3588</v>
       </c>
       <c r="G821" s="7">
@@ -30193,7 +30229,7 @@
         <v>2</v>
       </c>
       <c r="F822" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3600</v>
       </c>
       <c r="G822" s="7">
@@ -30223,7 +30259,7 @@
         <v>2</v>
       </c>
       <c r="F823" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3612</v>
       </c>
       <c r="G823" s="7">
@@ -30253,7 +30289,7 @@
         <v>2</v>
       </c>
       <c r="F824" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3624</v>
       </c>
       <c r="G824" s="7">
@@ -30283,7 +30319,7 @@
         <v>2</v>
       </c>
       <c r="F825" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3636</v>
       </c>
       <c r="G825" s="7">
@@ -30313,7 +30349,7 @@
         <v>2</v>
       </c>
       <c r="F826" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3648</v>
       </c>
       <c r="G826" s="7">
@@ -30343,7 +30379,7 @@
         <v>2</v>
       </c>
       <c r="F827" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3660</v>
       </c>
       <c r="G827" s="4">
@@ -30373,7 +30409,7 @@
         <v>2</v>
       </c>
       <c r="F828" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3672</v>
       </c>
       <c r="G828" s="7">
@@ -30403,7 +30439,7 @@
         <v>2</v>
       </c>
       <c r="F829" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3684</v>
       </c>
       <c r="G829" s="7">
@@ -30433,7 +30469,7 @@
         <v>2</v>
       </c>
       <c r="F830" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3696</v>
       </c>
       <c r="G830" s="7">
@@ -30463,7 +30499,7 @@
         <v>2</v>
       </c>
       <c r="F831" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3708</v>
       </c>
       <c r="G831" s="7">
@@ -30493,7 +30529,7 @@
         <v>2</v>
       </c>
       <c r="F832" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3720</v>
       </c>
       <c r="G832" s="7">
@@ -30523,7 +30559,7 @@
         <v>2</v>
       </c>
       <c r="F833" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3732</v>
       </c>
       <c r="G833" s="7">
@@ -30553,7 +30589,7 @@
         <v>2</v>
       </c>
       <c r="F834" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3744</v>
       </c>
       <c r="G834" s="7">
@@ -30583,7 +30619,7 @@
         <v>2</v>
       </c>
       <c r="F835" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3756</v>
       </c>
       <c r="G835" s="7">
@@ -30613,7 +30649,7 @@
         <v>2</v>
       </c>
       <c r="F836" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3768</v>
       </c>
       <c r="G836" s="7">
@@ -30643,7 +30679,7 @@
         <v>2</v>
       </c>
       <c r="F837" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3780</v>
       </c>
       <c r="G837" s="7">
@@ -30673,7 +30709,7 @@
         <v>2</v>
       </c>
       <c r="F838" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3792</v>
       </c>
       <c r="G838" s="7">
@@ -30703,7 +30739,7 @@
         <v>2</v>
       </c>
       <c r="F839" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3804</v>
       </c>
       <c r="G839" s="7">
@@ -30733,7 +30769,7 @@
         <v>2</v>
       </c>
       <c r="F840" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3816</v>
       </c>
       <c r="G840" s="7">
@@ -30763,7 +30799,7 @@
         <v>2</v>
       </c>
       <c r="F841" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3828</v>
       </c>
       <c r="G841" s="7">
@@ -30793,7 +30829,7 @@
         <v>2</v>
       </c>
       <c r="F842" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3840</v>
       </c>
       <c r="G842" s="4">
@@ -30823,7 +30859,7 @@
         <v>2</v>
       </c>
       <c r="F843" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3852</v>
       </c>
       <c r="G843" s="7">
@@ -30853,7 +30889,7 @@
         <v>2</v>
       </c>
       <c r="F844" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3864</v>
       </c>
       <c r="G844" s="7">
@@ -30883,7 +30919,7 @@
         <v>2</v>
       </c>
       <c r="F845" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3876</v>
       </c>
       <c r="G845" s="7">
@@ -30913,7 +30949,7 @@
         <v>2</v>
       </c>
       <c r="F846" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3888</v>
       </c>
       <c r="G846" s="7">
@@ -30943,7 +30979,7 @@
         <v>2</v>
       </c>
       <c r="F847" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3900</v>
       </c>
       <c r="G847" s="7">
@@ -30973,7 +31009,7 @@
         <v>2</v>
       </c>
       <c r="F848" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3912</v>
       </c>
       <c r="G848" s="7">
@@ -31003,7 +31039,7 @@
         <v>2</v>
       </c>
       <c r="F849" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3924</v>
       </c>
       <c r="G849" s="7">
@@ -31033,7 +31069,7 @@
         <v>2</v>
       </c>
       <c r="F850" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3936</v>
       </c>
       <c r="G850" s="7">
@@ -31063,7 +31099,7 @@
         <v>2</v>
       </c>
       <c r="F851" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3948</v>
       </c>
       <c r="G851" s="7">
@@ -31093,7 +31129,7 @@
         <v>2</v>
       </c>
       <c r="F852" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3960</v>
       </c>
       <c r="G852" s="7">
@@ -31123,7 +31159,7 @@
         <v>2</v>
       </c>
       <c r="F853" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3972</v>
       </c>
       <c r="G853" s="7">
@@ -31153,7 +31189,7 @@
         <v>2</v>
       </c>
       <c r="F854" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3984</v>
       </c>
       <c r="G854" s="7">
@@ -31183,7 +31219,7 @@
         <v>2</v>
       </c>
       <c r="F855" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3996</v>
       </c>
       <c r="G855" s="7">
@@ -31213,7 +31249,7 @@
         <v>2</v>
       </c>
       <c r="F856" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4008</v>
       </c>
       <c r="G856" s="7">
@@ -31243,7 +31279,7 @@
         <v>2</v>
       </c>
       <c r="F857" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4020</v>
       </c>
       <c r="G857" s="4">
@@ -31273,7 +31309,7 @@
         <v>2</v>
       </c>
       <c r="F858" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4032</v>
       </c>
       <c r="G858" s="7">
@@ -31303,7 +31339,7 @@
         <v>2</v>
       </c>
       <c r="F859" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4044</v>
       </c>
       <c r="G859" s="7">
@@ -31333,7 +31369,7 @@
         <v>2</v>
       </c>
       <c r="F860" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4056</v>
       </c>
       <c r="G860" s="7">
@@ -31363,7 +31399,7 @@
         <v>2</v>
       </c>
       <c r="F861" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4068</v>
       </c>
       <c r="G861" s="7">
@@ -31393,7 +31429,7 @@
         <v>2</v>
       </c>
       <c r="F862" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4080</v>
       </c>
       <c r="G862" s="7">
@@ -31423,7 +31459,7 @@
         <v>2</v>
       </c>
       <c r="F863" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4092</v>
       </c>
       <c r="G863" s="7">
@@ -31453,7 +31489,7 @@
         <v>2</v>
       </c>
       <c r="F864" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4104</v>
       </c>
       <c r="G864" s="7">
@@ -31483,7 +31519,7 @@
         <v>2</v>
       </c>
       <c r="F865" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4116</v>
       </c>
       <c r="G865" s="7">
@@ -31513,7 +31549,7 @@
         <v>2</v>
       </c>
       <c r="F866" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4128</v>
       </c>
       <c r="G866" s="7">
@@ -31543,7 +31579,7 @@
         <v>2</v>
       </c>
       <c r="F867" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4140</v>
       </c>
       <c r="G867" s="7">
@@ -31573,7 +31609,7 @@
         <v>2</v>
       </c>
       <c r="F868" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4152</v>
       </c>
       <c r="G868" s="7">
@@ -31603,7 +31639,7 @@
         <v>2</v>
       </c>
       <c r="F869" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4164</v>
       </c>
       <c r="G869" s="7">
@@ -31633,7 +31669,7 @@
         <v>2</v>
       </c>
       <c r="F870" s="7">
-        <f t="shared" ref="F870:F933" si="19">(C870-2000)*12</f>
+        <f t="shared" ref="F870:F933" si="20">(C870-2000)*12</f>
         <v>4176</v>
       </c>
       <c r="G870" s="7">
@@ -31663,7 +31699,7 @@
         <v>2</v>
       </c>
       <c r="F871" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4188</v>
       </c>
       <c r="G871" s="7">
@@ -31693,7 +31729,7 @@
         <v>2</v>
       </c>
       <c r="F872" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4200</v>
       </c>
       <c r="G872" s="4">
@@ -31723,7 +31759,7 @@
         <v>2</v>
       </c>
       <c r="F873" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4212</v>
       </c>
       <c r="G873" s="7">
@@ -31753,7 +31789,7 @@
         <v>2</v>
       </c>
       <c r="F874" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4224</v>
       </c>
       <c r="G874" s="7">
@@ -31783,7 +31819,7 @@
         <v>2</v>
       </c>
       <c r="F875" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4236</v>
       </c>
       <c r="G875" s="7">
@@ -31813,7 +31849,7 @@
         <v>2</v>
       </c>
       <c r="F876" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4248</v>
       </c>
       <c r="G876" s="7">
@@ -31843,7 +31879,7 @@
         <v>2</v>
       </c>
       <c r="F877" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4260</v>
       </c>
       <c r="G877" s="7">
@@ -31873,7 +31909,7 @@
         <v>2</v>
       </c>
       <c r="F878" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4272</v>
       </c>
       <c r="G878" s="7">
@@ -31903,7 +31939,7 @@
         <v>2</v>
       </c>
       <c r="F879" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4284</v>
       </c>
       <c r="G879" s="7">
@@ -31933,7 +31969,7 @@
         <v>2</v>
       </c>
       <c r="F880" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4296</v>
       </c>
       <c r="G880" s="7">
@@ -31963,7 +31999,7 @@
         <v>2</v>
       </c>
       <c r="F881" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4308</v>
       </c>
       <c r="G881" s="7">
@@ -31993,7 +32029,7 @@
         <v>2</v>
       </c>
       <c r="F882" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4320</v>
       </c>
       <c r="G882" s="7">
@@ -32023,7 +32059,7 @@
         <v>2</v>
       </c>
       <c r="F883" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4332</v>
       </c>
       <c r="G883" s="7">
@@ -32053,7 +32089,7 @@
         <v>2</v>
       </c>
       <c r="F884" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4344</v>
       </c>
       <c r="G884" s="7">
@@ -32083,7 +32119,7 @@
         <v>2</v>
       </c>
       <c r="F885" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4356</v>
       </c>
       <c r="G885" s="7">
@@ -32113,7 +32149,7 @@
         <v>2</v>
       </c>
       <c r="F886" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4368</v>
       </c>
       <c r="G886" s="7">
@@ -32143,7 +32179,7 @@
         <v>2</v>
       </c>
       <c r="F887" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4380</v>
       </c>
       <c r="G887" s="4">
@@ -32173,7 +32209,7 @@
         <v>2</v>
       </c>
       <c r="F888" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4392</v>
       </c>
       <c r="G888" s="7">
@@ -32203,7 +32239,7 @@
         <v>2</v>
       </c>
       <c r="F889" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4404</v>
       </c>
       <c r="G889" s="7">
@@ -32233,7 +32269,7 @@
         <v>2</v>
       </c>
       <c r="F890" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4416</v>
       </c>
       <c r="G890" s="7">
@@ -32263,7 +32299,7 @@
         <v>2</v>
       </c>
       <c r="F891" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4428</v>
       </c>
       <c r="G891" s="7">
@@ -32293,7 +32329,7 @@
         <v>2</v>
       </c>
       <c r="F892" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4440</v>
       </c>
       <c r="G892" s="7">
@@ -32323,7 +32359,7 @@
         <v>2</v>
       </c>
       <c r="F893" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4452</v>
       </c>
       <c r="G893" s="7">
@@ -32353,7 +32389,7 @@
         <v>2</v>
       </c>
       <c r="F894" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4464</v>
       </c>
       <c r="G894" s="7">
@@ -32383,7 +32419,7 @@
         <v>2</v>
       </c>
       <c r="F895" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4476</v>
       </c>
       <c r="G895" s="7">
@@ -32413,7 +32449,7 @@
         <v>2</v>
       </c>
       <c r="F896" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4488</v>
       </c>
       <c r="G896" s="7">
@@ -32443,7 +32479,7 @@
         <v>2</v>
       </c>
       <c r="F897" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4500</v>
       </c>
       <c r="G897" s="7">
@@ -32473,7 +32509,7 @@
         <v>2</v>
       </c>
       <c r="F898" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4512</v>
       </c>
       <c r="G898" s="7">
@@ -32503,7 +32539,7 @@
         <v>2</v>
       </c>
       <c r="F899" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4524</v>
       </c>
       <c r="G899" s="7">
@@ -32533,7 +32569,7 @@
         <v>2</v>
       </c>
       <c r="F900" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4536</v>
       </c>
       <c r="G900" s="7">
@@ -32563,7 +32599,7 @@
         <v>2</v>
       </c>
       <c r="F901" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4548</v>
       </c>
       <c r="G901" s="7">
@@ -32593,7 +32629,7 @@
         <v>2</v>
       </c>
       <c r="F902" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4560</v>
       </c>
       <c r="G902" s="4">
@@ -32623,7 +32659,7 @@
         <v>2</v>
       </c>
       <c r="F903" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4572</v>
       </c>
       <c r="G903" s="7">
@@ -32653,7 +32689,7 @@
         <v>2</v>
       </c>
       <c r="F904" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4584</v>
       </c>
       <c r="G904" s="7">
@@ -32683,7 +32719,7 @@
         <v>2</v>
       </c>
       <c r="F905" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4596</v>
       </c>
       <c r="G905" s="7">
@@ -32713,7 +32749,7 @@
         <v>2</v>
       </c>
       <c r="F906" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4608</v>
       </c>
       <c r="G906" s="7">
@@ -32743,7 +32779,7 @@
         <v>2</v>
       </c>
       <c r="F907" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4620</v>
       </c>
       <c r="G907" s="7">
@@ -32773,7 +32809,7 @@
         <v>2</v>
       </c>
       <c r="F908" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4632</v>
       </c>
       <c r="G908" s="7">
@@ -32803,7 +32839,7 @@
         <v>2</v>
       </c>
       <c r="F909" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4644</v>
       </c>
       <c r="G909" s="7">
@@ -32833,7 +32869,7 @@
         <v>2</v>
       </c>
       <c r="F910" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4656</v>
       </c>
       <c r="G910" s="7">
@@ -32863,7 +32899,7 @@
         <v>2</v>
       </c>
       <c r="F911" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4668</v>
       </c>
       <c r="G911" s="7">
@@ -32893,7 +32929,7 @@
         <v>2</v>
       </c>
       <c r="F912" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4680</v>
       </c>
       <c r="G912" s="7">
@@ -32923,7 +32959,7 @@
         <v>2</v>
       </c>
       <c r="F913" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4692</v>
       </c>
       <c r="G913" s="7">
@@ -32953,7 +32989,7 @@
         <v>2</v>
       </c>
       <c r="F914" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4704</v>
       </c>
       <c r="G914" s="7">
@@ -32983,7 +33019,7 @@
         <v>2</v>
       </c>
       <c r="F915" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4716</v>
       </c>
       <c r="G915" s="7">
@@ -33013,7 +33049,7 @@
         <v>2</v>
       </c>
       <c r="F916" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4728</v>
       </c>
       <c r="G916" s="7">
@@ -33043,7 +33079,7 @@
         <v>2</v>
       </c>
       <c r="F917" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4740</v>
       </c>
       <c r="G917" s="4">
@@ -33073,7 +33109,7 @@
         <v>2</v>
       </c>
       <c r="F918" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4752</v>
       </c>
       <c r="G918" s="7">
@@ -33103,7 +33139,7 @@
         <v>2</v>
       </c>
       <c r="F919" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4764</v>
       </c>
       <c r="G919" s="7">
@@ -33133,7 +33169,7 @@
         <v>2</v>
       </c>
       <c r="F920" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4776</v>
       </c>
       <c r="G920" s="7">
@@ -33163,7 +33199,7 @@
         <v>2</v>
       </c>
       <c r="F921" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4788</v>
       </c>
       <c r="G921" s="7">
@@ -33193,7 +33229,7 @@
         <v>2</v>
       </c>
       <c r="F922" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4800</v>
       </c>
       <c r="G922" s="7">
@@ -33223,7 +33259,7 @@
         <v>2</v>
       </c>
       <c r="F923" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4812</v>
       </c>
       <c r="G923" s="7">
@@ -33253,7 +33289,7 @@
         <v>2</v>
       </c>
       <c r="F924" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4824</v>
       </c>
       <c r="G924" s="7">
@@ -33283,7 +33319,7 @@
         <v>2</v>
       </c>
       <c r="F925" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4836</v>
       </c>
       <c r="G925" s="7">
@@ -33313,7 +33349,7 @@
         <v>2</v>
       </c>
       <c r="F926" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4848</v>
       </c>
       <c r="G926" s="7">
@@ -33343,7 +33379,7 @@
         <v>2</v>
       </c>
       <c r="F927" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4860</v>
       </c>
       <c r="G927" s="7">
@@ -33373,7 +33409,7 @@
         <v>2</v>
       </c>
       <c r="F928" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4872</v>
       </c>
       <c r="G928" s="7">
@@ -33403,7 +33439,7 @@
         <v>2</v>
       </c>
       <c r="F929" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4884</v>
       </c>
       <c r="G929" s="7">
@@ -33433,7 +33469,7 @@
         <v>2</v>
       </c>
       <c r="F930" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4896</v>
       </c>
       <c r="G930" s="7">
@@ -33463,7 +33499,7 @@
         <v>2</v>
       </c>
       <c r="F931" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4908</v>
       </c>
       <c r="G931" s="7">
@@ -33493,7 +33529,7 @@
         <v>2</v>
       </c>
       <c r="F932" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4920</v>
       </c>
       <c r="G932" s="4">
@@ -33523,7 +33559,7 @@
         <v>2</v>
       </c>
       <c r="F933" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4932</v>
       </c>
       <c r="G933" s="7">
@@ -33553,7 +33589,7 @@
         <v>2</v>
       </c>
       <c r="F934" s="7">
-        <f t="shared" ref="F934:F997" si="20">(C934-2000)*12</f>
+        <f t="shared" ref="F934:F997" si="21">(C934-2000)*12</f>
         <v>4944</v>
       </c>
       <c r="G934" s="7">
@@ -33583,7 +33619,7 @@
         <v>2</v>
       </c>
       <c r="F935" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4956</v>
       </c>
       <c r="G935" s="7">
@@ -33613,7 +33649,7 @@
         <v>2</v>
       </c>
       <c r="F936" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4968</v>
       </c>
       <c r="G936" s="7">
@@ -33643,7 +33679,7 @@
         <v>2</v>
       </c>
       <c r="F937" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4980</v>
       </c>
       <c r="G937" s="7">
@@ -33673,7 +33709,7 @@
         <v>2</v>
       </c>
       <c r="F938" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4992</v>
       </c>
       <c r="G938" s="7">
@@ -33703,7 +33739,7 @@
         <v>2</v>
       </c>
       <c r="F939" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5004</v>
       </c>
       <c r="G939" s="7">
@@ -33733,7 +33769,7 @@
         <v>2</v>
       </c>
       <c r="F940" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5016</v>
       </c>
       <c r="G940" s="7">
@@ -33763,7 +33799,7 @@
         <v>2</v>
       </c>
       <c r="F941" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5028</v>
       </c>
       <c r="G941" s="7">
@@ -33793,7 +33829,7 @@
         <v>2</v>
       </c>
       <c r="F942" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5040</v>
       </c>
       <c r="G942" s="7">
@@ -33823,7 +33859,7 @@
         <v>2</v>
       </c>
       <c r="F943" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5052</v>
       </c>
       <c r="G943" s="7">
@@ -33853,7 +33889,7 @@
         <v>2</v>
       </c>
       <c r="F944" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5064</v>
       </c>
       <c r="G944" s="7">
@@ -33883,7 +33919,7 @@
         <v>2</v>
       </c>
       <c r="F945" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5076</v>
       </c>
       <c r="G945" s="7">
@@ -33913,7 +33949,7 @@
         <v>2</v>
       </c>
       <c r="F946" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5088</v>
       </c>
       <c r="G946" s="7">
@@ -33943,7 +33979,7 @@
         <v>2</v>
       </c>
       <c r="F947" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5100</v>
       </c>
       <c r="G947" s="4">
@@ -33973,7 +34009,7 @@
         <v>2</v>
       </c>
       <c r="F948" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5112</v>
       </c>
       <c r="G948" s="6">
@@ -34003,7 +34039,7 @@
         <v>2</v>
       </c>
       <c r="F949" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5124</v>
       </c>
       <c r="G949" s="6">
@@ -34033,7 +34069,7 @@
         <v>2</v>
       </c>
       <c r="F950" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5136</v>
       </c>
       <c r="G950" s="6">
@@ -34063,7 +34099,7 @@
         <v>2</v>
       </c>
       <c r="F951" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5148</v>
       </c>
       <c r="G951" s="6">
@@ -34093,7 +34129,7 @@
         <v>2</v>
       </c>
       <c r="F952" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5160</v>
       </c>
       <c r="G952" s="6">
@@ -34123,7 +34159,7 @@
         <v>2</v>
       </c>
       <c r="F953" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5172</v>
       </c>
       <c r="G953" s="6">
@@ -34153,7 +34189,7 @@
         <v>2</v>
       </c>
       <c r="F954" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5184</v>
       </c>
       <c r="G954" s="6">
@@ -34183,7 +34219,7 @@
         <v>2</v>
       </c>
       <c r="F955" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5196</v>
       </c>
       <c r="G955" s="6">
@@ -34213,7 +34249,7 @@
         <v>2</v>
       </c>
       <c r="F956" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5208</v>
       </c>
       <c r="G956" s="6">
@@ -34243,7 +34279,7 @@
         <v>2</v>
       </c>
       <c r="F957" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5220</v>
       </c>
       <c r="G957" s="6">
@@ -34273,7 +34309,7 @@
         <v>2</v>
       </c>
       <c r="F958" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5232</v>
       </c>
       <c r="G958" s="6">
@@ -34303,7 +34339,7 @@
         <v>2</v>
       </c>
       <c r="F959" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5244</v>
       </c>
       <c r="G959" s="6">
@@ -34333,7 +34369,7 @@
         <v>2</v>
       </c>
       <c r="F960" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5256</v>
       </c>
       <c r="G960" s="6">
@@ -34363,7 +34399,7 @@
         <v>2</v>
       </c>
       <c r="F961" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5268</v>
       </c>
       <c r="G961" s="6">
@@ -34393,7 +34429,7 @@
         <v>2</v>
       </c>
       <c r="F962" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5280</v>
       </c>
       <c r="G962" s="9">
@@ -34423,7 +34459,7 @@
         <v>2</v>
       </c>
       <c r="F963" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5292</v>
       </c>
       <c r="G963" s="6">
@@ -34453,7 +34489,7 @@
         <v>2</v>
       </c>
       <c r="F964" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5304</v>
       </c>
       <c r="G964" s="6">
@@ -34483,7 +34519,7 @@
         <v>2</v>
       </c>
       <c r="F965" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5316</v>
       </c>
       <c r="G965" s="6">
@@ -34513,7 +34549,7 @@
         <v>2</v>
       </c>
       <c r="F966" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5328</v>
       </c>
       <c r="G966" s="6">
@@ -34543,7 +34579,7 @@
         <v>2</v>
       </c>
       <c r="F967" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5340</v>
       </c>
       <c r="G967" s="6">
@@ -34573,7 +34609,7 @@
         <v>2</v>
       </c>
       <c r="F968" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5352</v>
       </c>
       <c r="G968" s="6">
@@ -34603,7 +34639,7 @@
         <v>2</v>
       </c>
       <c r="F969" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5364</v>
       </c>
       <c r="G969" s="6">
@@ -34633,7 +34669,7 @@
         <v>2</v>
       </c>
       <c r="F970" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5376</v>
       </c>
       <c r="G970" s="6">
@@ -34663,7 +34699,7 @@
         <v>2</v>
       </c>
       <c r="F971" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5388</v>
       </c>
       <c r="G971" s="6">
@@ -34693,7 +34729,7 @@
         <v>2</v>
       </c>
       <c r="F972" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5400</v>
       </c>
       <c r="G972" s="6">
@@ -34723,7 +34759,7 @@
         <v>2</v>
       </c>
       <c r="F973" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5412</v>
       </c>
       <c r="G973" s="6">
@@ -34753,7 +34789,7 @@
         <v>2</v>
       </c>
       <c r="F974" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5424</v>
       </c>
       <c r="G974" s="6">
@@ -34783,7 +34819,7 @@
         <v>2</v>
       </c>
       <c r="F975" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5436</v>
       </c>
       <c r="G975" s="6">
@@ -34813,7 +34849,7 @@
         <v>2</v>
       </c>
       <c r="F976" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5448</v>
       </c>
       <c r="G976" s="6">
@@ -34843,7 +34879,7 @@
         <v>2</v>
       </c>
       <c r="F977" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5460</v>
       </c>
       <c r="G977" s="9">
@@ -34873,7 +34909,7 @@
         <v>2</v>
       </c>
       <c r="F978" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5472</v>
       </c>
       <c r="G978" s="6">
@@ -34903,7 +34939,7 @@
         <v>2</v>
       </c>
       <c r="F979" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5484</v>
       </c>
       <c r="G979" s="6">
@@ -34933,7 +34969,7 @@
         <v>2</v>
       </c>
       <c r="F980" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5496</v>
       </c>
       <c r="G980" s="6">
@@ -34963,7 +34999,7 @@
         <v>2</v>
       </c>
       <c r="F981" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5508</v>
       </c>
       <c r="G981" s="6">
@@ -34993,7 +35029,7 @@
         <v>2</v>
       </c>
       <c r="F982" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5520</v>
       </c>
       <c r="G982" s="6">
@@ -35023,7 +35059,7 @@
         <v>2</v>
       </c>
       <c r="F983" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5532</v>
       </c>
       <c r="G983" s="6">
@@ -35053,7 +35089,7 @@
         <v>2</v>
       </c>
       <c r="F984" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5544</v>
       </c>
       <c r="G984" s="6">
@@ -35083,7 +35119,7 @@
         <v>2</v>
       </c>
       <c r="F985" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5556</v>
       </c>
       <c r="G985" s="6">
@@ -35113,7 +35149,7 @@
         <v>2</v>
       </c>
       <c r="F986" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5568</v>
       </c>
       <c r="G986" s="6">
@@ -35143,7 +35179,7 @@
         <v>2</v>
       </c>
       <c r="F987" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5580</v>
       </c>
       <c r="G987" s="6">
@@ -35173,7 +35209,7 @@
         <v>2</v>
       </c>
       <c r="F988" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5592</v>
       </c>
       <c r="G988" s="6">
@@ -35203,7 +35239,7 @@
         <v>2</v>
       </c>
       <c r="F989" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5604</v>
       </c>
       <c r="G989" s="6">
@@ -35233,7 +35269,7 @@
         <v>2</v>
       </c>
       <c r="F990" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5616</v>
       </c>
       <c r="G990" s="6">
@@ -35263,7 +35299,7 @@
         <v>2</v>
       </c>
       <c r="F991" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5628</v>
       </c>
       <c r="G991" s="6">
@@ -35293,7 +35329,7 @@
         <v>2</v>
       </c>
       <c r="F992" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5640</v>
       </c>
       <c r="G992" s="9">
@@ -35323,7 +35359,7 @@
         <v>2</v>
       </c>
       <c r="F993" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5652</v>
       </c>
       <c r="G993" s="6">
@@ -35353,7 +35389,7 @@
         <v>2</v>
       </c>
       <c r="F994" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5664</v>
       </c>
       <c r="G994" s="6">
@@ -35383,7 +35419,7 @@
         <v>2</v>
       </c>
       <c r="F995" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5676</v>
       </c>
       <c r="G995" s="6">
@@ -35413,7 +35449,7 @@
         <v>2</v>
       </c>
       <c r="F996" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5688</v>
       </c>
       <c r="G996" s="6">
@@ -35443,7 +35479,7 @@
         <v>2</v>
       </c>
       <c r="F997" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5700</v>
       </c>
       <c r="G997" s="6">
@@ -35473,7 +35509,7 @@
         <v>2</v>
       </c>
       <c r="F998" s="6">
-        <f t="shared" ref="F998:F1007" si="21">(C998-2000)*12</f>
+        <f t="shared" ref="F998:F1007" si="22">(C998-2000)*12</f>
         <v>5712</v>
       </c>
       <c r="G998" s="6">
@@ -35503,7 +35539,7 @@
         <v>2</v>
       </c>
       <c r="F999" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5724</v>
       </c>
       <c r="G999" s="6">
@@ -35533,7 +35569,7 @@
         <v>2</v>
       </c>
       <c r="F1000" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5736</v>
       </c>
       <c r="G1000" s="6">
@@ -35563,7 +35599,7 @@
         <v>2</v>
       </c>
       <c r="F1001" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5748</v>
       </c>
       <c r="G1001" s="6">
@@ -35593,7 +35629,7 @@
         <v>2</v>
       </c>
       <c r="F1002" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5760</v>
       </c>
       <c r="G1002" s="6">
@@ -35623,7 +35659,7 @@
         <v>2</v>
       </c>
       <c r="F1003" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5772</v>
       </c>
       <c r="G1003" s="6">
@@ -35653,7 +35689,7 @@
         <v>2</v>
       </c>
       <c r="F1004" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5784</v>
       </c>
       <c r="G1004" s="6">
@@ -35683,7 +35719,7 @@
         <v>2</v>
       </c>
       <c r="F1005" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5796</v>
       </c>
       <c r="G1005" s="6">
@@ -35713,7 +35749,7 @@
         <v>2</v>
       </c>
       <c r="F1006" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5808</v>
       </c>
       <c r="G1006" s="6">
@@ -35743,7 +35779,7 @@
         <v>2</v>
       </c>
       <c r="F1007" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5820</v>
       </c>
       <c r="G1007" s="9">
@@ -35773,7 +35809,7 @@
         <v>2</v>
       </c>
       <c r="F1008" s="6">
-        <f t="shared" ref="F1008:F1037" si="22">(F1007)+36</f>
+        <f t="shared" ref="F1008:F1037" si="23">(F1007)+36</f>
         <v>5856</v>
       </c>
       <c r="G1008" s="6">
@@ -35803,7 +35839,7 @@
         <v>2</v>
       </c>
       <c r="F1009" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5892</v>
       </c>
       <c r="G1009" s="6">
@@ -35833,7 +35869,7 @@
         <v>2</v>
       </c>
       <c r="F1010" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5928</v>
       </c>
       <c r="G1010" s="6">
@@ -35863,7 +35899,7 @@
         <v>2</v>
       </c>
       <c r="F1011" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5964</v>
       </c>
       <c r="G1011" s="6">
@@ -35893,7 +35929,7 @@
         <v>2</v>
       </c>
       <c r="F1012" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6000</v>
       </c>
       <c r="G1012" s="6">
@@ -35923,7 +35959,7 @@
         <v>2</v>
       </c>
       <c r="F1013" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6036</v>
       </c>
       <c r="G1013" s="6">
@@ -35953,7 +35989,7 @@
         <v>2</v>
       </c>
       <c r="F1014" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6072</v>
       </c>
       <c r="G1014" s="6">
@@ -35983,7 +36019,7 @@
         <v>2</v>
       </c>
       <c r="F1015" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6108</v>
       </c>
       <c r="G1015" s="6">
@@ -36013,7 +36049,7 @@
         <v>2</v>
       </c>
       <c r="F1016" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6144</v>
       </c>
       <c r="G1016" s="6">
@@ -36043,7 +36079,7 @@
         <v>2</v>
       </c>
       <c r="F1017" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6180</v>
       </c>
       <c r="G1017" s="6">
@@ -36073,7 +36109,7 @@
         <v>2</v>
       </c>
       <c r="F1018" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6216</v>
       </c>
       <c r="G1018" s="6">
@@ -36103,7 +36139,7 @@
         <v>2</v>
       </c>
       <c r="F1019" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6252</v>
       </c>
       <c r="G1019" s="6">
@@ -36133,7 +36169,7 @@
         <v>2</v>
       </c>
       <c r="F1020" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6288</v>
       </c>
       <c r="G1020" s="6">
@@ -36163,7 +36199,7 @@
         <v>2</v>
       </c>
       <c r="F1021" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6324</v>
       </c>
       <c r="G1021" s="6">
@@ -36193,7 +36229,7 @@
         <v>2</v>
       </c>
       <c r="F1022" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6360</v>
       </c>
       <c r="G1022" s="9">
@@ -36223,7 +36259,7 @@
         <v>2</v>
       </c>
       <c r="F1023" s="6">
-        <f t="shared" ref="F1023:F1036" si="23">(F1022)+40</f>
+        <f t="shared" ref="F1023:F1037" si="24">(F1022)+40</f>
         <v>6400</v>
       </c>
       <c r="G1023" s="6">
@@ -36253,7 +36289,7 @@
         <v>2</v>
       </c>
       <c r="F1024" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6440</v>
       </c>
       <c r="G1024" s="6">
@@ -36283,7 +36319,7 @@
         <v>2</v>
       </c>
       <c r="F1025" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6480</v>
       </c>
       <c r="G1025" s="6">
@@ -36313,7 +36349,7 @@
         <v>2</v>
       </c>
       <c r="F1026" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6520</v>
       </c>
       <c r="G1026" s="6">
@@ -36343,7 +36379,7 @@
         <v>2</v>
       </c>
       <c r="F1027" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6560</v>
       </c>
       <c r="G1027" s="6">
@@ -36373,7 +36409,7 @@
         <v>2</v>
       </c>
       <c r="F1028" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6600</v>
       </c>
       <c r="G1028" s="6">
@@ -36403,7 +36439,7 @@
         <v>2</v>
       </c>
       <c r="F1029" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6640</v>
       </c>
       <c r="G1029" s="6">
@@ -36433,7 +36469,7 @@
         <v>2</v>
       </c>
       <c r="F1030" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6680</v>
       </c>
       <c r="G1030" s="6">
@@ -36463,7 +36499,7 @@
         <v>2</v>
       </c>
       <c r="F1031" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6720</v>
       </c>
       <c r="G1031" s="6">
@@ -36493,7 +36529,7 @@
         <v>2</v>
       </c>
       <c r="F1032" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6760</v>
       </c>
       <c r="G1032" s="6">
@@ -36523,7 +36559,7 @@
         <v>2</v>
       </c>
       <c r="F1033" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6800</v>
       </c>
       <c r="G1033" s="6">
@@ -36553,7 +36589,7 @@
         <v>2</v>
       </c>
       <c r="F1034" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6840</v>
       </c>
       <c r="G1034" s="6">
@@ -36583,7 +36619,7 @@
         <v>2</v>
       </c>
       <c r="F1035" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6880</v>
       </c>
       <c r="G1035" s="6">
@@ -36613,7 +36649,7 @@
         <v>2</v>
       </c>
       <c r="F1036" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6920</v>
       </c>
       <c r="G1036" s="6">
@@ -36643,7 +36679,7 @@
         <v>2</v>
       </c>
       <c r="F1037" s="9">
-        <f>(F1036)+40</f>
+        <f t="shared" si="24"/>
         <v>6960</v>
       </c>
       <c r="G1037" s="9">
@@ -37141,7 +37177,7 @@
         <v>3</v>
       </c>
       <c r="F1063" s="7">
-        <f t="shared" ref="F1063:F1082" si="24">F1062+30000</f>
+        <f t="shared" ref="F1063:F1082" si="25">F1062+30000</f>
         <v>330000</v>
       </c>
       <c r="G1063" s="7">
@@ -37168,7 +37204,7 @@
         <v>3</v>
       </c>
       <c r="F1064" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>360000</v>
       </c>
       <c r="G1064" s="7">
@@ -37195,7 +37231,7 @@
         <v>3</v>
       </c>
       <c r="F1065" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>390000</v>
       </c>
       <c r="G1065" s="7">
@@ -37222,7 +37258,7 @@
         <v>3</v>
       </c>
       <c r="F1066" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>420000</v>
       </c>
       <c r="G1066" s="7">
@@ -37249,7 +37285,7 @@
         <v>3</v>
       </c>
       <c r="F1067" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>450000</v>
       </c>
       <c r="G1067" s="7">
@@ -37276,7 +37312,7 @@
         <v>3</v>
       </c>
       <c r="F1068" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>480000</v>
       </c>
       <c r="G1068" s="7">
@@ -37303,7 +37339,7 @@
         <v>3</v>
       </c>
       <c r="F1069" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>510000</v>
       </c>
       <c r="G1069" s="7">
@@ -37330,7 +37366,7 @@
         <v>3</v>
       </c>
       <c r="F1070" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>540000</v>
       </c>
       <c r="G1070" s="7">
@@ -37357,7 +37393,7 @@
         <v>3</v>
       </c>
       <c r="F1071" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>570000</v>
       </c>
       <c r="G1071" s="7">
@@ -37384,7 +37420,7 @@
         <v>3</v>
       </c>
       <c r="F1072" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>600000</v>
       </c>
       <c r="G1072" s="7">
@@ -37411,7 +37447,7 @@
         <v>3</v>
       </c>
       <c r="F1073" s="7">
-        <f t="shared" ref="F1073:F1082" si="25">F1072+40000</f>
+        <f t="shared" ref="F1073:F1082" si="26">F1072+40000</f>
         <v>640000</v>
       </c>
       <c r="G1073" s="7">
@@ -37438,7 +37474,7 @@
         <v>3</v>
       </c>
       <c r="F1074" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>680000</v>
       </c>
       <c r="G1074" s="7">
@@ -37465,7 +37501,7 @@
         <v>3</v>
       </c>
       <c r="F1075" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>720000</v>
       </c>
       <c r="G1075" s="7">
@@ -37492,7 +37528,7 @@
         <v>3</v>
       </c>
       <c r="F1076" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>760000</v>
       </c>
       <c r="G1076" s="7">
@@ -37519,7 +37555,7 @@
         <v>3</v>
       </c>
       <c r="F1077" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>800000</v>
       </c>
       <c r="G1077" s="7">
@@ -37546,7 +37582,7 @@
         <v>3</v>
       </c>
       <c r="F1078" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>840000</v>
       </c>
       <c r="G1078" s="7">
@@ -37573,7 +37609,7 @@
         <v>3</v>
       </c>
       <c r="F1079" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>880000</v>
       </c>
       <c r="G1079" s="7">
@@ -37600,7 +37636,7 @@
         <v>3</v>
       </c>
       <c r="F1080" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>920000</v>
       </c>
       <c r="G1080" s="7">
@@ -37627,7 +37663,7 @@
         <v>3</v>
       </c>
       <c r="F1081" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>960000</v>
       </c>
       <c r="G1081" s="7">
@@ -37654,7 +37690,7 @@
         <v>3</v>
       </c>
       <c r="F1082" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1000000</v>
       </c>
       <c r="G1082" s="7">
@@ -38071,7 +38107,7 @@
         <v>4</v>
       </c>
       <c r="F1100" s="7">
-        <f t="shared" ref="F1100:F1109" si="26">F1099+250</f>
+        <f t="shared" ref="F1100:F1109" si="27">F1099+250</f>
         <v>3000</v>
       </c>
       <c r="G1100" s="7">
@@ -38098,7 +38134,7 @@
         <v>4</v>
       </c>
       <c r="F1101" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3250</v>
       </c>
       <c r="G1101" s="7">
@@ -38125,7 +38161,7 @@
         <v>4</v>
       </c>
       <c r="F1102" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3500</v>
       </c>
       <c r="G1102" s="7">
@@ -38152,7 +38188,7 @@
         <v>4</v>
       </c>
       <c r="F1103" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3750</v>
       </c>
       <c r="G1103" s="7">
@@ -38179,7 +38215,7 @@
         <v>4</v>
       </c>
       <c r="F1104" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4000</v>
       </c>
       <c r="G1104" s="7">
@@ -38206,7 +38242,7 @@
         <v>4</v>
       </c>
       <c r="F1105" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4250</v>
       </c>
       <c r="G1105" s="7">
@@ -38233,7 +38269,7 @@
         <v>4</v>
       </c>
       <c r="F1106" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4500</v>
       </c>
       <c r="G1106" s="7">
@@ -38260,7 +38296,7 @@
         <v>4</v>
       </c>
       <c r="F1107" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4750</v>
       </c>
       <c r="G1107" s="7">
@@ -38287,7 +38323,7 @@
         <v>4</v>
       </c>
       <c r="F1108" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5000</v>
       </c>
       <c r="G1108" s="7">
@@ -38314,7 +38350,7 @@
         <v>4</v>
       </c>
       <c r="F1109" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5250</v>
       </c>
       <c r="G1109" s="7">
@@ -38341,7 +38377,7 @@
         <v>5</v>
       </c>
       <c r="F1111" s="7">
-        <f t="shared" ref="F1111:F1120" si="27">(C1111-5000)*1000</f>
+        <f t="shared" ref="F1111:F1120" si="28">(C1111-5000)*1000</f>
         <v>1000</v>
       </c>
       <c r="G1111" s="7">
@@ -38368,7 +38404,7 @@
         <v>5</v>
       </c>
       <c r="F1112" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2000</v>
       </c>
       <c r="G1112" s="7">
@@ -38395,7 +38431,7 @@
         <v>5</v>
       </c>
       <c r="F1113" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3000</v>
       </c>
       <c r="G1113" s="7">
@@ -38422,7 +38458,7 @@
         <v>5</v>
       </c>
       <c r="F1114" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4000</v>
       </c>
       <c r="G1114" s="7">
@@ -38449,7 +38485,7 @@
         <v>5</v>
       </c>
       <c r="F1115" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5000</v>
       </c>
       <c r="G1115" s="7">
@@ -38476,7 +38512,7 @@
         <v>5</v>
       </c>
       <c r="F1116" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6000</v>
       </c>
       <c r="G1116" s="7">
@@ -38503,7 +38539,7 @@
         <v>5</v>
       </c>
       <c r="F1117" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7000</v>
       </c>
       <c r="G1117" s="7">
@@ -38530,7 +38566,7 @@
         <v>5</v>
       </c>
       <c r="F1118" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8000</v>
       </c>
       <c r="G1118" s="7">
@@ -38557,7 +38593,7 @@
         <v>5</v>
       </c>
       <c r="F1119" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>9000</v>
       </c>
       <c r="G1119" s="7">
@@ -38584,7 +38620,7 @@
         <v>5</v>
       </c>
       <c r="F1120" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>10000</v>
       </c>
       <c r="G1120" s="7">
@@ -38611,7 +38647,7 @@
         <v>5</v>
       </c>
       <c r="F1121" s="7">
-        <f t="shared" ref="F1121:F1136" si="28">F1120+1000</f>
+        <f t="shared" ref="F1121:F1136" si="29">F1120+1000</f>
         <v>11000</v>
       </c>
       <c r="G1121" s="7">
@@ -38638,7 +38674,7 @@
         <v>5</v>
       </c>
       <c r="F1122" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>12000</v>
       </c>
       <c r="G1122" s="7">
@@ -38665,7 +38701,7 @@
         <v>5</v>
       </c>
       <c r="F1123" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>13000</v>
       </c>
       <c r="G1123" s="7">
@@ -38692,7 +38728,7 @@
         <v>5</v>
       </c>
       <c r="F1124" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>14000</v>
       </c>
       <c r="G1124" s="7">
@@ -38719,7 +38755,7 @@
         <v>5</v>
       </c>
       <c r="F1125" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>15000</v>
       </c>
       <c r="G1125" s="7">
@@ -38746,7 +38782,7 @@
         <v>5</v>
       </c>
       <c r="F1126" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>16000</v>
       </c>
       <c r="G1126" s="7">
@@ -38773,7 +38809,7 @@
         <v>5</v>
       </c>
       <c r="F1127" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>17000</v>
       </c>
       <c r="G1127" s="7">
@@ -38800,7 +38836,7 @@
         <v>5</v>
       </c>
       <c r="F1128" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>18000</v>
       </c>
       <c r="G1128" s="7">
@@ -38827,7 +38863,7 @@
         <v>5</v>
       </c>
       <c r="F1129" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>19000</v>
       </c>
       <c r="G1129" s="7">
@@ -38854,7 +38890,7 @@
         <v>5</v>
       </c>
       <c r="F1130" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>20000</v>
       </c>
       <c r="G1130" s="7">
@@ -38881,7 +38917,7 @@
         <v>5</v>
       </c>
       <c r="F1131" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>21000</v>
       </c>
       <c r="G1131" s="7">
@@ -38908,7 +38944,7 @@
         <v>5</v>
       </c>
       <c r="F1132" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>22000</v>
       </c>
       <c r="G1132" s="7">
@@ -38935,7 +38971,7 @@
         <v>5</v>
       </c>
       <c r="F1133" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>23000</v>
       </c>
       <c r="G1133" s="7">
@@ -38962,7 +38998,7 @@
         <v>5</v>
       </c>
       <c r="F1134" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>24000</v>
       </c>
       <c r="G1134" s="7">
@@ -38989,7 +39025,7 @@
         <v>5</v>
       </c>
       <c r="F1135" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>25000</v>
       </c>
       <c r="G1135" s="7">
@@ -39016,7 +39052,7 @@
         <v>5</v>
       </c>
       <c r="F1136" s="7">
-        <f t="shared" ref="F1136:F1155" si="29">F1135+2000</f>
+        <f t="shared" ref="F1136:F1155" si="30">F1135+2000</f>
         <v>27000</v>
       </c>
       <c r="G1136" s="7">
@@ -39043,7 +39079,7 @@
         <v>5</v>
       </c>
       <c r="F1137" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>29000</v>
       </c>
       <c r="G1137" s="7">
@@ -39070,7 +39106,7 @@
         <v>5</v>
       </c>
       <c r="F1138" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>31000</v>
       </c>
       <c r="G1138" s="7">
@@ -39097,7 +39133,7 @@
         <v>5</v>
       </c>
       <c r="F1139" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>33000</v>
       </c>
       <c r="G1139" s="7">
@@ -39124,7 +39160,7 @@
         <v>5</v>
       </c>
       <c r="F1140" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>35000</v>
       </c>
       <c r="G1140" s="7">
@@ -39151,7 +39187,7 @@
         <v>5</v>
       </c>
       <c r="F1141" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>37000</v>
       </c>
       <c r="G1141" s="7">
@@ -39178,7 +39214,7 @@
         <v>5</v>
       </c>
       <c r="F1142" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>39000</v>
       </c>
       <c r="G1142" s="7">
@@ -39205,7 +39241,7 @@
         <v>5</v>
       </c>
       <c r="F1143" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>41000</v>
       </c>
       <c r="G1143" s="7">
@@ -39232,7 +39268,7 @@
         <v>5</v>
       </c>
       <c r="F1144" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>43000</v>
       </c>
       <c r="G1144" s="7">
@@ -39259,7 +39295,7 @@
         <v>5</v>
       </c>
       <c r="F1145" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>45000</v>
       </c>
       <c r="G1145" s="7">
@@ -39286,7 +39322,7 @@
         <v>5</v>
       </c>
       <c r="F1146" s="7">
-        <f t="shared" ref="F1146:F1162" si="30">F1145+3000</f>
+        <f t="shared" ref="F1146:F1162" si="31">F1145+3000</f>
         <v>48000</v>
       </c>
       <c r="G1146" s="7">
@@ -39313,7 +39349,7 @@
         <v>5</v>
       </c>
       <c r="F1147" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>51000</v>
       </c>
       <c r="G1147" s="7">
@@ -39340,7 +39376,7 @@
         <v>5</v>
       </c>
       <c r="F1148" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>54000</v>
       </c>
       <c r="G1148" s="7">
@@ -39367,7 +39403,7 @@
         <v>5</v>
       </c>
       <c r="F1149" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>57000</v>
       </c>
       <c r="G1149" s="7">
@@ -39394,7 +39430,7 @@
         <v>5</v>
       </c>
       <c r="F1150" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>60000</v>
       </c>
       <c r="G1150" s="7">
@@ -39421,7 +39457,7 @@
         <v>5</v>
       </c>
       <c r="F1151" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>63000</v>
       </c>
       <c r="G1151" s="7">
@@ -39448,7 +39484,7 @@
         <v>5</v>
       </c>
       <c r="F1152" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>66000</v>
       </c>
       <c r="G1152" s="7">
@@ -39475,7 +39511,7 @@
         <v>5</v>
       </c>
       <c r="F1153" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>69000</v>
       </c>
       <c r="G1153" s="7">
@@ -39502,7 +39538,7 @@
         <v>5</v>
       </c>
       <c r="F1154" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>72000</v>
       </c>
       <c r="G1154" s="7">
@@ -39529,7 +39565,7 @@
         <v>5</v>
       </c>
       <c r="F1155" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>75000</v>
       </c>
       <c r="G1155" s="7">
@@ -39556,7 +39592,7 @@
         <v>5</v>
       </c>
       <c r="F1156" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>78000</v>
       </c>
       <c r="G1156" s="7">
@@ -39583,7 +39619,7 @@
         <v>5</v>
       </c>
       <c r="F1157" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>81000</v>
       </c>
       <c r="G1157" s="7">
@@ -39610,7 +39646,7 @@
         <v>5</v>
       </c>
       <c r="F1158" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>84000</v>
       </c>
       <c r="G1158" s="7">
@@ -39637,7 +39673,7 @@
         <v>5</v>
       </c>
       <c r="F1159" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>87000</v>
       </c>
       <c r="G1159" s="7">
@@ -39664,7 +39700,7 @@
         <v>5</v>
       </c>
       <c r="F1160" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>90000</v>
       </c>
       <c r="G1160" s="7">
@@ -39691,7 +39727,7 @@
         <v>5</v>
       </c>
       <c r="F1161" s="7">
-        <f t="shared" ref="F1161:F1165" si="31">F1160+4000</f>
+        <f t="shared" ref="F1161:F1165" si="32">F1160+4000</f>
         <v>94000</v>
       </c>
       <c r="G1161" s="7">
@@ -39718,7 +39754,7 @@
         <v>5</v>
       </c>
       <c r="F1162" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>98000</v>
       </c>
       <c r="G1162" s="7">
@@ -39745,7 +39781,7 @@
         <v>5</v>
       </c>
       <c r="F1163" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>102000</v>
       </c>
       <c r="G1163" s="7">
@@ -39772,7 +39808,7 @@
         <v>5</v>
       </c>
       <c r="F1164" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>106000</v>
       </c>
       <c r="G1164" s="7">
@@ -39799,7 +39835,7 @@
         <v>5</v>
       </c>
       <c r="F1165" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>110000</v>
       </c>
       <c r="G1165" s="7">
@@ -40346,7 +40382,7 @@
         <v>6</v>
       </c>
       <c r="F1187" s="7">
-        <f t="shared" ref="F1187:F1201" si="32">F1186+100</f>
+        <f t="shared" ref="F1187:F1201" si="33">F1186+100</f>
         <v>2100</v>
       </c>
       <c r="G1187" s="7">
@@ -40373,7 +40409,7 @@
         <v>6</v>
       </c>
       <c r="F1188" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2200</v>
       </c>
       <c r="G1188" s="7">
@@ -40400,7 +40436,7 @@
         <v>6</v>
       </c>
       <c r="F1189" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2300</v>
       </c>
       <c r="G1189" s="7">
@@ -40427,7 +40463,7 @@
         <v>6</v>
       </c>
       <c r="F1190" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2400</v>
       </c>
       <c r="G1190" s="7">
@@ -40454,7 +40490,7 @@
         <v>6</v>
       </c>
       <c r="F1191" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2500</v>
       </c>
       <c r="G1191" s="7">
@@ -40481,7 +40517,7 @@
         <v>6</v>
       </c>
       <c r="F1192" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2600</v>
       </c>
       <c r="G1192" s="7">
@@ -40508,7 +40544,7 @@
         <v>6</v>
       </c>
       <c r="F1193" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2700</v>
       </c>
       <c r="G1193" s="7">
@@ -40535,7 +40571,7 @@
         <v>6</v>
       </c>
       <c r="F1194" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2800</v>
       </c>
       <c r="G1194" s="7">
@@ -40562,7 +40598,7 @@
         <v>6</v>
       </c>
       <c r="F1195" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2900</v>
       </c>
       <c r="G1195" s="7">
@@ -40589,7 +40625,7 @@
         <v>6</v>
       </c>
       <c r="F1196" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3000</v>
       </c>
       <c r="G1196" s="7">
@@ -40751,7 +40787,7 @@
         <v>6</v>
       </c>
       <c r="F1202" s="7">
-        <f t="shared" ref="F1202:F1211" si="33">F1201+300</f>
+        <f t="shared" ref="F1202:F1211" si="34">F1201+300</f>
         <v>4300</v>
       </c>
       <c r="G1202" s="7">
@@ -40778,7 +40814,7 @@
         <v>6</v>
       </c>
       <c r="F1203" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4600</v>
       </c>
       <c r="G1203" s="7">
@@ -40805,7 +40841,7 @@
         <v>6</v>
       </c>
       <c r="F1204" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4900</v>
       </c>
       <c r="G1204" s="7">
@@ -40832,7 +40868,7 @@
         <v>6</v>
       </c>
       <c r="F1205" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5200</v>
       </c>
       <c r="G1205" s="7">
@@ -40859,7 +40895,7 @@
         <v>6</v>
       </c>
       <c r="F1206" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5500</v>
       </c>
       <c r="G1206" s="7">
@@ -40886,7 +40922,7 @@
         <v>6</v>
       </c>
       <c r="F1207" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5800</v>
       </c>
       <c r="G1207" s="7">
@@ -40913,7 +40949,7 @@
         <v>6</v>
       </c>
       <c r="F1208" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6100</v>
       </c>
       <c r="G1208" s="7">
@@ -40940,7 +40976,7 @@
         <v>6</v>
       </c>
       <c r="F1209" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6400</v>
       </c>
       <c r="G1209" s="7">
@@ -40967,7 +41003,7 @@
         <v>6</v>
       </c>
       <c r="F1210" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6700</v>
       </c>
       <c r="G1210" s="7">
@@ -40994,7 +41030,7 @@
         <v>6</v>
       </c>
       <c r="F1211" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>7000</v>
       </c>
       <c r="G1211" s="7">
@@ -41021,7 +41057,7 @@
         <v>6</v>
       </c>
       <c r="F1212" s="7">
-        <f t="shared" ref="F1212:F1231" si="34">F1211+400</f>
+        <f t="shared" ref="F1212:F1231" si="35">F1211+400</f>
         <v>7400</v>
       </c>
       <c r="G1212" s="7">
@@ -41048,7 +41084,7 @@
         <v>6</v>
       </c>
       <c r="F1213" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7800</v>
       </c>
       <c r="G1213" s="7">
@@ -41075,7 +41111,7 @@
         <v>6</v>
       </c>
       <c r="F1214" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>8200</v>
       </c>
       <c r="G1214" s="7">
@@ -41102,7 +41138,7 @@
         <v>6</v>
       </c>
       <c r="F1215" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>8600</v>
       </c>
       <c r="G1215" s="7">
@@ -41129,7 +41165,7 @@
         <v>6</v>
       </c>
       <c r="F1216" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9000</v>
       </c>
       <c r="G1216" s="7">
@@ -41156,7 +41192,7 @@
         <v>6</v>
       </c>
       <c r="F1217" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9400</v>
       </c>
       <c r="G1217" s="7">
@@ -41183,7 +41219,7 @@
         <v>6</v>
       </c>
       <c r="F1218" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9800</v>
       </c>
       <c r="G1218" s="7">
@@ -41210,7 +41246,7 @@
         <v>6</v>
       </c>
       <c r="F1219" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>10200</v>
       </c>
       <c r="G1219" s="7">
@@ -41237,7 +41273,7 @@
         <v>6</v>
       </c>
       <c r="F1220" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>10600</v>
       </c>
       <c r="G1220" s="7">
@@ -41264,7 +41300,7 @@
         <v>6</v>
       </c>
       <c r="F1221" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11000</v>
       </c>
       <c r="G1221" s="7">
@@ -41291,7 +41327,7 @@
         <v>6</v>
       </c>
       <c r="F1222" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11400</v>
       </c>
       <c r="G1222" s="7">
@@ -41318,7 +41354,7 @@
         <v>6</v>
       </c>
       <c r="F1223" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11800</v>
       </c>
       <c r="G1223" s="7">
@@ -41345,7 +41381,7 @@
         <v>6</v>
       </c>
       <c r="F1224" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>12200</v>
       </c>
       <c r="G1224" s="7">
@@ -41372,7 +41408,7 @@
         <v>6</v>
       </c>
       <c r="F1225" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>12600</v>
       </c>
       <c r="G1225" s="7">
@@ -41399,7 +41435,7 @@
         <v>6</v>
       </c>
       <c r="F1226" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>13000</v>
       </c>
       <c r="G1226" s="7">
@@ -41426,7 +41462,7 @@
         <v>6</v>
       </c>
       <c r="F1227" s="7">
-        <f t="shared" ref="F1227:F1236" si="35">F1226+500</f>
+        <f t="shared" ref="F1227:F1236" si="36">F1226+500</f>
         <v>13500</v>
       </c>
       <c r="G1227" s="7">
@@ -41453,7 +41489,7 @@
         <v>6</v>
       </c>
       <c r="F1228" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14000</v>
       </c>
       <c r="G1228" s="7">
@@ -41480,7 +41516,7 @@
         <v>6</v>
       </c>
       <c r="F1229" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14500</v>
       </c>
       <c r="G1229" s="7">
@@ -41507,7 +41543,7 @@
         <v>6</v>
       </c>
       <c r="F1230" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15000</v>
       </c>
       <c r="G1230" s="7">
@@ -41534,7 +41570,7 @@
         <v>6</v>
       </c>
       <c r="F1231" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15500</v>
       </c>
       <c r="G1231" s="7">
@@ -41561,7 +41597,7 @@
         <v>6</v>
       </c>
       <c r="F1232" s="7">
-        <f t="shared" ref="F1232:F1237" si="36">F1231+750</f>
+        <f t="shared" ref="F1232:F1237" si="37">F1231+750</f>
         <v>16250</v>
       </c>
       <c r="G1232" s="7">
@@ -41588,7 +41624,7 @@
         <v>6</v>
       </c>
       <c r="F1233" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>17000</v>
       </c>
       <c r="G1233" s="7">
@@ -41615,7 +41651,7 @@
         <v>6</v>
       </c>
       <c r="F1234" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>17750</v>
       </c>
       <c r="G1234" s="7">
@@ -41642,7 +41678,7 @@
         <v>6</v>
       </c>
       <c r="F1235" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>18500</v>
       </c>
       <c r="G1235" s="7">
@@ -41669,7 +41705,7 @@
         <v>6</v>
       </c>
       <c r="F1236" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>19250</v>
       </c>
       <c r="G1236" s="7">
@@ -41696,7 +41732,7 @@
         <v>6</v>
       </c>
       <c r="F1237" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>20000</v>
       </c>
       <c r="G1237" s="7">
@@ -41723,7 +41759,7 @@
         <v>6</v>
       </c>
       <c r="F1238" s="7">
-        <f t="shared" ref="F1238:F1257" si="37">F1237+1500</f>
+        <f t="shared" ref="F1238:F1257" si="38">F1237+1500</f>
         <v>21500</v>
       </c>
       <c r="G1238" s="7">
@@ -41750,7 +41786,7 @@
         <v>6</v>
       </c>
       <c r="F1239" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>23000</v>
       </c>
       <c r="G1239" s="7">
@@ -41777,7 +41813,7 @@
         <v>6</v>
       </c>
       <c r="F1240" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>24500</v>
       </c>
       <c r="G1240" s="7">
@@ -41804,7 +41840,7 @@
         <v>6</v>
       </c>
       <c r="F1241" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>26000</v>
       </c>
       <c r="G1241" s="7">
@@ -41831,7 +41867,7 @@
         <v>6</v>
       </c>
       <c r="F1242" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>27500</v>
       </c>
       <c r="G1242" s="7">
@@ -41858,7 +41894,7 @@
         <v>6</v>
       </c>
       <c r="F1243" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>29000</v>
       </c>
       <c r="G1243" s="7">
@@ -41885,7 +41921,7 @@
         <v>6</v>
       </c>
       <c r="F1244" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>30500</v>
       </c>
       <c r="G1244" s="7">
@@ -41912,7 +41948,7 @@
         <v>6</v>
       </c>
       <c r="F1245" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>32000</v>
       </c>
       <c r="G1245" s="7">
@@ -41939,7 +41975,7 @@
         <v>6</v>
       </c>
       <c r="F1246" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>33500</v>
       </c>
       <c r="G1246" s="7">
@@ -41966,7 +42002,7 @@
         <v>6</v>
       </c>
       <c r="F1247" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>35000</v>
       </c>
       <c r="G1247" s="7">
@@ -41993,7 +42029,7 @@
         <v>6</v>
       </c>
       <c r="F1248" s="7">
-        <f t="shared" ref="F1248:F1256" si="38">F1247+2000</f>
+        <f t="shared" ref="F1248:F1256" si="39">F1247+2000</f>
         <v>37000</v>
       </c>
       <c r="G1248" s="7">
@@ -42020,7 +42056,7 @@
         <v>6</v>
       </c>
       <c r="F1249" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>39000</v>
       </c>
       <c r="G1249" s="7">
@@ -42047,7 +42083,7 @@
         <v>6</v>
       </c>
       <c r="F1250" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>41000</v>
       </c>
       <c r="G1250" s="7">
@@ -42074,7 +42110,7 @@
         <v>6</v>
       </c>
       <c r="F1251" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>43000</v>
       </c>
       <c r="G1251" s="7">
@@ -42101,7 +42137,7 @@
         <v>6</v>
       </c>
       <c r="F1252" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>45000</v>
       </c>
       <c r="G1252" s="7">
@@ -42128,7 +42164,7 @@
         <v>6</v>
       </c>
       <c r="F1253" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>47000</v>
       </c>
       <c r="G1253" s="7">
@@ -42155,7 +42191,7 @@
         <v>6</v>
       </c>
       <c r="F1254" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>49000</v>
       </c>
       <c r="G1254" s="7">
@@ -42182,7 +42218,7 @@
         <v>6</v>
       </c>
       <c r="F1255" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>51000</v>
       </c>
       <c r="G1255" s="7">
@@ -42209,7 +42245,7 @@
         <v>6</v>
       </c>
       <c r="F1256" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>53000</v>
       </c>
       <c r="G1256" s="7">
@@ -42236,7 +42272,7 @@
         <v>6</v>
       </c>
       <c r="F1257" s="7">
-        <f t="shared" ref="F1257:F1276" si="39">F1256+3000</f>
+        <f t="shared" ref="F1257:F1276" si="40">F1256+3000</f>
         <v>56000</v>
       </c>
       <c r="G1257" s="7">
@@ -42263,7 +42299,7 @@
         <v>6</v>
       </c>
       <c r="F1258" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>59000</v>
       </c>
       <c r="G1258" s="7">
@@ -42290,7 +42326,7 @@
         <v>6</v>
       </c>
       <c r="F1259" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>62000</v>
       </c>
       <c r="G1259" s="7">
@@ -42317,7 +42353,7 @@
         <v>6</v>
       </c>
       <c r="F1260" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>65000</v>
       </c>
       <c r="G1260" s="7">
@@ -42344,7 +42380,7 @@
         <v>6</v>
       </c>
       <c r="F1261" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>68000</v>
       </c>
       <c r="G1261" s="7">
@@ -42371,7 +42407,7 @@
         <v>6</v>
       </c>
       <c r="F1262" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>71000</v>
       </c>
       <c r="G1262" s="7">
@@ -42398,7 +42434,7 @@
         <v>6</v>
       </c>
       <c r="F1263" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>74000</v>
       </c>
       <c r="G1263" s="7">
@@ -42425,7 +42461,7 @@
         <v>6</v>
       </c>
       <c r="F1264" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>77000</v>
       </c>
       <c r="G1264" s="7">
@@ -42452,7 +42488,7 @@
         <v>6</v>
       </c>
       <c r="F1265" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>80000</v>
       </c>
       <c r="G1265" s="7">
@@ -42479,7 +42515,7 @@
         <v>6</v>
       </c>
       <c r="F1266" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>83000</v>
       </c>
       <c r="G1266" s="7">
@@ -42506,7 +42542,7 @@
         <v>6</v>
       </c>
       <c r="F1267" s="7">
-        <f t="shared" ref="F1267:F1276" si="40">F1266+4000</f>
+        <f t="shared" ref="F1267:F1276" si="41">F1266+4000</f>
         <v>87000</v>
       </c>
       <c r="G1267" s="7">
@@ -42533,7 +42569,7 @@
         <v>6</v>
       </c>
       <c r="F1268" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>91000</v>
       </c>
       <c r="G1268" s="7">
@@ -42560,7 +42596,7 @@
         <v>6</v>
       </c>
       <c r="F1269" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>95000</v>
       </c>
       <c r="G1269" s="7">
@@ -42587,7 +42623,7 @@
         <v>6</v>
       </c>
       <c r="F1270" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>99000</v>
       </c>
       <c r="G1270" s="7">
@@ -42614,7 +42650,7 @@
         <v>6</v>
       </c>
       <c r="F1271" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>103000</v>
       </c>
       <c r="G1271" s="7">
@@ -42641,7 +42677,7 @@
         <v>6</v>
       </c>
       <c r="F1272" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>107000</v>
       </c>
       <c r="G1272" s="7">
@@ -42668,7 +42704,7 @@
         <v>6</v>
       </c>
       <c r="F1273" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>111000</v>
       </c>
       <c r="G1273" s="7">
@@ -42695,7 +42731,7 @@
         <v>6</v>
       </c>
       <c r="F1274" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>115000</v>
       </c>
       <c r="G1274" s="7">
@@ -42722,7 +42758,7 @@
         <v>6</v>
       </c>
       <c r="F1275" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>119000</v>
       </c>
       <c r="G1275" s="7">
@@ -42749,7 +42785,7 @@
         <v>6</v>
       </c>
       <c r="F1276" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>123000</v>
       </c>
       <c r="G1276" s="7">
@@ -44020,7 +44056,7 @@
         <v>9</v>
       </c>
       <c r="F1327" s="7">
-        <f t="shared" ref="F1327:F1390" si="41">F1326+10</f>
+        <f t="shared" ref="F1327:F1390" si="42">F1326+10</f>
         <v>20</v>
       </c>
       <c r="G1327" s="7">
@@ -44047,7 +44083,7 @@
         <v>9</v>
       </c>
       <c r="F1328" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>30</v>
       </c>
       <c r="G1328" s="7">
@@ -44074,7 +44110,7 @@
         <v>9</v>
       </c>
       <c r="F1329" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>40</v>
       </c>
       <c r="G1329" s="7">
@@ -44101,7 +44137,7 @@
         <v>9</v>
       </c>
       <c r="F1330" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>50</v>
       </c>
       <c r="G1330" s="7">
@@ -44128,7 +44164,7 @@
         <v>9</v>
       </c>
       <c r="F1331" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>60</v>
       </c>
       <c r="G1331" s="7">
@@ -44155,7 +44191,7 @@
         <v>9</v>
       </c>
       <c r="F1332" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>70</v>
       </c>
       <c r="G1332" s="7">
@@ -44182,7 +44218,7 @@
         <v>9</v>
       </c>
       <c r="F1333" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>80</v>
       </c>
       <c r="G1333" s="7">
@@ -44209,7 +44245,7 @@
         <v>9</v>
       </c>
       <c r="F1334" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>90</v>
       </c>
       <c r="G1334" s="7">
@@ -44236,7 +44272,7 @@
         <v>9</v>
       </c>
       <c r="F1335" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>100</v>
       </c>
       <c r="G1335" s="7">
@@ -44263,7 +44299,7 @@
         <v>9</v>
       </c>
       <c r="F1336" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>110</v>
       </c>
       <c r="G1336" s="7">
@@ -44290,7 +44326,7 @@
         <v>9</v>
       </c>
       <c r="F1337" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>120</v>
       </c>
       <c r="G1337" s="7">
@@ -44317,7 +44353,7 @@
         <v>9</v>
       </c>
       <c r="F1338" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>130</v>
       </c>
       <c r="G1338" s="7">
@@ -44344,7 +44380,7 @@
         <v>9</v>
       </c>
       <c r="F1339" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>140</v>
       </c>
       <c r="G1339" s="7">
@@ -44371,7 +44407,7 @@
         <v>9</v>
       </c>
       <c r="F1340" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>150</v>
       </c>
       <c r="G1340" s="7">
@@ -44398,7 +44434,7 @@
         <v>9</v>
       </c>
       <c r="F1341" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>160</v>
       </c>
       <c r="G1341" s="7">
@@ -44425,7 +44461,7 @@
         <v>9</v>
       </c>
       <c r="F1342" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>170</v>
       </c>
       <c r="G1342" s="7">
@@ -44452,7 +44488,7 @@
         <v>9</v>
       </c>
       <c r="F1343" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>180</v>
       </c>
       <c r="G1343" s="7">
@@ -44479,7 +44515,7 @@
         <v>9</v>
       </c>
       <c r="F1344" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>190</v>
       </c>
       <c r="G1344" s="7">
@@ -44506,7 +44542,7 @@
         <v>9</v>
       </c>
       <c r="F1345" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>200</v>
       </c>
       <c r="G1345" s="7">
@@ -44533,7 +44569,7 @@
         <v>9</v>
       </c>
       <c r="F1346" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>210</v>
       </c>
       <c r="G1346" s="7">
@@ -44560,7 +44596,7 @@
         <v>9</v>
       </c>
       <c r="F1347" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>220</v>
       </c>
       <c r="G1347" s="7">
@@ -44587,7 +44623,7 @@
         <v>9</v>
       </c>
       <c r="F1348" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>230</v>
       </c>
       <c r="G1348" s="7">
@@ -44614,7 +44650,7 @@
         <v>9</v>
       </c>
       <c r="F1349" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>240</v>
       </c>
       <c r="G1349" s="7">
@@ -44641,7 +44677,7 @@
         <v>9</v>
       </c>
       <c r="F1350" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>250</v>
       </c>
       <c r="G1350" s="7">
@@ -44668,7 +44704,7 @@
         <v>9</v>
       </c>
       <c r="F1351" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>260</v>
       </c>
       <c r="G1351" s="7">
@@ -44695,7 +44731,7 @@
         <v>9</v>
       </c>
       <c r="F1352" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>270</v>
       </c>
       <c r="G1352" s="7">
@@ -44722,7 +44758,7 @@
         <v>9</v>
       </c>
       <c r="F1353" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>280</v>
       </c>
       <c r="G1353" s="7">
@@ -44749,7 +44785,7 @@
         <v>9</v>
       </c>
       <c r="F1354" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>290</v>
       </c>
       <c r="G1354" s="7">
@@ -44776,7 +44812,7 @@
         <v>9</v>
       </c>
       <c r="F1355" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>300</v>
       </c>
       <c r="G1355" s="7">
@@ -44803,7 +44839,7 @@
         <v>9</v>
       </c>
       <c r="F1356" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>310</v>
       </c>
       <c r="G1356" s="7">
@@ -44830,7 +44866,7 @@
         <v>9</v>
       </c>
       <c r="F1357" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>320</v>
       </c>
       <c r="G1357" s="7">
@@ -44857,7 +44893,7 @@
         <v>9</v>
       </c>
       <c r="F1358" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>330</v>
       </c>
       <c r="G1358" s="7">
@@ -44884,7 +44920,7 @@
         <v>9</v>
       </c>
       <c r="F1359" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>340</v>
       </c>
       <c r="G1359" s="7">
@@ -44911,7 +44947,7 @@
         <v>9</v>
       </c>
       <c r="F1360" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>350</v>
       </c>
       <c r="G1360" s="7">
@@ -44938,7 +44974,7 @@
         <v>9</v>
       </c>
       <c r="F1361" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>360</v>
       </c>
       <c r="G1361" s="7">
@@ -44965,7 +45001,7 @@
         <v>9</v>
       </c>
       <c r="F1362" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>370</v>
       </c>
       <c r="G1362" s="7">
@@ -44992,7 +45028,7 @@
         <v>9</v>
       </c>
       <c r="F1363" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>380</v>
       </c>
       <c r="G1363" s="7">
@@ -45019,7 +45055,7 @@
         <v>9</v>
       </c>
       <c r="F1364" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>390</v>
       </c>
       <c r="G1364" s="7">
@@ -45046,7 +45082,7 @@
         <v>9</v>
       </c>
       <c r="F1365" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>400</v>
       </c>
       <c r="G1365" s="7">
@@ -45073,7 +45109,7 @@
         <v>9</v>
       </c>
       <c r="F1366" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>410</v>
       </c>
       <c r="G1366" s="7">
@@ -45100,7 +45136,7 @@
         <v>9</v>
       </c>
       <c r="F1367" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>420</v>
       </c>
       <c r="G1367" s="7">
@@ -45127,7 +45163,7 @@
         <v>9</v>
       </c>
       <c r="F1368" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>430</v>
       </c>
       <c r="G1368" s="7">
@@ -45154,7 +45190,7 @@
         <v>9</v>
       </c>
       <c r="F1369" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>440</v>
       </c>
       <c r="G1369" s="7">
@@ -45181,7 +45217,7 @@
         <v>9</v>
       </c>
       <c r="F1370" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>450</v>
       </c>
       <c r="G1370" s="7">
@@ -45208,7 +45244,7 @@
         <v>9</v>
       </c>
       <c r="F1371" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>460</v>
       </c>
       <c r="G1371" s="7">
@@ -45235,7 +45271,7 @@
         <v>9</v>
       </c>
       <c r="F1372" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>470</v>
       </c>
       <c r="G1372" s="7">
@@ -45262,7 +45298,7 @@
         <v>9</v>
       </c>
       <c r="F1373" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>480</v>
       </c>
       <c r="G1373" s="7">
@@ -45289,7 +45325,7 @@
         <v>9</v>
       </c>
       <c r="F1374" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>490</v>
       </c>
       <c r="G1374" s="7">
@@ -45316,7 +45352,7 @@
         <v>9</v>
       </c>
       <c r="F1375" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>500</v>
       </c>
       <c r="G1375" s="7">
@@ -45343,7 +45379,7 @@
         <v>9</v>
       </c>
       <c r="F1376" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>510</v>
       </c>
       <c r="G1376" s="7">
@@ -45370,7 +45406,7 @@
         <v>9</v>
       </c>
       <c r="F1377" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>520</v>
       </c>
       <c r="G1377" s="7">
@@ -45397,7 +45433,7 @@
         <v>9</v>
       </c>
       <c r="F1378" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>530</v>
       </c>
       <c r="G1378" s="7">
@@ -45424,7 +45460,7 @@
         <v>9</v>
       </c>
       <c r="F1379" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>540</v>
       </c>
       <c r="G1379" s="7">
@@ -45451,7 +45487,7 @@
         <v>9</v>
       </c>
       <c r="F1380" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>550</v>
       </c>
       <c r="G1380" s="7">
@@ -45478,7 +45514,7 @@
         <v>9</v>
       </c>
       <c r="F1381" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>560</v>
       </c>
       <c r="G1381" s="7">
@@ -45505,7 +45541,7 @@
         <v>9</v>
       </c>
       <c r="F1382" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>570</v>
       </c>
       <c r="G1382" s="7">
@@ -45532,7 +45568,7 @@
         <v>9</v>
       </c>
       <c r="F1383" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>580</v>
       </c>
       <c r="G1383" s="7">
@@ -45559,7 +45595,7 @@
         <v>9</v>
       </c>
       <c r="F1384" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>590</v>
       </c>
       <c r="G1384" s="7">
@@ -45586,7 +45622,7 @@
         <v>9</v>
       </c>
       <c r="F1385" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>600</v>
       </c>
       <c r="G1385" s="7">
@@ -45613,7 +45649,7 @@
         <v>9</v>
       </c>
       <c r="F1386" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>610</v>
       </c>
       <c r="G1386" s="7">
@@ -45640,7 +45676,7 @@
         <v>9</v>
       </c>
       <c r="F1387" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>620</v>
       </c>
       <c r="G1387" s="7">
@@ -45667,7 +45703,7 @@
         <v>9</v>
       </c>
       <c r="F1388" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>630</v>
       </c>
       <c r="G1388" s="7">
@@ -45694,7 +45730,7 @@
         <v>9</v>
       </c>
       <c r="F1389" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>640</v>
       </c>
       <c r="G1389" s="7">
@@ -45721,7 +45757,7 @@
         <v>9</v>
       </c>
       <c r="F1390" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>650</v>
       </c>
       <c r="G1390" s="7">
@@ -45748,7 +45784,7 @@
         <v>9</v>
       </c>
       <c r="F1391" s="7">
-        <f t="shared" ref="F1391:F1454" si="42">F1390+10</f>
+        <f t="shared" ref="F1391:F1454" si="43">F1390+10</f>
         <v>660</v>
       </c>
       <c r="G1391" s="7">
@@ -45775,7 +45811,7 @@
         <v>9</v>
       </c>
       <c r="F1392" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>670</v>
       </c>
       <c r="G1392" s="7">
@@ -45802,7 +45838,7 @@
         <v>9</v>
       </c>
       <c r="F1393" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>680</v>
       </c>
       <c r="G1393" s="7">
@@ -45829,7 +45865,7 @@
         <v>9</v>
       </c>
       <c r="F1394" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>690</v>
       </c>
       <c r="G1394" s="7">
@@ -45856,7 +45892,7 @@
         <v>9</v>
       </c>
       <c r="F1395" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>700</v>
       </c>
       <c r="G1395" s="7">
@@ -45883,7 +45919,7 @@
         <v>9</v>
       </c>
       <c r="F1396" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>710</v>
       </c>
       <c r="G1396" s="7">
@@ -45910,7 +45946,7 @@
         <v>9</v>
       </c>
       <c r="F1397" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>720</v>
       </c>
       <c r="G1397" s="7">
@@ -45937,7 +45973,7 @@
         <v>9</v>
       </c>
       <c r="F1398" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>730</v>
       </c>
       <c r="G1398" s="7">
@@ -45964,7 +46000,7 @@
         <v>9</v>
       </c>
       <c r="F1399" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>740</v>
       </c>
       <c r="G1399" s="7">
@@ -45991,7 +46027,7 @@
         <v>9</v>
       </c>
       <c r="F1400" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>750</v>
       </c>
       <c r="G1400" s="7">
@@ -46018,7 +46054,7 @@
         <v>9</v>
       </c>
       <c r="F1401" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>760</v>
       </c>
       <c r="G1401" s="7">
@@ -46045,7 +46081,7 @@
         <v>9</v>
       </c>
       <c r="F1402" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>770</v>
       </c>
       <c r="G1402" s="7">
@@ -46072,7 +46108,7 @@
         <v>9</v>
       </c>
       <c r="F1403" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>780</v>
       </c>
       <c r="G1403" s="7">
@@ -46099,7 +46135,7 @@
         <v>9</v>
       </c>
       <c r="F1404" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>790</v>
       </c>
       <c r="G1404" s="7">
@@ -46126,7 +46162,7 @@
         <v>9</v>
       </c>
       <c r="F1405" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>800</v>
       </c>
       <c r="G1405" s="7">
@@ -46153,7 +46189,7 @@
         <v>9</v>
       </c>
       <c r="F1406" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>810</v>
       </c>
       <c r="G1406" s="7">
@@ -46180,7 +46216,7 @@
         <v>9</v>
       </c>
       <c r="F1407" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>820</v>
       </c>
       <c r="G1407" s="7">
@@ -46207,7 +46243,7 @@
         <v>9</v>
       </c>
       <c r="F1408" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>830</v>
       </c>
       <c r="G1408" s="7">
@@ -46234,7 +46270,7 @@
         <v>9</v>
       </c>
       <c r="F1409" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>840</v>
       </c>
       <c r="G1409" s="7">
@@ -46261,7 +46297,7 @@
         <v>9</v>
       </c>
       <c r="F1410" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>850</v>
       </c>
       <c r="G1410" s="7">
@@ -46288,7 +46324,7 @@
         <v>9</v>
       </c>
       <c r="F1411" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>860</v>
       </c>
       <c r="G1411" s="7">
@@ -46315,7 +46351,7 @@
         <v>9</v>
       </c>
       <c r="F1412" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>870</v>
       </c>
       <c r="G1412" s="7">
@@ -46342,7 +46378,7 @@
         <v>9</v>
       </c>
       <c r="F1413" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>880</v>
       </c>
       <c r="G1413" s="7">
@@ -46369,7 +46405,7 @@
         <v>9</v>
       </c>
       <c r="F1414" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>890</v>
       </c>
       <c r="G1414" s="7">
@@ -46396,7 +46432,7 @@
         <v>9</v>
       </c>
       <c r="F1415" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>900</v>
       </c>
       <c r="G1415" s="7">
@@ -46423,7 +46459,7 @@
         <v>9</v>
       </c>
       <c r="F1416" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>910</v>
       </c>
       <c r="G1416" s="7">
@@ -46450,7 +46486,7 @@
         <v>9</v>
       </c>
       <c r="F1417" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>920</v>
       </c>
       <c r="G1417" s="7">
@@ -46477,7 +46513,7 @@
         <v>9</v>
       </c>
       <c r="F1418" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>930</v>
       </c>
       <c r="G1418" s="7">
@@ -46504,7 +46540,7 @@
         <v>9</v>
       </c>
       <c r="F1419" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>940</v>
       </c>
       <c r="G1419" s="7">
@@ -46531,7 +46567,7 @@
         <v>9</v>
       </c>
       <c r="F1420" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>950</v>
       </c>
       <c r="G1420" s="7">
@@ -46558,7 +46594,7 @@
         <v>9</v>
       </c>
       <c r="F1421" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>960</v>
       </c>
       <c r="G1421" s="7">
@@ -46585,7 +46621,7 @@
         <v>9</v>
       </c>
       <c r="F1422" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>970</v>
       </c>
       <c r="G1422" s="7">
@@ -46612,7 +46648,7 @@
         <v>9</v>
       </c>
       <c r="F1423" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>980</v>
       </c>
       <c r="G1423" s="7">
@@ -46639,7 +46675,7 @@
         <v>9</v>
       </c>
       <c r="F1424" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>990</v>
       </c>
       <c r="G1424" s="7">
@@ -46666,7 +46702,7 @@
         <v>9</v>
       </c>
       <c r="F1425" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1000</v>
       </c>
       <c r="G1425" s="7">
@@ -46693,7 +46729,7 @@
         <v>9</v>
       </c>
       <c r="F1426" s="7">
-        <f t="shared" ref="F1426:F1489" si="43">F1425+20</f>
+        <f t="shared" ref="F1426:F1489" si="44">F1425+20</f>
         <v>1020</v>
       </c>
       <c r="G1426" s="7">
@@ -46703,7 +46739,7 @@
         <v>18</v>
       </c>
       <c r="I1426" s="7">
-        <f t="shared" ref="I1426:I1489" si="44">I1422+10</f>
+        <f t="shared" ref="I1426:I1489" si="45">I1422+10</f>
         <v>300</v>
       </c>
       <c r="J1426" s="7" t="s">
@@ -46721,7 +46757,7 @@
         <v>9</v>
       </c>
       <c r="F1427" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1040</v>
       </c>
       <c r="G1427" s="7">
@@ -46731,7 +46767,7 @@
         <v>19</v>
       </c>
       <c r="I1427" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>300</v>
       </c>
       <c r="J1427" s="7" t="s">
@@ -46749,7 +46785,7 @@
         <v>9</v>
       </c>
       <c r="F1428" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1060</v>
       </c>
       <c r="G1428" s="7">
@@ -46759,7 +46795,7 @@
         <v>20</v>
       </c>
       <c r="I1428" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>300</v>
       </c>
       <c r="J1428" s="7" t="s">
@@ -46777,7 +46813,7 @@
         <v>9</v>
       </c>
       <c r="F1429" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1080</v>
       </c>
       <c r="G1429" s="7">
@@ -46787,7 +46823,7 @@
         <v>24</v>
       </c>
       <c r="I1429" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>300</v>
       </c>
       <c r="J1429" s="7" t="s">
@@ -46805,7 +46841,7 @@
         <v>9</v>
       </c>
       <c r="F1430" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1100</v>
       </c>
       <c r="G1430" s="7">
@@ -46815,7 +46851,7 @@
         <v>18</v>
       </c>
       <c r="I1430" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>310</v>
       </c>
       <c r="J1430" s="7" t="s">
@@ -46833,7 +46869,7 @@
         <v>9</v>
       </c>
       <c r="F1431" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1120</v>
       </c>
       <c r="G1431" s="7">
@@ -46843,7 +46879,7 @@
         <v>19</v>
       </c>
       <c r="I1431" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>310</v>
       </c>
       <c r="J1431" s="7" t="s">
@@ -46861,7 +46897,7 @@
         <v>9</v>
       </c>
       <c r="F1432" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1140</v>
       </c>
       <c r="G1432" s="7">
@@ -46871,7 +46907,7 @@
         <v>20</v>
       </c>
       <c r="I1432" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>310</v>
       </c>
       <c r="J1432" s="7" t="s">
@@ -46889,7 +46925,7 @@
         <v>9</v>
       </c>
       <c r="F1433" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1160</v>
       </c>
       <c r="G1433" s="7">
@@ -46899,7 +46935,7 @@
         <v>24</v>
       </c>
       <c r="I1433" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>310</v>
       </c>
       <c r="J1433" s="7" t="s">
@@ -46917,7 +46953,7 @@
         <v>9</v>
       </c>
       <c r="F1434" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1180</v>
       </c>
       <c r="G1434" s="7">
@@ -46927,7 +46963,7 @@
         <v>18</v>
       </c>
       <c r="I1434" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>320</v>
       </c>
       <c r="J1434" s="7" t="s">
@@ -46945,7 +46981,7 @@
         <v>9</v>
       </c>
       <c r="F1435" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1200</v>
       </c>
       <c r="G1435" s="7">
@@ -46955,7 +46991,7 @@
         <v>19</v>
       </c>
       <c r="I1435" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>320</v>
       </c>
       <c r="J1435" s="7" t="s">
@@ -46973,7 +47009,7 @@
         <v>9</v>
       </c>
       <c r="F1436" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1220</v>
       </c>
       <c r="G1436" s="7">
@@ -46983,7 +47019,7 @@
         <v>20</v>
       </c>
       <c r="I1436" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>320</v>
       </c>
       <c r="J1436" s="7" t="s">
@@ -47001,7 +47037,7 @@
         <v>9</v>
       </c>
       <c r="F1437" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1240</v>
       </c>
       <c r="G1437" s="7">
@@ -47011,7 +47047,7 @@
         <v>24</v>
       </c>
       <c r="I1437" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>320</v>
       </c>
       <c r="J1437" s="7" t="s">
@@ -47029,7 +47065,7 @@
         <v>9</v>
       </c>
       <c r="F1438" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1260</v>
       </c>
       <c r="G1438" s="7">
@@ -47039,7 +47075,7 @@
         <v>18</v>
       </c>
       <c r="I1438" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>330</v>
       </c>
       <c r="J1438" s="7" t="s">
@@ -47057,7 +47093,7 @@
         <v>9</v>
       </c>
       <c r="F1439" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1280</v>
       </c>
       <c r="G1439" s="7">
@@ -47067,7 +47103,7 @@
         <v>19</v>
       </c>
       <c r="I1439" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>330</v>
       </c>
       <c r="J1439" s="7" t="s">
@@ -47085,7 +47121,7 @@
         <v>9</v>
       </c>
       <c r="F1440" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1300</v>
       </c>
       <c r="G1440" s="7">
@@ -47095,7 +47131,7 @@
         <v>20</v>
       </c>
       <c r="I1440" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>330</v>
       </c>
       <c r="J1440" s="7" t="s">
@@ -47113,7 +47149,7 @@
         <v>9</v>
       </c>
       <c r="F1441" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1320</v>
       </c>
       <c r="G1441" s="7">
@@ -47123,7 +47159,7 @@
         <v>24</v>
       </c>
       <c r="I1441" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>330</v>
       </c>
       <c r="J1441" s="7" t="s">
@@ -47141,7 +47177,7 @@
         <v>9</v>
       </c>
       <c r="F1442" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1340</v>
       </c>
       <c r="G1442" s="7">
@@ -47151,7 +47187,7 @@
         <v>18</v>
       </c>
       <c r="I1442" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>340</v>
       </c>
       <c r="J1442" s="7" t="s">
@@ -47169,7 +47205,7 @@
         <v>9</v>
       </c>
       <c r="F1443" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1360</v>
       </c>
       <c r="G1443" s="7">
@@ -47179,7 +47215,7 @@
         <v>19</v>
       </c>
       <c r="I1443" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>340</v>
       </c>
       <c r="J1443" s="7" t="s">
@@ -47197,7 +47233,7 @@
         <v>9</v>
       </c>
       <c r="F1444" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1380</v>
       </c>
       <c r="G1444" s="7">
@@ -47207,7 +47243,7 @@
         <v>20</v>
       </c>
       <c r="I1444" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>340</v>
       </c>
       <c r="J1444" s="7" t="s">
@@ -47225,7 +47261,7 @@
         <v>9</v>
       </c>
       <c r="F1445" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1400</v>
       </c>
       <c r="G1445" s="7">
@@ -47235,7 +47271,7 @@
         <v>24</v>
       </c>
       <c r="I1445" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>340</v>
       </c>
       <c r="J1445" s="7" t="s">
@@ -47253,7 +47289,7 @@
         <v>9</v>
       </c>
       <c r="F1446" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1420</v>
       </c>
       <c r="G1446" s="7">
@@ -47263,7 +47299,7 @@
         <v>18</v>
       </c>
       <c r="I1446" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>350</v>
       </c>
       <c r="J1446" s="7" t="s">
@@ -47281,7 +47317,7 @@
         <v>9</v>
       </c>
       <c r="F1447" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1440</v>
       </c>
       <c r="G1447" s="7">
@@ -47291,7 +47327,7 @@
         <v>19</v>
       </c>
       <c r="I1447" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>350</v>
       </c>
       <c r="J1447" s="7" t="s">
@@ -47309,7 +47345,7 @@
         <v>9</v>
       </c>
       <c r="F1448" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1460</v>
       </c>
       <c r="G1448" s="7">
@@ -47319,7 +47355,7 @@
         <v>20</v>
       </c>
       <c r="I1448" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>350</v>
       </c>
       <c r="J1448" s="7" t="s">
@@ -47337,7 +47373,7 @@
         <v>9</v>
       </c>
       <c r="F1449" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1480</v>
       </c>
       <c r="G1449" s="7">
@@ -47347,7 +47383,7 @@
         <v>24</v>
       </c>
       <c r="I1449" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>350</v>
       </c>
       <c r="J1449" s="7" t="s">
@@ -47365,7 +47401,7 @@
         <v>9</v>
       </c>
       <c r="F1450" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1500</v>
       </c>
       <c r="G1450" s="7">
@@ -47375,7 +47411,7 @@
         <v>18</v>
       </c>
       <c r="I1450" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>360</v>
       </c>
       <c r="J1450" s="7" t="s">
@@ -47393,7 +47429,7 @@
         <v>9</v>
       </c>
       <c r="F1451" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1520</v>
       </c>
       <c r="G1451" s="7">
@@ -47403,7 +47439,7 @@
         <v>19</v>
       </c>
       <c r="I1451" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>360</v>
       </c>
       <c r="J1451" s="7" t="s">
@@ -47421,7 +47457,7 @@
         <v>9</v>
       </c>
       <c r="F1452" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1540</v>
       </c>
       <c r="G1452" s="7">
@@ -47431,7 +47467,7 @@
         <v>20</v>
       </c>
       <c r="I1452" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>360</v>
       </c>
       <c r="J1452" s="7" t="s">
@@ -47449,7 +47485,7 @@
         <v>9</v>
       </c>
       <c r="F1453" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1560</v>
       </c>
       <c r="G1453" s="7">
@@ -47459,7 +47495,7 @@
         <v>24</v>
       </c>
       <c r="I1453" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>360</v>
       </c>
       <c r="J1453" s="7" t="s">
@@ -47477,7 +47513,7 @@
         <v>9</v>
       </c>
       <c r="F1454" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1580</v>
       </c>
       <c r="G1454" s="7">
@@ -47487,7 +47523,7 @@
         <v>18</v>
       </c>
       <c r="I1454" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>370</v>
       </c>
       <c r="J1454" s="7" t="s">
@@ -47505,7 +47541,7 @@
         <v>9</v>
       </c>
       <c r="F1455" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1600</v>
       </c>
       <c r="G1455" s="7">
@@ -47515,7 +47551,7 @@
         <v>19</v>
       </c>
       <c r="I1455" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>370</v>
       </c>
       <c r="J1455" s="7" t="s">
@@ -47533,7 +47569,7 @@
         <v>9</v>
       </c>
       <c r="F1456" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1620</v>
       </c>
       <c r="G1456" s="7">
@@ -47543,7 +47579,7 @@
         <v>20</v>
       </c>
       <c r="I1456" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>370</v>
       </c>
       <c r="J1456" s="7" t="s">
@@ -47561,7 +47597,7 @@
         <v>9</v>
       </c>
       <c r="F1457" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1640</v>
       </c>
       <c r="G1457" s="7">
@@ -47571,7 +47607,7 @@
         <v>24</v>
       </c>
       <c r="I1457" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>370</v>
       </c>
       <c r="J1457" s="7" t="s">
@@ -47589,7 +47625,7 @@
         <v>9</v>
       </c>
       <c r="F1458" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1660</v>
       </c>
       <c r="G1458" s="7">
@@ -47599,7 +47635,7 @@
         <v>18</v>
       </c>
       <c r="I1458" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>380</v>
       </c>
       <c r="J1458" s="7" t="s">
@@ -47617,7 +47653,7 @@
         <v>9</v>
       </c>
       <c r="F1459" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1680</v>
       </c>
       <c r="G1459" s="7">
@@ -47627,7 +47663,7 @@
         <v>19</v>
       </c>
       <c r="I1459" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>380</v>
       </c>
       <c r="J1459" s="7" t="s">
@@ -47645,7 +47681,7 @@
         <v>9</v>
       </c>
       <c r="F1460" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1700</v>
       </c>
       <c r="G1460" s="7">
@@ -47655,7 +47691,7 @@
         <v>20</v>
       </c>
       <c r="I1460" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>380</v>
       </c>
       <c r="J1460" s="7" t="s">
@@ -47673,7 +47709,7 @@
         <v>9</v>
       </c>
       <c r="F1461" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1720</v>
       </c>
       <c r="G1461" s="7">
@@ -47683,7 +47719,7 @@
         <v>24</v>
       </c>
       <c r="I1461" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>380</v>
       </c>
       <c r="J1461" s="7" t="s">
@@ -47701,7 +47737,7 @@
         <v>9</v>
       </c>
       <c r="F1462" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1740</v>
       </c>
       <c r="G1462" s="7">
@@ -47711,7 +47747,7 @@
         <v>18</v>
       </c>
       <c r="I1462" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>390</v>
       </c>
       <c r="J1462" s="7" t="s">
@@ -47729,7 +47765,7 @@
         <v>9</v>
       </c>
       <c r="F1463" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1760</v>
       </c>
       <c r="G1463" s="7">
@@ -47739,7 +47775,7 @@
         <v>19</v>
       </c>
       <c r="I1463" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>390</v>
       </c>
       <c r="J1463" s="7" t="s">
@@ -47757,7 +47793,7 @@
         <v>9</v>
       </c>
       <c r="F1464" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1780</v>
       </c>
       <c r="G1464" s="7">
@@ -47767,7 +47803,7 @@
         <v>20</v>
       </c>
       <c r="I1464" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>390</v>
       </c>
       <c r="J1464" s="7" t="s">
@@ -47785,7 +47821,7 @@
         <v>9</v>
       </c>
       <c r="F1465" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1800</v>
       </c>
       <c r="G1465" s="7">
@@ -47795,7 +47831,7 @@
         <v>24</v>
       </c>
       <c r="I1465" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>390</v>
       </c>
       <c r="J1465" s="7" t="s">
@@ -47813,7 +47849,7 @@
         <v>9</v>
       </c>
       <c r="F1466" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1820</v>
       </c>
       <c r="G1466" s="7">
@@ -47823,7 +47859,7 @@
         <v>18</v>
       </c>
       <c r="I1466" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>400</v>
       </c>
       <c r="J1466" s="7" t="s">
@@ -47841,7 +47877,7 @@
         <v>9</v>
       </c>
       <c r="F1467" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1840</v>
       </c>
       <c r="G1467" s="7">
@@ -47851,7 +47887,7 @@
         <v>19</v>
       </c>
       <c r="I1467" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>400</v>
       </c>
       <c r="J1467" s="7" t="s">
@@ -47869,7 +47905,7 @@
         <v>9</v>
       </c>
       <c r="F1468" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1860</v>
       </c>
       <c r="G1468" s="7">
@@ -47879,7 +47915,7 @@
         <v>20</v>
       </c>
       <c r="I1468" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>400</v>
       </c>
       <c r="J1468" s="7" t="s">
@@ -47897,7 +47933,7 @@
         <v>9</v>
       </c>
       <c r="F1469" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1880</v>
       </c>
       <c r="G1469" s="7">
@@ -47907,7 +47943,7 @@
         <v>24</v>
       </c>
       <c r="I1469" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>400</v>
       </c>
       <c r="J1469" s="7" t="s">
@@ -47925,7 +47961,7 @@
         <v>9</v>
       </c>
       <c r="F1470" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1900</v>
       </c>
       <c r="G1470" s="7">
@@ -47935,7 +47971,7 @@
         <v>18</v>
       </c>
       <c r="I1470" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>410</v>
       </c>
       <c r="J1470" s="7" t="s">
@@ -47953,7 +47989,7 @@
         <v>9</v>
       </c>
       <c r="F1471" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1920</v>
       </c>
       <c r="G1471" s="7">
@@ -47963,7 +47999,7 @@
         <v>19</v>
       </c>
       <c r="I1471" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>410</v>
       </c>
       <c r="J1471" s="7" t="s">
@@ -47981,7 +48017,7 @@
         <v>9</v>
       </c>
       <c r="F1472" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1940</v>
       </c>
       <c r="G1472" s="7">
@@ -47991,7 +48027,7 @@
         <v>20</v>
       </c>
       <c r="I1472" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>410</v>
       </c>
       <c r="J1472" s="7" t="s">
@@ -48009,7 +48045,7 @@
         <v>9</v>
       </c>
       <c r="F1473" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1960</v>
       </c>
       <c r="G1473" s="7">
@@ -48019,7 +48055,7 @@
         <v>24</v>
       </c>
       <c r="I1473" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>410</v>
       </c>
       <c r="J1473" s="7" t="s">
@@ -48037,7 +48073,7 @@
         <v>9</v>
       </c>
       <c r="F1474" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1980</v>
       </c>
       <c r="G1474" s="7">
@@ -48047,7 +48083,7 @@
         <v>18</v>
       </c>
       <c r="I1474" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>420</v>
       </c>
       <c r="J1474" s="7" t="s">
@@ -48065,7 +48101,7 @@
         <v>9</v>
       </c>
       <c r="F1475" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2000</v>
       </c>
       <c r="G1475" s="7">
@@ -48075,7 +48111,7 @@
         <v>19</v>
       </c>
       <c r="I1475" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>420</v>
       </c>
       <c r="J1475" s="7" t="s">
@@ -48093,7 +48129,7 @@
         <v>9</v>
       </c>
       <c r="F1476" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2020</v>
       </c>
       <c r="G1476" s="7">
@@ -48103,7 +48139,7 @@
         <v>20</v>
       </c>
       <c r="I1476" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>420</v>
       </c>
       <c r="J1476" s="7" t="s">
@@ -48121,7 +48157,7 @@
         <v>9</v>
       </c>
       <c r="F1477" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2040</v>
       </c>
       <c r="G1477" s="7">
@@ -48131,7 +48167,7 @@
         <v>24</v>
       </c>
       <c r="I1477" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>420</v>
       </c>
       <c r="J1477" s="7" t="s">
@@ -48149,7 +48185,7 @@
         <v>9</v>
       </c>
       <c r="F1478" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2060</v>
       </c>
       <c r="G1478" s="7">
@@ -48159,7 +48195,7 @@
         <v>18</v>
       </c>
       <c r="I1478" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>430</v>
       </c>
       <c r="J1478" s="7" t="s">
@@ -48177,7 +48213,7 @@
         <v>9</v>
       </c>
       <c r="F1479" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2080</v>
       </c>
       <c r="G1479" s="7">
@@ -48187,7 +48223,7 @@
         <v>19</v>
       </c>
       <c r="I1479" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>430</v>
       </c>
       <c r="J1479" s="7" t="s">
@@ -48205,7 +48241,7 @@
         <v>9</v>
       </c>
       <c r="F1480" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2100</v>
       </c>
       <c r="G1480" s="7">
@@ -48215,7 +48251,7 @@
         <v>20</v>
       </c>
       <c r="I1480" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>430</v>
       </c>
       <c r="J1480" s="7" t="s">
@@ -48233,7 +48269,7 @@
         <v>9</v>
       </c>
       <c r="F1481" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2120</v>
       </c>
       <c r="G1481" s="7">
@@ -48243,7 +48279,7 @@
         <v>24</v>
       </c>
       <c r="I1481" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>430</v>
       </c>
       <c r="J1481" s="7" t="s">
@@ -48261,7 +48297,7 @@
         <v>9</v>
       </c>
       <c r="F1482" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2140</v>
       </c>
       <c r="G1482" s="7">
@@ -48271,7 +48307,7 @@
         <v>18</v>
       </c>
       <c r="I1482" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>440</v>
       </c>
       <c r="J1482" s="7" t="s">
@@ -48289,7 +48325,7 @@
         <v>9</v>
       </c>
       <c r="F1483" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2160</v>
       </c>
       <c r="G1483" s="7">
@@ -48299,7 +48335,7 @@
         <v>19</v>
       </c>
       <c r="I1483" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>440</v>
       </c>
       <c r="J1483" s="7" t="s">
@@ -48317,7 +48353,7 @@
         <v>9</v>
       </c>
       <c r="F1484" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2180</v>
       </c>
       <c r="G1484" s="7">
@@ -48327,7 +48363,7 @@
         <v>20</v>
       </c>
       <c r="I1484" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>440</v>
       </c>
       <c r="J1484" s="7" t="s">
@@ -48345,7 +48381,7 @@
         <v>9</v>
       </c>
       <c r="F1485" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2200</v>
       </c>
       <c r="G1485" s="7">
@@ -48355,7 +48391,7 @@
         <v>24</v>
       </c>
       <c r="I1485" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>440</v>
       </c>
       <c r="J1485" s="7" t="s">
@@ -48373,7 +48409,7 @@
         <v>9</v>
       </c>
       <c r="F1486" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2220</v>
       </c>
       <c r="G1486" s="7">
@@ -48383,7 +48419,7 @@
         <v>18</v>
       </c>
       <c r="I1486" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>450</v>
       </c>
       <c r="J1486" s="7" t="s">
@@ -48401,7 +48437,7 @@
         <v>9</v>
       </c>
       <c r="F1487" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2240</v>
       </c>
       <c r="G1487" s="7">
@@ -48411,7 +48447,7 @@
         <v>19</v>
       </c>
       <c r="I1487" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>450</v>
       </c>
       <c r="J1487" s="7" t="s">
@@ -48429,7 +48465,7 @@
         <v>9</v>
       </c>
       <c r="F1488" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2260</v>
       </c>
       <c r="G1488" s="7">
@@ -48439,7 +48475,7 @@
         <v>20</v>
       </c>
       <c r="I1488" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>450</v>
       </c>
       <c r="J1488" s="7" t="s">
@@ -48457,7 +48493,7 @@
         <v>9</v>
       </c>
       <c r="F1489" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2280</v>
       </c>
       <c r="G1489" s="7">
@@ -48467,7 +48503,7 @@
         <v>24</v>
       </c>
       <c r="I1489" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>450</v>
       </c>
       <c r="J1489" s="7" t="s">
@@ -48485,7 +48521,7 @@
         <v>9</v>
       </c>
       <c r="F1490" s="7">
-        <f t="shared" ref="F1490:F1495" si="45">F1489+20</f>
+        <f t="shared" ref="F1490:F1495" si="46">F1489+20</f>
         <v>2300</v>
       </c>
       <c r="G1490" s="7">
@@ -48495,7 +48531,7 @@
         <v>18</v>
       </c>
       <c r="I1490" s="7">
-        <f t="shared" ref="I1490:I1505" si="46">I1486+10</f>
+        <f t="shared" ref="I1490:I1505" si="47">I1486+10</f>
         <v>460</v>
       </c>
       <c r="J1490" s="7" t="s">
@@ -48513,7 +48549,7 @@
         <v>9</v>
       </c>
       <c r="F1491" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2320</v>
       </c>
       <c r="G1491" s="7">
@@ -48523,7 +48559,7 @@
         <v>19</v>
       </c>
       <c r="I1491" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>460</v>
       </c>
       <c r="J1491" s="7" t="s">
@@ -48541,7 +48577,7 @@
         <v>9</v>
       </c>
       <c r="F1492" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2340</v>
       </c>
       <c r="G1492" s="7">
@@ -48551,7 +48587,7 @@
         <v>20</v>
       </c>
       <c r="I1492" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>460</v>
       </c>
       <c r="J1492" s="7" t="s">
@@ -48569,7 +48605,7 @@
         <v>9</v>
       </c>
       <c r="F1493" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2360</v>
       </c>
       <c r="G1493" s="7">
@@ -48579,7 +48615,7 @@
         <v>24</v>
       </c>
       <c r="I1493" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>460</v>
       </c>
       <c r="J1493" s="7" t="s">
@@ -48597,7 +48633,7 @@
         <v>9</v>
       </c>
       <c r="F1494" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2380</v>
       </c>
       <c r="G1494" s="7">
@@ -48607,7 +48643,7 @@
         <v>18</v>
       </c>
       <c r="I1494" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>470</v>
       </c>
       <c r="J1494" s="7" t="s">
@@ -48625,7 +48661,7 @@
         <v>9</v>
       </c>
       <c r="F1495" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2400</v>
       </c>
       <c r="G1495" s="7">
@@ -48635,7 +48671,7 @@
         <v>19</v>
       </c>
       <c r="I1495" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>470</v>
       </c>
       <c r="J1495" s="7" t="s">
@@ -48653,7 +48689,7 @@
         <v>9</v>
       </c>
       <c r="F1496" s="7">
-        <f t="shared" ref="F1496:F1517" si="47">F1495+30</f>
+        <f t="shared" ref="F1496:F1517" si="48">F1495+30</f>
         <v>2430</v>
       </c>
       <c r="G1496" s="7">
@@ -48663,7 +48699,7 @@
         <v>20</v>
       </c>
       <c r="I1496" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>470</v>
       </c>
       <c r="J1496" s="7" t="s">
@@ -48681,7 +48717,7 @@
         <v>9</v>
       </c>
       <c r="F1497" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2460</v>
       </c>
       <c r="G1497" s="7">
@@ -48691,7 +48727,7 @@
         <v>24</v>
       </c>
       <c r="I1497" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>470</v>
       </c>
       <c r="J1497" s="7" t="s">
@@ -48709,7 +48745,7 @@
         <v>9</v>
       </c>
       <c r="F1498" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2490</v>
       </c>
       <c r="G1498" s="7">
@@ -48719,7 +48755,7 @@
         <v>18</v>
       </c>
       <c r="I1498" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>480</v>
       </c>
       <c r="J1498" s="7" t="s">
@@ -48737,7 +48773,7 @@
         <v>9</v>
       </c>
       <c r="F1499" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2520</v>
       </c>
       <c r="G1499" s="7">
@@ -48747,7 +48783,7 @@
         <v>19</v>
       </c>
       <c r="I1499" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>480</v>
       </c>
       <c r="J1499" s="7" t="s">
@@ -48765,7 +48801,7 @@
         <v>9</v>
       </c>
       <c r="F1500" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2550</v>
       </c>
       <c r="G1500" s="7">
@@ -48775,7 +48811,7 @@
         <v>20</v>
       </c>
       <c r="I1500" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>480</v>
       </c>
       <c r="J1500" s="7" t="s">
@@ -48793,7 +48829,7 @@
         <v>9</v>
       </c>
       <c r="F1501" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2580</v>
       </c>
       <c r="G1501" s="7">
@@ -48803,7 +48839,7 @@
         <v>24</v>
       </c>
       <c r="I1501" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>480</v>
       </c>
       <c r="J1501" s="7" t="s">
@@ -48821,7 +48857,7 @@
         <v>9</v>
       </c>
       <c r="F1502" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2610</v>
       </c>
       <c r="G1502" s="7">
@@ -48831,7 +48867,7 @@
         <v>18</v>
       </c>
       <c r="I1502" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>490</v>
       </c>
       <c r="J1502" s="7" t="s">
@@ -48849,7 +48885,7 @@
         <v>9</v>
       </c>
       <c r="F1503" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2640</v>
       </c>
       <c r="G1503" s="7">
@@ -48859,7 +48895,7 @@
         <v>19</v>
       </c>
       <c r="I1503" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>490</v>
       </c>
       <c r="J1503" s="7" t="s">
@@ -48877,7 +48913,7 @@
         <v>9</v>
       </c>
       <c r="F1504" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2670</v>
       </c>
       <c r="G1504" s="7">
@@ -48887,7 +48923,7 @@
         <v>20</v>
       </c>
       <c r="I1504" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>490</v>
       </c>
       <c r="J1504" s="7" t="s">
@@ -48905,7 +48941,7 @@
         <v>9</v>
       </c>
       <c r="F1505" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2700</v>
       </c>
       <c r="G1505" s="7">
@@ -48915,7 +48951,7 @@
         <v>24</v>
       </c>
       <c r="I1505" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>490</v>
       </c>
       <c r="J1505" s="7" t="s">
@@ -48933,7 +48969,7 @@
         <v>9</v>
       </c>
       <c r="F1506" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2730</v>
       </c>
       <c r="G1506" s="7">
@@ -48943,7 +48979,7 @@
         <v>18</v>
       </c>
       <c r="I1506" s="7">
-        <f t="shared" ref="I1506:I1517" si="48">I1502+10</f>
+        <f t="shared" ref="I1506:I1529" si="49">I1502+10</f>
         <v>500</v>
       </c>
       <c r="J1506" s="7" t="s">
@@ -48961,7 +48997,7 @@
         <v>9</v>
       </c>
       <c r="F1507" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2760</v>
       </c>
       <c r="G1507" s="7">
@@ -48971,7 +49007,7 @@
         <v>19</v>
       </c>
       <c r="I1507" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>500</v>
       </c>
       <c r="J1507" s="7" t="s">
@@ -48989,7 +49025,7 @@
         <v>9</v>
       </c>
       <c r="F1508" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2790</v>
       </c>
       <c r="G1508" s="7">
@@ -48999,7 +49035,7 @@
         <v>20</v>
       </c>
       <c r="I1508" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>500</v>
       </c>
       <c r="J1508" s="7" t="s">
@@ -49017,7 +49053,7 @@
         <v>9</v>
       </c>
       <c r="F1509" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2820</v>
       </c>
       <c r="G1509" s="7">
@@ -49027,7 +49063,7 @@
         <v>24</v>
       </c>
       <c r="I1509" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>500</v>
       </c>
       <c r="J1509" s="7" t="s">
@@ -49045,7 +49081,7 @@
         <v>9</v>
       </c>
       <c r="F1510" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2850</v>
       </c>
       <c r="G1510" s="7">
@@ -49055,7 +49091,7 @@
         <v>18</v>
       </c>
       <c r="I1510" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>510</v>
       </c>
       <c r="J1510" s="7" t="s">
@@ -49073,7 +49109,7 @@
         <v>9</v>
       </c>
       <c r="F1511" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2880</v>
       </c>
       <c r="G1511" s="7">
@@ -49083,7 +49119,7 @@
         <v>19</v>
       </c>
       <c r="I1511" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>510</v>
       </c>
       <c r="J1511" s="7" t="s">
@@ -49101,7 +49137,7 @@
         <v>9</v>
       </c>
       <c r="F1512" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2910</v>
       </c>
       <c r="G1512" s="7">
@@ -49111,7 +49147,7 @@
         <v>20</v>
       </c>
       <c r="I1512" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>510</v>
       </c>
       <c r="J1512" s="7" t="s">
@@ -49129,7 +49165,7 @@
         <v>9</v>
       </c>
       <c r="F1513" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2940</v>
       </c>
       <c r="G1513" s="7">
@@ -49139,7 +49175,7 @@
         <v>24</v>
       </c>
       <c r="I1513" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>510</v>
       </c>
       <c r="J1513" s="7" t="s">
@@ -49157,7 +49193,7 @@
         <v>9</v>
       </c>
       <c r="F1514" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2970</v>
       </c>
       <c r="G1514" s="7">
@@ -49167,7 +49203,7 @@
         <v>18</v>
       </c>
       <c r="I1514" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>520</v>
       </c>
       <c r="J1514" s="7" t="s">
@@ -49185,7 +49221,7 @@
         <v>9</v>
       </c>
       <c r="F1515" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>3000</v>
       </c>
       <c r="G1515" s="7">
@@ -49195,7 +49231,7 @@
         <v>19</v>
       </c>
       <c r="I1515" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>520</v>
       </c>
       <c r="J1515" s="7" t="s">
@@ -49213,7 +49249,7 @@
         <v>9</v>
       </c>
       <c r="F1516" s="7">
-        <f>F1515+40</f>
+        <f t="shared" ref="F1516:F1529" si="50">F1515+40</f>
         <v>3040</v>
       </c>
       <c r="G1516" s="7">
@@ -49223,7 +49259,7 @@
         <v>20</v>
       </c>
       <c r="I1516" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>520</v>
       </c>
       <c r="J1516" s="7" t="s">
@@ -49241,7 +49277,7 @@
         <v>9</v>
       </c>
       <c r="F1517" s="7">
-        <f>F1516+40</f>
+        <f t="shared" si="50"/>
         <v>3080</v>
       </c>
       <c r="G1517" s="7">
@@ -49251,10 +49287,346 @@
         <v>24</v>
       </c>
       <c r="I1517" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>520</v>
       </c>
       <c r="J1517" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1518" customHeight="1" spans="3:10">
+      <c r="C1518" s="7">
+        <v>9193</v>
+      </c>
+      <c r="D1518" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E1518" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1518" s="7">
+        <f t="shared" si="50"/>
+        <v>3120</v>
+      </c>
+      <c r="G1518" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1518" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1518" s="7">
+        <f t="shared" si="49"/>
+        <v>530</v>
+      </c>
+      <c r="J1518" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1519" customHeight="1" spans="3:10">
+      <c r="C1519" s="7">
+        <v>9194</v>
+      </c>
+      <c r="D1519" s="7" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E1519" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1519" s="7">
+        <f t="shared" si="50"/>
+        <v>3160</v>
+      </c>
+      <c r="G1519" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1519" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1519" s="7">
+        <f t="shared" si="49"/>
+        <v>530</v>
+      </c>
+      <c r="J1519" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1520" customHeight="1" spans="3:10">
+      <c r="C1520" s="7">
+        <v>9195</v>
+      </c>
+      <c r="D1520" s="7" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E1520" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1520" s="7">
+        <f t="shared" si="50"/>
+        <v>3200</v>
+      </c>
+      <c r="G1520" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1520" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1520" s="7">
+        <f t="shared" si="49"/>
+        <v>530</v>
+      </c>
+      <c r="J1520" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1521" customHeight="1" spans="3:10">
+      <c r="C1521" s="7">
+        <v>9196</v>
+      </c>
+      <c r="D1521" s="7" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E1521" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1521" s="7">
+        <f t="shared" si="50"/>
+        <v>3240</v>
+      </c>
+      <c r="G1521" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1521" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1521" s="7">
+        <f t="shared" si="49"/>
+        <v>530</v>
+      </c>
+      <c r="J1521" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1522" customHeight="1" spans="3:10">
+      <c r="C1522" s="7">
+        <v>9197</v>
+      </c>
+      <c r="D1522" s="7" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E1522" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1522" s="7">
+        <f t="shared" si="50"/>
+        <v>3280</v>
+      </c>
+      <c r="G1522" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1522" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1522" s="7">
+        <f t="shared" si="49"/>
+        <v>540</v>
+      </c>
+      <c r="J1522" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1523" customHeight="1" spans="3:10">
+      <c r="C1523" s="7">
+        <v>9198</v>
+      </c>
+      <c r="D1523" s="7" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E1523" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1523" s="7">
+        <f t="shared" si="50"/>
+        <v>3320</v>
+      </c>
+      <c r="G1523" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1523" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1523" s="7">
+        <f t="shared" si="49"/>
+        <v>540</v>
+      </c>
+      <c r="J1523" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1524" customHeight="1" spans="3:10">
+      <c r="C1524" s="7">
+        <v>9199</v>
+      </c>
+      <c r="D1524" s="7" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E1524" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1524" s="7">
+        <f t="shared" si="50"/>
+        <v>3360</v>
+      </c>
+      <c r="G1524" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1524" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1524" s="7">
+        <f t="shared" si="49"/>
+        <v>540</v>
+      </c>
+      <c r="J1524" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1525" customHeight="1" spans="3:10">
+      <c r="C1525" s="7">
+        <v>9200</v>
+      </c>
+      <c r="D1525" s="7" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E1525" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1525" s="7">
+        <f t="shared" si="50"/>
+        <v>3400</v>
+      </c>
+      <c r="G1525" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1525" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1525" s="7">
+        <f t="shared" si="49"/>
+        <v>540</v>
+      </c>
+      <c r="J1525" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1526" customHeight="1" spans="3:10">
+      <c r="C1526" s="7">
+        <v>9201</v>
+      </c>
+      <c r="D1526" s="7" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E1526" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1526" s="7">
+        <f t="shared" si="50"/>
+        <v>3440</v>
+      </c>
+      <c r="G1526" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1526" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1526" s="7">
+        <f t="shared" si="49"/>
+        <v>550</v>
+      </c>
+      <c r="J1526" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1527" customHeight="1" spans="3:10">
+      <c r="C1527" s="7">
+        <v>9202</v>
+      </c>
+      <c r="D1527" s="7" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E1527" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1527" s="7">
+        <f t="shared" si="50"/>
+        <v>3480</v>
+      </c>
+      <c r="G1527" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1527" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1527" s="7">
+        <f t="shared" si="49"/>
+        <v>550</v>
+      </c>
+      <c r="J1527" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1528" customHeight="1" spans="3:10">
+      <c r="C1528" s="7">
+        <v>9203</v>
+      </c>
+      <c r="D1528" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E1528" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1528" s="7">
+        <f t="shared" si="50"/>
+        <v>3520</v>
+      </c>
+      <c r="G1528" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1528" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1528" s="7">
+        <f t="shared" si="49"/>
+        <v>550</v>
+      </c>
+      <c r="J1528" s="7" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1529" customHeight="1" spans="3:10">
+      <c r="C1529" s="7">
+        <v>9204</v>
+      </c>
+      <c r="D1529" s="7" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E1529" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1529" s="7">
+        <f t="shared" si="50"/>
+        <v>3560</v>
+      </c>
+      <c r="G1529" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1529" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1529" s="7">
+        <f t="shared" si="49"/>
+        <v>550</v>
+      </c>
+      <c r="J1529" s="7" t="s">
         <v>1375</v>
       </c>
     </row>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4127" uniqueCount="1594">
   <si>
     <t>#</t>
   </si>
@@ -3955,6 +3955,21 @@
     <t>BOSS之家100</t>
   </si>
   <si>
+    <t>BOSS之家101</t>
+  </si>
+  <si>
+    <t>BOSS之家102</t>
+  </si>
+  <si>
+    <t>BOSS之家103</t>
+  </si>
+  <si>
+    <t>BOSS之家104</t>
+  </si>
+  <si>
+    <t>BOSS之家105</t>
+  </si>
+  <si>
     <t>小试牛刀</t>
   </si>
   <si>
@@ -4214,6 +4229,36 @@
   </si>
   <si>
     <t>天下无敌4</t>
+  </si>
+  <si>
+    <t>初出茅庐5</t>
+  </si>
+  <si>
+    <t>小试牛刀5</t>
+  </si>
+  <si>
+    <t>初露锋芒5</t>
+  </si>
+  <si>
+    <t>武林新秀5</t>
+  </si>
+  <si>
+    <t>声名鹊起5</t>
+  </si>
+  <si>
+    <t>过关斩将5</t>
+  </si>
+  <si>
+    <t>独孤求败5</t>
+  </si>
+  <si>
+    <t>武林至尊5</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>天下无敌5</t>
   </si>
   <si>
     <t>攀登者1</t>
@@ -5512,10 +5557,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5836,7 +5881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K1529"/>
+  <dimension ref="A2:K1544"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="7"/>
@@ -42542,7 +42587,7 @@
         <v>6</v>
       </c>
       <c r="F1267" s="7">
-        <f t="shared" ref="F1267:F1276" si="41">F1266+4000</f>
+        <f t="shared" ref="F1267:F1281" si="41">F1266+4000</f>
         <v>87000</v>
       </c>
       <c r="G1267" s="7">
@@ -42801,946 +42846,936 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="1279" customHeight="1" spans="3:11">
+    <row r="1277" customHeight="1" spans="3:10">
+      <c r="C1277" s="7">
+        <v>6111</v>
+      </c>
+      <c r="D1277" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1277" s="7">
+        <v>6</v>
+      </c>
+      <c r="F1277" s="7">
+        <f t="shared" ref="F1277:F1281" si="42">F1276+10000</f>
+        <v>133000</v>
+      </c>
+      <c r="G1277" s="7">
+        <v>4</v>
+      </c>
+      <c r="H1277" s="7">
+        <v>0</v>
+      </c>
+      <c r="I1277" s="7">
+        <v>2</v>
+      </c>
+      <c r="J1277" s="7" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1278" customHeight="1" spans="3:10">
+      <c r="C1278" s="7">
+        <v>6112</v>
+      </c>
+      <c r="D1278" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E1278" s="7">
+        <v>6</v>
+      </c>
+      <c r="F1278" s="7">
+        <f t="shared" si="42"/>
+        <v>143000</v>
+      </c>
+      <c r="G1278" s="7">
+        <v>4</v>
+      </c>
+      <c r="H1278" s="7">
+        <v>0</v>
+      </c>
+      <c r="I1278" s="7">
+        <v>2</v>
+      </c>
+      <c r="J1278" s="7" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1279" customHeight="1" spans="3:10">
       <c r="C1279" s="7">
-        <v>8001</v>
-      </c>
-      <c r="D1279" s="10" t="s">
-        <v>1287</v>
+        <v>6113</v>
+      </c>
+      <c r="D1279" s="7" t="s">
+        <v>1289</v>
       </c>
       <c r="E1279" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F1279" s="7">
-        <v>10</v>
-      </c>
-      <c r="G1279" s="5">
-        <v>1</v>
-      </c>
-      <c r="H1279" s="5">
-        <v>20</v>
-      </c>
-      <c r="I1279" s="5">
-        <v>100</v>
-      </c>
-      <c r="J1279" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1279" s="11" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="1280" customHeight="1" spans="3:11">
+        <f t="shared" si="42"/>
+        <v>153000</v>
+      </c>
+      <c r="G1279" s="7">
+        <v>4</v>
+      </c>
+      <c r="H1279" s="7">
+        <v>0</v>
+      </c>
+      <c r="I1279" s="7">
+        <v>2</v>
+      </c>
+      <c r="J1279" s="7" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1280" customHeight="1" spans="3:10">
       <c r="C1280" s="7">
-        <v>8002</v>
-      </c>
-      <c r="D1280" s="10" t="s">
+        <v>6114</v>
+      </c>
+      <c r="D1280" s="7" t="s">
         <v>1290</v>
       </c>
       <c r="E1280" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F1280" s="7">
-        <v>30</v>
-      </c>
-      <c r="G1280" s="5">
-        <v>1</v>
+        <f t="shared" si="42"/>
+        <v>163000</v>
+      </c>
+      <c r="G1280" s="7">
+        <v>4</v>
       </c>
       <c r="H1280" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I1280" s="7">
-        <v>100</v>
-      </c>
-      <c r="J1280" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1280" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1280" s="7" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1281" customHeight="1" spans="3:10">
+      <c r="C1281" s="7">
+        <v>6115</v>
+      </c>
+      <c r="D1281" s="7" t="s">
         <v>1291</v>
       </c>
-    </row>
-    <row r="1281" customHeight="1" spans="3:11">
-      <c r="C1281" s="7">
-        <v>8003</v>
-      </c>
-      <c r="D1281" s="12" t="s">
-        <v>1292</v>
-      </c>
       <c r="E1281" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F1281" s="7">
-        <v>50</v>
-      </c>
-      <c r="G1281" s="5">
-        <v>1</v>
+        <f t="shared" si="42"/>
+        <v>173000</v>
+      </c>
+      <c r="G1281" s="7">
+        <v>4</v>
       </c>
       <c r="H1281" s="7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I1281" s="7">
-        <v>10</v>
-      </c>
-      <c r="J1281" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1281" s="11" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="1282" customHeight="1" spans="3:11">
-      <c r="C1282" s="7">
-        <v>8004</v>
-      </c>
-      <c r="D1282" s="10" t="s">
-        <v>1294</v>
-      </c>
-      <c r="E1282" s="7">
-        <v>8</v>
-      </c>
-      <c r="F1282" s="7">
-        <v>60</v>
-      </c>
-      <c r="G1282" s="5">
-        <v>1</v>
-      </c>
-      <c r="H1282" s="7">
-        <v>9</v>
-      </c>
-      <c r="I1282" s="7">
-        <v>50</v>
-      </c>
-      <c r="J1282" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1282" s="11" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="1283" customHeight="1" spans="3:11">
-      <c r="C1283" s="7">
-        <v>8005</v>
-      </c>
-      <c r="D1283" s="10" t="s">
-        <v>1296</v>
-      </c>
-      <c r="E1283" s="7">
-        <v>8</v>
-      </c>
-      <c r="F1283" s="7">
-        <v>70</v>
-      </c>
-      <c r="G1283" s="5">
-        <v>1</v>
-      </c>
-      <c r="H1283" s="7">
-        <v>30</v>
-      </c>
-      <c r="I1283" s="7">
-        <v>30</v>
-      </c>
-      <c r="J1283" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1283" s="11" t="s">
-        <v>1297</v>
+        <v>2</v>
+      </c>
+      <c r="J1281" s="7" t="s">
+        <v>1187</v>
       </c>
     </row>
     <row r="1284" customHeight="1" spans="3:11">
       <c r="C1284" s="7">
-        <v>8006</v>
+        <v>8001</v>
       </c>
       <c r="D1284" s="10" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="E1284" s="7">
         <v>8</v>
       </c>
       <c r="F1284" s="7">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G1284" s="5">
         <v>1</v>
       </c>
-      <c r="H1284" s="7">
-        <v>7</v>
-      </c>
-      <c r="I1284" s="7">
-        <v>10</v>
+      <c r="H1284" s="5">
+        <v>20</v>
+      </c>
+      <c r="I1284" s="5">
+        <v>100</v>
       </c>
       <c r="J1284" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1284" s="11" t="s">
-        <v>1299</v>
+        <v>1293</v>
+      </c>
+      <c r="K1284" s="12" t="s">
+        <v>1294</v>
       </c>
     </row>
     <row r="1285" customHeight="1" spans="3:11">
       <c r="C1285" s="7">
-        <v>8007</v>
+        <v>8002</v>
       </c>
       <c r="D1285" s="10" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="E1285" s="7">
         <v>8</v>
       </c>
       <c r="F1285" s="7">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G1285" s="5">
         <v>1</v>
       </c>
       <c r="H1285" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I1285" s="7">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J1285" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1285" s="11" t="s">
-        <v>1301</v>
+        <v>1293</v>
+      </c>
+      <c r="K1285" s="12" t="s">
+        <v>1296</v>
       </c>
     </row>
     <row r="1286" customHeight="1" spans="3:11">
       <c r="C1286" s="7">
-        <v>8008</v>
-      </c>
-      <c r="D1286" s="10" t="s">
-        <v>1302</v>
+        <v>8003</v>
+      </c>
+      <c r="D1286" s="11" t="s">
+        <v>1297</v>
       </c>
       <c r="E1286" s="7">
         <v>8</v>
       </c>
       <c r="F1286" s="7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G1286" s="5">
-        <v>2</v>
-      </c>
-      <c r="H1286" s="5">
-        <v>0</v>
-      </c>
-      <c r="I1286" s="5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H1286" s="7">
+        <v>8</v>
+      </c>
+      <c r="I1286" s="7">
+        <v>10</v>
       </c>
       <c r="J1286" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="K1286" s="3" t="s">
-        <v>26</v>
+        <v>1293</v>
+      </c>
+      <c r="K1286" s="12" t="s">
+        <v>1298</v>
       </c>
     </row>
     <row r="1287" customHeight="1" spans="3:11">
       <c r="C1287" s="7">
-        <v>8009</v>
+        <v>8004</v>
       </c>
       <c r="D1287" s="10" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="E1287" s="7">
         <v>8</v>
       </c>
       <c r="F1287" s="7">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="G1287" s="5">
         <v>1</v>
       </c>
-      <c r="H1287" s="5">
-        <v>20</v>
-      </c>
-      <c r="I1287" s="5">
-        <v>100</v>
+      <c r="H1287" s="7">
+        <v>9</v>
+      </c>
+      <c r="I1287" s="7">
+        <v>50</v>
       </c>
       <c r="J1287" s="5" t="s">
-        <v>1304</v>
-      </c>
-      <c r="K1287" s="11" t="s">
-        <v>1289</v>
+        <v>1293</v>
+      </c>
+      <c r="K1287" s="12" t="s">
+        <v>1300</v>
       </c>
     </row>
     <row r="1288" customHeight="1" spans="3:11">
       <c r="C1288" s="7">
-        <v>8010</v>
-      </c>
-      <c r="D1288" s="12" t="s">
-        <v>1305</v>
+        <v>8005</v>
+      </c>
+      <c r="D1288" s="10" t="s">
+        <v>1301</v>
       </c>
       <c r="E1288" s="7">
         <v>8</v>
       </c>
       <c r="F1288" s="7">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="G1288" s="5">
         <v>1</v>
       </c>
       <c r="H1288" s="7">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I1288" s="7">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J1288" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="K1288" s="11" t="s">
-        <v>1307</v>
+        <v>1293</v>
+      </c>
+      <c r="K1288" s="12" t="s">
+        <v>1302</v>
       </c>
     </row>
     <row r="1289" customHeight="1" spans="3:11">
       <c r="C1289" s="7">
-        <v>8011</v>
+        <v>8006</v>
       </c>
       <c r="D1289" s="10" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="E1289" s="7">
         <v>8</v>
       </c>
       <c r="F1289" s="7">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="G1289" s="5">
         <v>1</v>
       </c>
       <c r="H1289" s="7">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I1289" s="7">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J1289" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="K1289" s="11" t="s">
-        <v>1310</v>
+        <v>1293</v>
+      </c>
+      <c r="K1289" s="12" t="s">
+        <v>1304</v>
       </c>
     </row>
     <row r="1290" customHeight="1" spans="3:11">
       <c r="C1290" s="7">
-        <v>8012</v>
+        <v>8007</v>
       </c>
       <c r="D1290" s="10" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
       <c r="E1290" s="7">
         <v>8</v>
       </c>
       <c r="F1290" s="7">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="G1290" s="5">
         <v>1</v>
       </c>
       <c r="H1290" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I1290" s="7">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J1290" s="5" t="s">
-        <v>1312</v>
-      </c>
-      <c r="K1290" s="11" t="s">
-        <v>1313</v>
+        <v>1293</v>
+      </c>
+      <c r="K1290" s="12" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="1291" customHeight="1" spans="3:11">
       <c r="C1291" s="7">
-        <v>8013</v>
+        <v>8008</v>
       </c>
       <c r="D1291" s="10" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
       <c r="E1291" s="7">
         <v>8</v>
       </c>
       <c r="F1291" s="7">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="G1291" s="5">
-        <v>1</v>
-      </c>
-      <c r="H1291" s="7">
-        <v>12</v>
-      </c>
-      <c r="I1291" s="7">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="H1291" s="5">
+        <v>0</v>
+      </c>
+      <c r="I1291" s="5">
+        <v>1</v>
       </c>
       <c r="J1291" s="5" t="s">
-        <v>1315</v>
-      </c>
-      <c r="K1291" s="11" t="s">
-        <v>1301</v>
+        <v>1293</v>
+      </c>
+      <c r="K1291" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="1292" customHeight="1" spans="3:11">
       <c r="C1292" s="7">
-        <v>8014</v>
+        <v>8009</v>
       </c>
       <c r="D1292" s="10" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="E1292" s="7">
         <v>8</v>
       </c>
       <c r="F1292" s="7">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="G1292" s="5">
         <v>1</v>
       </c>
-      <c r="H1292" s="7">
-        <v>13</v>
-      </c>
-      <c r="I1292" s="7">
-        <v>30</v>
+      <c r="H1292" s="5">
+        <v>20</v>
+      </c>
+      <c r="I1292" s="5">
+        <v>100</v>
       </c>
       <c r="J1292" s="5" t="s">
-        <v>1317</v>
-      </c>
-      <c r="K1292" s="11" t="s">
-        <v>1318</v>
+        <v>1309</v>
+      </c>
+      <c r="K1292" s="12" t="s">
+        <v>1294</v>
       </c>
     </row>
     <row r="1293" customHeight="1" spans="3:11">
       <c r="C1293" s="7">
-        <v>8015</v>
-      </c>
-      <c r="D1293" s="10" t="s">
-        <v>1319</v>
+        <v>8010</v>
+      </c>
+      <c r="D1293" s="11" t="s">
+        <v>1310</v>
       </c>
       <c r="E1293" s="7">
         <v>8</v>
       </c>
       <c r="F1293" s="7">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G1293" s="5">
-        <v>6</v>
-      </c>
-      <c r="H1293" s="5">
-        <v>0</v>
-      </c>
-      <c r="I1293" s="5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H1293" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1293" s="7">
+        <v>100</v>
       </c>
       <c r="J1293" s="5" t="s">
-        <v>1320</v>
-      </c>
-      <c r="K1293" s="3" t="s">
-        <v>1321</v>
+        <v>1311</v>
+      </c>
+      <c r="K1293" s="12" t="s">
+        <v>1312</v>
       </c>
     </row>
     <row r="1294" customHeight="1" spans="3:11">
       <c r="C1294" s="7">
-        <v>8016</v>
+        <v>8011</v>
       </c>
       <c r="D1294" s="10" t="s">
-        <v>1322</v>
+        <v>1313</v>
       </c>
       <c r="E1294" s="7">
         <v>8</v>
       </c>
       <c r="F1294" s="7">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="G1294" s="5">
         <v>1</v>
       </c>
-      <c r="H1294" s="5">
-        <v>2004</v>
-      </c>
-      <c r="I1294" s="5">
-        <v>10</v>
+      <c r="H1294" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1294" s="7">
+        <v>100</v>
       </c>
       <c r="J1294" s="5" t="s">
-        <v>1323</v>
-      </c>
-      <c r="K1294" s="11" t="s">
-        <v>760</v>
+        <v>1314</v>
+      </c>
+      <c r="K1294" s="12" t="s">
+        <v>1315</v>
       </c>
     </row>
     <row r="1295" customHeight="1" spans="3:11">
       <c r="C1295" s="7">
-        <v>8017</v>
+        <v>8012</v>
       </c>
       <c r="D1295" s="10" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="E1295" s="7">
         <v>8</v>
       </c>
       <c r="F1295" s="7">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="G1295" s="5">
         <v>1</v>
       </c>
-      <c r="H1295" s="5">
-        <v>2005</v>
-      </c>
-      <c r="I1295" s="5">
-        <v>10</v>
+      <c r="H1295" s="7">
+        <v>7</v>
+      </c>
+      <c r="I1295" s="7">
+        <v>15</v>
       </c>
       <c r="J1295" s="5" t="s">
-        <v>1325</v>
-      </c>
-      <c r="K1295" s="11" t="s">
-        <v>1326</v>
+        <v>1317</v>
+      </c>
+      <c r="K1295" s="12" t="s">
+        <v>1318</v>
       </c>
     </row>
     <row r="1296" customHeight="1" spans="3:11">
       <c r="C1296" s="7">
-        <v>8018</v>
+        <v>8013</v>
       </c>
       <c r="D1296" s="10" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="E1296" s="7">
         <v>8</v>
       </c>
       <c r="F1296" s="7">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="G1296" s="5">
         <v>1</v>
       </c>
-      <c r="H1296" s="5">
-        <v>2006</v>
+      <c r="H1296" s="7">
+        <v>12</v>
       </c>
       <c r="I1296" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J1296" s="5" t="s">
-        <v>1328</v>
-      </c>
-      <c r="K1296" s="11" t="s">
-        <v>1329</v>
+        <v>1320</v>
+      </c>
+      <c r="K1296" s="12" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="1297" customHeight="1" spans="3:11">
       <c r="C1297" s="7">
-        <v>8019</v>
-      </c>
-      <c r="D1297" s="12" t="s">
-        <v>1330</v>
+        <v>8014</v>
+      </c>
+      <c r="D1297" s="10" t="s">
+        <v>1321</v>
       </c>
       <c r="E1297" s="7">
         <v>8</v>
       </c>
       <c r="F1297" s="7">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="G1297" s="5">
         <v>1</v>
       </c>
       <c r="H1297" s="7">
-        <v>2003</v>
+        <v>13</v>
       </c>
       <c r="I1297" s="7">
         <v>30</v>
       </c>
       <c r="J1297" s="5" t="s">
-        <v>1331</v>
-      </c>
-      <c r="K1297" s="11" t="s">
-        <v>1332</v>
+        <v>1322</v>
+      </c>
+      <c r="K1297" s="12" t="s">
+        <v>1323</v>
       </c>
     </row>
     <row r="1298" customHeight="1" spans="3:11">
       <c r="C1298" s="7">
-        <v>8020</v>
+        <v>8015</v>
       </c>
       <c r="D1298" s="10" t="s">
-        <v>1333</v>
+        <v>1324</v>
       </c>
       <c r="E1298" s="7">
         <v>8</v>
       </c>
       <c r="F1298" s="7">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="G1298" s="5">
-        <v>1</v>
-      </c>
-      <c r="H1298" s="7">
-        <v>2002</v>
-      </c>
-      <c r="I1298" s="7">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="H1298" s="5">
+        <v>0</v>
+      </c>
+      <c r="I1298" s="5">
+        <v>1</v>
       </c>
       <c r="J1298" s="5" t="s">
-        <v>1334</v>
-      </c>
-      <c r="K1298" s="11" t="s">
-        <v>1335</v>
+        <v>1325</v>
+      </c>
+      <c r="K1298" s="3" t="s">
+        <v>1326</v>
       </c>
     </row>
     <row r="1299" customHeight="1" spans="3:11">
       <c r="C1299" s="7">
-        <v>8021</v>
+        <v>8016</v>
       </c>
       <c r="D1299" s="10" t="s">
-        <v>1336</v>
+        <v>1327</v>
       </c>
       <c r="E1299" s="7">
         <v>8</v>
       </c>
       <c r="F1299" s="7">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="G1299" s="5">
         <v>1</v>
       </c>
-      <c r="H1299" s="7">
-        <v>2001</v>
-      </c>
-      <c r="I1299" s="7">
+      <c r="H1299" s="5">
+        <v>2004</v>
+      </c>
+      <c r="I1299" s="5">
         <v>10</v>
       </c>
       <c r="J1299" s="5" t="s">
-        <v>1337</v>
-      </c>
-      <c r="K1299" s="11" t="s">
-        <v>1338</v>
+        <v>1328</v>
+      </c>
+      <c r="K1299" s="12" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="1300" customHeight="1" spans="3:11">
       <c r="C1300" s="7">
-        <v>8022</v>
+        <v>8017</v>
       </c>
       <c r="D1300" s="10" t="s">
-        <v>1339</v>
+        <v>1329</v>
       </c>
       <c r="E1300" s="7">
         <v>8</v>
       </c>
       <c r="F1300" s="7">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="G1300" s="5">
         <v>1</v>
       </c>
-      <c r="H1300" s="7">
-        <v>2011</v>
-      </c>
-      <c r="I1300" s="7">
+      <c r="H1300" s="5">
+        <v>2005</v>
+      </c>
+      <c r="I1300" s="5">
         <v>10</v>
       </c>
       <c r="J1300" s="5" t="s">
-        <v>1340</v>
-      </c>
-      <c r="K1300" s="11" t="s">
-        <v>1341</v>
+        <v>1330</v>
+      </c>
+      <c r="K1300" s="12" t="s">
+        <v>1331</v>
       </c>
     </row>
     <row r="1301" customHeight="1" spans="3:11">
       <c r="C1301" s="7">
-        <v>8023</v>
+        <v>8018</v>
       </c>
       <c r="D1301" s="10" t="s">
-        <v>1342</v>
+        <v>1332</v>
       </c>
       <c r="E1301" s="7">
         <v>8</v>
       </c>
       <c r="F1301" s="7">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="G1301" s="5">
         <v>1</v>
       </c>
-      <c r="H1301" s="7">
-        <v>2010</v>
+      <c r="H1301" s="5">
+        <v>2006</v>
       </c>
       <c r="I1301" s="7">
         <v>10</v>
       </c>
       <c r="J1301" s="5" t="s">
-        <v>1343</v>
-      </c>
-      <c r="K1301" s="11" t="s">
-        <v>1344</v>
+        <v>1333</v>
+      </c>
+      <c r="K1301" s="12" t="s">
+        <v>1334</v>
       </c>
     </row>
     <row r="1302" customHeight="1" spans="3:11">
       <c r="C1302" s="7">
-        <v>8024</v>
-      </c>
-      <c r="D1302" s="10" t="s">
-        <v>1345</v>
+        <v>8019</v>
+      </c>
+      <c r="D1302" s="11" t="s">
+        <v>1335</v>
       </c>
       <c r="E1302" s="7">
         <v>8</v>
       </c>
       <c r="F1302" s="7">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G1302" s="5">
-        <v>6</v>
-      </c>
-      <c r="H1302" s="5">
-        <v>0</v>
-      </c>
-      <c r="I1302" s="5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H1302" s="7">
+        <v>2003</v>
+      </c>
+      <c r="I1302" s="7">
+        <v>30</v>
       </c>
       <c r="J1302" s="5" t="s">
-        <v>1346</v>
-      </c>
-      <c r="K1302" s="3" t="s">
-        <v>1321</v>
+        <v>1336</v>
+      </c>
+      <c r="K1302" s="12" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="1303" customHeight="1" spans="3:11">
       <c r="C1303" s="7">
-        <v>8025</v>
+        <v>8020</v>
       </c>
       <c r="D1303" s="10" t="s">
-        <v>1347</v>
+        <v>1338</v>
       </c>
       <c r="E1303" s="7">
         <v>8</v>
       </c>
       <c r="F1303" s="7">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="G1303" s="5">
         <v>1</v>
       </c>
-      <c r="H1303" s="5">
-        <v>2004</v>
-      </c>
-      <c r="I1303" s="5">
+      <c r="H1303" s="7">
+        <v>2002</v>
+      </c>
+      <c r="I1303" s="7">
         <v>20</v>
       </c>
       <c r="J1303" s="5" t="s">
-        <v>1348</v>
-      </c>
-      <c r="K1303" s="11" t="s">
-        <v>760</v>
+        <v>1339</v>
+      </c>
+      <c r="K1303" s="12" t="s">
+        <v>1340</v>
       </c>
     </row>
     <row r="1304" customHeight="1" spans="3:11">
       <c r="C1304" s="7">
-        <v>8026</v>
+        <v>8021</v>
       </c>
       <c r="D1304" s="10" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
       <c r="E1304" s="7">
         <v>8</v>
       </c>
       <c r="F1304" s="7">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="G1304" s="5">
         <v>1</v>
       </c>
-      <c r="H1304" s="5">
-        <v>2005</v>
-      </c>
-      <c r="I1304" s="5">
-        <v>20</v>
+      <c r="H1304" s="7">
+        <v>2001</v>
+      </c>
+      <c r="I1304" s="7">
+        <v>10</v>
       </c>
       <c r="J1304" s="5" t="s">
-        <v>1350</v>
-      </c>
-      <c r="K1304" s="11" t="s">
-        <v>1326</v>
+        <v>1342</v>
+      </c>
+      <c r="K1304" s="12" t="s">
+        <v>1343</v>
       </c>
     </row>
     <row r="1305" customHeight="1" spans="3:11">
       <c r="C1305" s="7">
-        <v>8027</v>
+        <v>8022</v>
       </c>
       <c r="D1305" s="10" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
       <c r="E1305" s="7">
         <v>8</v>
       </c>
       <c r="F1305" s="7">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="G1305" s="5">
         <v>1</v>
       </c>
-      <c r="H1305" s="5">
-        <v>2006</v>
-      </c>
-      <c r="I1305" s="5">
-        <v>20</v>
+      <c r="H1305" s="7">
+        <v>2011</v>
+      </c>
+      <c r="I1305" s="7">
+        <v>10</v>
       </c>
       <c r="J1305" s="5" t="s">
-        <v>1352</v>
-      </c>
-      <c r="K1305" s="11" t="s">
-        <v>1329</v>
+        <v>1345</v>
+      </c>
+      <c r="K1305" s="12" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="1306" customHeight="1" spans="3:11">
       <c r="C1306" s="7">
-        <v>8028</v>
-      </c>
-      <c r="D1306" s="12" t="s">
-        <v>1353</v>
+        <v>8023</v>
+      </c>
+      <c r="D1306" s="10" t="s">
+        <v>1347</v>
       </c>
       <c r="E1306" s="7">
         <v>8</v>
       </c>
       <c r="F1306" s="7">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="G1306" s="5">
         <v>1</v>
       </c>
       <c r="H1306" s="7">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="I1306" s="7">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="J1306" s="5" t="s">
-        <v>1354</v>
-      </c>
-      <c r="K1306" s="11" t="s">
-        <v>1332</v>
+        <v>1348</v>
+      </c>
+      <c r="K1306" s="12" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="1307" customHeight="1" spans="3:11">
       <c r="C1307" s="7">
-        <v>8029</v>
+        <v>8024</v>
       </c>
       <c r="D1307" s="10" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="E1307" s="7">
         <v>8</v>
       </c>
       <c r="F1307" s="7">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G1307" s="5">
-        <v>1</v>
-      </c>
-      <c r="H1307" s="7">
-        <v>2002</v>
-      </c>
-      <c r="I1307" s="7">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="H1307" s="5">
+        <v>0</v>
+      </c>
+      <c r="I1307" s="5">
+        <v>1</v>
       </c>
       <c r="J1307" s="5" t="s">
-        <v>1356</v>
-      </c>
-      <c r="K1307" s="11" t="s">
-        <v>1335</v>
+        <v>1351</v>
+      </c>
+      <c r="K1307" s="3" t="s">
+        <v>1326</v>
       </c>
     </row>
     <row r="1308" customHeight="1" spans="3:11">
       <c r="C1308" s="7">
-        <v>8030</v>
+        <v>8025</v>
       </c>
       <c r="D1308" s="10" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="E1308" s="7">
         <v>8</v>
       </c>
       <c r="F1308" s="7">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="G1308" s="5">
         <v>1</v>
       </c>
-      <c r="H1308" s="7">
-        <v>2001</v>
-      </c>
-      <c r="I1308" s="7">
+      <c r="H1308" s="5">
+        <v>2004</v>
+      </c>
+      <c r="I1308" s="5">
         <v>20</v>
       </c>
       <c r="J1308" s="5" t="s">
-        <v>1358</v>
-      </c>
-      <c r="K1308" s="11" t="s">
-        <v>1338</v>
+        <v>1353</v>
+      </c>
+      <c r="K1308" s="12" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="1309" customHeight="1" spans="3:11">
       <c r="C1309" s="7">
-        <v>8031</v>
+        <v>8026</v>
       </c>
       <c r="D1309" s="10" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="E1309" s="7">
         <v>8</v>
       </c>
       <c r="F1309" s="7">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="G1309" s="5">
         <v>1</v>
       </c>
-      <c r="H1309" s="7">
-        <v>2011</v>
-      </c>
-      <c r="I1309" s="7">
+      <c r="H1309" s="5">
+        <v>2005</v>
+      </c>
+      <c r="I1309" s="5">
         <v>20</v>
       </c>
       <c r="J1309" s="5" t="s">
-        <v>1360</v>
-      </c>
-      <c r="K1309" s="11" t="s">
-        <v>1341</v>
+        <v>1355</v>
+      </c>
+      <c r="K1309" s="12" t="s">
+        <v>1331</v>
       </c>
     </row>
     <row r="1310" customHeight="1" spans="3:11">
       <c r="C1310" s="7">
-        <v>8032</v>
+        <v>8027</v>
       </c>
       <c r="D1310" s="10" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="E1310" s="7">
         <v>8</v>
       </c>
       <c r="F1310" s="7">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="G1310" s="5">
         <v>1</v>
       </c>
-      <c r="H1310" s="7">
-        <v>2010</v>
-      </c>
-      <c r="I1310" s="7">
+      <c r="H1310" s="5">
+        <v>2006</v>
+      </c>
+      <c r="I1310" s="5">
         <v>20</v>
       </c>
       <c r="J1310" s="5" t="s">
-        <v>1362</v>
-      </c>
-      <c r="K1310" s="11" t="s">
-        <v>1344</v>
+        <v>1357</v>
+      </c>
+      <c r="K1310" s="12" t="s">
+        <v>1334</v>
       </c>
     </row>
     <row r="1311" customHeight="1" spans="3:11">
       <c r="C1311" s="7">
-        <v>8033</v>
-      </c>
-      <c r="D1311" s="10" t="s">
-        <v>1363</v>
+        <v>8028</v>
+      </c>
+      <c r="D1311" s="11" t="s">
+        <v>1358</v>
       </c>
       <c r="E1311" s="7">
         <v>8</v>
       </c>
       <c r="F1311" s="7">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G1311" s="5">
         <v>1</v>
@@ -43748,164 +43783,164 @@
       <c r="H1311" s="7">
         <v>2003</v>
       </c>
-      <c r="I1311" s="5">
+      <c r="I1311" s="7">
         <v>60</v>
       </c>
       <c r="J1311" s="5" t="s">
-        <v>1364</v>
-      </c>
-      <c r="K1311" s="11" t="s">
-        <v>1332</v>
+        <v>1359</v>
+      </c>
+      <c r="K1311" s="12" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="1312" customHeight="1" spans="3:11">
       <c r="C1312" s="7">
-        <v>8034</v>
+        <v>8029</v>
       </c>
       <c r="D1312" s="10" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="E1312" s="7">
         <v>8</v>
       </c>
       <c r="F1312" s="7">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="G1312" s="5">
         <v>1</v>
       </c>
-      <c r="H1312" s="5">
-        <v>2004</v>
-      </c>
-      <c r="I1312" s="5">
-        <v>30</v>
+      <c r="H1312" s="7">
+        <v>2002</v>
+      </c>
+      <c r="I1312" s="7">
+        <v>40</v>
       </c>
       <c r="J1312" s="5" t="s">
-        <v>1348</v>
-      </c>
-      <c r="K1312" s="11" t="s">
-        <v>760</v>
+        <v>1361</v>
+      </c>
+      <c r="K1312" s="12" t="s">
+        <v>1340</v>
       </c>
     </row>
     <row r="1313" customHeight="1" spans="3:11">
       <c r="C1313" s="7">
-        <v>8035</v>
+        <v>8030</v>
       </c>
       <c r="D1313" s="10" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="E1313" s="7">
         <v>8</v>
       </c>
       <c r="F1313" s="7">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="G1313" s="5">
         <v>1</v>
       </c>
-      <c r="H1313" s="5">
-        <v>2005</v>
-      </c>
-      <c r="I1313" s="5">
-        <v>30</v>
+      <c r="H1313" s="7">
+        <v>2001</v>
+      </c>
+      <c r="I1313" s="7">
+        <v>20</v>
       </c>
       <c r="J1313" s="5" t="s">
-        <v>1350</v>
-      </c>
-      <c r="K1313" s="11" t="s">
-        <v>1326</v>
+        <v>1363</v>
+      </c>
+      <c r="K1313" s="12" t="s">
+        <v>1343</v>
       </c>
     </row>
     <row r="1314" customHeight="1" spans="3:11">
       <c r="C1314" s="7">
-        <v>8036</v>
+        <v>8031</v>
       </c>
       <c r="D1314" s="10" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="E1314" s="7">
         <v>8</v>
       </c>
       <c r="F1314" s="7">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="G1314" s="5">
         <v>1</v>
       </c>
-      <c r="H1314" s="5">
-        <v>2006</v>
-      </c>
-      <c r="I1314" s="5">
-        <v>30</v>
+      <c r="H1314" s="7">
+        <v>2011</v>
+      </c>
+      <c r="I1314" s="7">
+        <v>20</v>
       </c>
       <c r="J1314" s="5" t="s">
-        <v>1352</v>
-      </c>
-      <c r="K1314" s="11" t="s">
-        <v>1329</v>
+        <v>1365</v>
+      </c>
+      <c r="K1314" s="12" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="1315" customHeight="1" spans="3:11">
       <c r="C1315" s="7">
-        <v>8037</v>
-      </c>
-      <c r="D1315" s="12" t="s">
-        <v>1368</v>
+        <v>8032</v>
+      </c>
+      <c r="D1315" s="10" t="s">
+        <v>1366</v>
       </c>
       <c r="E1315" s="7">
         <v>8</v>
       </c>
       <c r="F1315" s="7">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="G1315" s="5">
         <v>1</v>
       </c>
       <c r="H1315" s="7">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="I1315" s="7">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J1315" s="5" t="s">
-        <v>1354</v>
-      </c>
-      <c r="K1315" s="11" t="s">
-        <v>1332</v>
+        <v>1367</v>
+      </c>
+      <c r="K1315" s="12" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="1316" customHeight="1" spans="3:11">
       <c r="C1316" s="7">
-        <v>8038</v>
+        <v>8033</v>
       </c>
       <c r="D1316" s="10" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E1316" s="7">
         <v>8</v>
       </c>
       <c r="F1316" s="7">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="G1316" s="5">
         <v>1</v>
       </c>
       <c r="H1316" s="7">
-        <v>2002</v>
-      </c>
-      <c r="I1316" s="7">
-        <v>80</v>
+        <v>2003</v>
+      </c>
+      <c r="I1316" s="5">
+        <v>60</v>
       </c>
       <c r="J1316" s="5" t="s">
-        <v>1356</v>
-      </c>
-      <c r="K1316" s="11" t="s">
-        <v>1335</v>
+        <v>1369</v>
+      </c>
+      <c r="K1316" s="12" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="1317" customHeight="1" spans="3:11">
       <c r="C1317" s="7">
-        <v>8039</v>
+        <v>8034</v>
       </c>
       <c r="D1317" s="10" t="s">
         <v>1370</v>
@@ -43914,27 +43949,27 @@
         <v>8</v>
       </c>
       <c r="F1317" s="7">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="G1317" s="5">
         <v>1</v>
       </c>
-      <c r="H1317" s="7">
-        <v>2001</v>
+      <c r="H1317" s="5">
+        <v>2004</v>
       </c>
       <c r="I1317" s="5">
         <v>30</v>
       </c>
       <c r="J1317" s="5" t="s">
-        <v>1358</v>
-      </c>
-      <c r="K1317" s="11" t="s">
-        <v>1338</v>
+        <v>1353</v>
+      </c>
+      <c r="K1317" s="12" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="1318" customHeight="1" spans="3:11">
       <c r="C1318" s="7">
-        <v>8040</v>
+        <v>8035</v>
       </c>
       <c r="D1318" s="10" t="s">
         <v>1371</v>
@@ -43943,27 +43978,27 @@
         <v>8</v>
       </c>
       <c r="F1318" s="7">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="G1318" s="5">
         <v>1</v>
       </c>
-      <c r="H1318" s="7">
-        <v>2011</v>
+      <c r="H1318" s="5">
+        <v>2005</v>
       </c>
       <c r="I1318" s="5">
         <v>30</v>
       </c>
       <c r="J1318" s="5" t="s">
-        <v>1360</v>
-      </c>
-      <c r="K1318" s="11" t="s">
-        <v>1341</v>
+        <v>1355</v>
+      </c>
+      <c r="K1318" s="12" t="s">
+        <v>1331</v>
       </c>
     </row>
     <row r="1319" customHeight="1" spans="3:11">
       <c r="C1319" s="7">
-        <v>8041</v>
+        <v>8036</v>
       </c>
       <c r="D1319" s="10" t="s">
         <v>1372</v>
@@ -43972,36 +44007,36 @@
         <v>8</v>
       </c>
       <c r="F1319" s="7">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="G1319" s="5">
         <v>1</v>
       </c>
-      <c r="H1319" s="7">
-        <v>2010</v>
+      <c r="H1319" s="5">
+        <v>2006</v>
       </c>
       <c r="I1319" s="5">
         <v>30</v>
       </c>
       <c r="J1319" s="5" t="s">
-        <v>1362</v>
-      </c>
-      <c r="K1319" s="11" t="s">
-        <v>1344</v>
+        <v>1357</v>
+      </c>
+      <c r="K1319" s="12" t="s">
+        <v>1334</v>
       </c>
     </row>
     <row r="1320" customHeight="1" spans="3:11">
       <c r="C1320" s="7">
-        <v>8042</v>
-      </c>
-      <c r="D1320" s="10" t="s">
+        <v>8037</v>
+      </c>
+      <c r="D1320" s="11" t="s">
         <v>1373</v>
       </c>
       <c r="E1320" s="7">
         <v>8</v>
       </c>
       <c r="F1320" s="7">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G1320" s="5">
         <v>1</v>
@@ -44013,446 +44048,447 @@
         <v>90</v>
       </c>
       <c r="J1320" s="5" t="s">
-        <v>1364</v>
-      </c>
-      <c r="K1320" s="11" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="1326" customHeight="1" spans="3:10">
+        <v>1359</v>
+      </c>
+      <c r="K1320" s="12" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="1321" customHeight="1" spans="3:11">
+      <c r="C1321" s="7">
+        <v>8038</v>
+      </c>
+      <c r="D1321" s="10" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E1321" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1321" s="7">
+        <v>460</v>
+      </c>
+      <c r="G1321" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1321" s="7">
+        <v>2002</v>
+      </c>
+      <c r="I1321" s="7">
+        <v>80</v>
+      </c>
+      <c r="J1321" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K1321" s="12" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="1322" customHeight="1" spans="3:11">
+      <c r="C1322" s="7">
+        <v>8039</v>
+      </c>
+      <c r="D1322" s="10" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E1322" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1322" s="7">
+        <v>470</v>
+      </c>
+      <c r="G1322" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1322" s="7">
+        <v>2001</v>
+      </c>
+      <c r="I1322" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1322" s="5" t="s">
+        <v>1363</v>
+      </c>
+      <c r="K1322" s="12" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="1323" customHeight="1" spans="3:11">
+      <c r="C1323" s="7">
+        <v>8040</v>
+      </c>
+      <c r="D1323" s="10" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E1323" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1323" s="7">
+        <v>480</v>
+      </c>
+      <c r="G1323" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1323" s="7">
+        <v>2011</v>
+      </c>
+      <c r="I1323" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1323" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="K1323" s="12" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1324" customHeight="1" spans="3:11">
+      <c r="C1324" s="7">
+        <v>8041</v>
+      </c>
+      <c r="D1324" s="10" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E1324" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1324" s="7">
+        <v>490</v>
+      </c>
+      <c r="G1324" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1324" s="7">
+        <v>2010</v>
+      </c>
+      <c r="I1324" s="5">
+        <v>30</v>
+      </c>
+      <c r="J1324" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="K1324" s="12" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="1325" customHeight="1" spans="3:11">
+      <c r="C1325" s="7">
+        <v>8042</v>
+      </c>
+      <c r="D1325" s="10" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E1325" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1325" s="7">
+        <v>500</v>
+      </c>
+      <c r="G1325" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1325" s="7">
+        <v>2003</v>
+      </c>
+      <c r="I1325" s="7">
+        <v>90</v>
+      </c>
+      <c r="J1325" s="5" t="s">
+        <v>1369</v>
+      </c>
+      <c r="K1325" s="12" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="1326" customHeight="1" spans="3:11">
       <c r="C1326" s="7">
-        <v>9001</v>
-      </c>
-      <c r="D1326" s="7" t="s">
-        <v>1374</v>
+        <v>8043</v>
+      </c>
+      <c r="D1326" s="10" t="s">
+        <v>1379</v>
       </c>
       <c r="E1326" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1326" s="7">
-        <v>10</v>
-      </c>
-      <c r="G1326" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1326" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1326" s="7">
+        <v>520</v>
+      </c>
+      <c r="G1326" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1326" s="5">
+        <v>2004</v>
+      </c>
+      <c r="I1326" s="5">
+        <v>40</v>
+      </c>
+      <c r="J1326" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="K1326" s="12" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="1327" customHeight="1" spans="3:11">
+      <c r="C1327" s="7">
+        <v>8044</v>
+      </c>
+      <c r="D1327" s="10" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E1327" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1327" s="7">
+        <v>530</v>
+      </c>
+      <c r="G1327" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1327" s="5">
+        <v>2005</v>
+      </c>
+      <c r="I1327" s="5">
+        <v>40</v>
+      </c>
+      <c r="J1327" s="5" t="s">
+        <v>1355</v>
+      </c>
+      <c r="K1327" s="12" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="1328" customHeight="1" spans="3:11">
+      <c r="C1328" s="7">
+        <v>8045</v>
+      </c>
+      <c r="D1328" s="10" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E1328" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1328" s="7">
+        <v>540</v>
+      </c>
+      <c r="G1328" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1328" s="5">
+        <v>2006</v>
+      </c>
+      <c r="I1328" s="5">
+        <v>40</v>
+      </c>
+      <c r="J1328" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="K1328" s="12" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="1329" customHeight="1" spans="3:11">
+      <c r="C1329" s="7">
+        <v>8046</v>
+      </c>
+      <c r="D1329" s="11" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E1329" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1329" s="7">
+        <v>550</v>
+      </c>
+      <c r="G1329" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1329" s="7">
+        <v>2003</v>
+      </c>
+      <c r="I1329" s="7">
+        <v>100</v>
+      </c>
+      <c r="J1329" s="5" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K1329" s="12" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="1330" customHeight="1" spans="3:11">
+      <c r="C1330" s="7">
+        <v>8047</v>
+      </c>
+      <c r="D1330" s="10" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E1330" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1330" s="7">
+        <v>560</v>
+      </c>
+      <c r="G1330" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1330" s="7">
+        <v>2002</v>
+      </c>
+      <c r="I1330" s="7">
+        <v>150</v>
+      </c>
+      <c r="J1330" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K1330" s="12" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="1331" customHeight="1" spans="3:11">
+      <c r="C1331" s="7">
+        <v>8048</v>
+      </c>
+      <c r="D1331" s="10" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E1331" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1331" s="7">
+        <v>570</v>
+      </c>
+      <c r="G1331" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1331" s="7">
+        <v>2001</v>
+      </c>
+      <c r="I1331" s="5">
         <v>50</v>
       </c>
-      <c r="J1326" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1327" customHeight="1" spans="3:10">
-      <c r="C1327" s="7">
-        <v>9002</v>
-      </c>
-      <c r="D1327" s="7" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E1327" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1327" s="7">
-        <f t="shared" ref="F1327:F1390" si="42">F1326+10</f>
-        <v>20</v>
-      </c>
-      <c r="G1327" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1327" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1327" s="7">
+      <c r="J1331" s="5" t="s">
+        <v>1363</v>
+      </c>
+      <c r="K1331" s="12" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="1332" customHeight="1" spans="3:11">
+      <c r="C1332" s="7">
+        <v>8049</v>
+      </c>
+      <c r="D1332" s="10" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1332" s="7">
+        <v>8</v>
+      </c>
+      <c r="F1332" s="7">
+        <v>580</v>
+      </c>
+      <c r="G1332" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1332" s="7">
+        <v>2011</v>
+      </c>
+      <c r="I1332" s="5">
         <v>50</v>
       </c>
-      <c r="J1327" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1328" customHeight="1" spans="3:10">
-      <c r="C1328" s="7">
-        <v>9003</v>
-      </c>
-      <c r="D1328" s="7" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E1328" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1328" s="7">
-        <f t="shared" si="42"/>
-        <v>30</v>
-      </c>
-      <c r="G1328" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1328" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1328" s="7">
-        <v>50</v>
-      </c>
-      <c r="J1328" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1329" customHeight="1" spans="3:10">
-      <c r="C1329" s="7">
-        <v>9004</v>
-      </c>
-      <c r="D1329" s="7" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E1329" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1329" s="7">
-        <f t="shared" si="42"/>
-        <v>40</v>
-      </c>
-      <c r="G1329" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1329" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1329" s="7">
-        <v>50</v>
-      </c>
-      <c r="J1329" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1330" customHeight="1" spans="3:10">
-      <c r="C1330" s="7">
-        <v>9005</v>
-      </c>
-      <c r="D1330" s="7" t="s">
-        <v>1379</v>
-      </c>
-      <c r="E1330" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1330" s="7">
-        <f t="shared" si="42"/>
-        <v>50</v>
-      </c>
-      <c r="G1330" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1330" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1330" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1330" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1331" customHeight="1" spans="3:10">
-      <c r="C1331" s="7">
-        <v>9006</v>
-      </c>
-      <c r="D1331" s="7" t="s">
-        <v>1380</v>
-      </c>
-      <c r="E1331" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1331" s="7">
-        <f t="shared" si="42"/>
-        <v>60</v>
-      </c>
-      <c r="G1331" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1331" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1331" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1331" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1332" customHeight="1" spans="3:10">
-      <c r="C1332" s="7">
-        <v>9007</v>
-      </c>
-      <c r="D1332" s="7" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E1332" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1332" s="7">
-        <f t="shared" si="42"/>
-        <v>70</v>
-      </c>
-      <c r="G1332" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1332" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1332" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1332" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1333" customHeight="1" spans="3:10">
+      <c r="J1332" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="K1332" s="12" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1333" customHeight="1" spans="3:11">
       <c r="C1333" s="7">
-        <v>9008</v>
-      </c>
-      <c r="D1333" s="7" t="s">
-        <v>1382</v>
+        <v>8050</v>
+      </c>
+      <c r="D1333" s="10" t="s">
+        <v>1386</v>
       </c>
       <c r="E1333" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1333" s="7">
-        <f t="shared" si="42"/>
+        <v>590</v>
+      </c>
+      <c r="G1333" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1333" s="7">
+        <v>2010</v>
+      </c>
+      <c r="I1333" s="5">
         <v>80</v>
       </c>
-      <c r="G1333" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1333" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1333" s="7">
-        <v>60</v>
-      </c>
-      <c r="J1333" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1334" customHeight="1" spans="3:10">
+      <c r="J1333" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="K1333" s="12" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="1334" customHeight="1" spans="3:11">
       <c r="C1334" s="7">
-        <v>9009</v>
-      </c>
-      <c r="D1334" s="7" t="s">
-        <v>1383</v>
+        <v>8051</v>
+      </c>
+      <c r="D1334" s="10" t="s">
+        <v>1388</v>
       </c>
       <c r="E1334" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1334" s="7">
-        <f t="shared" si="42"/>
-        <v>90</v>
-      </c>
-      <c r="G1334" s="7">
+        <v>600</v>
+      </c>
+      <c r="G1334" s="5">
         <v>1</v>
       </c>
       <c r="H1334" s="7">
-        <v>18</v>
+        <v>2003</v>
       </c>
       <c r="I1334" s="7">
-        <v>70</v>
-      </c>
-      <c r="J1334" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1335" customHeight="1" spans="3:10">
-      <c r="C1335" s="7">
-        <v>9010</v>
-      </c>
-      <c r="D1335" s="7" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E1335" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1335" s="7">
-        <f t="shared" si="42"/>
         <v>100</v>
       </c>
-      <c r="G1335" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1335" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1335" s="7">
-        <v>70</v>
-      </c>
-      <c r="J1335" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1336" customHeight="1" spans="3:10">
-      <c r="C1336" s="7">
-        <v>9011</v>
-      </c>
-      <c r="D1336" s="7" t="s">
-        <v>1385</v>
-      </c>
-      <c r="E1336" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1336" s="7">
-        <f t="shared" si="42"/>
-        <v>110</v>
-      </c>
-      <c r="G1336" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1336" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1336" s="7">
-        <v>70</v>
-      </c>
-      <c r="J1336" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1337" customHeight="1" spans="3:10">
-      <c r="C1337" s="7">
-        <v>9012</v>
-      </c>
-      <c r="D1337" s="7" t="s">
-        <v>1386</v>
-      </c>
-      <c r="E1337" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1337" s="7">
-        <f t="shared" si="42"/>
-        <v>120</v>
-      </c>
-      <c r="G1337" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1337" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1337" s="7">
-        <v>70</v>
-      </c>
-      <c r="J1337" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1338" customHeight="1" spans="3:10">
-      <c r="C1338" s="7">
-        <v>9013</v>
-      </c>
-      <c r="D1338" s="7" t="s">
-        <v>1387</v>
-      </c>
-      <c r="E1338" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1338" s="7">
-        <f t="shared" si="42"/>
-        <v>130</v>
-      </c>
-      <c r="G1338" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1338" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1338" s="7">
-        <v>80</v>
-      </c>
-      <c r="J1338" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1339" customHeight="1" spans="3:10">
-      <c r="C1339" s="7">
-        <v>9014</v>
-      </c>
-      <c r="D1339" s="7" t="s">
-        <v>1388</v>
-      </c>
-      <c r="E1339" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1339" s="7">
-        <f t="shared" si="42"/>
-        <v>140</v>
-      </c>
-      <c r="G1339" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1339" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1339" s="7">
-        <v>80</v>
-      </c>
-      <c r="J1339" s="7" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="1340" customHeight="1" spans="3:10">
-      <c r="C1340" s="7">
-        <v>9015</v>
-      </c>
-      <c r="D1340" s="7" t="s">
-        <v>1389</v>
-      </c>
-      <c r="E1340" s="7">
-        <v>9</v>
-      </c>
-      <c r="F1340" s="7">
-        <f t="shared" si="42"/>
-        <v>150</v>
-      </c>
-      <c r="G1340" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1340" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1340" s="7">
-        <v>80</v>
-      </c>
-      <c r="J1340" s="7" t="s">
-        <v>1375</v>
+      <c r="J1334" s="5" t="s">
+        <v>1369</v>
+      </c>
+      <c r="K1334" s="12" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="1341" customHeight="1" spans="3:10">
       <c r="C1341" s="7">
-        <v>9016</v>
+        <v>9001</v>
       </c>
       <c r="D1341" s="7" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E1341" s="7">
         <v>9</v>
       </c>
       <c r="F1341" s="7">
-        <f t="shared" si="42"/>
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="G1341" s="7">
         <v>1</v>
       </c>
       <c r="H1341" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1341" s="7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J1341" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1342" customHeight="1" spans="3:10">
       <c r="C1342" s="7">
-        <v>9017</v>
+        <v>9002</v>
       </c>
       <c r="D1342" s="7" t="s">
         <v>1391</v>
@@ -44461,25 +44497,25 @@
         <v>9</v>
       </c>
       <c r="F1342" s="7">
-        <f t="shared" si="42"/>
-        <v>170</v>
+        <f t="shared" ref="F1342:F1405" si="43">F1341+10</f>
+        <v>20</v>
       </c>
       <c r="G1342" s="7">
         <v>1</v>
       </c>
       <c r="H1342" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1342" s="7">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J1342" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1343" customHeight="1" spans="3:10">
       <c r="C1343" s="7">
-        <v>9018</v>
+        <v>9003</v>
       </c>
       <c r="D1343" s="7" t="s">
         <v>1392</v>
@@ -44488,25 +44524,25 @@
         <v>9</v>
       </c>
       <c r="F1343" s="7">
-        <f t="shared" si="42"/>
-        <v>180</v>
+        <f t="shared" si="43"/>
+        <v>30</v>
       </c>
       <c r="G1343" s="7">
         <v>1</v>
       </c>
       <c r="H1343" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1343" s="7">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J1343" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1344" customHeight="1" spans="3:10">
       <c r="C1344" s="7">
-        <v>9019</v>
+        <v>9004</v>
       </c>
       <c r="D1344" s="7" t="s">
         <v>1393</v>
@@ -44515,25 +44551,25 @@
         <v>9</v>
       </c>
       <c r="F1344" s="7">
-        <f t="shared" si="42"/>
-        <v>190</v>
+        <f t="shared" si="43"/>
+        <v>40</v>
       </c>
       <c r="G1344" s="7">
         <v>1</v>
       </c>
       <c r="H1344" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1344" s="7">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J1344" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1345" customHeight="1" spans="3:10">
       <c r="C1345" s="7">
-        <v>9020</v>
+        <v>9005</v>
       </c>
       <c r="D1345" s="7" t="s">
         <v>1394</v>
@@ -44542,25 +44578,25 @@
         <v>9</v>
       </c>
       <c r="F1345" s="7">
-        <f t="shared" si="42"/>
-        <v>200</v>
+        <f t="shared" si="43"/>
+        <v>50</v>
       </c>
       <c r="G1345" s="7">
         <v>1</v>
       </c>
       <c r="H1345" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1345" s="7">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J1345" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1346" customHeight="1" spans="3:10">
       <c r="C1346" s="7">
-        <v>9021</v>
+        <v>9006</v>
       </c>
       <c r="D1346" s="7" t="s">
         <v>1395</v>
@@ -44569,25 +44605,25 @@
         <v>9</v>
       </c>
       <c r="F1346" s="7">
-        <f t="shared" si="42"/>
-        <v>210</v>
+        <f t="shared" si="43"/>
+        <v>60</v>
       </c>
       <c r="G1346" s="7">
         <v>1</v>
       </c>
       <c r="H1346" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1346" s="7">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J1346" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1347" customHeight="1" spans="3:10">
       <c r="C1347" s="7">
-        <v>9022</v>
+        <v>9007</v>
       </c>
       <c r="D1347" s="7" t="s">
         <v>1396</v>
@@ -44596,25 +44632,25 @@
         <v>9</v>
       </c>
       <c r="F1347" s="7">
-        <f t="shared" si="42"/>
-        <v>220</v>
+        <f t="shared" si="43"/>
+        <v>70</v>
       </c>
       <c r="G1347" s="7">
         <v>1</v>
       </c>
       <c r="H1347" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1347" s="7">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J1347" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1348" customHeight="1" spans="3:10">
       <c r="C1348" s="7">
-        <v>9023</v>
+        <v>9008</v>
       </c>
       <c r="D1348" s="7" t="s">
         <v>1397</v>
@@ -44623,25 +44659,25 @@
         <v>9</v>
       </c>
       <c r="F1348" s="7">
-        <f t="shared" si="42"/>
-        <v>230</v>
+        <f t="shared" si="43"/>
+        <v>80</v>
       </c>
       <c r="G1348" s="7">
         <v>1</v>
       </c>
       <c r="H1348" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1348" s="7">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J1348" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1349" customHeight="1" spans="3:10">
       <c r="C1349" s="7">
-        <v>9024</v>
+        <v>9009</v>
       </c>
       <c r="D1349" s="7" t="s">
         <v>1398</v>
@@ -44650,25 +44686,25 @@
         <v>9</v>
       </c>
       <c r="F1349" s="7">
-        <f t="shared" si="42"/>
-        <v>240</v>
+        <f t="shared" si="43"/>
+        <v>90</v>
       </c>
       <c r="G1349" s="7">
         <v>1</v>
       </c>
       <c r="H1349" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1349" s="7">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J1349" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1350" customHeight="1" spans="3:10">
       <c r="C1350" s="7">
-        <v>9025</v>
+        <v>9010</v>
       </c>
       <c r="D1350" s="7" t="s">
         <v>1399</v>
@@ -44677,25 +44713,25 @@
         <v>9</v>
       </c>
       <c r="F1350" s="7">
-        <f t="shared" si="42"/>
-        <v>250</v>
+        <f t="shared" si="43"/>
+        <v>100</v>
       </c>
       <c r="G1350" s="7">
         <v>1</v>
       </c>
       <c r="H1350" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1350" s="7">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J1350" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1351" customHeight="1" spans="3:10">
       <c r="C1351" s="7">
-        <v>9026</v>
+        <v>9011</v>
       </c>
       <c r="D1351" s="7" t="s">
         <v>1400</v>
@@ -44704,25 +44740,25 @@
         <v>9</v>
       </c>
       <c r="F1351" s="7">
-        <f t="shared" si="42"/>
-        <v>260</v>
+        <f t="shared" si="43"/>
+        <v>110</v>
       </c>
       <c r="G1351" s="7">
         <v>1</v>
       </c>
       <c r="H1351" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1351" s="7">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J1351" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1352" customHeight="1" spans="3:10">
       <c r="C1352" s="7">
-        <v>9027</v>
+        <v>9012</v>
       </c>
       <c r="D1352" s="7" t="s">
         <v>1401</v>
@@ -44731,25 +44767,25 @@
         <v>9</v>
       </c>
       <c r="F1352" s="7">
-        <f t="shared" si="42"/>
-        <v>270</v>
+        <f t="shared" si="43"/>
+        <v>120</v>
       </c>
       <c r="G1352" s="7">
         <v>1</v>
       </c>
       <c r="H1352" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1352" s="7">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J1352" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1353" customHeight="1" spans="3:10">
       <c r="C1353" s="7">
-        <v>9028</v>
+        <v>9013</v>
       </c>
       <c r="D1353" s="7" t="s">
         <v>1402</v>
@@ -44758,25 +44794,25 @@
         <v>9</v>
       </c>
       <c r="F1353" s="7">
-        <f t="shared" si="42"/>
-        <v>280</v>
+        <f t="shared" si="43"/>
+        <v>130</v>
       </c>
       <c r="G1353" s="7">
         <v>1</v>
       </c>
       <c r="H1353" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1353" s="7">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J1353" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1354" customHeight="1" spans="3:10">
       <c r="C1354" s="7">
-        <v>9029</v>
+        <v>9014</v>
       </c>
       <c r="D1354" s="7" t="s">
         <v>1403</v>
@@ -44785,25 +44821,25 @@
         <v>9</v>
       </c>
       <c r="F1354" s="7">
-        <f t="shared" si="42"/>
-        <v>290</v>
+        <f t="shared" si="43"/>
+        <v>140</v>
       </c>
       <c r="G1354" s="7">
         <v>1</v>
       </c>
       <c r="H1354" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1354" s="7">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J1354" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1355" customHeight="1" spans="3:10">
       <c r="C1355" s="7">
-        <v>9030</v>
+        <v>9015</v>
       </c>
       <c r="D1355" s="7" t="s">
         <v>1404</v>
@@ -44812,25 +44848,25 @@
         <v>9</v>
       </c>
       <c r="F1355" s="7">
-        <f t="shared" si="42"/>
-        <v>300</v>
+        <f t="shared" si="43"/>
+        <v>150</v>
       </c>
       <c r="G1355" s="7">
         <v>1</v>
       </c>
       <c r="H1355" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1355" s="7">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J1355" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1356" customHeight="1" spans="3:10">
       <c r="C1356" s="7">
-        <v>9031</v>
+        <v>9016</v>
       </c>
       <c r="D1356" s="7" t="s">
         <v>1405</v>
@@ -44839,25 +44875,25 @@
         <v>9</v>
       </c>
       <c r="F1356" s="7">
-        <f t="shared" si="42"/>
-        <v>310</v>
+        <f t="shared" si="43"/>
+        <v>160</v>
       </c>
       <c r="G1356" s="7">
         <v>1</v>
       </c>
       <c r="H1356" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1356" s="7">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J1356" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1357" customHeight="1" spans="3:10">
       <c r="C1357" s="7">
-        <v>9032</v>
+        <v>9017</v>
       </c>
       <c r="D1357" s="7" t="s">
         <v>1406</v>
@@ -44866,25 +44902,25 @@
         <v>9</v>
       </c>
       <c r="F1357" s="7">
-        <f t="shared" si="42"/>
-        <v>320</v>
+        <f t="shared" si="43"/>
+        <v>170</v>
       </c>
       <c r="G1357" s="7">
         <v>1</v>
       </c>
       <c r="H1357" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1357" s="7">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J1357" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1358" customHeight="1" spans="3:10">
       <c r="C1358" s="7">
-        <v>9033</v>
+        <v>9018</v>
       </c>
       <c r="D1358" s="7" t="s">
         <v>1407</v>
@@ -44893,25 +44929,25 @@
         <v>9</v>
       </c>
       <c r="F1358" s="7">
-        <f t="shared" si="42"/>
-        <v>330</v>
+        <f t="shared" si="43"/>
+        <v>180</v>
       </c>
       <c r="G1358" s="7">
         <v>1</v>
       </c>
       <c r="H1358" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1358" s="7">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="J1358" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1359" customHeight="1" spans="3:10">
       <c r="C1359" s="7">
-        <v>9034</v>
+        <v>9019</v>
       </c>
       <c r="D1359" s="7" t="s">
         <v>1408</v>
@@ -44920,25 +44956,25 @@
         <v>9</v>
       </c>
       <c r="F1359" s="7">
-        <f t="shared" si="42"/>
-        <v>340</v>
+        <f t="shared" si="43"/>
+        <v>190</v>
       </c>
       <c r="G1359" s="7">
         <v>1</v>
       </c>
       <c r="H1359" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1359" s="7">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="J1359" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1360" customHeight="1" spans="3:10">
       <c r="C1360" s="7">
-        <v>9035</v>
+        <v>9020</v>
       </c>
       <c r="D1360" s="7" t="s">
         <v>1409</v>
@@ -44947,25 +44983,25 @@
         <v>9</v>
       </c>
       <c r="F1360" s="7">
-        <f t="shared" si="42"/>
-        <v>350</v>
+        <f t="shared" si="43"/>
+        <v>200</v>
       </c>
       <c r="G1360" s="7">
         <v>1</v>
       </c>
       <c r="H1360" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1360" s="7">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="J1360" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1361" customHeight="1" spans="3:10">
       <c r="C1361" s="7">
-        <v>9036</v>
+        <v>9021</v>
       </c>
       <c r="D1361" s="7" t="s">
         <v>1410</v>
@@ -44974,25 +45010,25 @@
         <v>9</v>
       </c>
       <c r="F1361" s="7">
-        <f t="shared" si="42"/>
-        <v>360</v>
+        <f t="shared" si="43"/>
+        <v>210</v>
       </c>
       <c r="G1361" s="7">
         <v>1</v>
       </c>
       <c r="H1361" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1361" s="7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="J1361" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1362" customHeight="1" spans="3:10">
       <c r="C1362" s="7">
-        <v>9037</v>
+        <v>9022</v>
       </c>
       <c r="D1362" s="7" t="s">
         <v>1411</v>
@@ -45001,25 +45037,25 @@
         <v>9</v>
       </c>
       <c r="F1362" s="7">
-        <f t="shared" si="42"/>
-        <v>370</v>
+        <f t="shared" si="43"/>
+        <v>220</v>
       </c>
       <c r="G1362" s="7">
         <v>1</v>
       </c>
       <c r="H1362" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1362" s="7">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="J1362" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1363" customHeight="1" spans="3:10">
       <c r="C1363" s="7">
-        <v>9038</v>
+        <v>9023</v>
       </c>
       <c r="D1363" s="7" t="s">
         <v>1412</v>
@@ -45028,25 +45064,25 @@
         <v>9</v>
       </c>
       <c r="F1363" s="7">
-        <f t="shared" si="42"/>
-        <v>380</v>
+        <f t="shared" si="43"/>
+        <v>230</v>
       </c>
       <c r="G1363" s="7">
         <v>1</v>
       </c>
       <c r="H1363" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1363" s="7">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="J1363" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1364" customHeight="1" spans="3:10">
       <c r="C1364" s="7">
-        <v>9039</v>
+        <v>9024</v>
       </c>
       <c r="D1364" s="7" t="s">
         <v>1413</v>
@@ -45055,25 +45091,25 @@
         <v>9</v>
       </c>
       <c r="F1364" s="7">
-        <f t="shared" si="42"/>
-        <v>390</v>
+        <f t="shared" si="43"/>
+        <v>240</v>
       </c>
       <c r="G1364" s="7">
         <v>1</v>
       </c>
       <c r="H1364" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1364" s="7">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="J1364" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1365" customHeight="1" spans="3:10">
       <c r="C1365" s="7">
-        <v>9040</v>
+        <v>9025</v>
       </c>
       <c r="D1365" s="7" t="s">
         <v>1414</v>
@@ -45082,25 +45118,25 @@
         <v>9</v>
       </c>
       <c r="F1365" s="7">
-        <f t="shared" si="42"/>
-        <v>400</v>
+        <f t="shared" si="43"/>
+        <v>250</v>
       </c>
       <c r="G1365" s="7">
         <v>1</v>
       </c>
       <c r="H1365" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1365" s="7">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="J1365" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1366" customHeight="1" spans="3:10">
       <c r="C1366" s="7">
-        <v>9041</v>
+        <v>9026</v>
       </c>
       <c r="D1366" s="7" t="s">
         <v>1415</v>
@@ -45109,25 +45145,25 @@
         <v>9</v>
       </c>
       <c r="F1366" s="7">
-        <f t="shared" si="42"/>
-        <v>410</v>
+        <f t="shared" si="43"/>
+        <v>260</v>
       </c>
       <c r="G1366" s="7">
         <v>1</v>
       </c>
       <c r="H1366" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1366" s="7">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="J1366" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1367" customHeight="1" spans="3:10">
       <c r="C1367" s="7">
-        <v>9042</v>
+        <v>9027</v>
       </c>
       <c r="D1367" s="7" t="s">
         <v>1416</v>
@@ -45136,25 +45172,25 @@
         <v>9</v>
       </c>
       <c r="F1367" s="7">
-        <f t="shared" si="42"/>
-        <v>420</v>
+        <f t="shared" si="43"/>
+        <v>270</v>
       </c>
       <c r="G1367" s="7">
         <v>1</v>
       </c>
       <c r="H1367" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1367" s="7">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="J1367" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1368" customHeight="1" spans="3:10">
       <c r="C1368" s="7">
-        <v>9043</v>
+        <v>9028</v>
       </c>
       <c r="D1368" s="7" t="s">
         <v>1417</v>
@@ -45163,25 +45199,25 @@
         <v>9</v>
       </c>
       <c r="F1368" s="7">
-        <f t="shared" si="42"/>
-        <v>430</v>
+        <f t="shared" si="43"/>
+        <v>280</v>
       </c>
       <c r="G1368" s="7">
         <v>1</v>
       </c>
       <c r="H1368" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1368" s="7">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="J1368" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1369" customHeight="1" spans="3:10">
       <c r="C1369" s="7">
-        <v>9044</v>
+        <v>9029</v>
       </c>
       <c r="D1369" s="7" t="s">
         <v>1418</v>
@@ -45190,25 +45226,25 @@
         <v>9</v>
       </c>
       <c r="F1369" s="7">
-        <f t="shared" si="42"/>
-        <v>440</v>
+        <f t="shared" si="43"/>
+        <v>290</v>
       </c>
       <c r="G1369" s="7">
         <v>1</v>
       </c>
       <c r="H1369" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1369" s="7">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J1369" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1370" customHeight="1" spans="3:10">
       <c r="C1370" s="7">
-        <v>9045</v>
+        <v>9030</v>
       </c>
       <c r="D1370" s="7" t="s">
         <v>1419</v>
@@ -45217,25 +45253,25 @@
         <v>9</v>
       </c>
       <c r="F1370" s="7">
-        <f t="shared" si="42"/>
-        <v>450</v>
+        <f t="shared" si="43"/>
+        <v>300</v>
       </c>
       <c r="G1370" s="7">
         <v>1</v>
       </c>
       <c r="H1370" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1370" s="7">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="J1370" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1371" customHeight="1" spans="3:10">
       <c r="C1371" s="7">
-        <v>9046</v>
+        <v>9031</v>
       </c>
       <c r="D1371" s="7" t="s">
         <v>1420</v>
@@ -45244,25 +45280,25 @@
         <v>9</v>
       </c>
       <c r="F1371" s="7">
-        <f t="shared" si="42"/>
-        <v>460</v>
+        <f t="shared" si="43"/>
+        <v>310</v>
       </c>
       <c r="G1371" s="7">
         <v>1</v>
       </c>
       <c r="H1371" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1371" s="7">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="J1371" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1372" customHeight="1" spans="3:10">
       <c r="C1372" s="7">
-        <v>9047</v>
+        <v>9032</v>
       </c>
       <c r="D1372" s="7" t="s">
         <v>1421</v>
@@ -45271,25 +45307,25 @@
         <v>9</v>
       </c>
       <c r="F1372" s="7">
-        <f t="shared" si="42"/>
-        <v>470</v>
+        <f t="shared" si="43"/>
+        <v>320</v>
       </c>
       <c r="G1372" s="7">
         <v>1</v>
       </c>
       <c r="H1372" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1372" s="7">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="J1372" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1373" customHeight="1" spans="3:10">
       <c r="C1373" s="7">
-        <v>9048</v>
+        <v>9033</v>
       </c>
       <c r="D1373" s="7" t="s">
         <v>1422</v>
@@ -45298,25 +45334,25 @@
         <v>9</v>
       </c>
       <c r="F1373" s="7">
-        <f t="shared" si="42"/>
-        <v>480</v>
+        <f t="shared" si="43"/>
+        <v>330</v>
       </c>
       <c r="G1373" s="7">
         <v>1</v>
       </c>
       <c r="H1373" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1373" s="7">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="J1373" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1374" customHeight="1" spans="3:10">
       <c r="C1374" s="7">
-        <v>9049</v>
+        <v>9034</v>
       </c>
       <c r="D1374" s="7" t="s">
         <v>1423</v>
@@ -45325,25 +45361,25 @@
         <v>9</v>
       </c>
       <c r="F1374" s="7">
-        <f t="shared" si="42"/>
-        <v>490</v>
+        <f t="shared" si="43"/>
+        <v>340</v>
       </c>
       <c r="G1374" s="7">
         <v>1</v>
       </c>
       <c r="H1374" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1374" s="7">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="J1374" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1375" customHeight="1" spans="3:10">
       <c r="C1375" s="7">
-        <v>9050</v>
+        <v>9035</v>
       </c>
       <c r="D1375" s="7" t="s">
         <v>1424</v>
@@ -45352,25 +45388,25 @@
         <v>9</v>
       </c>
       <c r="F1375" s="7">
-        <f t="shared" si="42"/>
-        <v>500</v>
+        <f t="shared" si="43"/>
+        <v>350</v>
       </c>
       <c r="G1375" s="7">
         <v>1</v>
       </c>
       <c r="H1375" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1375" s="7">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="J1375" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1376" customHeight="1" spans="3:10">
       <c r="C1376" s="7">
-        <v>9051</v>
+        <v>9036</v>
       </c>
       <c r="D1376" s="7" t="s">
         <v>1425</v>
@@ -45379,25 +45415,25 @@
         <v>9</v>
       </c>
       <c r="F1376" s="7">
-        <f t="shared" si="42"/>
-        <v>510</v>
+        <f t="shared" si="43"/>
+        <v>360</v>
       </c>
       <c r="G1376" s="7">
         <v>1</v>
       </c>
       <c r="H1376" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1376" s="7">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="J1376" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1377" customHeight="1" spans="3:10">
       <c r="C1377" s="7">
-        <v>9052</v>
+        <v>9037</v>
       </c>
       <c r="D1377" s="7" t="s">
         <v>1426</v>
@@ -45406,25 +45442,25 @@
         <v>9</v>
       </c>
       <c r="F1377" s="7">
-        <f t="shared" si="42"/>
-        <v>520</v>
+        <f t="shared" si="43"/>
+        <v>370</v>
       </c>
       <c r="G1377" s="7">
         <v>1</v>
       </c>
       <c r="H1377" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1377" s="7">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="J1377" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1378" customHeight="1" spans="3:10">
       <c r="C1378" s="7">
-        <v>9053</v>
+        <v>9038</v>
       </c>
       <c r="D1378" s="7" t="s">
         <v>1427</v>
@@ -45433,25 +45469,25 @@
         <v>9</v>
       </c>
       <c r="F1378" s="7">
-        <f t="shared" si="42"/>
-        <v>530</v>
+        <f t="shared" si="43"/>
+        <v>380</v>
       </c>
       <c r="G1378" s="7">
         <v>1</v>
       </c>
       <c r="H1378" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1378" s="7">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="J1378" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1379" customHeight="1" spans="3:10">
       <c r="C1379" s="7">
-        <v>9054</v>
+        <v>9039</v>
       </c>
       <c r="D1379" s="7" t="s">
         <v>1428</v>
@@ -45460,25 +45496,25 @@
         <v>9</v>
       </c>
       <c r="F1379" s="7">
-        <f t="shared" si="42"/>
-        <v>540</v>
+        <f t="shared" si="43"/>
+        <v>390</v>
       </c>
       <c r="G1379" s="7">
         <v>1</v>
       </c>
       <c r="H1379" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1379" s="7">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="J1379" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1380" customHeight="1" spans="3:10">
       <c r="C1380" s="7">
-        <v>9055</v>
+        <v>9040</v>
       </c>
       <c r="D1380" s="7" t="s">
         <v>1429</v>
@@ -45487,25 +45523,25 @@
         <v>9</v>
       </c>
       <c r="F1380" s="7">
-        <f t="shared" si="42"/>
-        <v>550</v>
+        <f t="shared" si="43"/>
+        <v>400</v>
       </c>
       <c r="G1380" s="7">
         <v>1</v>
       </c>
       <c r="H1380" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1380" s="7">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="J1380" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1381" customHeight="1" spans="3:10">
       <c r="C1381" s="7">
-        <v>9056</v>
+        <v>9041</v>
       </c>
       <c r="D1381" s="7" t="s">
         <v>1430</v>
@@ -45514,25 +45550,25 @@
         <v>9</v>
       </c>
       <c r="F1381" s="7">
-        <f t="shared" si="42"/>
-        <v>560</v>
+        <f t="shared" si="43"/>
+        <v>410</v>
       </c>
       <c r="G1381" s="7">
         <v>1</v>
       </c>
       <c r="H1381" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1381" s="7">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="J1381" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1382" customHeight="1" spans="3:10">
       <c r="C1382" s="7">
-        <v>9057</v>
+        <v>9042</v>
       </c>
       <c r="D1382" s="7" t="s">
         <v>1431</v>
@@ -45541,25 +45577,25 @@
         <v>9</v>
       </c>
       <c r="F1382" s="7">
-        <f t="shared" si="42"/>
-        <v>570</v>
+        <f t="shared" si="43"/>
+        <v>420</v>
       </c>
       <c r="G1382" s="7">
         <v>1</v>
       </c>
       <c r="H1382" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1382" s="7">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="J1382" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1383" customHeight="1" spans="3:10">
       <c r="C1383" s="7">
-        <v>9058</v>
+        <v>9043</v>
       </c>
       <c r="D1383" s="7" t="s">
         <v>1432</v>
@@ -45568,25 +45604,25 @@
         <v>9</v>
       </c>
       <c r="F1383" s="7">
-        <f t="shared" si="42"/>
-        <v>580</v>
+        <f t="shared" si="43"/>
+        <v>430</v>
       </c>
       <c r="G1383" s="7">
         <v>1</v>
       </c>
       <c r="H1383" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1383" s="7">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="J1383" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1384" customHeight="1" spans="3:10">
       <c r="C1384" s="7">
-        <v>9059</v>
+        <v>9044</v>
       </c>
       <c r="D1384" s="7" t="s">
         <v>1433</v>
@@ -45595,25 +45631,25 @@
         <v>9</v>
       </c>
       <c r="F1384" s="7">
-        <f t="shared" si="42"/>
-        <v>590</v>
+        <f t="shared" si="43"/>
+        <v>440</v>
       </c>
       <c r="G1384" s="7">
         <v>1</v>
       </c>
       <c r="H1384" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1384" s="7">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="J1384" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1385" customHeight="1" spans="3:10">
       <c r="C1385" s="7">
-        <v>9060</v>
+        <v>9045</v>
       </c>
       <c r="D1385" s="7" t="s">
         <v>1434</v>
@@ -45622,25 +45658,25 @@
         <v>9</v>
       </c>
       <c r="F1385" s="7">
-        <f t="shared" si="42"/>
-        <v>600</v>
+        <f t="shared" si="43"/>
+        <v>450</v>
       </c>
       <c r="G1385" s="7">
         <v>1</v>
       </c>
       <c r="H1385" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1385" s="7">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="J1385" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1386" customHeight="1" spans="3:10">
       <c r="C1386" s="7">
-        <v>9061</v>
+        <v>9046</v>
       </c>
       <c r="D1386" s="7" t="s">
         <v>1435</v>
@@ -45649,25 +45685,25 @@
         <v>9</v>
       </c>
       <c r="F1386" s="7">
-        <f t="shared" si="42"/>
-        <v>610</v>
+        <f t="shared" si="43"/>
+        <v>460</v>
       </c>
       <c r="G1386" s="7">
         <v>1</v>
       </c>
       <c r="H1386" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1386" s="7">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="J1386" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1387" customHeight="1" spans="3:10">
       <c r="C1387" s="7">
-        <v>9062</v>
+        <v>9047</v>
       </c>
       <c r="D1387" s="7" t="s">
         <v>1436</v>
@@ -45676,25 +45712,25 @@
         <v>9</v>
       </c>
       <c r="F1387" s="7">
-        <f t="shared" si="42"/>
-        <v>620</v>
+        <f t="shared" si="43"/>
+        <v>470</v>
       </c>
       <c r="G1387" s="7">
         <v>1</v>
       </c>
       <c r="H1387" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1387" s="7">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="J1387" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1388" customHeight="1" spans="3:10">
       <c r="C1388" s="7">
-        <v>9063</v>
+        <v>9048</v>
       </c>
       <c r="D1388" s="7" t="s">
         <v>1437</v>
@@ -45703,25 +45739,25 @@
         <v>9</v>
       </c>
       <c r="F1388" s="7">
-        <f t="shared" si="42"/>
-        <v>630</v>
+        <f t="shared" si="43"/>
+        <v>480</v>
       </c>
       <c r="G1388" s="7">
         <v>1</v>
       </c>
       <c r="H1388" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1388" s="7">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="J1388" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1389" customHeight="1" spans="3:10">
       <c r="C1389" s="7">
-        <v>9064</v>
+        <v>9049</v>
       </c>
       <c r="D1389" s="7" t="s">
         <v>1438</v>
@@ -45730,25 +45766,25 @@
         <v>9</v>
       </c>
       <c r="F1389" s="7">
-        <f t="shared" si="42"/>
-        <v>640</v>
+        <f t="shared" si="43"/>
+        <v>490</v>
       </c>
       <c r="G1389" s="7">
         <v>1</v>
       </c>
       <c r="H1389" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1389" s="7">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="J1389" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1390" customHeight="1" spans="3:10">
       <c r="C1390" s="7">
-        <v>9065</v>
+        <v>9050</v>
       </c>
       <c r="D1390" s="7" t="s">
         <v>1439</v>
@@ -45757,25 +45793,25 @@
         <v>9</v>
       </c>
       <c r="F1390" s="7">
-        <f t="shared" si="42"/>
-        <v>650</v>
+        <f t="shared" si="43"/>
+        <v>500</v>
       </c>
       <c r="G1390" s="7">
         <v>1</v>
       </c>
       <c r="H1390" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1390" s="7">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="J1390" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1391" customHeight="1" spans="3:10">
       <c r="C1391" s="7">
-        <v>9066</v>
+        <v>9051</v>
       </c>
       <c r="D1391" s="7" t="s">
         <v>1440</v>
@@ -45784,25 +45820,25 @@
         <v>9</v>
       </c>
       <c r="F1391" s="7">
-        <f t="shared" ref="F1391:F1454" si="43">F1390+10</f>
-        <v>660</v>
+        <f t="shared" si="43"/>
+        <v>510</v>
       </c>
       <c r="G1391" s="7">
         <v>1</v>
       </c>
       <c r="H1391" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1391" s="7">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="J1391" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1392" customHeight="1" spans="3:10">
       <c r="C1392" s="7">
-        <v>9067</v>
+        <v>9052</v>
       </c>
       <c r="D1392" s="7" t="s">
         <v>1441</v>
@@ -45812,24 +45848,24 @@
       </c>
       <c r="F1392" s="7">
         <f t="shared" si="43"/>
-        <v>670</v>
+        <v>520</v>
       </c>
       <c r="G1392" s="7">
         <v>1</v>
       </c>
       <c r="H1392" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1392" s="7">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="J1392" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1393" customHeight="1" spans="3:10">
       <c r="C1393" s="7">
-        <v>9068</v>
+        <v>9053</v>
       </c>
       <c r="D1393" s="7" t="s">
         <v>1442</v>
@@ -45839,24 +45875,24 @@
       </c>
       <c r="F1393" s="7">
         <f t="shared" si="43"/>
-        <v>680</v>
+        <v>530</v>
       </c>
       <c r="G1393" s="7">
         <v>1</v>
       </c>
       <c r="H1393" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1393" s="7">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="J1393" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1394" customHeight="1" spans="3:10">
       <c r="C1394" s="7">
-        <v>9069</v>
+        <v>9054</v>
       </c>
       <c r="D1394" s="7" t="s">
         <v>1443</v>
@@ -45866,24 +45902,24 @@
       </c>
       <c r="F1394" s="7">
         <f t="shared" si="43"/>
-        <v>690</v>
+        <v>540</v>
       </c>
       <c r="G1394" s="7">
         <v>1</v>
       </c>
       <c r="H1394" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1394" s="7">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="J1394" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1395" customHeight="1" spans="3:10">
       <c r="C1395" s="7">
-        <v>9070</v>
+        <v>9055</v>
       </c>
       <c r="D1395" s="7" t="s">
         <v>1444</v>
@@ -45893,24 +45929,24 @@
       </c>
       <c r="F1395" s="7">
         <f t="shared" si="43"/>
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="G1395" s="7">
         <v>1</v>
       </c>
       <c r="H1395" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1395" s="7">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="J1395" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1396" customHeight="1" spans="3:10">
       <c r="C1396" s="7">
-        <v>9071</v>
+        <v>9056</v>
       </c>
       <c r="D1396" s="7" t="s">
         <v>1445</v>
@@ -45920,24 +45956,24 @@
       </c>
       <c r="F1396" s="7">
         <f t="shared" si="43"/>
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="G1396" s="7">
         <v>1</v>
       </c>
       <c r="H1396" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1396" s="7">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="J1396" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1397" customHeight="1" spans="3:10">
       <c r="C1397" s="7">
-        <v>9072</v>
+        <v>9057</v>
       </c>
       <c r="D1397" s="7" t="s">
         <v>1446</v>
@@ -45947,24 +45983,24 @@
       </c>
       <c r="F1397" s="7">
         <f t="shared" si="43"/>
-        <v>720</v>
+        <v>570</v>
       </c>
       <c r="G1397" s="7">
         <v>1</v>
       </c>
       <c r="H1397" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1397" s="7">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="J1397" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1398" customHeight="1" spans="3:10">
       <c r="C1398" s="7">
-        <v>9073</v>
+        <v>9058</v>
       </c>
       <c r="D1398" s="7" t="s">
         <v>1447</v>
@@ -45974,24 +46010,24 @@
       </c>
       <c r="F1398" s="7">
         <f t="shared" si="43"/>
-        <v>730</v>
+        <v>580</v>
       </c>
       <c r="G1398" s="7">
         <v>1</v>
       </c>
       <c r="H1398" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1398" s="7">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="J1398" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1399" customHeight="1" spans="3:10">
       <c r="C1399" s="7">
-        <v>9074</v>
+        <v>9059</v>
       </c>
       <c r="D1399" s="7" t="s">
         <v>1448</v>
@@ -46001,24 +46037,24 @@
       </c>
       <c r="F1399" s="7">
         <f t="shared" si="43"/>
-        <v>740</v>
+        <v>590</v>
       </c>
       <c r="G1399" s="7">
         <v>1</v>
       </c>
       <c r="H1399" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1399" s="7">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="J1399" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1400" customHeight="1" spans="3:10">
       <c r="C1400" s="7">
-        <v>9075</v>
+        <v>9060</v>
       </c>
       <c r="D1400" s="7" t="s">
         <v>1449</v>
@@ -46028,24 +46064,24 @@
       </c>
       <c r="F1400" s="7">
         <f t="shared" si="43"/>
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="G1400" s="7">
         <v>1</v>
       </c>
       <c r="H1400" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1400" s="7">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="J1400" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1401" customHeight="1" spans="3:10">
       <c r="C1401" s="7">
-        <v>9076</v>
+        <v>9061</v>
       </c>
       <c r="D1401" s="7" t="s">
         <v>1450</v>
@@ -46055,24 +46091,24 @@
       </c>
       <c r="F1401" s="7">
         <f t="shared" si="43"/>
-        <v>760</v>
+        <v>610</v>
       </c>
       <c r="G1401" s="7">
         <v>1</v>
       </c>
       <c r="H1401" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1401" s="7">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="J1401" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1402" customHeight="1" spans="3:10">
       <c r="C1402" s="7">
-        <v>9077</v>
+        <v>9062</v>
       </c>
       <c r="D1402" s="7" t="s">
         <v>1451</v>
@@ -46082,24 +46118,24 @@
       </c>
       <c r="F1402" s="7">
         <f t="shared" si="43"/>
-        <v>770</v>
+        <v>620</v>
       </c>
       <c r="G1402" s="7">
         <v>1</v>
       </c>
       <c r="H1402" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1402" s="7">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="J1402" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1403" customHeight="1" spans="3:10">
       <c r="C1403" s="7">
-        <v>9078</v>
+        <v>9063</v>
       </c>
       <c r="D1403" s="7" t="s">
         <v>1452</v>
@@ -46109,24 +46145,24 @@
       </c>
       <c r="F1403" s="7">
         <f t="shared" si="43"/>
-        <v>780</v>
+        <v>630</v>
       </c>
       <c r="G1403" s="7">
         <v>1</v>
       </c>
       <c r="H1403" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1403" s="7">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="J1403" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1404" customHeight="1" spans="3:10">
       <c r="C1404" s="7">
-        <v>9079</v>
+        <v>9064</v>
       </c>
       <c r="D1404" s="7" t="s">
         <v>1453</v>
@@ -46136,24 +46172,24 @@
       </c>
       <c r="F1404" s="7">
         <f t="shared" si="43"/>
-        <v>790</v>
+        <v>640</v>
       </c>
       <c r="G1404" s="7">
         <v>1</v>
       </c>
       <c r="H1404" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1404" s="7">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="J1404" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1405" customHeight="1" spans="3:10">
       <c r="C1405" s="7">
-        <v>9080</v>
+        <v>9065</v>
       </c>
       <c r="D1405" s="7" t="s">
         <v>1454</v>
@@ -46163,24 +46199,24 @@
       </c>
       <c r="F1405" s="7">
         <f t="shared" si="43"/>
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="G1405" s="7">
         <v>1</v>
       </c>
       <c r="H1405" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1405" s="7">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="J1405" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1406" customHeight="1" spans="3:10">
       <c r="C1406" s="7">
-        <v>9081</v>
+        <v>9066</v>
       </c>
       <c r="D1406" s="7" t="s">
         <v>1455</v>
@@ -46189,25 +46225,25 @@
         <v>9</v>
       </c>
       <c r="F1406" s="7">
-        <f t="shared" si="43"/>
-        <v>810</v>
+        <f t="shared" ref="F1406:F1469" si="44">F1405+10</f>
+        <v>660</v>
       </c>
       <c r="G1406" s="7">
         <v>1</v>
       </c>
       <c r="H1406" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1406" s="7">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="J1406" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1407" customHeight="1" spans="3:10">
       <c r="C1407" s="7">
-        <v>9082</v>
+        <v>9067</v>
       </c>
       <c r="D1407" s="7" t="s">
         <v>1456</v>
@@ -46216,25 +46252,25 @@
         <v>9</v>
       </c>
       <c r="F1407" s="7">
-        <f t="shared" si="43"/>
-        <v>820</v>
+        <f t="shared" si="44"/>
+        <v>670</v>
       </c>
       <c r="G1407" s="7">
         <v>1</v>
       </c>
       <c r="H1407" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1407" s="7">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="J1407" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1408" customHeight="1" spans="3:10">
       <c r="C1408" s="7">
-        <v>9083</v>
+        <v>9068</v>
       </c>
       <c r="D1408" s="7" t="s">
         <v>1457</v>
@@ -46243,25 +46279,25 @@
         <v>9</v>
       </c>
       <c r="F1408" s="7">
-        <f t="shared" si="43"/>
-        <v>830</v>
+        <f t="shared" si="44"/>
+        <v>680</v>
       </c>
       <c r="G1408" s="7">
         <v>1</v>
       </c>
       <c r="H1408" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1408" s="7">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="J1408" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1409" customHeight="1" spans="3:10">
       <c r="C1409" s="7">
-        <v>9084</v>
+        <v>9069</v>
       </c>
       <c r="D1409" s="7" t="s">
         <v>1458</v>
@@ -46270,25 +46306,25 @@
         <v>9</v>
       </c>
       <c r="F1409" s="7">
-        <f t="shared" si="43"/>
-        <v>840</v>
+        <f t="shared" si="44"/>
+        <v>690</v>
       </c>
       <c r="G1409" s="7">
         <v>1</v>
       </c>
       <c r="H1409" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1409" s="7">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="J1409" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1410" customHeight="1" spans="3:10">
       <c r="C1410" s="7">
-        <v>9085</v>
+        <v>9070</v>
       </c>
       <c r="D1410" s="7" t="s">
         <v>1459</v>
@@ -46297,25 +46333,25 @@
         <v>9</v>
       </c>
       <c r="F1410" s="7">
-        <f t="shared" si="43"/>
-        <v>850</v>
+        <f t="shared" si="44"/>
+        <v>700</v>
       </c>
       <c r="G1410" s="7">
         <v>1</v>
       </c>
       <c r="H1410" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1410" s="7">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="J1410" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1411" customHeight="1" spans="3:10">
       <c r="C1411" s="7">
-        <v>9086</v>
+        <v>9071</v>
       </c>
       <c r="D1411" s="7" t="s">
         <v>1460</v>
@@ -46324,25 +46360,25 @@
         <v>9</v>
       </c>
       <c r="F1411" s="7">
-        <f t="shared" si="43"/>
-        <v>860</v>
+        <f t="shared" si="44"/>
+        <v>710</v>
       </c>
       <c r="G1411" s="7">
         <v>1</v>
       </c>
       <c r="H1411" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1411" s="7">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="J1411" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1412" customHeight="1" spans="3:10">
       <c r="C1412" s="7">
-        <v>9087</v>
+        <v>9072</v>
       </c>
       <c r="D1412" s="7" t="s">
         <v>1461</v>
@@ -46351,25 +46387,25 @@
         <v>9</v>
       </c>
       <c r="F1412" s="7">
-        <f t="shared" si="43"/>
-        <v>870</v>
+        <f t="shared" si="44"/>
+        <v>720</v>
       </c>
       <c r="G1412" s="7">
         <v>1</v>
       </c>
       <c r="H1412" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1412" s="7">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="J1412" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1413" customHeight="1" spans="3:10">
       <c r="C1413" s="7">
-        <v>9088</v>
+        <v>9073</v>
       </c>
       <c r="D1413" s="7" t="s">
         <v>1462</v>
@@ -46378,25 +46414,25 @@
         <v>9</v>
       </c>
       <c r="F1413" s="7">
-        <f t="shared" si="43"/>
-        <v>880</v>
+        <f t="shared" si="44"/>
+        <v>730</v>
       </c>
       <c r="G1413" s="7">
         <v>1</v>
       </c>
       <c r="H1413" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1413" s="7">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="J1413" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1414" customHeight="1" spans="3:10">
       <c r="C1414" s="7">
-        <v>9089</v>
+        <v>9074</v>
       </c>
       <c r="D1414" s="7" t="s">
         <v>1463</v>
@@ -46405,25 +46441,25 @@
         <v>9</v>
       </c>
       <c r="F1414" s="7">
-        <f t="shared" si="43"/>
-        <v>890</v>
+        <f t="shared" si="44"/>
+        <v>740</v>
       </c>
       <c r="G1414" s="7">
         <v>1</v>
       </c>
       <c r="H1414" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1414" s="7">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="J1414" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1415" customHeight="1" spans="3:10">
       <c r="C1415" s="7">
-        <v>9090</v>
+        <v>9075</v>
       </c>
       <c r="D1415" s="7" t="s">
         <v>1464</v>
@@ -46432,25 +46468,25 @@
         <v>9</v>
       </c>
       <c r="F1415" s="7">
-        <f t="shared" si="43"/>
-        <v>900</v>
+        <f t="shared" si="44"/>
+        <v>750</v>
       </c>
       <c r="G1415" s="7">
         <v>1</v>
       </c>
       <c r="H1415" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1415" s="7">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="J1415" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1416" customHeight="1" spans="3:10">
       <c r="C1416" s="7">
-        <v>9091</v>
+        <v>9076</v>
       </c>
       <c r="D1416" s="7" t="s">
         <v>1465</v>
@@ -46459,25 +46495,25 @@
         <v>9</v>
       </c>
       <c r="F1416" s="7">
-        <f t="shared" si="43"/>
-        <v>910</v>
+        <f t="shared" si="44"/>
+        <v>760</v>
       </c>
       <c r="G1416" s="7">
         <v>1</v>
       </c>
       <c r="H1416" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1416" s="7">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="J1416" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1417" customHeight="1" spans="3:10">
       <c r="C1417" s="7">
-        <v>9092</v>
+        <v>9077</v>
       </c>
       <c r="D1417" s="7" t="s">
         <v>1466</v>
@@ -46486,25 +46522,25 @@
         <v>9</v>
       </c>
       <c r="F1417" s="7">
-        <f t="shared" si="43"/>
-        <v>920</v>
+        <f t="shared" si="44"/>
+        <v>770</v>
       </c>
       <c r="G1417" s="7">
         <v>1</v>
       </c>
       <c r="H1417" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1417" s="7">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="J1417" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1418" customHeight="1" spans="3:10">
       <c r="C1418" s="7">
-        <v>9093</v>
+        <v>9078</v>
       </c>
       <c r="D1418" s="7" t="s">
         <v>1467</v>
@@ -46513,25 +46549,25 @@
         <v>9</v>
       </c>
       <c r="F1418" s="7">
-        <f t="shared" si="43"/>
-        <v>930</v>
+        <f t="shared" si="44"/>
+        <v>780</v>
       </c>
       <c r="G1418" s="7">
         <v>1</v>
       </c>
       <c r="H1418" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1418" s="7">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="J1418" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1419" customHeight="1" spans="3:10">
       <c r="C1419" s="7">
-        <v>9094</v>
+        <v>9079</v>
       </c>
       <c r="D1419" s="7" t="s">
         <v>1468</v>
@@ -46540,25 +46576,25 @@
         <v>9</v>
       </c>
       <c r="F1419" s="7">
-        <f t="shared" si="43"/>
-        <v>940</v>
+        <f t="shared" si="44"/>
+        <v>790</v>
       </c>
       <c r="G1419" s="7">
         <v>1</v>
       </c>
       <c r="H1419" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1419" s="7">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="J1419" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1420" customHeight="1" spans="3:10">
       <c r="C1420" s="7">
-        <v>9095</v>
+        <v>9080</v>
       </c>
       <c r="D1420" s="7" t="s">
         <v>1469</v>
@@ -46567,25 +46603,25 @@
         <v>9</v>
       </c>
       <c r="F1420" s="7">
-        <f t="shared" si="43"/>
-        <v>950</v>
+        <f t="shared" si="44"/>
+        <v>800</v>
       </c>
       <c r="G1420" s="7">
         <v>1</v>
       </c>
       <c r="H1420" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1420" s="7">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="J1420" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1421" customHeight="1" spans="3:10">
       <c r="C1421" s="7">
-        <v>9096</v>
+        <v>9081</v>
       </c>
       <c r="D1421" s="7" t="s">
         <v>1470</v>
@@ -46594,25 +46630,25 @@
         <v>9</v>
       </c>
       <c r="F1421" s="7">
-        <f t="shared" si="43"/>
-        <v>960</v>
+        <f t="shared" si="44"/>
+        <v>810</v>
       </c>
       <c r="G1421" s="7">
         <v>1</v>
       </c>
       <c r="H1421" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1421" s="7">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="J1421" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1422" customHeight="1" spans="3:10">
       <c r="C1422" s="7">
-        <v>9097</v>
+        <v>9082</v>
       </c>
       <c r="D1422" s="7" t="s">
         <v>1471</v>
@@ -46621,25 +46657,25 @@
         <v>9</v>
       </c>
       <c r="F1422" s="7">
-        <f t="shared" si="43"/>
-        <v>970</v>
+        <f t="shared" si="44"/>
+        <v>820</v>
       </c>
       <c r="G1422" s="7">
         <v>1</v>
       </c>
       <c r="H1422" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1422" s="7">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="J1422" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1423" customHeight="1" spans="3:10">
       <c r="C1423" s="7">
-        <v>9098</v>
+        <v>9083</v>
       </c>
       <c r="D1423" s="7" t="s">
         <v>1472</v>
@@ -46648,25 +46684,25 @@
         <v>9</v>
       </c>
       <c r="F1423" s="7">
-        <f t="shared" si="43"/>
-        <v>980</v>
+        <f t="shared" si="44"/>
+        <v>830</v>
       </c>
       <c r="G1423" s="7">
         <v>1</v>
       </c>
       <c r="H1423" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1423" s="7">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="J1423" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1424" customHeight="1" spans="3:10">
       <c r="C1424" s="7">
-        <v>9099</v>
+        <v>9084</v>
       </c>
       <c r="D1424" s="7" t="s">
         <v>1473</v>
@@ -46675,25 +46711,25 @@
         <v>9</v>
       </c>
       <c r="F1424" s="7">
-        <f t="shared" si="43"/>
-        <v>990</v>
+        <f t="shared" si="44"/>
+        <v>840</v>
       </c>
       <c r="G1424" s="7">
         <v>1</v>
       </c>
       <c r="H1424" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1424" s="7">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="J1424" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1425" customHeight="1" spans="3:10">
       <c r="C1425" s="7">
-        <v>9100</v>
+        <v>9085</v>
       </c>
       <c r="D1425" s="7" t="s">
         <v>1474</v>
@@ -46702,25 +46738,25 @@
         <v>9</v>
       </c>
       <c r="F1425" s="7">
-        <f t="shared" si="43"/>
-        <v>1000</v>
+        <f t="shared" si="44"/>
+        <v>850</v>
       </c>
       <c r="G1425" s="7">
         <v>1</v>
       </c>
       <c r="H1425" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1425" s="7">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="J1425" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1426" customHeight="1" spans="3:10">
       <c r="C1426" s="7">
-        <v>9101</v>
+        <v>9086</v>
       </c>
       <c r="D1426" s="7" t="s">
         <v>1475</v>
@@ -46729,26 +46765,25 @@
         <v>9</v>
       </c>
       <c r="F1426" s="7">
-        <f t="shared" ref="F1426:F1489" si="44">F1425+20</f>
-        <v>1020</v>
+        <f t="shared" si="44"/>
+        <v>860</v>
       </c>
       <c r="G1426" s="7">
         <v>1</v>
       </c>
       <c r="H1426" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1426" s="7">
-        <f t="shared" ref="I1426:I1489" si="45">I1422+10</f>
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="J1426" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1427" customHeight="1" spans="3:10">
       <c r="C1427" s="7">
-        <v>9102</v>
+        <v>9087</v>
       </c>
       <c r="D1427" s="7" t="s">
         <v>1476</v>
@@ -46758,25 +46793,24 @@
       </c>
       <c r="F1427" s="7">
         <f t="shared" si="44"/>
-        <v>1040</v>
+        <v>870</v>
       </c>
       <c r="G1427" s="7">
         <v>1</v>
       </c>
       <c r="H1427" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1427" s="7">
-        <f t="shared" si="45"/>
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="J1427" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1428" customHeight="1" spans="3:10">
       <c r="C1428" s="7">
-        <v>9103</v>
+        <v>9088</v>
       </c>
       <c r="D1428" s="7" t="s">
         <v>1477</v>
@@ -46786,25 +46820,24 @@
       </c>
       <c r="F1428" s="7">
         <f t="shared" si="44"/>
-        <v>1060</v>
+        <v>880</v>
       </c>
       <c r="G1428" s="7">
         <v>1</v>
       </c>
       <c r="H1428" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1428" s="7">
-        <f t="shared" si="45"/>
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="J1428" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1429" customHeight="1" spans="3:10">
       <c r="C1429" s="7">
-        <v>9104</v>
+        <v>9089</v>
       </c>
       <c r="D1429" s="7" t="s">
         <v>1478</v>
@@ -46814,25 +46847,24 @@
       </c>
       <c r="F1429" s="7">
         <f t="shared" si="44"/>
-        <v>1080</v>
+        <v>890</v>
       </c>
       <c r="G1429" s="7">
         <v>1</v>
       </c>
       <c r="H1429" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1429" s="7">
-        <f t="shared" si="45"/>
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="J1429" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1430" customHeight="1" spans="3:10">
       <c r="C1430" s="7">
-        <v>9105</v>
+        <v>9090</v>
       </c>
       <c r="D1430" s="7" t="s">
         <v>1479</v>
@@ -46842,25 +46874,24 @@
       </c>
       <c r="F1430" s="7">
         <f t="shared" si="44"/>
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="G1430" s="7">
         <v>1</v>
       </c>
       <c r="H1430" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1430" s="7">
-        <f t="shared" si="45"/>
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="J1430" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1431" customHeight="1" spans="3:10">
       <c r="C1431" s="7">
-        <v>9106</v>
+        <v>9091</v>
       </c>
       <c r="D1431" s="7" t="s">
         <v>1480</v>
@@ -46870,25 +46901,24 @@
       </c>
       <c r="F1431" s="7">
         <f t="shared" si="44"/>
-        <v>1120</v>
+        <v>910</v>
       </c>
       <c r="G1431" s="7">
         <v>1</v>
       </c>
       <c r="H1431" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1431" s="7">
-        <f t="shared" si="45"/>
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="J1431" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1432" customHeight="1" spans="3:10">
       <c r="C1432" s="7">
-        <v>9107</v>
+        <v>9092</v>
       </c>
       <c r="D1432" s="7" t="s">
         <v>1481</v>
@@ -46898,25 +46928,24 @@
       </c>
       <c r="F1432" s="7">
         <f t="shared" si="44"/>
-        <v>1140</v>
+        <v>920</v>
       </c>
       <c r="G1432" s="7">
         <v>1</v>
       </c>
       <c r="H1432" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1432" s="7">
-        <f t="shared" si="45"/>
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="J1432" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1433" customHeight="1" spans="3:10">
       <c r="C1433" s="7">
-        <v>9108</v>
+        <v>9093</v>
       </c>
       <c r="D1433" s="7" t="s">
         <v>1482</v>
@@ -46926,25 +46955,24 @@
       </c>
       <c r="F1433" s="7">
         <f t="shared" si="44"/>
-        <v>1160</v>
+        <v>930</v>
       </c>
       <c r="G1433" s="7">
         <v>1</v>
       </c>
       <c r="H1433" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1433" s="7">
-        <f t="shared" si="45"/>
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="J1433" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1434" customHeight="1" spans="3:10">
       <c r="C1434" s="7">
-        <v>9109</v>
+        <v>9094</v>
       </c>
       <c r="D1434" s="7" t="s">
         <v>1483</v>
@@ -46954,25 +46982,24 @@
       </c>
       <c r="F1434" s="7">
         <f t="shared" si="44"/>
-        <v>1180</v>
+        <v>940</v>
       </c>
       <c r="G1434" s="7">
         <v>1</v>
       </c>
       <c r="H1434" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1434" s="7">
-        <f t="shared" si="45"/>
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="J1434" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1435" customHeight="1" spans="3:10">
       <c r="C1435" s="7">
-        <v>9110</v>
+        <v>9095</v>
       </c>
       <c r="D1435" s="7" t="s">
         <v>1484</v>
@@ -46982,25 +47009,24 @@
       </c>
       <c r="F1435" s="7">
         <f t="shared" si="44"/>
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="G1435" s="7">
         <v>1</v>
       </c>
       <c r="H1435" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1435" s="7">
-        <f t="shared" si="45"/>
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="J1435" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1436" customHeight="1" spans="3:10">
       <c r="C1436" s="7">
-        <v>9111</v>
+        <v>9096</v>
       </c>
       <c r="D1436" s="7" t="s">
         <v>1485</v>
@@ -47010,25 +47036,24 @@
       </c>
       <c r="F1436" s="7">
         <f t="shared" si="44"/>
-        <v>1220</v>
+        <v>960</v>
       </c>
       <c r="G1436" s="7">
         <v>1</v>
       </c>
       <c r="H1436" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1436" s="7">
-        <f t="shared" si="45"/>
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="J1436" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1437" customHeight="1" spans="3:10">
       <c r="C1437" s="7">
-        <v>9112</v>
+        <v>9097</v>
       </c>
       <c r="D1437" s="7" t="s">
         <v>1486</v>
@@ -47038,25 +47063,24 @@
       </c>
       <c r="F1437" s="7">
         <f t="shared" si="44"/>
-        <v>1240</v>
+        <v>970</v>
       </c>
       <c r="G1437" s="7">
         <v>1</v>
       </c>
       <c r="H1437" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1437" s="7">
-        <f t="shared" si="45"/>
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="J1437" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1438" customHeight="1" spans="3:10">
       <c r="C1438" s="7">
-        <v>9113</v>
+        <v>9098</v>
       </c>
       <c r="D1438" s="7" t="s">
         <v>1487</v>
@@ -47066,25 +47090,24 @@
       </c>
       <c r="F1438" s="7">
         <f t="shared" si="44"/>
-        <v>1260</v>
+        <v>980</v>
       </c>
       <c r="G1438" s="7">
         <v>1</v>
       </c>
       <c r="H1438" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1438" s="7">
-        <f t="shared" si="45"/>
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="J1438" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1439" customHeight="1" spans="3:10">
       <c r="C1439" s="7">
-        <v>9114</v>
+        <v>9099</v>
       </c>
       <c r="D1439" s="7" t="s">
         <v>1488</v>
@@ -47094,25 +47117,24 @@
       </c>
       <c r="F1439" s="7">
         <f t="shared" si="44"/>
-        <v>1280</v>
+        <v>990</v>
       </c>
       <c r="G1439" s="7">
         <v>1</v>
       </c>
       <c r="H1439" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1439" s="7">
-        <f t="shared" si="45"/>
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="J1439" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1440" customHeight="1" spans="3:10">
       <c r="C1440" s="7">
-        <v>9115</v>
+        <v>9100</v>
       </c>
       <c r="D1440" s="7" t="s">
         <v>1489</v>
@@ -47122,25 +47144,24 @@
       </c>
       <c r="F1440" s="7">
         <f t="shared" si="44"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="G1440" s="7">
         <v>1</v>
       </c>
       <c r="H1440" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1440" s="7">
-        <f t="shared" si="45"/>
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="J1440" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1441" customHeight="1" spans="3:10">
       <c r="C1441" s="7">
-        <v>9116</v>
+        <v>9101</v>
       </c>
       <c r="D1441" s="7" t="s">
         <v>1490</v>
@@ -47149,26 +47170,26 @@
         <v>9</v>
       </c>
       <c r="F1441" s="7">
-        <f t="shared" si="44"/>
-        <v>1320</v>
+        <f t="shared" ref="F1441:F1504" si="45">F1440+20</f>
+        <v>1020</v>
       </c>
       <c r="G1441" s="7">
         <v>1</v>
       </c>
       <c r="H1441" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1441" s="7">
-        <f t="shared" si="45"/>
-        <v>330</v>
+        <f t="shared" ref="I1441:I1504" si="46">I1437+10</f>
+        <v>300</v>
       </c>
       <c r="J1441" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1442" customHeight="1" spans="3:10">
       <c r="C1442" s="7">
-        <v>9117</v>
+        <v>9102</v>
       </c>
       <c r="D1442" s="7" t="s">
         <v>1491</v>
@@ -47177,26 +47198,26 @@
         <v>9</v>
       </c>
       <c r="F1442" s="7">
-        <f t="shared" si="44"/>
-        <v>1340</v>
+        <f t="shared" si="45"/>
+        <v>1040</v>
       </c>
       <c r="G1442" s="7">
         <v>1</v>
       </c>
       <c r="H1442" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1442" s="7">
-        <f t="shared" si="45"/>
-        <v>340</v>
+        <f t="shared" si="46"/>
+        <v>300</v>
       </c>
       <c r="J1442" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1443" customHeight="1" spans="3:10">
       <c r="C1443" s="7">
-        <v>9118</v>
+        <v>9103</v>
       </c>
       <c r="D1443" s="7" t="s">
         <v>1492</v>
@@ -47205,26 +47226,26 @@
         <v>9</v>
       </c>
       <c r="F1443" s="7">
-        <f t="shared" si="44"/>
-        <v>1360</v>
+        <f t="shared" si="45"/>
+        <v>1060</v>
       </c>
       <c r="G1443" s="7">
         <v>1</v>
       </c>
       <c r="H1443" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1443" s="7">
-        <f t="shared" si="45"/>
-        <v>340</v>
+        <f t="shared" si="46"/>
+        <v>300</v>
       </c>
       <c r="J1443" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1444" customHeight="1" spans="3:10">
       <c r="C1444" s="7">
-        <v>9119</v>
+        <v>9104</v>
       </c>
       <c r="D1444" s="7" t="s">
         <v>1493</v>
@@ -47233,26 +47254,26 @@
         <v>9</v>
       </c>
       <c r="F1444" s="7">
-        <f t="shared" si="44"/>
-        <v>1380</v>
+        <f t="shared" si="45"/>
+        <v>1080</v>
       </c>
       <c r="G1444" s="7">
         <v>1</v>
       </c>
       <c r="H1444" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1444" s="7">
-        <f t="shared" si="45"/>
-        <v>340</v>
+        <f t="shared" si="46"/>
+        <v>300</v>
       </c>
       <c r="J1444" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1445" customHeight="1" spans="3:10">
       <c r="C1445" s="7">
-        <v>9120</v>
+        <v>9105</v>
       </c>
       <c r="D1445" s="7" t="s">
         <v>1494</v>
@@ -47261,26 +47282,26 @@
         <v>9</v>
       </c>
       <c r="F1445" s="7">
-        <f t="shared" si="44"/>
-        <v>1400</v>
+        <f t="shared" si="45"/>
+        <v>1100</v>
       </c>
       <c r="G1445" s="7">
         <v>1</v>
       </c>
       <c r="H1445" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1445" s="7">
-        <f t="shared" si="45"/>
-        <v>340</v>
+        <f t="shared" si="46"/>
+        <v>310</v>
       </c>
       <c r="J1445" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1446" customHeight="1" spans="3:10">
       <c r="C1446" s="7">
-        <v>9121</v>
+        <v>9106</v>
       </c>
       <c r="D1446" s="7" t="s">
         <v>1495</v>
@@ -47289,26 +47310,26 @@
         <v>9</v>
       </c>
       <c r="F1446" s="7">
-        <f t="shared" si="44"/>
-        <v>1420</v>
+        <f t="shared" si="45"/>
+        <v>1120</v>
       </c>
       <c r="G1446" s="7">
         <v>1</v>
       </c>
       <c r="H1446" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1446" s="7">
-        <f t="shared" si="45"/>
-        <v>350</v>
+        <f t="shared" si="46"/>
+        <v>310</v>
       </c>
       <c r="J1446" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1447" customHeight="1" spans="3:10">
       <c r="C1447" s="7">
-        <v>9122</v>
+        <v>9107</v>
       </c>
       <c r="D1447" s="7" t="s">
         <v>1496</v>
@@ -47317,26 +47338,26 @@
         <v>9</v>
       </c>
       <c r="F1447" s="7">
-        <f t="shared" si="44"/>
-        <v>1440</v>
+        <f t="shared" si="45"/>
+        <v>1140</v>
       </c>
       <c r="G1447" s="7">
         <v>1</v>
       </c>
       <c r="H1447" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1447" s="7">
-        <f t="shared" si="45"/>
-        <v>350</v>
+        <f t="shared" si="46"/>
+        <v>310</v>
       </c>
       <c r="J1447" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1448" customHeight="1" spans="3:10">
       <c r="C1448" s="7">
-        <v>9123</v>
+        <v>9108</v>
       </c>
       <c r="D1448" s="7" t="s">
         <v>1497</v>
@@ -47345,26 +47366,26 @@
         <v>9</v>
       </c>
       <c r="F1448" s="7">
-        <f t="shared" si="44"/>
-        <v>1460</v>
+        <f t="shared" si="45"/>
+        <v>1160</v>
       </c>
       <c r="G1448" s="7">
         <v>1</v>
       </c>
       <c r="H1448" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1448" s="7">
-        <f t="shared" si="45"/>
-        <v>350</v>
+        <f t="shared" si="46"/>
+        <v>310</v>
       </c>
       <c r="J1448" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1449" customHeight="1" spans="3:10">
       <c r="C1449" s="7">
-        <v>9124</v>
+        <v>9109</v>
       </c>
       <c r="D1449" s="7" t="s">
         <v>1498</v>
@@ -47373,26 +47394,26 @@
         <v>9</v>
       </c>
       <c r="F1449" s="7">
-        <f t="shared" si="44"/>
-        <v>1480</v>
+        <f t="shared" si="45"/>
+        <v>1180</v>
       </c>
       <c r="G1449" s="7">
         <v>1</v>
       </c>
       <c r="H1449" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1449" s="7">
-        <f t="shared" si="45"/>
-        <v>350</v>
+        <f t="shared" si="46"/>
+        <v>320</v>
       </c>
       <c r="J1449" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1450" customHeight="1" spans="3:10">
       <c r="C1450" s="7">
-        <v>9125</v>
+        <v>9110</v>
       </c>
       <c r="D1450" s="7" t="s">
         <v>1499</v>
@@ -47401,26 +47422,26 @@
         <v>9</v>
       </c>
       <c r="F1450" s="7">
-        <f t="shared" si="44"/>
-        <v>1500</v>
+        <f t="shared" si="45"/>
+        <v>1200</v>
       </c>
       <c r="G1450" s="7">
         <v>1</v>
       </c>
       <c r="H1450" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1450" s="7">
-        <f t="shared" si="45"/>
-        <v>360</v>
+        <f t="shared" si="46"/>
+        <v>320</v>
       </c>
       <c r="J1450" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1451" customHeight="1" spans="3:10">
       <c r="C1451" s="7">
-        <v>9126</v>
+        <v>9111</v>
       </c>
       <c r="D1451" s="7" t="s">
         <v>1500</v>
@@ -47429,26 +47450,26 @@
         <v>9</v>
       </c>
       <c r="F1451" s="7">
-        <f t="shared" si="44"/>
-        <v>1520</v>
+        <f t="shared" si="45"/>
+        <v>1220</v>
       </c>
       <c r="G1451" s="7">
         <v>1</v>
       </c>
       <c r="H1451" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1451" s="7">
-        <f t="shared" si="45"/>
-        <v>360</v>
+        <f t="shared" si="46"/>
+        <v>320</v>
       </c>
       <c r="J1451" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1452" customHeight="1" spans="3:10">
       <c r="C1452" s="7">
-        <v>9127</v>
+        <v>9112</v>
       </c>
       <c r="D1452" s="7" t="s">
         <v>1501</v>
@@ -47457,26 +47478,26 @@
         <v>9</v>
       </c>
       <c r="F1452" s="7">
-        <f t="shared" si="44"/>
-        <v>1540</v>
+        <f t="shared" si="45"/>
+        <v>1240</v>
       </c>
       <c r="G1452" s="7">
         <v>1</v>
       </c>
       <c r="H1452" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1452" s="7">
-        <f t="shared" si="45"/>
-        <v>360</v>
+        <f t="shared" si="46"/>
+        <v>320</v>
       </c>
       <c r="J1452" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1453" customHeight="1" spans="3:10">
       <c r="C1453" s="7">
-        <v>9128</v>
+        <v>9113</v>
       </c>
       <c r="D1453" s="7" t="s">
         <v>1502</v>
@@ -47485,26 +47506,26 @@
         <v>9</v>
       </c>
       <c r="F1453" s="7">
-        <f t="shared" si="44"/>
-        <v>1560</v>
+        <f t="shared" si="45"/>
+        <v>1260</v>
       </c>
       <c r="G1453" s="7">
         <v>1</v>
       </c>
       <c r="H1453" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1453" s="7">
-        <f t="shared" si="45"/>
-        <v>360</v>
+        <f t="shared" si="46"/>
+        <v>330</v>
       </c>
       <c r="J1453" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1454" customHeight="1" spans="3:10">
       <c r="C1454" s="7">
-        <v>9129</v>
+        <v>9114</v>
       </c>
       <c r="D1454" s="7" t="s">
         <v>1503</v>
@@ -47513,26 +47534,26 @@
         <v>9</v>
       </c>
       <c r="F1454" s="7">
-        <f t="shared" si="44"/>
-        <v>1580</v>
+        <f t="shared" si="45"/>
+        <v>1280</v>
       </c>
       <c r="G1454" s="7">
         <v>1</v>
       </c>
       <c r="H1454" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1454" s="7">
-        <f t="shared" si="45"/>
-        <v>370</v>
+        <f t="shared" si="46"/>
+        <v>330</v>
       </c>
       <c r="J1454" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1455" customHeight="1" spans="3:10">
       <c r="C1455" s="7">
-        <v>9130</v>
+        <v>9115</v>
       </c>
       <c r="D1455" s="7" t="s">
         <v>1504</v>
@@ -47541,26 +47562,26 @@
         <v>9</v>
       </c>
       <c r="F1455" s="7">
-        <f t="shared" si="44"/>
-        <v>1600</v>
+        <f t="shared" si="45"/>
+        <v>1300</v>
       </c>
       <c r="G1455" s="7">
         <v>1</v>
       </c>
       <c r="H1455" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1455" s="7">
-        <f t="shared" si="45"/>
-        <v>370</v>
+        <f t="shared" si="46"/>
+        <v>330</v>
       </c>
       <c r="J1455" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1456" customHeight="1" spans="3:10">
       <c r="C1456" s="7">
-        <v>9131</v>
+        <v>9116</v>
       </c>
       <c r="D1456" s="7" t="s">
         <v>1505</v>
@@ -47569,26 +47590,26 @@
         <v>9</v>
       </c>
       <c r="F1456" s="7">
-        <f t="shared" si="44"/>
-        <v>1620</v>
+        <f t="shared" si="45"/>
+        <v>1320</v>
       </c>
       <c r="G1456" s="7">
         <v>1</v>
       </c>
       <c r="H1456" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1456" s="7">
-        <f t="shared" si="45"/>
-        <v>370</v>
+        <f t="shared" si="46"/>
+        <v>330</v>
       </c>
       <c r="J1456" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1457" customHeight="1" spans="3:10">
       <c r="C1457" s="7">
-        <v>9132</v>
+        <v>9117</v>
       </c>
       <c r="D1457" s="7" t="s">
         <v>1506</v>
@@ -47597,26 +47618,26 @@
         <v>9</v>
       </c>
       <c r="F1457" s="7">
-        <f t="shared" si="44"/>
-        <v>1640</v>
+        <f t="shared" si="45"/>
+        <v>1340</v>
       </c>
       <c r="G1457" s="7">
         <v>1</v>
       </c>
       <c r="H1457" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1457" s="7">
-        <f t="shared" si="45"/>
-        <v>370</v>
+        <f t="shared" si="46"/>
+        <v>340</v>
       </c>
       <c r="J1457" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1458" customHeight="1" spans="3:10">
       <c r="C1458" s="7">
-        <v>9133</v>
+        <v>9118</v>
       </c>
       <c r="D1458" s="7" t="s">
         <v>1507</v>
@@ -47625,26 +47646,26 @@
         <v>9</v>
       </c>
       <c r="F1458" s="7">
-        <f t="shared" si="44"/>
-        <v>1660</v>
+        <f t="shared" si="45"/>
+        <v>1360</v>
       </c>
       <c r="G1458" s="7">
         <v>1</v>
       </c>
       <c r="H1458" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1458" s="7">
-        <f t="shared" si="45"/>
-        <v>380</v>
+        <f t="shared" si="46"/>
+        <v>340</v>
       </c>
       <c r="J1458" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1459" customHeight="1" spans="3:10">
       <c r="C1459" s="7">
-        <v>9134</v>
+        <v>9119</v>
       </c>
       <c r="D1459" s="7" t="s">
         <v>1508</v>
@@ -47653,26 +47674,26 @@
         <v>9</v>
       </c>
       <c r="F1459" s="7">
-        <f t="shared" si="44"/>
-        <v>1680</v>
+        <f t="shared" si="45"/>
+        <v>1380</v>
       </c>
       <c r="G1459" s="7">
         <v>1</v>
       </c>
       <c r="H1459" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1459" s="7">
-        <f t="shared" si="45"/>
-        <v>380</v>
+        <f t="shared" si="46"/>
+        <v>340</v>
       </c>
       <c r="J1459" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1460" customHeight="1" spans="3:10">
       <c r="C1460" s="7">
-        <v>9135</v>
+        <v>9120</v>
       </c>
       <c r="D1460" s="7" t="s">
         <v>1509</v>
@@ -47681,26 +47702,26 @@
         <v>9</v>
       </c>
       <c r="F1460" s="7">
-        <f t="shared" si="44"/>
-        <v>1700</v>
+        <f t="shared" si="45"/>
+        <v>1400</v>
       </c>
       <c r="G1460" s="7">
         <v>1</v>
       </c>
       <c r="H1460" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1460" s="7">
-        <f t="shared" si="45"/>
-        <v>380</v>
+        <f t="shared" si="46"/>
+        <v>340</v>
       </c>
       <c r="J1460" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1461" customHeight="1" spans="3:10">
       <c r="C1461" s="7">
-        <v>9136</v>
+        <v>9121</v>
       </c>
       <c r="D1461" s="7" t="s">
         <v>1510</v>
@@ -47709,26 +47730,26 @@
         <v>9</v>
       </c>
       <c r="F1461" s="7">
-        <f t="shared" si="44"/>
-        <v>1720</v>
+        <f t="shared" si="45"/>
+        <v>1420</v>
       </c>
       <c r="G1461" s="7">
         <v>1</v>
       </c>
       <c r="H1461" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1461" s="7">
-        <f t="shared" si="45"/>
-        <v>380</v>
+        <f t="shared" si="46"/>
+        <v>350</v>
       </c>
       <c r="J1461" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1462" customHeight="1" spans="3:10">
       <c r="C1462" s="7">
-        <v>9137</v>
+        <v>9122</v>
       </c>
       <c r="D1462" s="7" t="s">
         <v>1511</v>
@@ -47737,26 +47758,26 @@
         <v>9</v>
       </c>
       <c r="F1462" s="7">
-        <f t="shared" si="44"/>
-        <v>1740</v>
+        <f t="shared" si="45"/>
+        <v>1440</v>
       </c>
       <c r="G1462" s="7">
         <v>1</v>
       </c>
       <c r="H1462" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1462" s="7">
-        <f t="shared" si="45"/>
-        <v>390</v>
+        <f t="shared" si="46"/>
+        <v>350</v>
       </c>
       <c r="J1462" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1463" customHeight="1" spans="3:10">
       <c r="C1463" s="7">
-        <v>9138</v>
+        <v>9123</v>
       </c>
       <c r="D1463" s="7" t="s">
         <v>1512</v>
@@ -47765,26 +47786,26 @@
         <v>9</v>
       </c>
       <c r="F1463" s="7">
-        <f t="shared" si="44"/>
-        <v>1760</v>
+        <f t="shared" si="45"/>
+        <v>1460</v>
       </c>
       <c r="G1463" s="7">
         <v>1</v>
       </c>
       <c r="H1463" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1463" s="7">
-        <f t="shared" si="45"/>
-        <v>390</v>
+        <f t="shared" si="46"/>
+        <v>350</v>
       </c>
       <c r="J1463" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1464" customHeight="1" spans="3:10">
       <c r="C1464" s="7">
-        <v>9139</v>
+        <v>9124</v>
       </c>
       <c r="D1464" s="7" t="s">
         <v>1513</v>
@@ -47793,26 +47814,26 @@
         <v>9</v>
       </c>
       <c r="F1464" s="7">
-        <f t="shared" si="44"/>
-        <v>1780</v>
+        <f t="shared" si="45"/>
+        <v>1480</v>
       </c>
       <c r="G1464" s="7">
         <v>1</v>
       </c>
       <c r="H1464" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1464" s="7">
-        <f t="shared" si="45"/>
-        <v>390</v>
+        <f t="shared" si="46"/>
+        <v>350</v>
       </c>
       <c r="J1464" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1465" customHeight="1" spans="3:10">
       <c r="C1465" s="7">
-        <v>9140</v>
+        <v>9125</v>
       </c>
       <c r="D1465" s="7" t="s">
         <v>1514</v>
@@ -47821,26 +47842,26 @@
         <v>9</v>
       </c>
       <c r="F1465" s="7">
-        <f t="shared" si="44"/>
-        <v>1800</v>
+        <f t="shared" si="45"/>
+        <v>1500</v>
       </c>
       <c r="G1465" s="7">
         <v>1</v>
       </c>
       <c r="H1465" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1465" s="7">
-        <f t="shared" si="45"/>
-        <v>390</v>
+        <f t="shared" si="46"/>
+        <v>360</v>
       </c>
       <c r="J1465" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1466" customHeight="1" spans="3:10">
       <c r="C1466" s="7">
-        <v>9141</v>
+        <v>9126</v>
       </c>
       <c r="D1466" s="7" t="s">
         <v>1515</v>
@@ -47849,26 +47870,26 @@
         <v>9</v>
       </c>
       <c r="F1466" s="7">
-        <f t="shared" si="44"/>
-        <v>1820</v>
+        <f t="shared" si="45"/>
+        <v>1520</v>
       </c>
       <c r="G1466" s="7">
         <v>1</v>
       </c>
       <c r="H1466" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1466" s="7">
-        <f t="shared" si="45"/>
-        <v>400</v>
+        <f t="shared" si="46"/>
+        <v>360</v>
       </c>
       <c r="J1466" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1467" customHeight="1" spans="3:10">
       <c r="C1467" s="7">
-        <v>9142</v>
+        <v>9127</v>
       </c>
       <c r="D1467" s="7" t="s">
         <v>1516</v>
@@ -47877,26 +47898,26 @@
         <v>9</v>
       </c>
       <c r="F1467" s="7">
-        <f t="shared" si="44"/>
-        <v>1840</v>
+        <f t="shared" si="45"/>
+        <v>1540</v>
       </c>
       <c r="G1467" s="7">
         <v>1</v>
       </c>
       <c r="H1467" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1467" s="7">
-        <f t="shared" si="45"/>
-        <v>400</v>
+        <f t="shared" si="46"/>
+        <v>360</v>
       </c>
       <c r="J1467" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1468" customHeight="1" spans="3:10">
       <c r="C1468" s="7">
-        <v>9143</v>
+        <v>9128</v>
       </c>
       <c r="D1468" s="7" t="s">
         <v>1517</v>
@@ -47905,26 +47926,26 @@
         <v>9</v>
       </c>
       <c r="F1468" s="7">
-        <f t="shared" si="44"/>
-        <v>1860</v>
+        <f t="shared" si="45"/>
+        <v>1560</v>
       </c>
       <c r="G1468" s="7">
         <v>1</v>
       </c>
       <c r="H1468" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1468" s="7">
-        <f t="shared" si="45"/>
-        <v>400</v>
+        <f t="shared" si="46"/>
+        <v>360</v>
       </c>
       <c r="J1468" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1469" customHeight="1" spans="3:10">
       <c r="C1469" s="7">
-        <v>9144</v>
+        <v>9129</v>
       </c>
       <c r="D1469" s="7" t="s">
         <v>1518</v>
@@ -47933,26 +47954,26 @@
         <v>9</v>
       </c>
       <c r="F1469" s="7">
-        <f t="shared" si="44"/>
-        <v>1880</v>
+        <f t="shared" si="45"/>
+        <v>1580</v>
       </c>
       <c r="G1469" s="7">
         <v>1</v>
       </c>
       <c r="H1469" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1469" s="7">
-        <f t="shared" si="45"/>
-        <v>400</v>
+        <f t="shared" si="46"/>
+        <v>370</v>
       </c>
       <c r="J1469" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1470" customHeight="1" spans="3:10">
       <c r="C1470" s="7">
-        <v>9145</v>
+        <v>9130</v>
       </c>
       <c r="D1470" s="7" t="s">
         <v>1519</v>
@@ -47961,26 +47982,26 @@
         <v>9</v>
       </c>
       <c r="F1470" s="7">
-        <f t="shared" si="44"/>
-        <v>1900</v>
+        <f t="shared" si="45"/>
+        <v>1600</v>
       </c>
       <c r="G1470" s="7">
         <v>1</v>
       </c>
       <c r="H1470" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1470" s="7">
-        <f t="shared" si="45"/>
-        <v>410</v>
+        <f t="shared" si="46"/>
+        <v>370</v>
       </c>
       <c r="J1470" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1471" customHeight="1" spans="3:10">
       <c r="C1471" s="7">
-        <v>9146</v>
+        <v>9131</v>
       </c>
       <c r="D1471" s="7" t="s">
         <v>1520</v>
@@ -47989,26 +48010,26 @@
         <v>9</v>
       </c>
       <c r="F1471" s="7">
-        <f t="shared" si="44"/>
-        <v>1920</v>
+        <f t="shared" si="45"/>
+        <v>1620</v>
       </c>
       <c r="G1471" s="7">
         <v>1</v>
       </c>
       <c r="H1471" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1471" s="7">
-        <f t="shared" si="45"/>
-        <v>410</v>
+        <f t="shared" si="46"/>
+        <v>370</v>
       </c>
       <c r="J1471" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1472" customHeight="1" spans="3:10">
       <c r="C1472" s="7">
-        <v>9147</v>
+        <v>9132</v>
       </c>
       <c r="D1472" s="7" t="s">
         <v>1521</v>
@@ -48017,26 +48038,26 @@
         <v>9</v>
       </c>
       <c r="F1472" s="7">
-        <f t="shared" si="44"/>
-        <v>1940</v>
+        <f t="shared" si="45"/>
+        <v>1640</v>
       </c>
       <c r="G1472" s="7">
         <v>1</v>
       </c>
       <c r="H1472" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1472" s="7">
-        <f t="shared" si="45"/>
-        <v>410</v>
+        <f t="shared" si="46"/>
+        <v>370</v>
       </c>
       <c r="J1472" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1473" customHeight="1" spans="3:10">
       <c r="C1473" s="7">
-        <v>9148</v>
+        <v>9133</v>
       </c>
       <c r="D1473" s="7" t="s">
         <v>1522</v>
@@ -48045,26 +48066,26 @@
         <v>9</v>
       </c>
       <c r="F1473" s="7">
-        <f t="shared" si="44"/>
-        <v>1960</v>
+        <f t="shared" si="45"/>
+        <v>1660</v>
       </c>
       <c r="G1473" s="7">
         <v>1</v>
       </c>
       <c r="H1473" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1473" s="7">
-        <f t="shared" si="45"/>
-        <v>410</v>
+        <f t="shared" si="46"/>
+        <v>380</v>
       </c>
       <c r="J1473" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1474" customHeight="1" spans="3:10">
       <c r="C1474" s="7">
-        <v>9149</v>
+        <v>9134</v>
       </c>
       <c r="D1474" s="7" t="s">
         <v>1523</v>
@@ -48073,26 +48094,26 @@
         <v>9</v>
       </c>
       <c r="F1474" s="7">
-        <f t="shared" si="44"/>
-        <v>1980</v>
+        <f t="shared" si="45"/>
+        <v>1680</v>
       </c>
       <c r="G1474" s="7">
         <v>1</v>
       </c>
       <c r="H1474" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1474" s="7">
-        <f t="shared" si="45"/>
-        <v>420</v>
+        <f t="shared" si="46"/>
+        <v>380</v>
       </c>
       <c r="J1474" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1475" customHeight="1" spans="3:10">
       <c r="C1475" s="7">
-        <v>9150</v>
+        <v>9135</v>
       </c>
       <c r="D1475" s="7" t="s">
         <v>1524</v>
@@ -48101,26 +48122,26 @@
         <v>9</v>
       </c>
       <c r="F1475" s="7">
-        <f t="shared" si="44"/>
-        <v>2000</v>
+        <f t="shared" si="45"/>
+        <v>1700</v>
       </c>
       <c r="G1475" s="7">
         <v>1</v>
       </c>
       <c r="H1475" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1475" s="7">
-        <f t="shared" si="45"/>
-        <v>420</v>
+        <f t="shared" si="46"/>
+        <v>380</v>
       </c>
       <c r="J1475" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1476" customHeight="1" spans="3:10">
       <c r="C1476" s="7">
-        <v>9151</v>
+        <v>9136</v>
       </c>
       <c r="D1476" s="7" t="s">
         <v>1525</v>
@@ -48129,26 +48150,26 @@
         <v>9</v>
       </c>
       <c r="F1476" s="7">
-        <f t="shared" si="44"/>
-        <v>2020</v>
+        <f t="shared" si="45"/>
+        <v>1720</v>
       </c>
       <c r="G1476" s="7">
         <v>1</v>
       </c>
       <c r="H1476" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1476" s="7">
-        <f t="shared" si="45"/>
-        <v>420</v>
+        <f t="shared" si="46"/>
+        <v>380</v>
       </c>
       <c r="J1476" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1477" customHeight="1" spans="3:10">
       <c r="C1477" s="7">
-        <v>9152</v>
+        <v>9137</v>
       </c>
       <c r="D1477" s="7" t="s">
         <v>1526</v>
@@ -48157,26 +48178,26 @@
         <v>9</v>
       </c>
       <c r="F1477" s="7">
-        <f t="shared" si="44"/>
-        <v>2040</v>
+        <f t="shared" si="45"/>
+        <v>1740</v>
       </c>
       <c r="G1477" s="7">
         <v>1</v>
       </c>
       <c r="H1477" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1477" s="7">
-        <f t="shared" si="45"/>
-        <v>420</v>
+        <f t="shared" si="46"/>
+        <v>390</v>
       </c>
       <c r="J1477" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1478" customHeight="1" spans="3:10">
       <c r="C1478" s="7">
-        <v>9153</v>
+        <v>9138</v>
       </c>
       <c r="D1478" s="7" t="s">
         <v>1527</v>
@@ -48185,26 +48206,26 @@
         <v>9</v>
       </c>
       <c r="F1478" s="7">
-        <f t="shared" si="44"/>
-        <v>2060</v>
+        <f t="shared" si="45"/>
+        <v>1760</v>
       </c>
       <c r="G1478" s="7">
         <v>1</v>
       </c>
       <c r="H1478" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1478" s="7">
-        <f t="shared" si="45"/>
-        <v>430</v>
+        <f t="shared" si="46"/>
+        <v>390</v>
       </c>
       <c r="J1478" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1479" customHeight="1" spans="3:10">
       <c r="C1479" s="7">
-        <v>9154</v>
+        <v>9139</v>
       </c>
       <c r="D1479" s="7" t="s">
         <v>1528</v>
@@ -48213,26 +48234,26 @@
         <v>9</v>
       </c>
       <c r="F1479" s="7">
-        <f t="shared" si="44"/>
-        <v>2080</v>
+        <f t="shared" si="45"/>
+        <v>1780</v>
       </c>
       <c r="G1479" s="7">
         <v>1</v>
       </c>
       <c r="H1479" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1479" s="7">
-        <f t="shared" si="45"/>
-        <v>430</v>
+        <f t="shared" si="46"/>
+        <v>390</v>
       </c>
       <c r="J1479" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1480" customHeight="1" spans="3:10">
       <c r="C1480" s="7">
-        <v>9155</v>
+        <v>9140</v>
       </c>
       <c r="D1480" s="7" t="s">
         <v>1529</v>
@@ -48241,26 +48262,26 @@
         <v>9</v>
       </c>
       <c r="F1480" s="7">
-        <f t="shared" si="44"/>
-        <v>2100</v>
+        <f t="shared" si="45"/>
+        <v>1800</v>
       </c>
       <c r="G1480" s="7">
         <v>1</v>
       </c>
       <c r="H1480" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1480" s="7">
-        <f t="shared" si="45"/>
-        <v>430</v>
+        <f t="shared" si="46"/>
+        <v>390</v>
       </c>
       <c r="J1480" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1481" customHeight="1" spans="3:10">
       <c r="C1481" s="7">
-        <v>9156</v>
+        <v>9141</v>
       </c>
       <c r="D1481" s="7" t="s">
         <v>1530</v>
@@ -48269,26 +48290,26 @@
         <v>9</v>
       </c>
       <c r="F1481" s="7">
-        <f t="shared" si="44"/>
-        <v>2120</v>
+        <f t="shared" si="45"/>
+        <v>1820</v>
       </c>
       <c r="G1481" s="7">
         <v>1</v>
       </c>
       <c r="H1481" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1481" s="7">
-        <f t="shared" si="45"/>
-        <v>430</v>
+        <f t="shared" si="46"/>
+        <v>400</v>
       </c>
       <c r="J1481" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1482" customHeight="1" spans="3:10">
       <c r="C1482" s="7">
-        <v>9157</v>
+        <v>9142</v>
       </c>
       <c r="D1482" s="7" t="s">
         <v>1531</v>
@@ -48297,26 +48318,26 @@
         <v>9</v>
       </c>
       <c r="F1482" s="7">
-        <f t="shared" si="44"/>
-        <v>2140</v>
+        <f t="shared" si="45"/>
+        <v>1840</v>
       </c>
       <c r="G1482" s="7">
         <v>1</v>
       </c>
       <c r="H1482" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1482" s="7">
-        <f t="shared" si="45"/>
-        <v>440</v>
+        <f t="shared" si="46"/>
+        <v>400</v>
       </c>
       <c r="J1482" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1483" customHeight="1" spans="3:10">
       <c r="C1483" s="7">
-        <v>9158</v>
+        <v>9143</v>
       </c>
       <c r="D1483" s="7" t="s">
         <v>1532</v>
@@ -48325,26 +48346,26 @@
         <v>9</v>
       </c>
       <c r="F1483" s="7">
-        <f t="shared" si="44"/>
-        <v>2160</v>
+        <f t="shared" si="45"/>
+        <v>1860</v>
       </c>
       <c r="G1483" s="7">
         <v>1</v>
       </c>
       <c r="H1483" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1483" s="7">
-        <f t="shared" si="45"/>
-        <v>440</v>
+        <f t="shared" si="46"/>
+        <v>400</v>
       </c>
       <c r="J1483" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1484" customHeight="1" spans="3:10">
       <c r="C1484" s="7">
-        <v>9159</v>
+        <v>9144</v>
       </c>
       <c r="D1484" s="7" t="s">
         <v>1533</v>
@@ -48353,26 +48374,26 @@
         <v>9</v>
       </c>
       <c r="F1484" s="7">
-        <f t="shared" si="44"/>
-        <v>2180</v>
+        <f t="shared" si="45"/>
+        <v>1880</v>
       </c>
       <c r="G1484" s="7">
         <v>1</v>
       </c>
       <c r="H1484" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1484" s="7">
-        <f t="shared" si="45"/>
-        <v>440</v>
+        <f t="shared" si="46"/>
+        <v>400</v>
       </c>
       <c r="J1484" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1485" customHeight="1" spans="3:10">
       <c r="C1485" s="7">
-        <v>9160</v>
+        <v>9145</v>
       </c>
       <c r="D1485" s="7" t="s">
         <v>1534</v>
@@ -48381,26 +48402,26 @@
         <v>9</v>
       </c>
       <c r="F1485" s="7">
-        <f t="shared" si="44"/>
-        <v>2200</v>
+        <f t="shared" si="45"/>
+        <v>1900</v>
       </c>
       <c r="G1485" s="7">
         <v>1</v>
       </c>
       <c r="H1485" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1485" s="7">
-        <f t="shared" si="45"/>
-        <v>440</v>
+        <f t="shared" si="46"/>
+        <v>410</v>
       </c>
       <c r="J1485" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1486" customHeight="1" spans="3:10">
       <c r="C1486" s="7">
-        <v>9161</v>
+        <v>9146</v>
       </c>
       <c r="D1486" s="7" t="s">
         <v>1535</v>
@@ -48409,26 +48430,26 @@
         <v>9</v>
       </c>
       <c r="F1486" s="7">
-        <f t="shared" si="44"/>
-        <v>2220</v>
+        <f t="shared" si="45"/>
+        <v>1920</v>
       </c>
       <c r="G1486" s="7">
         <v>1</v>
       </c>
       <c r="H1486" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1486" s="7">
-        <f t="shared" si="45"/>
-        <v>450</v>
+        <f t="shared" si="46"/>
+        <v>410</v>
       </c>
       <c r="J1486" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1487" customHeight="1" spans="3:10">
       <c r="C1487" s="7">
-        <v>9162</v>
+        <v>9147</v>
       </c>
       <c r="D1487" s="7" t="s">
         <v>1536</v>
@@ -48437,26 +48458,26 @@
         <v>9</v>
       </c>
       <c r="F1487" s="7">
-        <f t="shared" si="44"/>
-        <v>2240</v>
+        <f t="shared" si="45"/>
+        <v>1940</v>
       </c>
       <c r="G1487" s="7">
         <v>1</v>
       </c>
       <c r="H1487" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1487" s="7">
-        <f t="shared" si="45"/>
-        <v>450</v>
+        <f t="shared" si="46"/>
+        <v>410</v>
       </c>
       <c r="J1487" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1488" customHeight="1" spans="3:10">
       <c r="C1488" s="7">
-        <v>9163</v>
+        <v>9148</v>
       </c>
       <c r="D1488" s="7" t="s">
         <v>1537</v>
@@ -48465,26 +48486,26 @@
         <v>9</v>
       </c>
       <c r="F1488" s="7">
-        <f t="shared" si="44"/>
-        <v>2260</v>
+        <f t="shared" si="45"/>
+        <v>1960</v>
       </c>
       <c r="G1488" s="7">
         <v>1</v>
       </c>
       <c r="H1488" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1488" s="7">
-        <f t="shared" si="45"/>
-        <v>450</v>
+        <f t="shared" si="46"/>
+        <v>410</v>
       </c>
       <c r="J1488" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1489" customHeight="1" spans="3:10">
       <c r="C1489" s="7">
-        <v>9164</v>
+        <v>9149</v>
       </c>
       <c r="D1489" s="7" t="s">
         <v>1538</v>
@@ -48493,26 +48514,26 @@
         <v>9</v>
       </c>
       <c r="F1489" s="7">
-        <f t="shared" si="44"/>
-        <v>2280</v>
+        <f t="shared" si="45"/>
+        <v>1980</v>
       </c>
       <c r="G1489" s="7">
         <v>1</v>
       </c>
       <c r="H1489" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1489" s="7">
-        <f t="shared" si="45"/>
-        <v>450</v>
+        <f t="shared" si="46"/>
+        <v>420</v>
       </c>
       <c r="J1489" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1490" customHeight="1" spans="3:10">
       <c r="C1490" s="7">
-        <v>9165</v>
+        <v>9150</v>
       </c>
       <c r="D1490" s="7" t="s">
         <v>1539</v>
@@ -48521,26 +48542,26 @@
         <v>9</v>
       </c>
       <c r="F1490" s="7">
-        <f t="shared" ref="F1490:F1495" si="46">F1489+20</f>
-        <v>2300</v>
+        <f t="shared" si="45"/>
+        <v>2000</v>
       </c>
       <c r="G1490" s="7">
         <v>1</v>
       </c>
       <c r="H1490" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1490" s="7">
-        <f t="shared" ref="I1490:I1505" si="47">I1486+10</f>
-        <v>460</v>
+        <f t="shared" si="46"/>
+        <v>420</v>
       </c>
       <c r="J1490" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1491" customHeight="1" spans="3:10">
       <c r="C1491" s="7">
-        <v>9166</v>
+        <v>9151</v>
       </c>
       <c r="D1491" s="7" t="s">
         <v>1540</v>
@@ -48549,26 +48570,26 @@
         <v>9</v>
       </c>
       <c r="F1491" s="7">
+        <f t="shared" si="45"/>
+        <v>2020</v>
+      </c>
+      <c r="G1491" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1491" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1491" s="7">
         <f t="shared" si="46"/>
-        <v>2320</v>
-      </c>
-      <c r="G1491" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1491" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1491" s="7">
-        <f t="shared" si="47"/>
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="J1491" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1492" customHeight="1" spans="3:10">
       <c r="C1492" s="7">
-        <v>9167</v>
+        <v>9152</v>
       </c>
       <c r="D1492" s="7" t="s">
         <v>1541</v>
@@ -48577,26 +48598,26 @@
         <v>9</v>
       </c>
       <c r="F1492" s="7">
+        <f t="shared" si="45"/>
+        <v>2040</v>
+      </c>
+      <c r="G1492" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1492" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1492" s="7">
         <f t="shared" si="46"/>
-        <v>2340</v>
-      </c>
-      <c r="G1492" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1492" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1492" s="7">
-        <f t="shared" si="47"/>
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="J1492" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1493" customHeight="1" spans="3:10">
       <c r="C1493" s="7">
-        <v>9168</v>
+        <v>9153</v>
       </c>
       <c r="D1493" s="7" t="s">
         <v>1542</v>
@@ -48605,26 +48626,26 @@
         <v>9</v>
       </c>
       <c r="F1493" s="7">
+        <f t="shared" si="45"/>
+        <v>2060</v>
+      </c>
+      <c r="G1493" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1493" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1493" s="7">
         <f t="shared" si="46"/>
-        <v>2360</v>
-      </c>
-      <c r="G1493" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1493" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1493" s="7">
-        <f t="shared" si="47"/>
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="J1493" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1494" customHeight="1" spans="3:10">
       <c r="C1494" s="7">
-        <v>9169</v>
+        <v>9154</v>
       </c>
       <c r="D1494" s="7" t="s">
         <v>1543</v>
@@ -48633,26 +48654,26 @@
         <v>9</v>
       </c>
       <c r="F1494" s="7">
+        <f t="shared" si="45"/>
+        <v>2080</v>
+      </c>
+      <c r="G1494" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1494" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1494" s="7">
         <f t="shared" si="46"/>
-        <v>2380</v>
-      </c>
-      <c r="G1494" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1494" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1494" s="7">
-        <f t="shared" si="47"/>
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="J1494" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1495" customHeight="1" spans="3:10">
       <c r="C1495" s="7">
-        <v>9170</v>
+        <v>9155</v>
       </c>
       <c r="D1495" s="7" t="s">
         <v>1544</v>
@@ -48661,26 +48682,26 @@
         <v>9</v>
       </c>
       <c r="F1495" s="7">
+        <f t="shared" si="45"/>
+        <v>2100</v>
+      </c>
+      <c r="G1495" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1495" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1495" s="7">
         <f t="shared" si="46"/>
-        <v>2400</v>
-      </c>
-      <c r="G1495" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1495" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1495" s="7">
-        <f t="shared" si="47"/>
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="J1495" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1496" customHeight="1" spans="3:10">
       <c r="C1496" s="7">
-        <v>9171</v>
+        <v>9156</v>
       </c>
       <c r="D1496" s="7" t="s">
         <v>1545</v>
@@ -48689,26 +48710,26 @@
         <v>9</v>
       </c>
       <c r="F1496" s="7">
-        <f t="shared" ref="F1496:F1517" si="48">F1495+30</f>
-        <v>2430</v>
+        <f t="shared" si="45"/>
+        <v>2120</v>
       </c>
       <c r="G1496" s="7">
         <v>1</v>
       </c>
       <c r="H1496" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1496" s="7">
-        <f t="shared" si="47"/>
-        <v>470</v>
+        <f t="shared" si="46"/>
+        <v>430</v>
       </c>
       <c r="J1496" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1497" customHeight="1" spans="3:10">
       <c r="C1497" s="7">
-        <v>9172</v>
+        <v>9157</v>
       </c>
       <c r="D1497" s="7" t="s">
         <v>1546</v>
@@ -48717,26 +48738,26 @@
         <v>9</v>
       </c>
       <c r="F1497" s="7">
-        <f t="shared" si="48"/>
-        <v>2460</v>
+        <f t="shared" si="45"/>
+        <v>2140</v>
       </c>
       <c r="G1497" s="7">
         <v>1</v>
       </c>
       <c r="H1497" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1497" s="7">
-        <f t="shared" si="47"/>
-        <v>470</v>
+        <f t="shared" si="46"/>
+        <v>440</v>
       </c>
       <c r="J1497" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1498" customHeight="1" spans="3:10">
       <c r="C1498" s="7">
-        <v>9173</v>
+        <v>9158</v>
       </c>
       <c r="D1498" s="7" t="s">
         <v>1547</v>
@@ -48745,26 +48766,26 @@
         <v>9</v>
       </c>
       <c r="F1498" s="7">
-        <f t="shared" si="48"/>
-        <v>2490</v>
+        <f t="shared" si="45"/>
+        <v>2160</v>
       </c>
       <c r="G1498" s="7">
         <v>1</v>
       </c>
       <c r="H1498" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1498" s="7">
-        <f t="shared" si="47"/>
-        <v>480</v>
+        <f t="shared" si="46"/>
+        <v>440</v>
       </c>
       <c r="J1498" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1499" customHeight="1" spans="3:10">
       <c r="C1499" s="7">
-        <v>9174</v>
+        <v>9159</v>
       </c>
       <c r="D1499" s="7" t="s">
         <v>1548</v>
@@ -48773,26 +48794,26 @@
         <v>9</v>
       </c>
       <c r="F1499" s="7">
-        <f t="shared" si="48"/>
-        <v>2520</v>
+        <f t="shared" si="45"/>
+        <v>2180</v>
       </c>
       <c r="G1499" s="7">
         <v>1</v>
       </c>
       <c r="H1499" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1499" s="7">
-        <f t="shared" si="47"/>
-        <v>480</v>
+        <f t="shared" si="46"/>
+        <v>440</v>
       </c>
       <c r="J1499" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1500" customHeight="1" spans="3:10">
       <c r="C1500" s="7">
-        <v>9175</v>
+        <v>9160</v>
       </c>
       <c r="D1500" s="7" t="s">
         <v>1549</v>
@@ -48801,26 +48822,26 @@
         <v>9</v>
       </c>
       <c r="F1500" s="7">
-        <f t="shared" si="48"/>
-        <v>2550</v>
+        <f t="shared" si="45"/>
+        <v>2200</v>
       </c>
       <c r="G1500" s="7">
         <v>1</v>
       </c>
       <c r="H1500" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1500" s="7">
-        <f t="shared" si="47"/>
-        <v>480</v>
+        <f t="shared" si="46"/>
+        <v>440</v>
       </c>
       <c r="J1500" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1501" customHeight="1" spans="3:10">
       <c r="C1501" s="7">
-        <v>9176</v>
+        <v>9161</v>
       </c>
       <c r="D1501" s="7" t="s">
         <v>1550</v>
@@ -48829,26 +48850,26 @@
         <v>9</v>
       </c>
       <c r="F1501" s="7">
-        <f t="shared" si="48"/>
-        <v>2580</v>
+        <f t="shared" si="45"/>
+        <v>2220</v>
       </c>
       <c r="G1501" s="7">
         <v>1</v>
       </c>
       <c r="H1501" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1501" s="7">
-        <f t="shared" si="47"/>
-        <v>480</v>
+        <f t="shared" si="46"/>
+        <v>450</v>
       </c>
       <c r="J1501" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1502" customHeight="1" spans="3:10">
       <c r="C1502" s="7">
-        <v>9177</v>
+        <v>9162</v>
       </c>
       <c r="D1502" s="7" t="s">
         <v>1551</v>
@@ -48857,26 +48878,26 @@
         <v>9</v>
       </c>
       <c r="F1502" s="7">
-        <f t="shared" si="48"/>
-        <v>2610</v>
+        <f t="shared" si="45"/>
+        <v>2240</v>
       </c>
       <c r="G1502" s="7">
         <v>1</v>
       </c>
       <c r="H1502" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1502" s="7">
-        <f t="shared" si="47"/>
-        <v>490</v>
+        <f t="shared" si="46"/>
+        <v>450</v>
       </c>
       <c r="J1502" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1503" customHeight="1" spans="3:10">
       <c r="C1503" s="7">
-        <v>9178</v>
+        <v>9163</v>
       </c>
       <c r="D1503" s="7" t="s">
         <v>1552</v>
@@ -48885,26 +48906,26 @@
         <v>9</v>
       </c>
       <c r="F1503" s="7">
-        <f t="shared" si="48"/>
-        <v>2640</v>
+        <f t="shared" si="45"/>
+        <v>2260</v>
       </c>
       <c r="G1503" s="7">
         <v>1</v>
       </c>
       <c r="H1503" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1503" s="7">
-        <f t="shared" si="47"/>
-        <v>490</v>
+        <f t="shared" si="46"/>
+        <v>450</v>
       </c>
       <c r="J1503" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1504" customHeight="1" spans="3:10">
       <c r="C1504" s="7">
-        <v>9179</v>
+        <v>9164</v>
       </c>
       <c r="D1504" s="7" t="s">
         <v>1553</v>
@@ -48913,26 +48934,26 @@
         <v>9</v>
       </c>
       <c r="F1504" s="7">
-        <f t="shared" si="48"/>
-        <v>2670</v>
+        <f t="shared" si="45"/>
+        <v>2280</v>
       </c>
       <c r="G1504" s="7">
         <v>1</v>
       </c>
       <c r="H1504" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1504" s="7">
-        <f t="shared" si="47"/>
-        <v>490</v>
+        <f t="shared" si="46"/>
+        <v>450</v>
       </c>
       <c r="J1504" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1505" customHeight="1" spans="3:10">
       <c r="C1505" s="7">
-        <v>9180</v>
+        <v>9165</v>
       </c>
       <c r="D1505" s="7" t="s">
         <v>1554</v>
@@ -48941,26 +48962,26 @@
         <v>9</v>
       </c>
       <c r="F1505" s="7">
-        <f t="shared" si="48"/>
-        <v>2700</v>
+        <f t="shared" ref="F1505:F1510" si="47">F1504+20</f>
+        <v>2300</v>
       </c>
       <c r="G1505" s="7">
         <v>1</v>
       </c>
       <c r="H1505" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1505" s="7">
-        <f t="shared" si="47"/>
-        <v>490</v>
+        <f t="shared" ref="I1505:I1520" si="48">I1501+10</f>
+        <v>460</v>
       </c>
       <c r="J1505" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1506" customHeight="1" spans="3:10">
       <c r="C1506" s="7">
-        <v>9181</v>
+        <v>9166</v>
       </c>
       <c r="D1506" s="7" t="s">
         <v>1555</v>
@@ -48969,26 +48990,26 @@
         <v>9</v>
       </c>
       <c r="F1506" s="7">
+        <f t="shared" si="47"/>
+        <v>2320</v>
+      </c>
+      <c r="G1506" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1506" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1506" s="7">
         <f t="shared" si="48"/>
-        <v>2730</v>
-      </c>
-      <c r="G1506" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1506" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1506" s="7">
-        <f t="shared" ref="I1506:I1529" si="49">I1502+10</f>
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="J1506" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1507" customHeight="1" spans="3:10">
       <c r="C1507" s="7">
-        <v>9182</v>
+        <v>9167</v>
       </c>
       <c r="D1507" s="7" t="s">
         <v>1556</v>
@@ -48997,26 +49018,26 @@
         <v>9</v>
       </c>
       <c r="F1507" s="7">
+        <f t="shared" si="47"/>
+        <v>2340</v>
+      </c>
+      <c r="G1507" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1507" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1507" s="7">
         <f t="shared" si="48"/>
-        <v>2760</v>
-      </c>
-      <c r="G1507" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1507" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1507" s="7">
-        <f t="shared" si="49"/>
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="J1507" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1508" customHeight="1" spans="3:10">
       <c r="C1508" s="7">
-        <v>9183</v>
+        <v>9168</v>
       </c>
       <c r="D1508" s="7" t="s">
         <v>1557</v>
@@ -49025,26 +49046,26 @@
         <v>9</v>
       </c>
       <c r="F1508" s="7">
+        <f t="shared" si="47"/>
+        <v>2360</v>
+      </c>
+      <c r="G1508" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1508" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1508" s="7">
         <f t="shared" si="48"/>
-        <v>2790</v>
-      </c>
-      <c r="G1508" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1508" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1508" s="7">
-        <f t="shared" si="49"/>
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="J1508" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1509" customHeight="1" spans="3:10">
       <c r="C1509" s="7">
-        <v>9184</v>
+        <v>9169</v>
       </c>
       <c r="D1509" s="7" t="s">
         <v>1558</v>
@@ -49053,26 +49074,26 @@
         <v>9</v>
       </c>
       <c r="F1509" s="7">
+        <f t="shared" si="47"/>
+        <v>2380</v>
+      </c>
+      <c r="G1509" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1509" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1509" s="7">
         <f t="shared" si="48"/>
-        <v>2820</v>
-      </c>
-      <c r="G1509" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1509" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1509" s="7">
-        <f t="shared" si="49"/>
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="J1509" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1510" customHeight="1" spans="3:10">
       <c r="C1510" s="7">
-        <v>9185</v>
+        <v>9170</v>
       </c>
       <c r="D1510" s="7" t="s">
         <v>1559</v>
@@ -49081,26 +49102,26 @@
         <v>9</v>
       </c>
       <c r="F1510" s="7">
+        <f t="shared" si="47"/>
+        <v>2400</v>
+      </c>
+      <c r="G1510" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1510" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1510" s="7">
         <f t="shared" si="48"/>
-        <v>2850</v>
-      </c>
-      <c r="G1510" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1510" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1510" s="7">
-        <f t="shared" si="49"/>
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="J1510" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1511" customHeight="1" spans="3:10">
       <c r="C1511" s="7">
-        <v>9186</v>
+        <v>9171</v>
       </c>
       <c r="D1511" s="7" t="s">
         <v>1560</v>
@@ -49109,26 +49130,26 @@
         <v>9</v>
       </c>
       <c r="F1511" s="7">
+        <f t="shared" ref="F1511:F1532" si="49">F1510+30</f>
+        <v>2430</v>
+      </c>
+      <c r="G1511" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1511" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1511" s="7">
         <f t="shared" si="48"/>
-        <v>2880</v>
-      </c>
-      <c r="G1511" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1511" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1511" s="7">
-        <f t="shared" si="49"/>
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="J1511" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1512" customHeight="1" spans="3:10">
       <c r="C1512" s="7">
-        <v>9187</v>
+        <v>9172</v>
       </c>
       <c r="D1512" s="7" t="s">
         <v>1561</v>
@@ -49137,26 +49158,26 @@
         <v>9</v>
       </c>
       <c r="F1512" s="7">
+        <f t="shared" si="49"/>
+        <v>2460</v>
+      </c>
+      <c r="G1512" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1512" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1512" s="7">
         <f t="shared" si="48"/>
-        <v>2910</v>
-      </c>
-      <c r="G1512" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1512" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1512" s="7">
-        <f t="shared" si="49"/>
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="J1512" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1513" customHeight="1" spans="3:10">
       <c r="C1513" s="7">
-        <v>9188</v>
+        <v>9173</v>
       </c>
       <c r="D1513" s="7" t="s">
         <v>1562</v>
@@ -49165,26 +49186,26 @@
         <v>9</v>
       </c>
       <c r="F1513" s="7">
+        <f t="shared" si="49"/>
+        <v>2490</v>
+      </c>
+      <c r="G1513" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1513" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1513" s="7">
         <f t="shared" si="48"/>
-        <v>2940</v>
-      </c>
-      <c r="G1513" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1513" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1513" s="7">
-        <f t="shared" si="49"/>
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="J1513" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1514" customHeight="1" spans="3:10">
       <c r="C1514" s="7">
-        <v>9189</v>
+        <v>9174</v>
       </c>
       <c r="D1514" s="7" t="s">
         <v>1563</v>
@@ -49193,26 +49214,26 @@
         <v>9</v>
       </c>
       <c r="F1514" s="7">
+        <f t="shared" si="49"/>
+        <v>2520</v>
+      </c>
+      <c r="G1514" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1514" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1514" s="7">
         <f t="shared" si="48"/>
-        <v>2970</v>
-      </c>
-      <c r="G1514" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1514" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1514" s="7">
-        <f t="shared" si="49"/>
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="J1514" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1515" customHeight="1" spans="3:10">
       <c r="C1515" s="7">
-        <v>9190</v>
+        <v>9175</v>
       </c>
       <c r="D1515" s="7" t="s">
         <v>1564</v>
@@ -49221,26 +49242,26 @@
         <v>9</v>
       </c>
       <c r="F1515" s="7">
+        <f t="shared" si="49"/>
+        <v>2550</v>
+      </c>
+      <c r="G1515" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1515" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1515" s="7">
         <f t="shared" si="48"/>
-        <v>3000</v>
-      </c>
-      <c r="G1515" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1515" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1515" s="7">
-        <f t="shared" si="49"/>
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="J1515" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1516" customHeight="1" spans="3:10">
       <c r="C1516" s="7">
-        <v>9191</v>
+        <v>9176</v>
       </c>
       <c r="D1516" s="7" t="s">
         <v>1565</v>
@@ -49249,26 +49270,26 @@
         <v>9</v>
       </c>
       <c r="F1516" s="7">
-        <f t="shared" ref="F1516:F1529" si="50">F1515+40</f>
-        <v>3040</v>
+        <f t="shared" si="49"/>
+        <v>2580</v>
       </c>
       <c r="G1516" s="7">
         <v>1</v>
       </c>
       <c r="H1516" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1516" s="7">
-        <f t="shared" si="49"/>
-        <v>520</v>
+        <f t="shared" si="48"/>
+        <v>480</v>
       </c>
       <c r="J1516" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1517" customHeight="1" spans="3:10">
       <c r="C1517" s="7">
-        <v>9192</v>
+        <v>9177</v>
       </c>
       <c r="D1517" s="7" t="s">
         <v>1566</v>
@@ -49277,26 +49298,26 @@
         <v>9</v>
       </c>
       <c r="F1517" s="7">
-        <f t="shared" si="50"/>
-        <v>3080</v>
+        <f t="shared" si="49"/>
+        <v>2610</v>
       </c>
       <c r="G1517" s="7">
         <v>1</v>
       </c>
       <c r="H1517" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1517" s="7">
-        <f t="shared" si="49"/>
-        <v>520</v>
+        <f t="shared" si="48"/>
+        <v>490</v>
       </c>
       <c r="J1517" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1518" customHeight="1" spans="3:10">
       <c r="C1518" s="7">
-        <v>9193</v>
+        <v>9178</v>
       </c>
       <c r="D1518" s="7" t="s">
         <v>1567</v>
@@ -49305,26 +49326,26 @@
         <v>9</v>
       </c>
       <c r="F1518" s="7">
-        <f t="shared" si="50"/>
-        <v>3120</v>
+        <f t="shared" si="49"/>
+        <v>2640</v>
       </c>
       <c r="G1518" s="7">
         <v>1</v>
       </c>
       <c r="H1518" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1518" s="7">
-        <f t="shared" si="49"/>
-        <v>530</v>
+        <f t="shared" si="48"/>
+        <v>490</v>
       </c>
       <c r="J1518" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1519" customHeight="1" spans="3:10">
       <c r="C1519" s="7">
-        <v>9194</v>
+        <v>9179</v>
       </c>
       <c r="D1519" s="7" t="s">
         <v>1568</v>
@@ -49333,26 +49354,26 @@
         <v>9</v>
       </c>
       <c r="F1519" s="7">
-        <f t="shared" si="50"/>
-        <v>3160</v>
+        <f t="shared" si="49"/>
+        <v>2670</v>
       </c>
       <c r="G1519" s="7">
         <v>1</v>
       </c>
       <c r="H1519" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1519" s="7">
-        <f t="shared" si="49"/>
-        <v>530</v>
+        <f t="shared" si="48"/>
+        <v>490</v>
       </c>
       <c r="J1519" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1520" customHeight="1" spans="3:10">
       <c r="C1520" s="7">
-        <v>9195</v>
+        <v>9180</v>
       </c>
       <c r="D1520" s="7" t="s">
         <v>1569</v>
@@ -49361,26 +49382,26 @@
         <v>9</v>
       </c>
       <c r="F1520" s="7">
-        <f t="shared" si="50"/>
-        <v>3200</v>
+        <f t="shared" si="49"/>
+        <v>2700</v>
       </c>
       <c r="G1520" s="7">
         <v>1</v>
       </c>
       <c r="H1520" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I1520" s="7">
-        <f t="shared" si="49"/>
-        <v>530</v>
+        <f t="shared" si="48"/>
+        <v>490</v>
       </c>
       <c r="J1520" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1521" customHeight="1" spans="3:10">
       <c r="C1521" s="7">
-        <v>9196</v>
+        <v>9181</v>
       </c>
       <c r="D1521" s="7" t="s">
         <v>1570</v>
@@ -49389,26 +49410,26 @@
         <v>9</v>
       </c>
       <c r="F1521" s="7">
-        <f t="shared" si="50"/>
-        <v>3240</v>
+        <f t="shared" si="49"/>
+        <v>2730</v>
       </c>
       <c r="G1521" s="7">
         <v>1</v>
       </c>
       <c r="H1521" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I1521" s="7">
-        <f t="shared" si="49"/>
-        <v>530</v>
+        <f t="shared" ref="I1521:I1544" si="50">I1517+10</f>
+        <v>500</v>
       </c>
       <c r="J1521" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1522" customHeight="1" spans="3:10">
       <c r="C1522" s="7">
-        <v>9197</v>
+        <v>9182</v>
       </c>
       <c r="D1522" s="7" t="s">
         <v>1571</v>
@@ -49417,26 +49438,26 @@
         <v>9</v>
       </c>
       <c r="F1522" s="7">
+        <f t="shared" si="49"/>
+        <v>2760</v>
+      </c>
+      <c r="G1522" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1522" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1522" s="7">
         <f t="shared" si="50"/>
-        <v>3280</v>
-      </c>
-      <c r="G1522" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1522" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1522" s="7">
-        <f t="shared" si="49"/>
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="J1522" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1523" customHeight="1" spans="3:10">
       <c r="C1523" s="7">
-        <v>9198</v>
+        <v>9183</v>
       </c>
       <c r="D1523" s="7" t="s">
         <v>1572</v>
@@ -49445,26 +49466,26 @@
         <v>9</v>
       </c>
       <c r="F1523" s="7">
+        <f t="shared" si="49"/>
+        <v>2790</v>
+      </c>
+      <c r="G1523" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1523" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1523" s="7">
         <f t="shared" si="50"/>
-        <v>3320</v>
-      </c>
-      <c r="G1523" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1523" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1523" s="7">
-        <f t="shared" si="49"/>
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="J1523" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1524" customHeight="1" spans="3:10">
       <c r="C1524" s="7">
-        <v>9199</v>
+        <v>9184</v>
       </c>
       <c r="D1524" s="7" t="s">
         <v>1573</v>
@@ -49473,26 +49494,26 @@
         <v>9</v>
       </c>
       <c r="F1524" s="7">
+        <f t="shared" si="49"/>
+        <v>2820</v>
+      </c>
+      <c r="G1524" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1524" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1524" s="7">
         <f t="shared" si="50"/>
-        <v>3360</v>
-      </c>
-      <c r="G1524" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1524" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1524" s="7">
-        <f t="shared" si="49"/>
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="J1524" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1525" customHeight="1" spans="3:10">
       <c r="C1525" s="7">
-        <v>9200</v>
+        <v>9185</v>
       </c>
       <c r="D1525" s="7" t="s">
         <v>1574</v>
@@ -49501,26 +49522,26 @@
         <v>9</v>
       </c>
       <c r="F1525" s="7">
+        <f t="shared" si="49"/>
+        <v>2850</v>
+      </c>
+      <c r="G1525" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1525" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1525" s="7">
         <f t="shared" si="50"/>
-        <v>3400</v>
-      </c>
-      <c r="G1525" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1525" s="7">
-        <v>24</v>
-      </c>
-      <c r="I1525" s="7">
-        <f t="shared" si="49"/>
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="J1525" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1526" customHeight="1" spans="3:10">
       <c r="C1526" s="7">
-        <v>9201</v>
+        <v>9186</v>
       </c>
       <c r="D1526" s="7" t="s">
         <v>1575</v>
@@ -49529,26 +49550,26 @@
         <v>9</v>
       </c>
       <c r="F1526" s="7">
+        <f t="shared" si="49"/>
+        <v>2880</v>
+      </c>
+      <c r="G1526" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1526" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1526" s="7">
         <f t="shared" si="50"/>
-        <v>3440</v>
-      </c>
-      <c r="G1526" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1526" s="7">
-        <v>18</v>
-      </c>
-      <c r="I1526" s="7">
-        <f t="shared" si="49"/>
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="J1526" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1527" customHeight="1" spans="3:10">
       <c r="C1527" s="7">
-        <v>9202</v>
+        <v>9187</v>
       </c>
       <c r="D1527" s="7" t="s">
         <v>1576</v>
@@ -49557,26 +49578,26 @@
         <v>9</v>
       </c>
       <c r="F1527" s="7">
+        <f t="shared" si="49"/>
+        <v>2910</v>
+      </c>
+      <c r="G1527" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1527" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1527" s="7">
         <f t="shared" si="50"/>
-        <v>3480</v>
-      </c>
-      <c r="G1527" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1527" s="7">
-        <v>19</v>
-      </c>
-      <c r="I1527" s="7">
-        <f t="shared" si="49"/>
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="J1527" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1528" customHeight="1" spans="3:10">
       <c r="C1528" s="7">
-        <v>9203</v>
+        <v>9188</v>
       </c>
       <c r="D1528" s="7" t="s">
         <v>1577</v>
@@ -49585,26 +49606,26 @@
         <v>9</v>
       </c>
       <c r="F1528" s="7">
+        <f t="shared" si="49"/>
+        <v>2940</v>
+      </c>
+      <c r="G1528" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1528" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1528" s="7">
         <f t="shared" si="50"/>
-        <v>3520</v>
-      </c>
-      <c r="G1528" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1528" s="7">
-        <v>20</v>
-      </c>
-      <c r="I1528" s="7">
-        <f t="shared" si="49"/>
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="J1528" s="7" t="s">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1529" customHeight="1" spans="3:10">
       <c r="C1529" s="7">
-        <v>9204</v>
+        <v>9189</v>
       </c>
       <c r="D1529" s="7" t="s">
         <v>1578</v>
@@ -49613,21 +49634,441 @@
         <v>9</v>
       </c>
       <c r="F1529" s="7">
+        <f t="shared" si="49"/>
+        <v>2970</v>
+      </c>
+      <c r="G1529" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1529" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1529" s="7">
         <f t="shared" si="50"/>
+        <v>520</v>
+      </c>
+      <c r="J1529" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1530" customHeight="1" spans="3:10">
+      <c r="C1530" s="7">
+        <v>9190</v>
+      </c>
+      <c r="D1530" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E1530" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1530" s="7">
+        <f t="shared" si="49"/>
+        <v>3000</v>
+      </c>
+      <c r="G1530" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1530" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1530" s="7">
+        <f t="shared" si="50"/>
+        <v>520</v>
+      </c>
+      <c r="J1530" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1531" customHeight="1" spans="3:10">
+      <c r="C1531" s="7">
+        <v>9191</v>
+      </c>
+      <c r="D1531" s="7" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E1531" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1531" s="7">
+        <f t="shared" ref="F1531:F1544" si="51">F1530+40</f>
+        <v>3040</v>
+      </c>
+      <c r="G1531" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1531" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1531" s="7">
+        <f t="shared" si="50"/>
+        <v>520</v>
+      </c>
+      <c r="J1531" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1532" customHeight="1" spans="3:10">
+      <c r="C1532" s="7">
+        <v>9192</v>
+      </c>
+      <c r="D1532" s="7" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E1532" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1532" s="7">
+        <f t="shared" si="51"/>
+        <v>3080</v>
+      </c>
+      <c r="G1532" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1532" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1532" s="7">
+        <f t="shared" si="50"/>
+        <v>520</v>
+      </c>
+      <c r="J1532" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1533" customHeight="1" spans="3:10">
+      <c r="C1533" s="7">
+        <v>9193</v>
+      </c>
+      <c r="D1533" s="7" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E1533" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1533" s="7">
+        <f t="shared" si="51"/>
+        <v>3120</v>
+      </c>
+      <c r="G1533" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1533" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1533" s="7">
+        <f t="shared" si="50"/>
+        <v>530</v>
+      </c>
+      <c r="J1533" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1534" customHeight="1" spans="3:10">
+      <c r="C1534" s="7">
+        <v>9194</v>
+      </c>
+      <c r="D1534" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E1534" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1534" s="7">
+        <f t="shared" si="51"/>
+        <v>3160</v>
+      </c>
+      <c r="G1534" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1534" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1534" s="7">
+        <f t="shared" si="50"/>
+        <v>530</v>
+      </c>
+      <c r="J1534" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1535" customHeight="1" spans="3:10">
+      <c r="C1535" s="7">
+        <v>9195</v>
+      </c>
+      <c r="D1535" s="7" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E1535" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1535" s="7">
+        <f t="shared" si="51"/>
+        <v>3200</v>
+      </c>
+      <c r="G1535" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1535" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1535" s="7">
+        <f t="shared" si="50"/>
+        <v>530</v>
+      </c>
+      <c r="J1535" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1536" customHeight="1" spans="3:10">
+      <c r="C1536" s="7">
+        <v>9196</v>
+      </c>
+      <c r="D1536" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E1536" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1536" s="7">
+        <f t="shared" si="51"/>
+        <v>3240</v>
+      </c>
+      <c r="G1536" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1536" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1536" s="7">
+        <f t="shared" si="50"/>
+        <v>530</v>
+      </c>
+      <c r="J1536" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1537" customHeight="1" spans="3:10">
+      <c r="C1537" s="7">
+        <v>9197</v>
+      </c>
+      <c r="D1537" s="7" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E1537" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1537" s="7">
+        <f t="shared" si="51"/>
+        <v>3280</v>
+      </c>
+      <c r="G1537" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1537" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1537" s="7">
+        <f t="shared" si="50"/>
+        <v>540</v>
+      </c>
+      <c r="J1537" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1538" customHeight="1" spans="3:10">
+      <c r="C1538" s="7">
+        <v>9198</v>
+      </c>
+      <c r="D1538" s="7" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E1538" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1538" s="7">
+        <f t="shared" si="51"/>
+        <v>3320</v>
+      </c>
+      <c r="G1538" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1538" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1538" s="7">
+        <f t="shared" si="50"/>
+        <v>540</v>
+      </c>
+      <c r="J1538" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1539" customHeight="1" spans="3:10">
+      <c r="C1539" s="7">
+        <v>9199</v>
+      </c>
+      <c r="D1539" s="7" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E1539" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1539" s="7">
+        <f t="shared" si="51"/>
+        <v>3360</v>
+      </c>
+      <c r="G1539" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1539" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1539" s="7">
+        <f t="shared" si="50"/>
+        <v>540</v>
+      </c>
+      <c r="J1539" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1540" customHeight="1" spans="3:10">
+      <c r="C1540" s="7">
+        <v>9200</v>
+      </c>
+      <c r="D1540" s="7" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E1540" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1540" s="7">
+        <f t="shared" si="51"/>
+        <v>3400</v>
+      </c>
+      <c r="G1540" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1540" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1540" s="7">
+        <f t="shared" si="50"/>
+        <v>540</v>
+      </c>
+      <c r="J1540" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1541" customHeight="1" spans="3:10">
+      <c r="C1541" s="7">
+        <v>9201</v>
+      </c>
+      <c r="D1541" s="7" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E1541" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1541" s="7">
+        <f t="shared" si="51"/>
+        <v>3440</v>
+      </c>
+      <c r="G1541" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1541" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1541" s="7">
+        <f t="shared" si="50"/>
+        <v>550</v>
+      </c>
+      <c r="J1541" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1542" customHeight="1" spans="3:10">
+      <c r="C1542" s="7">
+        <v>9202</v>
+      </c>
+      <c r="D1542" s="7" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E1542" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1542" s="7">
+        <f t="shared" si="51"/>
+        <v>3480</v>
+      </c>
+      <c r="G1542" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1542" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1542" s="7">
+        <f t="shared" si="50"/>
+        <v>550</v>
+      </c>
+      <c r="J1542" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1543" customHeight="1" spans="3:10">
+      <c r="C1543" s="7">
+        <v>9203</v>
+      </c>
+      <c r="D1543" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E1543" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1543" s="7">
+        <f t="shared" si="51"/>
+        <v>3520</v>
+      </c>
+      <c r="G1543" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1543" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1543" s="7">
+        <f t="shared" si="50"/>
+        <v>550</v>
+      </c>
+      <c r="J1543" s="7" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1544" customHeight="1" spans="3:10">
+      <c r="C1544" s="7">
+        <v>9204</v>
+      </c>
+      <c r="D1544" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E1544" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1544" s="7">
+        <f t="shared" si="51"/>
         <v>3560</v>
       </c>
-      <c r="G1529" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1529" s="7">
+      <c r="G1544" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1544" s="7">
         <v>24</v>
       </c>
-      <c r="I1529" s="7">
-        <f t="shared" si="49"/>
+      <c r="I1544" s="7">
+        <f t="shared" si="50"/>
         <v>550</v>
       </c>
-      <c r="J1529" s="7" t="s">
-        <v>1375</v>
+      <c r="J1544" s="7" t="s">
+        <v>1390</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4321" uniqueCount="1698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4361" uniqueCount="1718">
   <si>
     <t>#</t>
   </si>
@@ -5186,6 +5186,66 @@
   </si>
   <si>
     <t>攀登者228</t>
+  </si>
+  <si>
+    <t>攀登者229</t>
+  </si>
+  <si>
+    <t>攀登者230</t>
+  </si>
+  <si>
+    <t>攀登者231</t>
+  </si>
+  <si>
+    <t>攀登者232</t>
+  </si>
+  <si>
+    <t>攀登者233</t>
+  </si>
+  <si>
+    <t>攀登者234</t>
+  </si>
+  <si>
+    <t>攀登者235</t>
+  </si>
+  <si>
+    <t>攀登者236</t>
+  </si>
+  <si>
+    <t>攀登者237</t>
+  </si>
+  <si>
+    <t>攀登者238</t>
+  </si>
+  <si>
+    <t>攀登者239</t>
+  </si>
+  <si>
+    <t>攀登者240</t>
+  </si>
+  <si>
+    <t>攀登者241</t>
+  </si>
+  <si>
+    <t>攀登者242</t>
+  </si>
+  <si>
+    <t>攀登者243</t>
+  </si>
+  <si>
+    <t>攀登者244</t>
+  </si>
+  <si>
+    <t>攀登者245</t>
+  </si>
+  <si>
+    <t>攀登者246</t>
+  </si>
+  <si>
+    <t>攀登者247</t>
+  </si>
+  <si>
+    <t>攀登者248</t>
   </si>
 </sst>
 </file>
@@ -6193,7 +6253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K1623"/>
+  <dimension ref="A2:K1643"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="7"/>
@@ -46281,7 +46341,7 @@
         <v>8</v>
       </c>
       <c r="F1391" s="7">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G1391" s="5">
         <v>1</v>
@@ -51259,7 +51319,7 @@
         <v>18</v>
       </c>
       <c r="I1576" s="7">
-        <f t="shared" ref="I1576:I1623" si="53">I1572+10</f>
+        <f t="shared" ref="I1576:I1627" si="53">I1572+10</f>
         <v>500</v>
       </c>
       <c r="J1576" s="7" t="s">
@@ -52257,7 +52317,7 @@
         <v>9</v>
       </c>
       <c r="F1612" s="7">
-        <f t="shared" ref="F1612:F1623" si="55">F1611+50</f>
+        <f t="shared" ref="F1612:F1627" si="55">F1611+50</f>
         <v>4090</v>
       </c>
       <c r="G1612" s="7">
@@ -52579,6 +52639,566 @@
         <v>610</v>
       </c>
       <c r="J1623" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1624" customHeight="1" spans="3:10">
+      <c r="C1624" s="7">
+        <v>9229</v>
+      </c>
+      <c r="D1624" s="7" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E1624" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1624" s="7">
+        <f t="shared" si="55"/>
+        <v>4690</v>
+      </c>
+      <c r="G1624" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1624" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1624" s="7">
+        <f t="shared" si="53"/>
+        <v>620</v>
+      </c>
+      <c r="J1624" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1625" customHeight="1" spans="3:10">
+      <c r="C1625" s="7">
+        <v>9230</v>
+      </c>
+      <c r="D1625" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E1625" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1625" s="7">
+        <f t="shared" si="55"/>
+        <v>4740</v>
+      </c>
+      <c r="G1625" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1625" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1625" s="7">
+        <f t="shared" si="53"/>
+        <v>620</v>
+      </c>
+      <c r="J1625" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1626" customHeight="1" spans="3:10">
+      <c r="C1626" s="7">
+        <v>9231</v>
+      </c>
+      <c r="D1626" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E1626" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1626" s="7">
+        <f t="shared" si="55"/>
+        <v>4790</v>
+      </c>
+      <c r="G1626" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1626" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1626" s="7">
+        <f t="shared" si="53"/>
+        <v>620</v>
+      </c>
+      <c r="J1626" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1627" customHeight="1" spans="3:10">
+      <c r="C1627" s="7">
+        <v>9232</v>
+      </c>
+      <c r="D1627" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E1627" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1627" s="7">
+        <f t="shared" si="55"/>
+        <v>4840</v>
+      </c>
+      <c r="G1627" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1627" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1627" s="7">
+        <f t="shared" si="53"/>
+        <v>620</v>
+      </c>
+      <c r="J1627" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1628" customHeight="1" spans="3:10">
+      <c r="C1628" s="7">
+        <v>9233</v>
+      </c>
+      <c r="D1628" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E1628" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1628" s="7">
+        <f t="shared" ref="F1628:F1635" si="56">F1627+50</f>
+        <v>4890</v>
+      </c>
+      <c r="G1628" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1628" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1628" s="7">
+        <f t="shared" ref="I1628:I1635" si="57">I1624+10</f>
+        <v>630</v>
+      </c>
+      <c r="J1628" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1629" customHeight="1" spans="3:10">
+      <c r="C1629" s="7">
+        <v>9234</v>
+      </c>
+      <c r="D1629" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E1629" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1629" s="7">
+        <f t="shared" si="56"/>
+        <v>4940</v>
+      </c>
+      <c r="G1629" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1629" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1629" s="7">
+        <f t="shared" si="57"/>
+        <v>630</v>
+      </c>
+      <c r="J1629" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1630" customHeight="1" spans="3:10">
+      <c r="C1630" s="7">
+        <v>9235</v>
+      </c>
+      <c r="D1630" s="7" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E1630" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1630" s="7">
+        <f t="shared" si="56"/>
+        <v>4990</v>
+      </c>
+      <c r="G1630" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1630" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1630" s="7">
+        <f t="shared" si="57"/>
+        <v>630</v>
+      </c>
+      <c r="J1630" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1631" customHeight="1" spans="3:10">
+      <c r="C1631" s="7">
+        <v>9236</v>
+      </c>
+      <c r="D1631" s="7" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E1631" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1631" s="7">
+        <f t="shared" si="56"/>
+        <v>5040</v>
+      </c>
+      <c r="G1631" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1631" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1631" s="7">
+        <f t="shared" si="57"/>
+        <v>630</v>
+      </c>
+      <c r="J1631" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1632" customHeight="1" spans="3:10">
+      <c r="C1632" s="7">
+        <v>9237</v>
+      </c>
+      <c r="D1632" s="7" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E1632" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1632" s="7">
+        <f t="shared" si="56"/>
+        <v>5090</v>
+      </c>
+      <c r="G1632" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1632" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1632" s="7">
+        <f t="shared" si="57"/>
+        <v>640</v>
+      </c>
+      <c r="J1632" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1633" customHeight="1" spans="3:10">
+      <c r="C1633" s="7">
+        <v>9238</v>
+      </c>
+      <c r="D1633" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E1633" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1633" s="7">
+        <f t="shared" si="56"/>
+        <v>5140</v>
+      </c>
+      <c r="G1633" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1633" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1633" s="7">
+        <f t="shared" si="57"/>
+        <v>640</v>
+      </c>
+      <c r="J1633" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1634" customHeight="1" spans="3:10">
+      <c r="C1634" s="7">
+        <v>9239</v>
+      </c>
+      <c r="D1634" s="7" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E1634" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1634" s="7">
+        <f t="shared" si="56"/>
+        <v>5190</v>
+      </c>
+      <c r="G1634" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1634" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1634" s="7">
+        <f t="shared" si="57"/>
+        <v>640</v>
+      </c>
+      <c r="J1634" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1635" customHeight="1" spans="3:10">
+      <c r="C1635" s="7">
+        <v>9240</v>
+      </c>
+      <c r="D1635" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E1635" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1635" s="7">
+        <f t="shared" si="56"/>
+        <v>5240</v>
+      </c>
+      <c r="G1635" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1635" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1635" s="7">
+        <f t="shared" si="57"/>
+        <v>640</v>
+      </c>
+      <c r="J1635" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1636" customHeight="1" spans="3:10">
+      <c r="C1636" s="7">
+        <v>9241</v>
+      </c>
+      <c r="D1636" s="7" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E1636" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1636" s="7">
+        <f t="shared" ref="F1636:F1643" si="58">F1635+50</f>
+        <v>5290</v>
+      </c>
+      <c r="G1636" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1636" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1636" s="7">
+        <f t="shared" ref="I1636:I1643" si="59">I1632+10</f>
+        <v>650</v>
+      </c>
+      <c r="J1636" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1637" customHeight="1" spans="3:10">
+      <c r="C1637" s="7">
+        <v>9242</v>
+      </c>
+      <c r="D1637" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="E1637" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1637" s="7">
+        <f t="shared" si="58"/>
+        <v>5340</v>
+      </c>
+      <c r="G1637" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1637" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1637" s="7">
+        <f t="shared" si="59"/>
+        <v>650</v>
+      </c>
+      <c r="J1637" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1638" customHeight="1" spans="3:10">
+      <c r="C1638" s="7">
+        <v>9243</v>
+      </c>
+      <c r="D1638" s="7" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E1638" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1638" s="7">
+        <f t="shared" si="58"/>
+        <v>5390</v>
+      </c>
+      <c r="G1638" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1638" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1638" s="7">
+        <f t="shared" si="59"/>
+        <v>650</v>
+      </c>
+      <c r="J1638" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1639" customHeight="1" spans="3:10">
+      <c r="C1639" s="7">
+        <v>9244</v>
+      </c>
+      <c r="D1639" s="7" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E1639" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1639" s="7">
+        <f t="shared" si="58"/>
+        <v>5440</v>
+      </c>
+      <c r="G1639" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1639" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1639" s="7">
+        <f t="shared" si="59"/>
+        <v>650</v>
+      </c>
+      <c r="J1639" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1640" customHeight="1" spans="3:10">
+      <c r="C1640" s="7">
+        <v>9245</v>
+      </c>
+      <c r="D1640" s="7" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E1640" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1640" s="7">
+        <f t="shared" si="58"/>
+        <v>5490</v>
+      </c>
+      <c r="G1640" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1640" s="7">
+        <v>18</v>
+      </c>
+      <c r="I1640" s="7">
+        <f t="shared" si="59"/>
+        <v>660</v>
+      </c>
+      <c r="J1640" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1641" customHeight="1" spans="3:10">
+      <c r="C1641" s="7">
+        <v>9246</v>
+      </c>
+      <c r="D1641" s="7" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E1641" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1641" s="7">
+        <f t="shared" si="58"/>
+        <v>5540</v>
+      </c>
+      <c r="G1641" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1641" s="7">
+        <v>19</v>
+      </c>
+      <c r="I1641" s="7">
+        <f t="shared" si="59"/>
+        <v>660</v>
+      </c>
+      <c r="J1641" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1642" customHeight="1" spans="3:10">
+      <c r="C1642" s="7">
+        <v>9247</v>
+      </c>
+      <c r="D1642" s="7" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E1642" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1642" s="7">
+        <f t="shared" si="58"/>
+        <v>5590</v>
+      </c>
+      <c r="G1642" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1642" s="7">
+        <v>20</v>
+      </c>
+      <c r="I1642" s="7">
+        <f t="shared" si="59"/>
+        <v>660</v>
+      </c>
+      <c r="J1642" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1643" customHeight="1" spans="3:10">
+      <c r="C1643" s="7">
+        <v>9248</v>
+      </c>
+      <c r="D1643" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E1643" s="7">
+        <v>9</v>
+      </c>
+      <c r="F1643" s="7">
+        <f t="shared" si="58"/>
+        <v>5640</v>
+      </c>
+      <c r="G1643" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1643" s="7">
+        <v>24</v>
+      </c>
+      <c r="I1643" s="7">
+        <f t="shared" si="59"/>
+        <v>660</v>
+      </c>
+      <c r="J1643" s="7" t="s">
         <v>1470</v>
       </c>
     </row>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4388" uniqueCount="1731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4388" uniqueCount="1740">
   <si>
     <t>#</t>
   </si>
@@ -4504,40 +4504,67 @@
     <t>初出茅庐7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭20层数</t>
+  </si>
+  <si>
     <t>物伤倍率</t>
   </si>
   <si>
     <t>小试牛刀7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭30层数</t>
+  </si>
+  <si>
     <t>法伤倍率</t>
   </si>
   <si>
     <t>初露锋芒7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭40层数</t>
+  </si>
+  <si>
     <t>道伤倍率</t>
   </si>
   <si>
     <t>武林新秀7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭50层数</t>
+  </si>
+  <si>
     <t>声名鹊起7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭60层数</t>
+  </si>
+  <si>
     <t>过关斩将7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭100层数</t>
+  </si>
+  <si>
+    <t>独孤求败7</t>
+  </si>
+  <si>
+    <t>守卫龙城通过寂灭70层数</t>
+  </si>
+  <si>
     <t>破韧倍率</t>
   </si>
   <si>
-    <t>独孤求败7</t>
-  </si>
-  <si>
     <t>武林至尊7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭90层数</t>
+  </si>
+  <si>
     <t>天下无敌7</t>
+  </si>
+  <si>
+    <t>守卫龙城通过寂灭80层数</t>
   </si>
   <si>
     <t>攀登者1</t>
@@ -46386,7 +46413,7 @@
         <v>1</v>
       </c>
       <c r="H1391" s="7">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="I1391" s="5">
         <v>60</v>
@@ -46421,10 +46448,10 @@
         <v>100</v>
       </c>
       <c r="J1393" s="5" t="s">
-        <v>1451</v>
+        <v>1470</v>
       </c>
       <c r="K1393" s="11" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1394" customHeight="1" spans="3:11">
@@ -46432,7 +46459,7 @@
         <v>8062</v>
       </c>
       <c r="D1394" s="10" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="E1394" s="7">
         <v>8</v>
@@ -46450,10 +46477,10 @@
         <v>100</v>
       </c>
       <c r="J1394" s="5" t="s">
-        <v>1453</v>
+        <v>1473</v>
       </c>
       <c r="K1394" s="11" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1395" customHeight="1" spans="3:11">
@@ -46461,7 +46488,7 @@
         <v>8063</v>
       </c>
       <c r="D1395" s="10" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E1395" s="7">
         <v>8</v>
@@ -46479,10 +46506,10 @@
         <v>100</v>
       </c>
       <c r="J1395" s="5" t="s">
-        <v>1455</v>
+        <v>1476</v>
       </c>
       <c r="K1395" s="11" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1396" customHeight="1" spans="3:11">
@@ -46490,7 +46517,7 @@
         <v>8064</v>
       </c>
       <c r="D1396" s="12" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="E1396" s="7">
         <v>8</v>
@@ -46508,7 +46535,7 @@
         <v>300</v>
       </c>
       <c r="J1396" s="5" t="s">
-        <v>1457</v>
+        <v>1479</v>
       </c>
       <c r="K1396" s="11" t="s">
         <v>1380</v>
@@ -46519,7 +46546,7 @@
         <v>8065</v>
       </c>
       <c r="D1397" s="10" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="E1397" s="7">
         <v>8</v>
@@ -46534,13 +46561,13 @@
         <v>2010</v>
       </c>
       <c r="I1397" s="5">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J1397" s="5" t="s">
-        <v>1459</v>
+        <v>1481</v>
       </c>
       <c r="K1397" s="11" t="s">
-        <v>1447</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="1398" customHeight="1" spans="3:11">
@@ -46548,7 +46575,7 @@
         <v>8066</v>
       </c>
       <c r="D1398" s="10" t="s">
-        <v>1477</v>
+        <v>1482</v>
       </c>
       <c r="E1398" s="7">
         <v>8</v>
@@ -46560,16 +46587,16 @@
         <v>1</v>
       </c>
       <c r="H1398" s="7">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I1398" s="5">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J1398" s="5" t="s">
-        <v>1461</v>
+        <v>1483</v>
       </c>
       <c r="K1398" s="11" t="s">
-        <v>1478</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1399" customHeight="1" spans="3:11">
@@ -46577,7 +46604,7 @@
         <v>8067</v>
       </c>
       <c r="D1399" s="10" t="s">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="E1399" s="7">
         <v>8</v>
@@ -46589,16 +46616,16 @@
         <v>1</v>
       </c>
       <c r="H1399" s="7">
-        <v>2001</v>
+        <v>2013</v>
       </c>
       <c r="I1399" s="5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1399" s="5" t="s">
-        <v>1463</v>
+        <v>1485</v>
       </c>
       <c r="K1399" s="11" t="s">
-        <v>1386</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1400" customHeight="1" spans="3:11">
@@ -46606,7 +46633,7 @@
         <v>8068</v>
       </c>
       <c r="D1400" s="10" t="s">
-        <v>1480</v>
+        <v>1487</v>
       </c>
       <c r="E1400" s="7">
         <v>8</v>
@@ -46624,7 +46651,7 @@
         <v>15</v>
       </c>
       <c r="J1400" s="5" t="s">
-        <v>1465</v>
+        <v>1488</v>
       </c>
       <c r="K1400" s="7" t="s">
         <v>1466</v>
@@ -46635,7 +46662,7 @@
         <v>8069</v>
       </c>
       <c r="D1401" s="10" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
       <c r="E1401" s="7">
         <v>8</v>
@@ -46647,16 +46674,16 @@
         <v>1</v>
       </c>
       <c r="H1401" s="7">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="I1401" s="5">
         <v>100</v>
       </c>
       <c r="J1401" s="5" t="s">
-        <v>1468</v>
+        <v>1490</v>
       </c>
       <c r="K1401" s="11" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="1406" customHeight="1" spans="3:11">
@@ -46664,7 +46691,7 @@
         <v>9001</v>
       </c>
       <c r="D1406" s="7" t="s">
-        <v>1482</v>
+        <v>1491</v>
       </c>
       <c r="E1406" s="7">
         <v>9</v>
@@ -46682,7 +46709,7 @@
         <v>50</v>
       </c>
       <c r="J1406" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1407" customHeight="1" spans="3:11">
@@ -46690,7 +46717,7 @@
         <v>9002</v>
       </c>
       <c r="D1407" s="7" t="s">
-        <v>1484</v>
+        <v>1493</v>
       </c>
       <c r="E1407" s="7">
         <v>9</v>
@@ -46709,7 +46736,7 @@
         <v>50</v>
       </c>
       <c r="J1407" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1408" customHeight="1" spans="3:11">
@@ -46717,7 +46744,7 @@
         <v>9003</v>
       </c>
       <c r="D1408" s="7" t="s">
-        <v>1485</v>
+        <v>1494</v>
       </c>
       <c r="E1408" s="7">
         <v>9</v>
@@ -46736,7 +46763,7 @@
         <v>50</v>
       </c>
       <c r="J1408" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1409" customHeight="1" spans="3:10">
@@ -46744,7 +46771,7 @@
         <v>9004</v>
       </c>
       <c r="D1409" s="7" t="s">
-        <v>1486</v>
+        <v>1495</v>
       </c>
       <c r="E1409" s="7">
         <v>9</v>
@@ -46763,7 +46790,7 @@
         <v>50</v>
       </c>
       <c r="J1409" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1410" customHeight="1" spans="3:10">
@@ -46771,7 +46798,7 @@
         <v>9005</v>
       </c>
       <c r="D1410" s="7" t="s">
-        <v>1487</v>
+        <v>1496</v>
       </c>
       <c r="E1410" s="7">
         <v>9</v>
@@ -46790,7 +46817,7 @@
         <v>60</v>
       </c>
       <c r="J1410" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1411" customHeight="1" spans="3:10">
@@ -46798,7 +46825,7 @@
         <v>9006</v>
       </c>
       <c r="D1411" s="7" t="s">
-        <v>1488</v>
+        <v>1497</v>
       </c>
       <c r="E1411" s="7">
         <v>9</v>
@@ -46817,7 +46844,7 @@
         <v>60</v>
       </c>
       <c r="J1411" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1412" customHeight="1" spans="3:10">
@@ -46825,7 +46852,7 @@
         <v>9007</v>
       </c>
       <c r="D1412" s="7" t="s">
-        <v>1489</v>
+        <v>1498</v>
       </c>
       <c r="E1412" s="7">
         <v>9</v>
@@ -46844,7 +46871,7 @@
         <v>60</v>
       </c>
       <c r="J1412" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1413" customHeight="1" spans="3:10">
@@ -46852,7 +46879,7 @@
         <v>9008</v>
       </c>
       <c r="D1413" s="7" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="E1413" s="7">
         <v>9</v>
@@ -46871,7 +46898,7 @@
         <v>60</v>
       </c>
       <c r="J1413" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1414" customHeight="1" spans="3:10">
@@ -46879,7 +46906,7 @@
         <v>9009</v>
       </c>
       <c r="D1414" s="7" t="s">
-        <v>1491</v>
+        <v>1500</v>
       </c>
       <c r="E1414" s="7">
         <v>9</v>
@@ -46898,7 +46925,7 @@
         <v>70</v>
       </c>
       <c r="J1414" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1415" customHeight="1" spans="3:10">
@@ -46906,7 +46933,7 @@
         <v>9010</v>
       </c>
       <c r="D1415" s="7" t="s">
-        <v>1492</v>
+        <v>1501</v>
       </c>
       <c r="E1415" s="7">
         <v>9</v>
@@ -46925,7 +46952,7 @@
         <v>70</v>
       </c>
       <c r="J1415" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1416" customHeight="1" spans="3:10">
@@ -46933,7 +46960,7 @@
         <v>9011</v>
       </c>
       <c r="D1416" s="7" t="s">
-        <v>1493</v>
+        <v>1502</v>
       </c>
       <c r="E1416" s="7">
         <v>9</v>
@@ -46952,7 +46979,7 @@
         <v>70</v>
       </c>
       <c r="J1416" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1417" customHeight="1" spans="3:10">
@@ -46960,7 +46987,7 @@
         <v>9012</v>
       </c>
       <c r="D1417" s="7" t="s">
-        <v>1494</v>
+        <v>1503</v>
       </c>
       <c r="E1417" s="7">
         <v>9</v>
@@ -46979,7 +47006,7 @@
         <v>70</v>
       </c>
       <c r="J1417" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1418" customHeight="1" spans="3:10">
@@ -46987,7 +47014,7 @@
         <v>9013</v>
       </c>
       <c r="D1418" s="7" t="s">
-        <v>1495</v>
+        <v>1504</v>
       </c>
       <c r="E1418" s="7">
         <v>9</v>
@@ -47006,7 +47033,7 @@
         <v>80</v>
       </c>
       <c r="J1418" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1419" customHeight="1" spans="3:10">
@@ -47014,7 +47041,7 @@
         <v>9014</v>
       </c>
       <c r="D1419" s="7" t="s">
-        <v>1496</v>
+        <v>1505</v>
       </c>
       <c r="E1419" s="7">
         <v>9</v>
@@ -47033,7 +47060,7 @@
         <v>80</v>
       </c>
       <c r="J1419" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1420" customHeight="1" spans="3:10">
@@ -47041,7 +47068,7 @@
         <v>9015</v>
       </c>
       <c r="D1420" s="7" t="s">
-        <v>1497</v>
+        <v>1506</v>
       </c>
       <c r="E1420" s="7">
         <v>9</v>
@@ -47060,7 +47087,7 @@
         <v>80</v>
       </c>
       <c r="J1420" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1421" customHeight="1" spans="3:10">
@@ -47068,7 +47095,7 @@
         <v>9016</v>
       </c>
       <c r="D1421" s="7" t="s">
-        <v>1498</v>
+        <v>1507</v>
       </c>
       <c r="E1421" s="7">
         <v>9</v>
@@ -47087,7 +47114,7 @@
         <v>80</v>
       </c>
       <c r="J1421" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1422" customHeight="1" spans="3:10">
@@ -47095,7 +47122,7 @@
         <v>9017</v>
       </c>
       <c r="D1422" s="7" t="s">
-        <v>1499</v>
+        <v>1508</v>
       </c>
       <c r="E1422" s="7">
         <v>9</v>
@@ -47114,7 +47141,7 @@
         <v>90</v>
       </c>
       <c r="J1422" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1423" customHeight="1" spans="3:10">
@@ -47122,7 +47149,7 @@
         <v>9018</v>
       </c>
       <c r="D1423" s="7" t="s">
-        <v>1500</v>
+        <v>1509</v>
       </c>
       <c r="E1423" s="7">
         <v>9</v>
@@ -47141,7 +47168,7 @@
         <v>90</v>
       </c>
       <c r="J1423" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1424" customHeight="1" spans="3:10">
@@ -47149,7 +47176,7 @@
         <v>9019</v>
       </c>
       <c r="D1424" s="7" t="s">
-        <v>1501</v>
+        <v>1510</v>
       </c>
       <c r="E1424" s="7">
         <v>9</v>
@@ -47168,7 +47195,7 @@
         <v>90</v>
       </c>
       <c r="J1424" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1425" customHeight="1" spans="3:10">
@@ -47176,7 +47203,7 @@
         <v>9020</v>
       </c>
       <c r="D1425" s="7" t="s">
-        <v>1502</v>
+        <v>1511</v>
       </c>
       <c r="E1425" s="7">
         <v>9</v>
@@ -47195,7 +47222,7 @@
         <v>90</v>
       </c>
       <c r="J1425" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1426" customHeight="1" spans="3:10">
@@ -47203,7 +47230,7 @@
         <v>9021</v>
       </c>
       <c r="D1426" s="7" t="s">
-        <v>1503</v>
+        <v>1512</v>
       </c>
       <c r="E1426" s="7">
         <v>9</v>
@@ -47222,7 +47249,7 @@
         <v>100</v>
       </c>
       <c r="J1426" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1427" customHeight="1" spans="3:10">
@@ -47230,7 +47257,7 @@
         <v>9022</v>
       </c>
       <c r="D1427" s="7" t="s">
-        <v>1504</v>
+        <v>1513</v>
       </c>
       <c r="E1427" s="7">
         <v>9</v>
@@ -47249,7 +47276,7 @@
         <v>100</v>
       </c>
       <c r="J1427" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1428" customHeight="1" spans="3:10">
@@ -47257,7 +47284,7 @@
         <v>9023</v>
       </c>
       <c r="D1428" s="7" t="s">
-        <v>1505</v>
+        <v>1514</v>
       </c>
       <c r="E1428" s="7">
         <v>9</v>
@@ -47276,7 +47303,7 @@
         <v>100</v>
       </c>
       <c r="J1428" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1429" customHeight="1" spans="3:10">
@@ -47284,7 +47311,7 @@
         <v>9024</v>
       </c>
       <c r="D1429" s="7" t="s">
-        <v>1506</v>
+        <v>1515</v>
       </c>
       <c r="E1429" s="7">
         <v>9</v>
@@ -47303,7 +47330,7 @@
         <v>100</v>
       </c>
       <c r="J1429" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1430" customHeight="1" spans="3:10">
@@ -47311,7 +47338,7 @@
         <v>9025</v>
       </c>
       <c r="D1430" s="7" t="s">
-        <v>1507</v>
+        <v>1516</v>
       </c>
       <c r="E1430" s="7">
         <v>9</v>
@@ -47330,7 +47357,7 @@
         <v>110</v>
       </c>
       <c r="J1430" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1431" customHeight="1" spans="3:10">
@@ -47338,7 +47365,7 @@
         <v>9026</v>
       </c>
       <c r="D1431" s="7" t="s">
-        <v>1508</v>
+        <v>1517</v>
       </c>
       <c r="E1431" s="7">
         <v>9</v>
@@ -47357,7 +47384,7 @@
         <v>110</v>
       </c>
       <c r="J1431" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1432" customHeight="1" spans="3:10">
@@ -47365,7 +47392,7 @@
         <v>9027</v>
       </c>
       <c r="D1432" s="7" t="s">
-        <v>1509</v>
+        <v>1518</v>
       </c>
       <c r="E1432" s="7">
         <v>9</v>
@@ -47384,7 +47411,7 @@
         <v>110</v>
       </c>
       <c r="J1432" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1433" customHeight="1" spans="3:10">
@@ -47392,7 +47419,7 @@
         <v>9028</v>
       </c>
       <c r="D1433" s="7" t="s">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="E1433" s="7">
         <v>9</v>
@@ -47411,7 +47438,7 @@
         <v>110</v>
       </c>
       <c r="J1433" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1434" customHeight="1" spans="3:10">
@@ -47419,7 +47446,7 @@
         <v>9029</v>
       </c>
       <c r="D1434" s="7" t="s">
-        <v>1511</v>
+        <v>1520</v>
       </c>
       <c r="E1434" s="7">
         <v>9</v>
@@ -47438,7 +47465,7 @@
         <v>120</v>
       </c>
       <c r="J1434" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1435" customHeight="1" spans="3:10">
@@ -47446,7 +47473,7 @@
         <v>9030</v>
       </c>
       <c r="D1435" s="7" t="s">
-        <v>1512</v>
+        <v>1521</v>
       </c>
       <c r="E1435" s="7">
         <v>9</v>
@@ -47465,7 +47492,7 @@
         <v>120</v>
       </c>
       <c r="J1435" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1436" customHeight="1" spans="3:10">
@@ -47473,7 +47500,7 @@
         <v>9031</v>
       </c>
       <c r="D1436" s="7" t="s">
-        <v>1513</v>
+        <v>1522</v>
       </c>
       <c r="E1436" s="7">
         <v>9</v>
@@ -47492,7 +47519,7 @@
         <v>120</v>
       </c>
       <c r="J1436" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1437" customHeight="1" spans="3:10">
@@ -47500,7 +47527,7 @@
         <v>9032</v>
       </c>
       <c r="D1437" s="7" t="s">
-        <v>1514</v>
+        <v>1523</v>
       </c>
       <c r="E1437" s="7">
         <v>9</v>
@@ -47519,7 +47546,7 @@
         <v>120</v>
       </c>
       <c r="J1437" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1438" customHeight="1" spans="3:10">
@@ -47527,7 +47554,7 @@
         <v>9033</v>
       </c>
       <c r="D1438" s="7" t="s">
-        <v>1515</v>
+        <v>1524</v>
       </c>
       <c r="E1438" s="7">
         <v>9</v>
@@ -47546,7 +47573,7 @@
         <v>130</v>
       </c>
       <c r="J1438" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1439" customHeight="1" spans="3:10">
@@ -47554,7 +47581,7 @@
         <v>9034</v>
       </c>
       <c r="D1439" s="7" t="s">
-        <v>1516</v>
+        <v>1525</v>
       </c>
       <c r="E1439" s="7">
         <v>9</v>
@@ -47573,7 +47600,7 @@
         <v>130</v>
       </c>
       <c r="J1439" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1440" customHeight="1" spans="3:10">
@@ -47581,7 +47608,7 @@
         <v>9035</v>
       </c>
       <c r="D1440" s="7" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="E1440" s="7">
         <v>9</v>
@@ -47600,7 +47627,7 @@
         <v>130</v>
       </c>
       <c r="J1440" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1441" customHeight="1" spans="3:10">
@@ -47608,7 +47635,7 @@
         <v>9036</v>
       </c>
       <c r="D1441" s="7" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="E1441" s="7">
         <v>9</v>
@@ -47627,7 +47654,7 @@
         <v>130</v>
       </c>
       <c r="J1441" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1442" customHeight="1" spans="3:10">
@@ -47635,7 +47662,7 @@
         <v>9037</v>
       </c>
       <c r="D1442" s="7" t="s">
-        <v>1519</v>
+        <v>1528</v>
       </c>
       <c r="E1442" s="7">
         <v>9</v>
@@ -47654,7 +47681,7 @@
         <v>140</v>
       </c>
       <c r="J1442" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1443" customHeight="1" spans="3:10">
@@ -47662,7 +47689,7 @@
         <v>9038</v>
       </c>
       <c r="D1443" s="7" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="E1443" s="7">
         <v>9</v>
@@ -47681,7 +47708,7 @@
         <v>140</v>
       </c>
       <c r="J1443" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1444" customHeight="1" spans="3:10">
@@ -47689,7 +47716,7 @@
         <v>9039</v>
       </c>
       <c r="D1444" s="7" t="s">
-        <v>1521</v>
+        <v>1530</v>
       </c>
       <c r="E1444" s="7">
         <v>9</v>
@@ -47708,7 +47735,7 @@
         <v>140</v>
       </c>
       <c r="J1444" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1445" customHeight="1" spans="3:10">
@@ -47716,7 +47743,7 @@
         <v>9040</v>
       </c>
       <c r="D1445" s="7" t="s">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="E1445" s="7">
         <v>9</v>
@@ -47735,7 +47762,7 @@
         <v>140</v>
       </c>
       <c r="J1445" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1446" customHeight="1" spans="3:10">
@@ -47743,7 +47770,7 @@
         <v>9041</v>
       </c>
       <c r="D1446" s="7" t="s">
-        <v>1523</v>
+        <v>1532</v>
       </c>
       <c r="E1446" s="7">
         <v>9</v>
@@ -47762,7 +47789,7 @@
         <v>150</v>
       </c>
       <c r="J1446" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1447" customHeight="1" spans="3:10">
@@ -47770,7 +47797,7 @@
         <v>9042</v>
       </c>
       <c r="D1447" s="7" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="E1447" s="7">
         <v>9</v>
@@ -47789,7 +47816,7 @@
         <v>150</v>
       </c>
       <c r="J1447" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1448" customHeight="1" spans="3:10">
@@ -47797,7 +47824,7 @@
         <v>9043</v>
       </c>
       <c r="D1448" s="7" t="s">
-        <v>1525</v>
+        <v>1534</v>
       </c>
       <c r="E1448" s="7">
         <v>9</v>
@@ -47816,7 +47843,7 @@
         <v>150</v>
       </c>
       <c r="J1448" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1449" customHeight="1" spans="3:10">
@@ -47824,7 +47851,7 @@
         <v>9044</v>
       </c>
       <c r="D1449" s="7" t="s">
-        <v>1526</v>
+        <v>1535</v>
       </c>
       <c r="E1449" s="7">
         <v>9</v>
@@ -47843,7 +47870,7 @@
         <v>150</v>
       </c>
       <c r="J1449" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1450" customHeight="1" spans="3:10">
@@ -47851,7 +47878,7 @@
         <v>9045</v>
       </c>
       <c r="D1450" s="7" t="s">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="E1450" s="7">
         <v>9</v>
@@ -47870,7 +47897,7 @@
         <v>160</v>
       </c>
       <c r="J1450" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1451" customHeight="1" spans="3:10">
@@ -47878,7 +47905,7 @@
         <v>9046</v>
       </c>
       <c r="D1451" s="7" t="s">
-        <v>1528</v>
+        <v>1537</v>
       </c>
       <c r="E1451" s="7">
         <v>9</v>
@@ -47897,7 +47924,7 @@
         <v>160</v>
       </c>
       <c r="J1451" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1452" customHeight="1" spans="3:10">
@@ -47905,7 +47932,7 @@
         <v>9047</v>
       </c>
       <c r="D1452" s="7" t="s">
-        <v>1529</v>
+        <v>1538</v>
       </c>
       <c r="E1452" s="7">
         <v>9</v>
@@ -47924,7 +47951,7 @@
         <v>160</v>
       </c>
       <c r="J1452" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1453" customHeight="1" spans="3:10">
@@ -47932,7 +47959,7 @@
         <v>9048</v>
       </c>
       <c r="D1453" s="7" t="s">
-        <v>1530</v>
+        <v>1539</v>
       </c>
       <c r="E1453" s="7">
         <v>9</v>
@@ -47951,7 +47978,7 @@
         <v>160</v>
       </c>
       <c r="J1453" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1454" customHeight="1" spans="3:10">
@@ -47959,7 +47986,7 @@
         <v>9049</v>
       </c>
       <c r="D1454" s="7" t="s">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="E1454" s="7">
         <v>9</v>
@@ -47978,7 +48005,7 @@
         <v>170</v>
       </c>
       <c r="J1454" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1455" customHeight="1" spans="3:10">
@@ -47986,7 +48013,7 @@
         <v>9050</v>
       </c>
       <c r="D1455" s="7" t="s">
-        <v>1532</v>
+        <v>1541</v>
       </c>
       <c r="E1455" s="7">
         <v>9</v>
@@ -48005,7 +48032,7 @@
         <v>170</v>
       </c>
       <c r="J1455" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1456" customHeight="1" spans="3:10">
@@ -48013,7 +48040,7 @@
         <v>9051</v>
       </c>
       <c r="D1456" s="7" t="s">
-        <v>1533</v>
+        <v>1542</v>
       </c>
       <c r="E1456" s="7">
         <v>9</v>
@@ -48032,7 +48059,7 @@
         <v>170</v>
       </c>
       <c r="J1456" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1457" customHeight="1" spans="3:10">
@@ -48040,7 +48067,7 @@
         <v>9052</v>
       </c>
       <c r="D1457" s="7" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="E1457" s="7">
         <v>9</v>
@@ -48059,7 +48086,7 @@
         <v>170</v>
       </c>
       <c r="J1457" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1458" customHeight="1" spans="3:10">
@@ -48067,7 +48094,7 @@
         <v>9053</v>
       </c>
       <c r="D1458" s="7" t="s">
-        <v>1535</v>
+        <v>1544</v>
       </c>
       <c r="E1458" s="7">
         <v>9</v>
@@ -48086,7 +48113,7 @@
         <v>180</v>
       </c>
       <c r="J1458" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1459" customHeight="1" spans="3:10">
@@ -48094,7 +48121,7 @@
         <v>9054</v>
       </c>
       <c r="D1459" s="7" t="s">
-        <v>1536</v>
+        <v>1545</v>
       </c>
       <c r="E1459" s="7">
         <v>9</v>
@@ -48113,7 +48140,7 @@
         <v>180</v>
       </c>
       <c r="J1459" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1460" customHeight="1" spans="3:10">
@@ -48121,7 +48148,7 @@
         <v>9055</v>
       </c>
       <c r="D1460" s="7" t="s">
-        <v>1537</v>
+        <v>1546</v>
       </c>
       <c r="E1460" s="7">
         <v>9</v>
@@ -48140,7 +48167,7 @@
         <v>180</v>
       </c>
       <c r="J1460" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1461" customHeight="1" spans="3:10">
@@ -48148,7 +48175,7 @@
         <v>9056</v>
       </c>
       <c r="D1461" s="7" t="s">
-        <v>1538</v>
+        <v>1547</v>
       </c>
       <c r="E1461" s="7">
         <v>9</v>
@@ -48167,7 +48194,7 @@
         <v>180</v>
       </c>
       <c r="J1461" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1462" customHeight="1" spans="3:10">
@@ -48175,7 +48202,7 @@
         <v>9057</v>
       </c>
       <c r="D1462" s="7" t="s">
-        <v>1539</v>
+        <v>1548</v>
       </c>
       <c r="E1462" s="7">
         <v>9</v>
@@ -48194,7 +48221,7 @@
         <v>190</v>
       </c>
       <c r="J1462" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1463" customHeight="1" spans="3:10">
@@ -48202,7 +48229,7 @@
         <v>9058</v>
       </c>
       <c r="D1463" s="7" t="s">
-        <v>1540</v>
+        <v>1549</v>
       </c>
       <c r="E1463" s="7">
         <v>9</v>
@@ -48221,7 +48248,7 @@
         <v>190</v>
       </c>
       <c r="J1463" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1464" customHeight="1" spans="3:10">
@@ -48229,7 +48256,7 @@
         <v>9059</v>
       </c>
       <c r="D1464" s="7" t="s">
-        <v>1541</v>
+        <v>1550</v>
       </c>
       <c r="E1464" s="7">
         <v>9</v>
@@ -48248,7 +48275,7 @@
         <v>190</v>
       </c>
       <c r="J1464" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1465" customHeight="1" spans="3:10">
@@ -48256,7 +48283,7 @@
         <v>9060</v>
       </c>
       <c r="D1465" s="7" t="s">
-        <v>1542</v>
+        <v>1551</v>
       </c>
       <c r="E1465" s="7">
         <v>9</v>
@@ -48275,7 +48302,7 @@
         <v>190</v>
       </c>
       <c r="J1465" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1466" customHeight="1" spans="3:10">
@@ -48283,7 +48310,7 @@
         <v>9061</v>
       </c>
       <c r="D1466" s="7" t="s">
-        <v>1543</v>
+        <v>1552</v>
       </c>
       <c r="E1466" s="7">
         <v>9</v>
@@ -48302,7 +48329,7 @@
         <v>200</v>
       </c>
       <c r="J1466" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1467" customHeight="1" spans="3:10">
@@ -48310,7 +48337,7 @@
         <v>9062</v>
       </c>
       <c r="D1467" s="7" t="s">
-        <v>1544</v>
+        <v>1553</v>
       </c>
       <c r="E1467" s="7">
         <v>9</v>
@@ -48329,7 +48356,7 @@
         <v>200</v>
       </c>
       <c r="J1467" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1468" customHeight="1" spans="3:10">
@@ -48337,7 +48364,7 @@
         <v>9063</v>
       </c>
       <c r="D1468" s="7" t="s">
-        <v>1545</v>
+        <v>1554</v>
       </c>
       <c r="E1468" s="7">
         <v>9</v>
@@ -48356,7 +48383,7 @@
         <v>200</v>
       </c>
       <c r="J1468" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1469" customHeight="1" spans="3:10">
@@ -48364,7 +48391,7 @@
         <v>9064</v>
       </c>
       <c r="D1469" s="7" t="s">
-        <v>1546</v>
+        <v>1555</v>
       </c>
       <c r="E1469" s="7">
         <v>9</v>
@@ -48383,7 +48410,7 @@
         <v>200</v>
       </c>
       <c r="J1469" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1470" customHeight="1" spans="3:10">
@@ -48391,7 +48418,7 @@
         <v>9065</v>
       </c>
       <c r="D1470" s="7" t="s">
-        <v>1547</v>
+        <v>1556</v>
       </c>
       <c r="E1470" s="7">
         <v>9</v>
@@ -48410,7 +48437,7 @@
         <v>210</v>
       </c>
       <c r="J1470" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1471" customHeight="1" spans="3:10">
@@ -48418,7 +48445,7 @@
         <v>9066</v>
       </c>
       <c r="D1471" s="7" t="s">
-        <v>1548</v>
+        <v>1557</v>
       </c>
       <c r="E1471" s="7">
         <v>9</v>
@@ -48437,7 +48464,7 @@
         <v>210</v>
       </c>
       <c r="J1471" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1472" customHeight="1" spans="3:10">
@@ -48445,7 +48472,7 @@
         <v>9067</v>
       </c>
       <c r="D1472" s="7" t="s">
-        <v>1549</v>
+        <v>1558</v>
       </c>
       <c r="E1472" s="7">
         <v>9</v>
@@ -48464,7 +48491,7 @@
         <v>210</v>
       </c>
       <c r="J1472" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1473" customHeight="1" spans="3:10">
@@ -48472,7 +48499,7 @@
         <v>9068</v>
       </c>
       <c r="D1473" s="7" t="s">
-        <v>1550</v>
+        <v>1559</v>
       </c>
       <c r="E1473" s="7">
         <v>9</v>
@@ -48491,7 +48518,7 @@
         <v>210</v>
       </c>
       <c r="J1473" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1474" customHeight="1" spans="3:10">
@@ -48499,7 +48526,7 @@
         <v>9069</v>
       </c>
       <c r="D1474" s="7" t="s">
-        <v>1551</v>
+        <v>1560</v>
       </c>
       <c r="E1474" s="7">
         <v>9</v>
@@ -48518,7 +48545,7 @@
         <v>220</v>
       </c>
       <c r="J1474" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1475" customHeight="1" spans="3:10">
@@ -48526,7 +48553,7 @@
         <v>9070</v>
       </c>
       <c r="D1475" s="7" t="s">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="E1475" s="7">
         <v>9</v>
@@ -48545,7 +48572,7 @@
         <v>220</v>
       </c>
       <c r="J1475" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1476" customHeight="1" spans="3:10">
@@ -48553,7 +48580,7 @@
         <v>9071</v>
       </c>
       <c r="D1476" s="7" t="s">
-        <v>1553</v>
+        <v>1562</v>
       </c>
       <c r="E1476" s="7">
         <v>9</v>
@@ -48572,7 +48599,7 @@
         <v>220</v>
       </c>
       <c r="J1476" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1477" customHeight="1" spans="3:10">
@@ -48580,7 +48607,7 @@
         <v>9072</v>
       </c>
       <c r="D1477" s="7" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="E1477" s="7">
         <v>9</v>
@@ -48599,7 +48626,7 @@
         <v>220</v>
       </c>
       <c r="J1477" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1478" customHeight="1" spans="3:10">
@@ -48607,7 +48634,7 @@
         <v>9073</v>
       </c>
       <c r="D1478" s="7" t="s">
-        <v>1555</v>
+        <v>1564</v>
       </c>
       <c r="E1478" s="7">
         <v>9</v>
@@ -48626,7 +48653,7 @@
         <v>230</v>
       </c>
       <c r="J1478" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1479" customHeight="1" spans="3:10">
@@ -48634,7 +48661,7 @@
         <v>9074</v>
       </c>
       <c r="D1479" s="7" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
       <c r="E1479" s="7">
         <v>9</v>
@@ -48653,7 +48680,7 @@
         <v>230</v>
       </c>
       <c r="J1479" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1480" customHeight="1" spans="3:10">
@@ -48661,7 +48688,7 @@
         <v>9075</v>
       </c>
       <c r="D1480" s="7" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="E1480" s="7">
         <v>9</v>
@@ -48680,7 +48707,7 @@
         <v>230</v>
       </c>
       <c r="J1480" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1481" customHeight="1" spans="3:10">
@@ -48688,7 +48715,7 @@
         <v>9076</v>
       </c>
       <c r="D1481" s="7" t="s">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="E1481" s="7">
         <v>9</v>
@@ -48707,7 +48734,7 @@
         <v>230</v>
       </c>
       <c r="J1481" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1482" customHeight="1" spans="3:10">
@@ -48715,7 +48742,7 @@
         <v>9077</v>
       </c>
       <c r="D1482" s="7" t="s">
-        <v>1559</v>
+        <v>1568</v>
       </c>
       <c r="E1482" s="7">
         <v>9</v>
@@ -48734,7 +48761,7 @@
         <v>240</v>
       </c>
       <c r="J1482" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1483" customHeight="1" spans="3:10">
@@ -48742,7 +48769,7 @@
         <v>9078</v>
       </c>
       <c r="D1483" s="7" t="s">
-        <v>1560</v>
+        <v>1569</v>
       </c>
       <c r="E1483" s="7">
         <v>9</v>
@@ -48761,7 +48788,7 @@
         <v>240</v>
       </c>
       <c r="J1483" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1484" customHeight="1" spans="3:10">
@@ -48769,7 +48796,7 @@
         <v>9079</v>
       </c>
       <c r="D1484" s="7" t="s">
-        <v>1561</v>
+        <v>1570</v>
       </c>
       <c r="E1484" s="7">
         <v>9</v>
@@ -48788,7 +48815,7 @@
         <v>240</v>
       </c>
       <c r="J1484" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1485" customHeight="1" spans="3:10">
@@ -48796,7 +48823,7 @@
         <v>9080</v>
       </c>
       <c r="D1485" s="7" t="s">
-        <v>1562</v>
+        <v>1571</v>
       </c>
       <c r="E1485" s="7">
         <v>9</v>
@@ -48815,7 +48842,7 @@
         <v>240</v>
       </c>
       <c r="J1485" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1486" customHeight="1" spans="3:10">
@@ -48823,7 +48850,7 @@
         <v>9081</v>
       </c>
       <c r="D1486" s="7" t="s">
-        <v>1563</v>
+        <v>1572</v>
       </c>
       <c r="E1486" s="7">
         <v>9</v>
@@ -48842,7 +48869,7 @@
         <v>250</v>
       </c>
       <c r="J1486" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1487" customHeight="1" spans="3:10">
@@ -48850,7 +48877,7 @@
         <v>9082</v>
       </c>
       <c r="D1487" s="7" t="s">
-        <v>1564</v>
+        <v>1573</v>
       </c>
       <c r="E1487" s="7">
         <v>9</v>
@@ -48869,7 +48896,7 @@
         <v>250</v>
       </c>
       <c r="J1487" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1488" customHeight="1" spans="3:10">
@@ -48877,7 +48904,7 @@
         <v>9083</v>
       </c>
       <c r="D1488" s="7" t="s">
-        <v>1565</v>
+        <v>1574</v>
       </c>
       <c r="E1488" s="7">
         <v>9</v>
@@ -48896,7 +48923,7 @@
         <v>250</v>
       </c>
       <c r="J1488" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1489" customHeight="1" spans="3:10">
@@ -48904,7 +48931,7 @@
         <v>9084</v>
       </c>
       <c r="D1489" s="7" t="s">
-        <v>1566</v>
+        <v>1575</v>
       </c>
       <c r="E1489" s="7">
         <v>9</v>
@@ -48923,7 +48950,7 @@
         <v>250</v>
       </c>
       <c r="J1489" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1490" customHeight="1" spans="3:10">
@@ -48931,7 +48958,7 @@
         <v>9085</v>
       </c>
       <c r="D1490" s="7" t="s">
-        <v>1567</v>
+        <v>1576</v>
       </c>
       <c r="E1490" s="7">
         <v>9</v>
@@ -48950,7 +48977,7 @@
         <v>260</v>
       </c>
       <c r="J1490" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1491" customHeight="1" spans="3:10">
@@ -48958,7 +48985,7 @@
         <v>9086</v>
       </c>
       <c r="D1491" s="7" t="s">
-        <v>1568</v>
+        <v>1577</v>
       </c>
       <c r="E1491" s="7">
         <v>9</v>
@@ -48977,7 +49004,7 @@
         <v>260</v>
       </c>
       <c r="J1491" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1492" customHeight="1" spans="3:10">
@@ -48985,7 +49012,7 @@
         <v>9087</v>
       </c>
       <c r="D1492" s="7" t="s">
-        <v>1569</v>
+        <v>1578</v>
       </c>
       <c r="E1492" s="7">
         <v>9</v>
@@ -49004,7 +49031,7 @@
         <v>260</v>
       </c>
       <c r="J1492" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1493" customHeight="1" spans="3:10">
@@ -49012,7 +49039,7 @@
         <v>9088</v>
       </c>
       <c r="D1493" s="7" t="s">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="E1493" s="7">
         <v>9</v>
@@ -49031,7 +49058,7 @@
         <v>260</v>
       </c>
       <c r="J1493" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1494" customHeight="1" spans="3:10">
@@ -49039,7 +49066,7 @@
         <v>9089</v>
       </c>
       <c r="D1494" s="7" t="s">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="E1494" s="7">
         <v>9</v>
@@ -49058,7 +49085,7 @@
         <v>270</v>
       </c>
       <c r="J1494" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1495" customHeight="1" spans="3:10">
@@ -49066,7 +49093,7 @@
         <v>9090</v>
       </c>
       <c r="D1495" s="7" t="s">
-        <v>1572</v>
+        <v>1581</v>
       </c>
       <c r="E1495" s="7">
         <v>9</v>
@@ -49085,7 +49112,7 @@
         <v>270</v>
       </c>
       <c r="J1495" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1496" customHeight="1" spans="3:10">
@@ -49093,7 +49120,7 @@
         <v>9091</v>
       </c>
       <c r="D1496" s="7" t="s">
-        <v>1573</v>
+        <v>1582</v>
       </c>
       <c r="E1496" s="7">
         <v>9</v>
@@ -49112,7 +49139,7 @@
         <v>270</v>
       </c>
       <c r="J1496" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1497" customHeight="1" spans="3:10">
@@ -49120,7 +49147,7 @@
         <v>9092</v>
       </c>
       <c r="D1497" s="7" t="s">
-        <v>1574</v>
+        <v>1583</v>
       </c>
       <c r="E1497" s="7">
         <v>9</v>
@@ -49139,7 +49166,7 @@
         <v>270</v>
       </c>
       <c r="J1497" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1498" customHeight="1" spans="3:10">
@@ -49147,7 +49174,7 @@
         <v>9093</v>
       </c>
       <c r="D1498" s="7" t="s">
-        <v>1575</v>
+        <v>1584</v>
       </c>
       <c r="E1498" s="7">
         <v>9</v>
@@ -49166,7 +49193,7 @@
         <v>280</v>
       </c>
       <c r="J1498" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1499" customHeight="1" spans="3:10">
@@ -49174,7 +49201,7 @@
         <v>9094</v>
       </c>
       <c r="D1499" s="7" t="s">
-        <v>1576</v>
+        <v>1585</v>
       </c>
       <c r="E1499" s="7">
         <v>9</v>
@@ -49193,7 +49220,7 @@
         <v>280</v>
       </c>
       <c r="J1499" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1500" customHeight="1" spans="3:10">
@@ -49201,7 +49228,7 @@
         <v>9095</v>
       </c>
       <c r="D1500" s="7" t="s">
-        <v>1577</v>
+        <v>1586</v>
       </c>
       <c r="E1500" s="7">
         <v>9</v>
@@ -49220,7 +49247,7 @@
         <v>280</v>
       </c>
       <c r="J1500" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1501" customHeight="1" spans="3:10">
@@ -49228,7 +49255,7 @@
         <v>9096</v>
       </c>
       <c r="D1501" s="7" t="s">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="E1501" s="7">
         <v>9</v>
@@ -49247,7 +49274,7 @@
         <v>280</v>
       </c>
       <c r="J1501" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1502" customHeight="1" spans="3:10">
@@ -49255,7 +49282,7 @@
         <v>9097</v>
       </c>
       <c r="D1502" s="7" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="E1502" s="7">
         <v>9</v>
@@ -49274,7 +49301,7 @@
         <v>290</v>
       </c>
       <c r="J1502" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1503" customHeight="1" spans="3:10">
@@ -49282,7 +49309,7 @@
         <v>9098</v>
       </c>
       <c r="D1503" s="7" t="s">
-        <v>1580</v>
+        <v>1589</v>
       </c>
       <c r="E1503" s="7">
         <v>9</v>
@@ -49301,7 +49328,7 @@
         <v>290</v>
       </c>
       <c r="J1503" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1504" customHeight="1" spans="3:10">
@@ -49309,7 +49336,7 @@
         <v>9099</v>
       </c>
       <c r="D1504" s="7" t="s">
-        <v>1581</v>
+        <v>1590</v>
       </c>
       <c r="E1504" s="7">
         <v>9</v>
@@ -49328,7 +49355,7 @@
         <v>290</v>
       </c>
       <c r="J1504" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1505" customHeight="1" spans="3:10">
@@ -49336,7 +49363,7 @@
         <v>9100</v>
       </c>
       <c r="D1505" s="7" t="s">
-        <v>1582</v>
+        <v>1591</v>
       </c>
       <c r="E1505" s="7">
         <v>9</v>
@@ -49355,7 +49382,7 @@
         <v>290</v>
       </c>
       <c r="J1505" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1506" customHeight="1" spans="3:10">
@@ -49363,7 +49390,7 @@
         <v>9101</v>
       </c>
       <c r="D1506" s="7" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="E1506" s="7">
         <v>9</v>
@@ -49383,7 +49410,7 @@
         <v>300</v>
       </c>
       <c r="J1506" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1507" customHeight="1" spans="3:10">
@@ -49391,7 +49418,7 @@
         <v>9102</v>
       </c>
       <c r="D1507" s="7" t="s">
-        <v>1584</v>
+        <v>1593</v>
       </c>
       <c r="E1507" s="7">
         <v>9</v>
@@ -49411,7 +49438,7 @@
         <v>300</v>
       </c>
       <c r="J1507" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1508" customHeight="1" spans="3:10">
@@ -49419,7 +49446,7 @@
         <v>9103</v>
       </c>
       <c r="D1508" s="7" t="s">
-        <v>1585</v>
+        <v>1594</v>
       </c>
       <c r="E1508" s="7">
         <v>9</v>
@@ -49439,7 +49466,7 @@
         <v>300</v>
       </c>
       <c r="J1508" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1509" customHeight="1" spans="3:10">
@@ -49447,7 +49474,7 @@
         <v>9104</v>
       </c>
       <c r="D1509" s="7" t="s">
-        <v>1586</v>
+        <v>1595</v>
       </c>
       <c r="E1509" s="7">
         <v>9</v>
@@ -49467,7 +49494,7 @@
         <v>300</v>
       </c>
       <c r="J1509" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1510" customHeight="1" spans="3:10">
@@ -49475,7 +49502,7 @@
         <v>9105</v>
       </c>
       <c r="D1510" s="7" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="E1510" s="7">
         <v>9</v>
@@ -49495,7 +49522,7 @@
         <v>310</v>
       </c>
       <c r="J1510" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1511" customHeight="1" spans="3:10">
@@ -49503,7 +49530,7 @@
         <v>9106</v>
       </c>
       <c r="D1511" s="7" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="E1511" s="7">
         <v>9</v>
@@ -49523,7 +49550,7 @@
         <v>310</v>
       </c>
       <c r="J1511" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1512" customHeight="1" spans="3:10">
@@ -49531,7 +49558,7 @@
         <v>9107</v>
       </c>
       <c r="D1512" s="7" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="E1512" s="7">
         <v>9</v>
@@ -49551,7 +49578,7 @@
         <v>310</v>
       </c>
       <c r="J1512" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1513" customHeight="1" spans="3:10">
@@ -49559,7 +49586,7 @@
         <v>9108</v>
       </c>
       <c r="D1513" s="7" t="s">
-        <v>1590</v>
+        <v>1599</v>
       </c>
       <c r="E1513" s="7">
         <v>9</v>
@@ -49579,7 +49606,7 @@
         <v>310</v>
       </c>
       <c r="J1513" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1514" customHeight="1" spans="3:10">
@@ -49587,7 +49614,7 @@
         <v>9109</v>
       </c>
       <c r="D1514" s="7" t="s">
-        <v>1591</v>
+        <v>1600</v>
       </c>
       <c r="E1514" s="7">
         <v>9</v>
@@ -49607,7 +49634,7 @@
         <v>320</v>
       </c>
       <c r="J1514" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1515" customHeight="1" spans="3:10">
@@ -49615,7 +49642,7 @@
         <v>9110</v>
       </c>
       <c r="D1515" s="7" t="s">
-        <v>1592</v>
+        <v>1601</v>
       </c>
       <c r="E1515" s="7">
         <v>9</v>
@@ -49635,7 +49662,7 @@
         <v>320</v>
       </c>
       <c r="J1515" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1516" customHeight="1" spans="3:10">
@@ -49643,7 +49670,7 @@
         <v>9111</v>
       </c>
       <c r="D1516" s="7" t="s">
-        <v>1593</v>
+        <v>1602</v>
       </c>
       <c r="E1516" s="7">
         <v>9</v>
@@ -49663,7 +49690,7 @@
         <v>320</v>
       </c>
       <c r="J1516" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1517" customHeight="1" spans="3:10">
@@ -49671,7 +49698,7 @@
         <v>9112</v>
       </c>
       <c r="D1517" s="7" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="E1517" s="7">
         <v>9</v>
@@ -49691,7 +49718,7 @@
         <v>320</v>
       </c>
       <c r="J1517" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1518" customHeight="1" spans="3:10">
@@ -49699,7 +49726,7 @@
         <v>9113</v>
       </c>
       <c r="D1518" s="7" t="s">
-        <v>1595</v>
+        <v>1604</v>
       </c>
       <c r="E1518" s="7">
         <v>9</v>
@@ -49719,7 +49746,7 @@
         <v>330</v>
       </c>
       <c r="J1518" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1519" customHeight="1" spans="3:10">
@@ -49727,7 +49754,7 @@
         <v>9114</v>
       </c>
       <c r="D1519" s="7" t="s">
-        <v>1596</v>
+        <v>1605</v>
       </c>
       <c r="E1519" s="7">
         <v>9</v>
@@ -49747,7 +49774,7 @@
         <v>330</v>
       </c>
       <c r="J1519" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1520" customHeight="1" spans="3:10">
@@ -49755,7 +49782,7 @@
         <v>9115</v>
       </c>
       <c r="D1520" s="7" t="s">
-        <v>1597</v>
+        <v>1606</v>
       </c>
       <c r="E1520" s="7">
         <v>9</v>
@@ -49775,7 +49802,7 @@
         <v>330</v>
       </c>
       <c r="J1520" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1521" customHeight="1" spans="3:10">
@@ -49783,7 +49810,7 @@
         <v>9116</v>
       </c>
       <c r="D1521" s="7" t="s">
-        <v>1598</v>
+        <v>1607</v>
       </c>
       <c r="E1521" s="7">
         <v>9</v>
@@ -49803,7 +49830,7 @@
         <v>330</v>
       </c>
       <c r="J1521" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1522" customHeight="1" spans="3:10">
@@ -49811,7 +49838,7 @@
         <v>9117</v>
       </c>
       <c r="D1522" s="7" t="s">
-        <v>1599</v>
+        <v>1608</v>
       </c>
       <c r="E1522" s="7">
         <v>9</v>
@@ -49831,7 +49858,7 @@
         <v>340</v>
       </c>
       <c r="J1522" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1523" customHeight="1" spans="3:10">
@@ -49839,7 +49866,7 @@
         <v>9118</v>
       </c>
       <c r="D1523" s="7" t="s">
-        <v>1600</v>
+        <v>1609</v>
       </c>
       <c r="E1523" s="7">
         <v>9</v>
@@ -49859,7 +49886,7 @@
         <v>340</v>
       </c>
       <c r="J1523" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1524" customHeight="1" spans="3:10">
@@ -49867,7 +49894,7 @@
         <v>9119</v>
       </c>
       <c r="D1524" s="7" t="s">
-        <v>1601</v>
+        <v>1610</v>
       </c>
       <c r="E1524" s="7">
         <v>9</v>
@@ -49887,7 +49914,7 @@
         <v>340</v>
       </c>
       <c r="J1524" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1525" customHeight="1" spans="3:10">
@@ -49895,7 +49922,7 @@
         <v>9120</v>
       </c>
       <c r="D1525" s="7" t="s">
-        <v>1602</v>
+        <v>1611</v>
       </c>
       <c r="E1525" s="7">
         <v>9</v>
@@ -49915,7 +49942,7 @@
         <v>340</v>
       </c>
       <c r="J1525" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1526" customHeight="1" spans="3:10">
@@ -49923,7 +49950,7 @@
         <v>9121</v>
       </c>
       <c r="D1526" s="7" t="s">
-        <v>1603</v>
+        <v>1612</v>
       </c>
       <c r="E1526" s="7">
         <v>9</v>
@@ -49943,7 +49970,7 @@
         <v>350</v>
       </c>
       <c r="J1526" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1527" customHeight="1" spans="3:10">
@@ -49951,7 +49978,7 @@
         <v>9122</v>
       </c>
       <c r="D1527" s="7" t="s">
-        <v>1604</v>
+        <v>1613</v>
       </c>
       <c r="E1527" s="7">
         <v>9</v>
@@ -49971,7 +49998,7 @@
         <v>350</v>
       </c>
       <c r="J1527" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1528" customHeight="1" spans="3:10">
@@ -49979,7 +50006,7 @@
         <v>9123</v>
       </c>
       <c r="D1528" s="7" t="s">
-        <v>1605</v>
+        <v>1614</v>
       </c>
       <c r="E1528" s="7">
         <v>9</v>
@@ -49999,7 +50026,7 @@
         <v>350</v>
       </c>
       <c r="J1528" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1529" customHeight="1" spans="3:10">
@@ -50007,7 +50034,7 @@
         <v>9124</v>
       </c>
       <c r="D1529" s="7" t="s">
-        <v>1606</v>
+        <v>1615</v>
       </c>
       <c r="E1529" s="7">
         <v>9</v>
@@ -50027,7 +50054,7 @@
         <v>350</v>
       </c>
       <c r="J1529" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1530" customHeight="1" spans="3:10">
@@ -50035,7 +50062,7 @@
         <v>9125</v>
       </c>
       <c r="D1530" s="7" t="s">
-        <v>1607</v>
+        <v>1616</v>
       </c>
       <c r="E1530" s="7">
         <v>9</v>
@@ -50055,7 +50082,7 @@
         <v>360</v>
       </c>
       <c r="J1530" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1531" customHeight="1" spans="3:10">
@@ -50063,7 +50090,7 @@
         <v>9126</v>
       </c>
       <c r="D1531" s="7" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="E1531" s="7">
         <v>9</v>
@@ -50083,7 +50110,7 @@
         <v>360</v>
       </c>
       <c r="J1531" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1532" customHeight="1" spans="3:10">
@@ -50091,7 +50118,7 @@
         <v>9127</v>
       </c>
       <c r="D1532" s="7" t="s">
-        <v>1609</v>
+        <v>1618</v>
       </c>
       <c r="E1532" s="7">
         <v>9</v>
@@ -50111,7 +50138,7 @@
         <v>360</v>
       </c>
       <c r="J1532" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1533" customHeight="1" spans="3:10">
@@ -50119,7 +50146,7 @@
         <v>9128</v>
       </c>
       <c r="D1533" s="7" t="s">
-        <v>1610</v>
+        <v>1619</v>
       </c>
       <c r="E1533" s="7">
         <v>9</v>
@@ -50139,7 +50166,7 @@
         <v>360</v>
       </c>
       <c r="J1533" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1534" customHeight="1" spans="3:10">
@@ -50147,7 +50174,7 @@
         <v>9129</v>
       </c>
       <c r="D1534" s="7" t="s">
-        <v>1611</v>
+        <v>1620</v>
       </c>
       <c r="E1534" s="7">
         <v>9</v>
@@ -50167,7 +50194,7 @@
         <v>370</v>
       </c>
       <c r="J1534" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1535" customHeight="1" spans="3:10">
@@ -50175,7 +50202,7 @@
         <v>9130</v>
       </c>
       <c r="D1535" s="7" t="s">
-        <v>1612</v>
+        <v>1621</v>
       </c>
       <c r="E1535" s="7">
         <v>9</v>
@@ -50195,7 +50222,7 @@
         <v>370</v>
       </c>
       <c r="J1535" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1536" customHeight="1" spans="3:10">
@@ -50203,7 +50230,7 @@
         <v>9131</v>
       </c>
       <c r="D1536" s="7" t="s">
-        <v>1613</v>
+        <v>1622</v>
       </c>
       <c r="E1536" s="7">
         <v>9</v>
@@ -50223,7 +50250,7 @@
         <v>370</v>
       </c>
       <c r="J1536" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1537" customHeight="1" spans="3:10">
@@ -50231,7 +50258,7 @@
         <v>9132</v>
       </c>
       <c r="D1537" s="7" t="s">
-        <v>1614</v>
+        <v>1623</v>
       </c>
       <c r="E1537" s="7">
         <v>9</v>
@@ -50251,7 +50278,7 @@
         <v>370</v>
       </c>
       <c r="J1537" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1538" customHeight="1" spans="3:10">
@@ -50259,7 +50286,7 @@
         <v>9133</v>
       </c>
       <c r="D1538" s="7" t="s">
-        <v>1615</v>
+        <v>1624</v>
       </c>
       <c r="E1538" s="7">
         <v>9</v>
@@ -50279,7 +50306,7 @@
         <v>380</v>
       </c>
       <c r="J1538" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1539" customHeight="1" spans="3:10">
@@ -50287,7 +50314,7 @@
         <v>9134</v>
       </c>
       <c r="D1539" s="7" t="s">
-        <v>1616</v>
+        <v>1625</v>
       </c>
       <c r="E1539" s="7">
         <v>9</v>
@@ -50307,7 +50334,7 @@
         <v>380</v>
       </c>
       <c r="J1539" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1540" customHeight="1" spans="3:10">
@@ -50315,7 +50342,7 @@
         <v>9135</v>
       </c>
       <c r="D1540" s="7" t="s">
-        <v>1617</v>
+        <v>1626</v>
       </c>
       <c r="E1540" s="7">
         <v>9</v>
@@ -50335,7 +50362,7 @@
         <v>380</v>
       </c>
       <c r="J1540" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1541" customHeight="1" spans="3:10">
@@ -50343,7 +50370,7 @@
         <v>9136</v>
       </c>
       <c r="D1541" s="7" t="s">
-        <v>1618</v>
+        <v>1627</v>
       </c>
       <c r="E1541" s="7">
         <v>9</v>
@@ -50363,7 +50390,7 @@
         <v>380</v>
       </c>
       <c r="J1541" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1542" customHeight="1" spans="3:10">
@@ -50371,7 +50398,7 @@
         <v>9137</v>
       </c>
       <c r="D1542" s="7" t="s">
-        <v>1619</v>
+        <v>1628</v>
       </c>
       <c r="E1542" s="7">
         <v>9</v>
@@ -50391,7 +50418,7 @@
         <v>390</v>
       </c>
       <c r="J1542" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1543" customHeight="1" spans="3:10">
@@ -50399,7 +50426,7 @@
         <v>9138</v>
       </c>
       <c r="D1543" s="7" t="s">
-        <v>1620</v>
+        <v>1629</v>
       </c>
       <c r="E1543" s="7">
         <v>9</v>
@@ -50419,7 +50446,7 @@
         <v>390</v>
       </c>
       <c r="J1543" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1544" customHeight="1" spans="3:10">
@@ -50427,7 +50454,7 @@
         <v>9139</v>
       </c>
       <c r="D1544" s="7" t="s">
-        <v>1621</v>
+        <v>1630</v>
       </c>
       <c r="E1544" s="7">
         <v>9</v>
@@ -50447,7 +50474,7 @@
         <v>390</v>
       </c>
       <c r="J1544" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1545" customHeight="1" spans="3:10">
@@ -50455,7 +50482,7 @@
         <v>9140</v>
       </c>
       <c r="D1545" s="7" t="s">
-        <v>1622</v>
+        <v>1631</v>
       </c>
       <c r="E1545" s="7">
         <v>9</v>
@@ -50475,7 +50502,7 @@
         <v>390</v>
       </c>
       <c r="J1545" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1546" customHeight="1" spans="3:10">
@@ -50483,7 +50510,7 @@
         <v>9141</v>
       </c>
       <c r="D1546" s="7" t="s">
-        <v>1623</v>
+        <v>1632</v>
       </c>
       <c r="E1546" s="7">
         <v>9</v>
@@ -50503,7 +50530,7 @@
         <v>400</v>
       </c>
       <c r="J1546" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1547" customHeight="1" spans="3:10">
@@ -50511,7 +50538,7 @@
         <v>9142</v>
       </c>
       <c r="D1547" s="7" t="s">
-        <v>1624</v>
+        <v>1633</v>
       </c>
       <c r="E1547" s="7">
         <v>9</v>
@@ -50531,7 +50558,7 @@
         <v>400</v>
       </c>
       <c r="J1547" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1548" customHeight="1" spans="3:10">
@@ -50539,7 +50566,7 @@
         <v>9143</v>
       </c>
       <c r="D1548" s="7" t="s">
-        <v>1625</v>
+        <v>1634</v>
       </c>
       <c r="E1548" s="7">
         <v>9</v>
@@ -50559,7 +50586,7 @@
         <v>400</v>
       </c>
       <c r="J1548" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1549" customHeight="1" spans="3:10">
@@ -50567,7 +50594,7 @@
         <v>9144</v>
       </c>
       <c r="D1549" s="7" t="s">
-        <v>1626</v>
+        <v>1635</v>
       </c>
       <c r="E1549" s="7">
         <v>9</v>
@@ -50587,7 +50614,7 @@
         <v>400</v>
       </c>
       <c r="J1549" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1550" customHeight="1" spans="3:10">
@@ -50595,7 +50622,7 @@
         <v>9145</v>
       </c>
       <c r="D1550" s="7" t="s">
-        <v>1627</v>
+        <v>1636</v>
       </c>
       <c r="E1550" s="7">
         <v>9</v>
@@ -50615,7 +50642,7 @@
         <v>410</v>
       </c>
       <c r="J1550" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1551" customHeight="1" spans="3:10">
@@ -50623,7 +50650,7 @@
         <v>9146</v>
       </c>
       <c r="D1551" s="7" t="s">
-        <v>1628</v>
+        <v>1637</v>
       </c>
       <c r="E1551" s="7">
         <v>9</v>
@@ -50643,7 +50670,7 @@
         <v>410</v>
       </c>
       <c r="J1551" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1552" customHeight="1" spans="3:10">
@@ -50651,7 +50678,7 @@
         <v>9147</v>
       </c>
       <c r="D1552" s="7" t="s">
-        <v>1629</v>
+        <v>1638</v>
       </c>
       <c r="E1552" s="7">
         <v>9</v>
@@ -50671,7 +50698,7 @@
         <v>410</v>
       </c>
       <c r="J1552" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1553" customHeight="1" spans="3:10">
@@ -50679,7 +50706,7 @@
         <v>9148</v>
       </c>
       <c r="D1553" s="7" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="E1553" s="7">
         <v>9</v>
@@ -50699,7 +50726,7 @@
         <v>410</v>
       </c>
       <c r="J1553" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1554" customHeight="1" spans="3:10">
@@ -50707,7 +50734,7 @@
         <v>9149</v>
       </c>
       <c r="D1554" s="7" t="s">
-        <v>1631</v>
+        <v>1640</v>
       </c>
       <c r="E1554" s="7">
         <v>9</v>
@@ -50727,7 +50754,7 @@
         <v>420</v>
       </c>
       <c r="J1554" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1555" customHeight="1" spans="3:10">
@@ -50735,7 +50762,7 @@
         <v>9150</v>
       </c>
       <c r="D1555" s="7" t="s">
-        <v>1632</v>
+        <v>1641</v>
       </c>
       <c r="E1555" s="7">
         <v>9</v>
@@ -50755,7 +50782,7 @@
         <v>420</v>
       </c>
       <c r="J1555" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1556" customHeight="1" spans="3:10">
@@ -50763,7 +50790,7 @@
         <v>9151</v>
       </c>
       <c r="D1556" s="7" t="s">
-        <v>1633</v>
+        <v>1642</v>
       </c>
       <c r="E1556" s="7">
         <v>9</v>
@@ -50783,7 +50810,7 @@
         <v>420</v>
       </c>
       <c r="J1556" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1557" customHeight="1" spans="3:10">
@@ -50791,7 +50818,7 @@
         <v>9152</v>
       </c>
       <c r="D1557" s="7" t="s">
-        <v>1634</v>
+        <v>1643</v>
       </c>
       <c r="E1557" s="7">
         <v>9</v>
@@ -50811,7 +50838,7 @@
         <v>420</v>
       </c>
       <c r="J1557" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1558" customHeight="1" spans="3:10">
@@ -50819,7 +50846,7 @@
         <v>9153</v>
       </c>
       <c r="D1558" s="7" t="s">
-        <v>1635</v>
+        <v>1644</v>
       </c>
       <c r="E1558" s="7">
         <v>9</v>
@@ -50839,7 +50866,7 @@
         <v>430</v>
       </c>
       <c r="J1558" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1559" customHeight="1" spans="3:10">
@@ -50847,7 +50874,7 @@
         <v>9154</v>
       </c>
       <c r="D1559" s="7" t="s">
-        <v>1636</v>
+        <v>1645</v>
       </c>
       <c r="E1559" s="7">
         <v>9</v>
@@ -50867,7 +50894,7 @@
         <v>430</v>
       </c>
       <c r="J1559" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1560" customHeight="1" spans="3:10">
@@ -50875,7 +50902,7 @@
         <v>9155</v>
       </c>
       <c r="D1560" s="7" t="s">
-        <v>1637</v>
+        <v>1646</v>
       </c>
       <c r="E1560" s="7">
         <v>9</v>
@@ -50895,7 +50922,7 @@
         <v>430</v>
       </c>
       <c r="J1560" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1561" customHeight="1" spans="3:10">
@@ -50903,7 +50930,7 @@
         <v>9156</v>
       </c>
       <c r="D1561" s="7" t="s">
-        <v>1638</v>
+        <v>1647</v>
       </c>
       <c r="E1561" s="7">
         <v>9</v>
@@ -50923,7 +50950,7 @@
         <v>430</v>
       </c>
       <c r="J1561" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1562" customHeight="1" spans="3:10">
@@ -50931,7 +50958,7 @@
         <v>9157</v>
       </c>
       <c r="D1562" s="7" t="s">
-        <v>1639</v>
+        <v>1648</v>
       </c>
       <c r="E1562" s="7">
         <v>9</v>
@@ -50951,7 +50978,7 @@
         <v>440</v>
       </c>
       <c r="J1562" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1563" customHeight="1" spans="3:10">
@@ -50959,7 +50986,7 @@
         <v>9158</v>
       </c>
       <c r="D1563" s="7" t="s">
-        <v>1640</v>
+        <v>1649</v>
       </c>
       <c r="E1563" s="7">
         <v>9</v>
@@ -50979,7 +51006,7 @@
         <v>440</v>
       </c>
       <c r="J1563" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1564" customHeight="1" spans="3:10">
@@ -50987,7 +51014,7 @@
         <v>9159</v>
       </c>
       <c r="D1564" s="7" t="s">
-        <v>1641</v>
+        <v>1650</v>
       </c>
       <c r="E1564" s="7">
         <v>9</v>
@@ -51007,7 +51034,7 @@
         <v>440</v>
       </c>
       <c r="J1564" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1565" customHeight="1" spans="3:10">
@@ -51015,7 +51042,7 @@
         <v>9160</v>
       </c>
       <c r="D1565" s="7" t="s">
-        <v>1642</v>
+        <v>1651</v>
       </c>
       <c r="E1565" s="7">
         <v>9</v>
@@ -51035,7 +51062,7 @@
         <v>440</v>
       </c>
       <c r="J1565" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1566" customHeight="1" spans="3:10">
@@ -51043,7 +51070,7 @@
         <v>9161</v>
       </c>
       <c r="D1566" s="7" t="s">
-        <v>1643</v>
+        <v>1652</v>
       </c>
       <c r="E1566" s="7">
         <v>9</v>
@@ -51063,7 +51090,7 @@
         <v>450</v>
       </c>
       <c r="J1566" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1567" customHeight="1" spans="3:10">
@@ -51071,7 +51098,7 @@
         <v>9162</v>
       </c>
       <c r="D1567" s="7" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="E1567" s="7">
         <v>9</v>
@@ -51091,7 +51118,7 @@
         <v>450</v>
       </c>
       <c r="J1567" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1568" customHeight="1" spans="3:10">
@@ -51099,7 +51126,7 @@
         <v>9163</v>
       </c>
       <c r="D1568" s="7" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="E1568" s="7">
         <v>9</v>
@@ -51119,7 +51146,7 @@
         <v>450</v>
       </c>
       <c r="J1568" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1569" customHeight="1" spans="3:10">
@@ -51127,7 +51154,7 @@
         <v>9164</v>
       </c>
       <c r="D1569" s="7" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="E1569" s="7">
         <v>9</v>
@@ -51147,7 +51174,7 @@
         <v>450</v>
       </c>
       <c r="J1569" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1570" customHeight="1" spans="3:10">
@@ -51155,7 +51182,7 @@
         <v>9165</v>
       </c>
       <c r="D1570" s="7" t="s">
-        <v>1647</v>
+        <v>1656</v>
       </c>
       <c r="E1570" s="7">
         <v>9</v>
@@ -51175,7 +51202,7 @@
         <v>460</v>
       </c>
       <c r="J1570" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1571" customHeight="1" spans="3:10">
@@ -51183,7 +51210,7 @@
         <v>9166</v>
       </c>
       <c r="D1571" s="7" t="s">
-        <v>1648</v>
+        <v>1657</v>
       </c>
       <c r="E1571" s="7">
         <v>9</v>
@@ -51203,7 +51230,7 @@
         <v>460</v>
       </c>
       <c r="J1571" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1572" customHeight="1" spans="3:10">
@@ -51211,7 +51238,7 @@
         <v>9167</v>
       </c>
       <c r="D1572" s="7" t="s">
-        <v>1649</v>
+        <v>1658</v>
       </c>
       <c r="E1572" s="7">
         <v>9</v>
@@ -51231,7 +51258,7 @@
         <v>460</v>
       </c>
       <c r="J1572" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1573" customHeight="1" spans="3:10">
@@ -51239,7 +51266,7 @@
         <v>9168</v>
       </c>
       <c r="D1573" s="7" t="s">
-        <v>1650</v>
+        <v>1659</v>
       </c>
       <c r="E1573" s="7">
         <v>9</v>
@@ -51259,7 +51286,7 @@
         <v>460</v>
       </c>
       <c r="J1573" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1574" customHeight="1" spans="3:10">
@@ -51267,7 +51294,7 @@
         <v>9169</v>
       </c>
       <c r="D1574" s="7" t="s">
-        <v>1651</v>
+        <v>1660</v>
       </c>
       <c r="E1574" s="7">
         <v>9</v>
@@ -51287,7 +51314,7 @@
         <v>470</v>
       </c>
       <c r="J1574" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1575" customHeight="1" spans="3:10">
@@ -51295,7 +51322,7 @@
         <v>9170</v>
       </c>
       <c r="D1575" s="7" t="s">
-        <v>1652</v>
+        <v>1661</v>
       </c>
       <c r="E1575" s="7">
         <v>9</v>
@@ -51315,7 +51342,7 @@
         <v>470</v>
       </c>
       <c r="J1575" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1576" customHeight="1" spans="3:10">
@@ -51323,7 +51350,7 @@
         <v>9171</v>
       </c>
       <c r="D1576" s="7" t="s">
-        <v>1653</v>
+        <v>1662</v>
       </c>
       <c r="E1576" s="7">
         <v>9</v>
@@ -51343,7 +51370,7 @@
         <v>470</v>
       </c>
       <c r="J1576" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1577" customHeight="1" spans="3:10">
@@ -51351,7 +51378,7 @@
         <v>9172</v>
       </c>
       <c r="D1577" s="7" t="s">
-        <v>1654</v>
+        <v>1663</v>
       </c>
       <c r="E1577" s="7">
         <v>9</v>
@@ -51371,7 +51398,7 @@
         <v>470</v>
       </c>
       <c r="J1577" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1578" customHeight="1" spans="3:10">
@@ -51379,7 +51406,7 @@
         <v>9173</v>
       </c>
       <c r="D1578" s="7" t="s">
-        <v>1655</v>
+        <v>1664</v>
       </c>
       <c r="E1578" s="7">
         <v>9</v>
@@ -51399,7 +51426,7 @@
         <v>480</v>
       </c>
       <c r="J1578" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1579" customHeight="1" spans="3:10">
@@ -51407,7 +51434,7 @@
         <v>9174</v>
       </c>
       <c r="D1579" s="7" t="s">
-        <v>1656</v>
+        <v>1665</v>
       </c>
       <c r="E1579" s="7">
         <v>9</v>
@@ -51427,7 +51454,7 @@
         <v>480</v>
       </c>
       <c r="J1579" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1580" customHeight="1" spans="3:10">
@@ -51435,7 +51462,7 @@
         <v>9175</v>
       </c>
       <c r="D1580" s="7" t="s">
-        <v>1657</v>
+        <v>1666</v>
       </c>
       <c r="E1580" s="7">
         <v>9</v>
@@ -51455,7 +51482,7 @@
         <v>480</v>
       </c>
       <c r="J1580" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1581" customHeight="1" spans="3:10">
@@ -51463,7 +51490,7 @@
         <v>9176</v>
       </c>
       <c r="D1581" s="7" t="s">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="E1581" s="7">
         <v>9</v>
@@ -51483,7 +51510,7 @@
         <v>480</v>
       </c>
       <c r="J1581" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1582" customHeight="1" spans="3:10">
@@ -51491,7 +51518,7 @@
         <v>9177</v>
       </c>
       <c r="D1582" s="7" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="E1582" s="7">
         <v>9</v>
@@ -51511,7 +51538,7 @@
         <v>490</v>
       </c>
       <c r="J1582" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1583" customHeight="1" spans="3:10">
@@ -51519,7 +51546,7 @@
         <v>9178</v>
       </c>
       <c r="D1583" s="7" t="s">
-        <v>1660</v>
+        <v>1669</v>
       </c>
       <c r="E1583" s="7">
         <v>9</v>
@@ -51539,7 +51566,7 @@
         <v>490</v>
       </c>
       <c r="J1583" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1584" customHeight="1" spans="3:10">
@@ -51547,7 +51574,7 @@
         <v>9179</v>
       </c>
       <c r="D1584" s="7" t="s">
-        <v>1661</v>
+        <v>1670</v>
       </c>
       <c r="E1584" s="7">
         <v>9</v>
@@ -51567,7 +51594,7 @@
         <v>490</v>
       </c>
       <c r="J1584" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1585" customHeight="1" spans="3:10">
@@ -51575,7 +51602,7 @@
         <v>9180</v>
       </c>
       <c r="D1585" s="7" t="s">
-        <v>1662</v>
+        <v>1671</v>
       </c>
       <c r="E1585" s="7">
         <v>9</v>
@@ -51595,7 +51622,7 @@
         <v>490</v>
       </c>
       <c r="J1585" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1586" customHeight="1" spans="3:10">
@@ -51603,7 +51630,7 @@
         <v>9181</v>
       </c>
       <c r="D1586" s="7" t="s">
-        <v>1663</v>
+        <v>1672</v>
       </c>
       <c r="E1586" s="7">
         <v>9</v>
@@ -51623,7 +51650,7 @@
         <v>500</v>
       </c>
       <c r="J1586" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1587" customHeight="1" spans="3:10">
@@ -51631,7 +51658,7 @@
         <v>9182</v>
       </c>
       <c r="D1587" s="7" t="s">
-        <v>1664</v>
+        <v>1673</v>
       </c>
       <c r="E1587" s="7">
         <v>9</v>
@@ -51651,7 +51678,7 @@
         <v>500</v>
       </c>
       <c r="J1587" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1588" customHeight="1" spans="3:10">
@@ -51659,7 +51686,7 @@
         <v>9183</v>
       </c>
       <c r="D1588" s="7" t="s">
-        <v>1665</v>
+        <v>1674</v>
       </c>
       <c r="E1588" s="7">
         <v>9</v>
@@ -51679,7 +51706,7 @@
         <v>500</v>
       </c>
       <c r="J1588" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1589" customHeight="1" spans="3:10">
@@ -51687,7 +51714,7 @@
         <v>9184</v>
       </c>
       <c r="D1589" s="7" t="s">
-        <v>1666</v>
+        <v>1675</v>
       </c>
       <c r="E1589" s="7">
         <v>9</v>
@@ -51707,7 +51734,7 @@
         <v>500</v>
       </c>
       <c r="J1589" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1590" customHeight="1" spans="3:10">
@@ -51715,7 +51742,7 @@
         <v>9185</v>
       </c>
       <c r="D1590" s="7" t="s">
-        <v>1667</v>
+        <v>1676</v>
       </c>
       <c r="E1590" s="7">
         <v>9</v>
@@ -51735,7 +51762,7 @@
         <v>510</v>
       </c>
       <c r="J1590" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1591" customHeight="1" spans="3:10">
@@ -51743,7 +51770,7 @@
         <v>9186</v>
       </c>
       <c r="D1591" s="7" t="s">
-        <v>1668</v>
+        <v>1677</v>
       </c>
       <c r="E1591" s="7">
         <v>9</v>
@@ -51763,7 +51790,7 @@
         <v>510</v>
       </c>
       <c r="J1591" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1592" customHeight="1" spans="3:10">
@@ -51771,7 +51798,7 @@
         <v>9187</v>
       </c>
       <c r="D1592" s="7" t="s">
-        <v>1669</v>
+        <v>1678</v>
       </c>
       <c r="E1592" s="7">
         <v>9</v>
@@ -51791,7 +51818,7 @@
         <v>510</v>
       </c>
       <c r="J1592" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1593" customHeight="1" spans="3:10">
@@ -51799,7 +51826,7 @@
         <v>9188</v>
       </c>
       <c r="D1593" s="7" t="s">
-        <v>1670</v>
+        <v>1679</v>
       </c>
       <c r="E1593" s="7">
         <v>9</v>
@@ -51819,7 +51846,7 @@
         <v>510</v>
       </c>
       <c r="J1593" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1594" customHeight="1" spans="3:10">
@@ -51827,7 +51854,7 @@
         <v>9189</v>
       </c>
       <c r="D1594" s="7" t="s">
-        <v>1671</v>
+        <v>1680</v>
       </c>
       <c r="E1594" s="7">
         <v>9</v>
@@ -51847,7 +51874,7 @@
         <v>520</v>
       </c>
       <c r="J1594" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1595" customHeight="1" spans="3:10">
@@ -51855,7 +51882,7 @@
         <v>9190</v>
       </c>
       <c r="D1595" s="7" t="s">
-        <v>1672</v>
+        <v>1681</v>
       </c>
       <c r="E1595" s="7">
         <v>9</v>
@@ -51875,7 +51902,7 @@
         <v>520</v>
       </c>
       <c r="J1595" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1596" customHeight="1" spans="3:10">
@@ -51883,7 +51910,7 @@
         <v>9191</v>
       </c>
       <c r="D1596" s="7" t="s">
-        <v>1673</v>
+        <v>1682</v>
       </c>
       <c r="E1596" s="7">
         <v>9</v>
@@ -51903,7 +51930,7 @@
         <v>520</v>
       </c>
       <c r="J1596" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1597" customHeight="1" spans="3:10">
@@ -51911,7 +51938,7 @@
         <v>9192</v>
       </c>
       <c r="D1597" s="7" t="s">
-        <v>1674</v>
+        <v>1683</v>
       </c>
       <c r="E1597" s="7">
         <v>9</v>
@@ -51931,7 +51958,7 @@
         <v>520</v>
       </c>
       <c r="J1597" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1598" customHeight="1" spans="3:10">
@@ -51939,7 +51966,7 @@
         <v>9193</v>
       </c>
       <c r="D1598" s="7" t="s">
-        <v>1675</v>
+        <v>1684</v>
       </c>
       <c r="E1598" s="7">
         <v>9</v>
@@ -51959,7 +51986,7 @@
         <v>530</v>
       </c>
       <c r="J1598" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1599" customHeight="1" spans="3:10">
@@ -51967,7 +51994,7 @@
         <v>9194</v>
       </c>
       <c r="D1599" s="7" t="s">
-        <v>1676</v>
+        <v>1685</v>
       </c>
       <c r="E1599" s="7">
         <v>9</v>
@@ -51987,7 +52014,7 @@
         <v>530</v>
       </c>
       <c r="J1599" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1600" customHeight="1" spans="3:10">
@@ -51995,7 +52022,7 @@
         <v>9195</v>
       </c>
       <c r="D1600" s="7" t="s">
-        <v>1677</v>
+        <v>1686</v>
       </c>
       <c r="E1600" s="7">
         <v>9</v>
@@ -52015,7 +52042,7 @@
         <v>530</v>
       </c>
       <c r="J1600" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1601" customHeight="1" spans="3:10">
@@ -52023,7 +52050,7 @@
         <v>9196</v>
       </c>
       <c r="D1601" s="7" t="s">
-        <v>1678</v>
+        <v>1687</v>
       </c>
       <c r="E1601" s="7">
         <v>9</v>
@@ -52043,7 +52070,7 @@
         <v>530</v>
       </c>
       <c r="J1601" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1602" customHeight="1" spans="3:10">
@@ -52051,7 +52078,7 @@
         <v>9197</v>
       </c>
       <c r="D1602" s="7" t="s">
-        <v>1679</v>
+        <v>1688</v>
       </c>
       <c r="E1602" s="7">
         <v>9</v>
@@ -52071,7 +52098,7 @@
         <v>540</v>
       </c>
       <c r="J1602" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1603" customHeight="1" spans="3:10">
@@ -52079,7 +52106,7 @@
         <v>9198</v>
       </c>
       <c r="D1603" s="7" t="s">
-        <v>1680</v>
+        <v>1689</v>
       </c>
       <c r="E1603" s="7">
         <v>9</v>
@@ -52099,7 +52126,7 @@
         <v>540</v>
       </c>
       <c r="J1603" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1604" customHeight="1" spans="3:10">
@@ -52107,7 +52134,7 @@
         <v>9199</v>
       </c>
       <c r="D1604" s="7" t="s">
-        <v>1681</v>
+        <v>1690</v>
       </c>
       <c r="E1604" s="7">
         <v>9</v>
@@ -52127,7 +52154,7 @@
         <v>540</v>
       </c>
       <c r="J1604" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1605" customHeight="1" spans="3:10">
@@ -52135,7 +52162,7 @@
         <v>9200</v>
       </c>
       <c r="D1605" s="7" t="s">
-        <v>1682</v>
+        <v>1691</v>
       </c>
       <c r="E1605" s="7">
         <v>9</v>
@@ -52155,7 +52182,7 @@
         <v>540</v>
       </c>
       <c r="J1605" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1606" customHeight="1" spans="3:10">
@@ -52163,7 +52190,7 @@
         <v>9201</v>
       </c>
       <c r="D1606" s="7" t="s">
-        <v>1683</v>
+        <v>1692</v>
       </c>
       <c r="E1606" s="7">
         <v>9</v>
@@ -52183,7 +52210,7 @@
         <v>550</v>
       </c>
       <c r="J1606" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1607" customHeight="1" spans="3:10">
@@ -52191,7 +52218,7 @@
         <v>9202</v>
       </c>
       <c r="D1607" s="7" t="s">
-        <v>1684</v>
+        <v>1693</v>
       </c>
       <c r="E1607" s="7">
         <v>9</v>
@@ -52211,7 +52238,7 @@
         <v>550</v>
       </c>
       <c r="J1607" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1608" customHeight="1" spans="3:10">
@@ -52219,7 +52246,7 @@
         <v>9203</v>
       </c>
       <c r="D1608" s="7" t="s">
-        <v>1685</v>
+        <v>1694</v>
       </c>
       <c r="E1608" s="7">
         <v>9</v>
@@ -52239,7 +52266,7 @@
         <v>550</v>
       </c>
       <c r="J1608" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1609" customHeight="1" spans="3:10">
@@ -52247,7 +52274,7 @@
         <v>9204</v>
       </c>
       <c r="D1609" s="7" t="s">
-        <v>1686</v>
+        <v>1695</v>
       </c>
       <c r="E1609" s="7">
         <v>9</v>
@@ -52267,7 +52294,7 @@
         <v>550</v>
       </c>
       <c r="J1609" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1610" customHeight="1" spans="3:10">
@@ -52275,7 +52302,7 @@
         <v>9205</v>
       </c>
       <c r="D1610" s="7" t="s">
-        <v>1687</v>
+        <v>1696</v>
       </c>
       <c r="E1610" s="7">
         <v>9</v>
@@ -52295,7 +52322,7 @@
         <v>560</v>
       </c>
       <c r="J1610" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1611" customHeight="1" spans="3:10">
@@ -52303,7 +52330,7 @@
         <v>9206</v>
       </c>
       <c r="D1611" s="7" t="s">
-        <v>1688</v>
+        <v>1697</v>
       </c>
       <c r="E1611" s="7">
         <v>9</v>
@@ -52323,7 +52350,7 @@
         <v>560</v>
       </c>
       <c r="J1611" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1612" customHeight="1" spans="3:10">
@@ -52331,7 +52358,7 @@
         <v>9207</v>
       </c>
       <c r="D1612" s="7" t="s">
-        <v>1689</v>
+        <v>1698</v>
       </c>
       <c r="E1612" s="7">
         <v>9</v>
@@ -52351,7 +52378,7 @@
         <v>560</v>
       </c>
       <c r="J1612" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1613" customHeight="1" spans="3:10">
@@ -52359,7 +52386,7 @@
         <v>9208</v>
       </c>
       <c r="D1613" s="7" t="s">
-        <v>1690</v>
+        <v>1699</v>
       </c>
       <c r="E1613" s="7">
         <v>9</v>
@@ -52379,7 +52406,7 @@
         <v>560</v>
       </c>
       <c r="J1613" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1614" customHeight="1" spans="3:10">
@@ -52387,7 +52414,7 @@
         <v>9209</v>
       </c>
       <c r="D1614" s="7" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="E1614" s="7">
         <v>9</v>
@@ -52407,7 +52434,7 @@
         <v>570</v>
       </c>
       <c r="J1614" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1615" customHeight="1" spans="3:10">
@@ -52415,7 +52442,7 @@
         <v>9210</v>
       </c>
       <c r="D1615" s="7" t="s">
-        <v>1692</v>
+        <v>1701</v>
       </c>
       <c r="E1615" s="7">
         <v>9</v>
@@ -52435,7 +52462,7 @@
         <v>570</v>
       </c>
       <c r="J1615" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1616" customHeight="1" spans="3:10">
@@ -52443,7 +52470,7 @@
         <v>9211</v>
       </c>
       <c r="D1616" s="7" t="s">
-        <v>1693</v>
+        <v>1702</v>
       </c>
       <c r="E1616" s="7">
         <v>9</v>
@@ -52463,7 +52490,7 @@
         <v>570</v>
       </c>
       <c r="J1616" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1617" customHeight="1" spans="3:10">
@@ -52471,7 +52498,7 @@
         <v>9212</v>
       </c>
       <c r="D1617" s="7" t="s">
-        <v>1694</v>
+        <v>1703</v>
       </c>
       <c r="E1617" s="7">
         <v>9</v>
@@ -52491,7 +52518,7 @@
         <v>570</v>
       </c>
       <c r="J1617" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1618" customHeight="1" spans="3:10">
@@ -52499,7 +52526,7 @@
         <v>9213</v>
       </c>
       <c r="D1618" s="7" t="s">
-        <v>1695</v>
+        <v>1704</v>
       </c>
       <c r="E1618" s="7">
         <v>9</v>
@@ -52519,7 +52546,7 @@
         <v>580</v>
       </c>
       <c r="J1618" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1619" customHeight="1" spans="3:10">
@@ -52527,7 +52554,7 @@
         <v>9214</v>
       </c>
       <c r="D1619" s="7" t="s">
-        <v>1696</v>
+        <v>1705</v>
       </c>
       <c r="E1619" s="7">
         <v>9</v>
@@ -52547,7 +52574,7 @@
         <v>580</v>
       </c>
       <c r="J1619" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1620" customHeight="1" spans="3:10">
@@ -52555,7 +52582,7 @@
         <v>9215</v>
       </c>
       <c r="D1620" s="7" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="E1620" s="7">
         <v>9</v>
@@ -52575,7 +52602,7 @@
         <v>580</v>
       </c>
       <c r="J1620" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1621" customHeight="1" spans="3:10">
@@ -52583,7 +52610,7 @@
         <v>9216</v>
       </c>
       <c r="D1621" s="7" t="s">
-        <v>1698</v>
+        <v>1707</v>
       </c>
       <c r="E1621" s="7">
         <v>9</v>
@@ -52603,7 +52630,7 @@
         <v>580</v>
       </c>
       <c r="J1621" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1622" customHeight="1" spans="3:10">
@@ -52611,7 +52638,7 @@
         <v>9217</v>
       </c>
       <c r="D1622" s="7" t="s">
-        <v>1699</v>
+        <v>1708</v>
       </c>
       <c r="E1622" s="7">
         <v>9</v>
@@ -52631,7 +52658,7 @@
         <v>590</v>
       </c>
       <c r="J1622" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1623" customHeight="1" spans="3:10">
@@ -52639,7 +52666,7 @@
         <v>9218</v>
       </c>
       <c r="D1623" s="7" t="s">
-        <v>1700</v>
+        <v>1709</v>
       </c>
       <c r="E1623" s="7">
         <v>9</v>
@@ -52659,7 +52686,7 @@
         <v>590</v>
       </c>
       <c r="J1623" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1624" customHeight="1" spans="3:10">
@@ -52667,7 +52694,7 @@
         <v>9219</v>
       </c>
       <c r="D1624" s="7" t="s">
-        <v>1701</v>
+        <v>1710</v>
       </c>
       <c r="E1624" s="7">
         <v>9</v>
@@ -52687,7 +52714,7 @@
         <v>590</v>
       </c>
       <c r="J1624" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1625" customHeight="1" spans="3:10">
@@ -52695,7 +52722,7 @@
         <v>9220</v>
       </c>
       <c r="D1625" s="7" t="s">
-        <v>1702</v>
+        <v>1711</v>
       </c>
       <c r="E1625" s="7">
         <v>9</v>
@@ -52715,7 +52742,7 @@
         <v>590</v>
       </c>
       <c r="J1625" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1626" customHeight="1" spans="3:10">
@@ -52723,7 +52750,7 @@
         <v>9221</v>
       </c>
       <c r="D1626" s="7" t="s">
-        <v>1703</v>
+        <v>1712</v>
       </c>
       <c r="E1626" s="7">
         <v>9</v>
@@ -52743,7 +52770,7 @@
         <v>600</v>
       </c>
       <c r="J1626" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1627" customHeight="1" spans="3:10">
@@ -52751,7 +52778,7 @@
         <v>9222</v>
       </c>
       <c r="D1627" s="7" t="s">
-        <v>1704</v>
+        <v>1713</v>
       </c>
       <c r="E1627" s="7">
         <v>9</v>
@@ -52771,7 +52798,7 @@
         <v>600</v>
       </c>
       <c r="J1627" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1628" customHeight="1" spans="3:10">
@@ -52779,7 +52806,7 @@
         <v>9223</v>
       </c>
       <c r="D1628" s="7" t="s">
-        <v>1705</v>
+        <v>1714</v>
       </c>
       <c r="E1628" s="7">
         <v>9</v>
@@ -52799,7 +52826,7 @@
         <v>600</v>
       </c>
       <c r="J1628" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1629" customHeight="1" spans="3:10">
@@ -52807,7 +52834,7 @@
         <v>9224</v>
       </c>
       <c r="D1629" s="7" t="s">
-        <v>1706</v>
+        <v>1715</v>
       </c>
       <c r="E1629" s="7">
         <v>9</v>
@@ -52827,7 +52854,7 @@
         <v>600</v>
       </c>
       <c r="J1629" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1630" customHeight="1" spans="3:10">
@@ -52835,7 +52862,7 @@
         <v>9225</v>
       </c>
       <c r="D1630" s="7" t="s">
-        <v>1707</v>
+        <v>1716</v>
       </c>
       <c r="E1630" s="7">
         <v>9</v>
@@ -52855,7 +52882,7 @@
         <v>610</v>
       </c>
       <c r="J1630" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1631" customHeight="1" spans="3:10">
@@ -52863,7 +52890,7 @@
         <v>9226</v>
       </c>
       <c r="D1631" s="7" t="s">
-        <v>1708</v>
+        <v>1717</v>
       </c>
       <c r="E1631" s="7">
         <v>9</v>
@@ -52883,7 +52910,7 @@
         <v>610</v>
       </c>
       <c r="J1631" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1632" customHeight="1" spans="3:10">
@@ -52891,7 +52918,7 @@
         <v>9227</v>
       </c>
       <c r="D1632" s="7" t="s">
-        <v>1709</v>
+        <v>1718</v>
       </c>
       <c r="E1632" s="7">
         <v>9</v>
@@ -52911,7 +52938,7 @@
         <v>610</v>
       </c>
       <c r="J1632" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1633" customHeight="1" spans="3:10">
@@ -52919,7 +52946,7 @@
         <v>9228</v>
       </c>
       <c r="D1633" s="7" t="s">
-        <v>1710</v>
+        <v>1719</v>
       </c>
       <c r="E1633" s="7">
         <v>9</v>
@@ -52939,7 +52966,7 @@
         <v>610</v>
       </c>
       <c r="J1633" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1634" customHeight="1" spans="3:10">
@@ -52947,7 +52974,7 @@
         <v>9229</v>
       </c>
       <c r="D1634" s="7" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="E1634" s="7">
         <v>9</v>
@@ -52967,7 +52994,7 @@
         <v>620</v>
       </c>
       <c r="J1634" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1635" customHeight="1" spans="3:10">
@@ -52975,7 +53002,7 @@
         <v>9230</v>
       </c>
       <c r="D1635" s="7" t="s">
-        <v>1712</v>
+        <v>1721</v>
       </c>
       <c r="E1635" s="7">
         <v>9</v>
@@ -52995,7 +53022,7 @@
         <v>620</v>
       </c>
       <c r="J1635" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1636" customHeight="1" spans="3:10">
@@ -53003,7 +53030,7 @@
         <v>9231</v>
       </c>
       <c r="D1636" s="7" t="s">
-        <v>1713</v>
+        <v>1722</v>
       </c>
       <c r="E1636" s="7">
         <v>9</v>
@@ -53023,7 +53050,7 @@
         <v>620</v>
       </c>
       <c r="J1636" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1637" customHeight="1" spans="3:10">
@@ -53031,7 +53058,7 @@
         <v>9232</v>
       </c>
       <c r="D1637" s="7" t="s">
-        <v>1714</v>
+        <v>1723</v>
       </c>
       <c r="E1637" s="7">
         <v>9</v>
@@ -53051,7 +53078,7 @@
         <v>620</v>
       </c>
       <c r="J1637" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1638" customHeight="1" spans="3:10">
@@ -53059,7 +53086,7 @@
         <v>9233</v>
       </c>
       <c r="D1638" s="7" t="s">
-        <v>1715</v>
+        <v>1724</v>
       </c>
       <c r="E1638" s="7">
         <v>9</v>
@@ -53079,7 +53106,7 @@
         <v>630</v>
       </c>
       <c r="J1638" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1639" customHeight="1" spans="3:10">
@@ -53087,7 +53114,7 @@
         <v>9234</v>
       </c>
       <c r="D1639" s="7" t="s">
-        <v>1716</v>
+        <v>1725</v>
       </c>
       <c r="E1639" s="7">
         <v>9</v>
@@ -53107,7 +53134,7 @@
         <v>630</v>
       </c>
       <c r="J1639" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1640" customHeight="1" spans="3:10">
@@ -53115,7 +53142,7 @@
         <v>9235</v>
       </c>
       <c r="D1640" s="7" t="s">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="E1640" s="7">
         <v>9</v>
@@ -53135,7 +53162,7 @@
         <v>630</v>
       </c>
       <c r="J1640" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1641" customHeight="1" spans="3:10">
@@ -53143,7 +53170,7 @@
         <v>9236</v>
       </c>
       <c r="D1641" s="7" t="s">
-        <v>1718</v>
+        <v>1727</v>
       </c>
       <c r="E1641" s="7">
         <v>9</v>
@@ -53163,7 +53190,7 @@
         <v>630</v>
       </c>
       <c r="J1641" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1642" customHeight="1" spans="3:10">
@@ -53171,7 +53198,7 @@
         <v>9237</v>
       </c>
       <c r="D1642" s="7" t="s">
-        <v>1719</v>
+        <v>1728</v>
       </c>
       <c r="E1642" s="7">
         <v>9</v>
@@ -53191,7 +53218,7 @@
         <v>640</v>
       </c>
       <c r="J1642" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1643" customHeight="1" spans="3:10">
@@ -53199,7 +53226,7 @@
         <v>9238</v>
       </c>
       <c r="D1643" s="7" t="s">
-        <v>1720</v>
+        <v>1729</v>
       </c>
       <c r="E1643" s="7">
         <v>9</v>
@@ -53219,7 +53246,7 @@
         <v>640</v>
       </c>
       <c r="J1643" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1644" customHeight="1" spans="3:10">
@@ -53227,7 +53254,7 @@
         <v>9239</v>
       </c>
       <c r="D1644" s="7" t="s">
-        <v>1721</v>
+        <v>1730</v>
       </c>
       <c r="E1644" s="7">
         <v>9</v>
@@ -53247,7 +53274,7 @@
         <v>640</v>
       </c>
       <c r="J1644" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1645" customHeight="1" spans="3:10">
@@ -53255,7 +53282,7 @@
         <v>9240</v>
       </c>
       <c r="D1645" s="7" t="s">
-        <v>1722</v>
+        <v>1731</v>
       </c>
       <c r="E1645" s="7">
         <v>9</v>
@@ -53275,7 +53302,7 @@
         <v>640</v>
       </c>
       <c r="J1645" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1646" customHeight="1" spans="3:10">
@@ -53283,7 +53310,7 @@
         <v>9241</v>
       </c>
       <c r="D1646" s="7" t="s">
-        <v>1723</v>
+        <v>1732</v>
       </c>
       <c r="E1646" s="7">
         <v>9</v>
@@ -53303,7 +53330,7 @@
         <v>650</v>
       </c>
       <c r="J1646" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1647" customHeight="1" spans="3:10">
@@ -53311,7 +53338,7 @@
         <v>9242</v>
       </c>
       <c r="D1647" s="7" t="s">
-        <v>1724</v>
+        <v>1733</v>
       </c>
       <c r="E1647" s="7">
         <v>9</v>
@@ -53331,7 +53358,7 @@
         <v>650</v>
       </c>
       <c r="J1647" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1648" customHeight="1" spans="3:10">
@@ -53339,7 +53366,7 @@
         <v>9243</v>
       </c>
       <c r="D1648" s="7" t="s">
-        <v>1725</v>
+        <v>1734</v>
       </c>
       <c r="E1648" s="7">
         <v>9</v>
@@ -53359,7 +53386,7 @@
         <v>650</v>
       </c>
       <c r="J1648" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1649" customHeight="1" spans="3:10">
@@ -53367,7 +53394,7 @@
         <v>9244</v>
       </c>
       <c r="D1649" s="7" t="s">
-        <v>1726</v>
+        <v>1735</v>
       </c>
       <c r="E1649" s="7">
         <v>9</v>
@@ -53387,7 +53414,7 @@
         <v>650</v>
       </c>
       <c r="J1649" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1650" customHeight="1" spans="3:10">
@@ -53395,7 +53422,7 @@
         <v>9245</v>
       </c>
       <c r="D1650" s="7" t="s">
-        <v>1727</v>
+        <v>1736</v>
       </c>
       <c r="E1650" s="7">
         <v>9</v>
@@ -53415,7 +53442,7 @@
         <v>660</v>
       </c>
       <c r="J1650" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1651" customHeight="1" spans="3:10">
@@ -53423,7 +53450,7 @@
         <v>9246</v>
       </c>
       <c r="D1651" s="7" t="s">
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="E1651" s="7">
         <v>9</v>
@@ -53443,7 +53470,7 @@
         <v>660</v>
       </c>
       <c r="J1651" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1652" customHeight="1" spans="3:10">
@@ -53451,7 +53478,7 @@
         <v>9247</v>
       </c>
       <c r="D1652" s="7" t="s">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="E1652" s="7">
         <v>9</v>
@@ -53471,7 +53498,7 @@
         <v>660</v>
       </c>
       <c r="J1652" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1653" customHeight="1" spans="3:10">
@@ -53479,7 +53506,7 @@
         <v>9248</v>
       </c>
       <c r="D1653" s="7" t="s">
-        <v>1730</v>
+        <v>1739</v>
       </c>
       <c r="E1653" s="7">
         <v>9</v>
@@ -53499,7 +53526,7 @@
         <v>660</v>
       </c>
       <c r="J1653" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -4543,28 +4543,28 @@
     <t>过关斩将7</t>
   </si>
   <si>
+    <t>守卫龙城通过寂灭70层数</t>
+  </si>
+  <si>
+    <t>独孤求败7</t>
+  </si>
+  <si>
+    <t>守卫龙城通过寂灭80层数</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>武林至尊7</t>
+  </si>
+  <si>
+    <t>守卫龙城通过寂灭90层数</t>
+  </si>
+  <si>
+    <t>天下无敌7</t>
+  </si>
+  <si>
     <t>守卫龙城通过寂灭100层数</t>
-  </si>
-  <si>
-    <t>独孤求败7</t>
-  </si>
-  <si>
-    <t>守卫龙城通过寂灭70层数</t>
-  </si>
-  <si>
-    <t>破韧倍率</t>
-  </si>
-  <si>
-    <t>武林至尊7</t>
-  </si>
-  <si>
-    <t>守卫龙城通过寂灭90层数</t>
-  </si>
-  <si>
-    <t>天下无敌7</t>
-  </si>
-  <si>
-    <t>守卫龙城通过寂灭80层数</t>
   </si>
   <si>
     <t>攀登者1</t>
@@ -46668,7 +46668,7 @@
         <v>8</v>
       </c>
       <c r="F1401" s="7">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G1401" s="5">
         <v>1</v>
